--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -90,6 +90,9 @@
     <t>Display Name</t>
   </si>
   <si>
+    <t>Metadata</t>
+  </si>
+  <si>
     <t>Pool A</t>
   </si>
   <si>
@@ -99,7 +102,7 @@
     <t>Team Gamma</t>
   </si>
   <si>
-    <t>C. LANNISTER</t>
+    <t>LANNISTER</t>
   </si>
   <si>
     <t>Daenerys Targaryen</t>
@@ -108,7 +111,7 @@
     <t>Team Delta</t>
   </si>
   <si>
-    <t>D. TARGARYEN</t>
+    <t>TARGARYEN</t>
   </si>
   <si>
     <t>Eddard Stark</t>
@@ -117,7 +120,7 @@
     <t>Team Epsilon</t>
   </si>
   <si>
-    <t>E. STARK</t>
+    <t>STARK</t>
   </si>
   <si>
     <t>Pool B</t>
@@ -129,7 +132,7 @@
     <t>Team Zeta</t>
   </si>
   <si>
-    <t>F. BAGGINS</t>
+    <t>BAGGINS</t>
   </si>
   <si>
     <t>Gandalf The Grey</t>
@@ -138,7 +141,7 @@
     <t>Team Eta</t>
   </si>
   <si>
-    <t>G. GREY</t>
+    <t>GANDALF</t>
   </si>
   <si>
     <t>Hermione Granger</t>
@@ -147,7 +150,7 @@
     <t>Team Theta</t>
   </si>
   <si>
-    <t>H. GRANGER</t>
+    <t>GRANGER</t>
   </si>
   <si>
     <t>Pool C</t>
@@ -159,7 +162,7 @@
     <t>Team Iota</t>
   </si>
   <si>
-    <t>I. MONTOYA</t>
+    <t>MONTOYA</t>
   </si>
   <si>
     <t>Jon Snow</t>
@@ -168,7 +171,7 @@
     <t>Team Kappa</t>
   </si>
   <si>
-    <t>J. SNOW</t>
+    <t>SNOW</t>
   </si>
   <si>
     <t>Katniss Everdeen</t>
@@ -177,7 +180,7 @@
     <t>Team Lambda</t>
   </si>
   <si>
-    <t>K. EVERDEEN</t>
+    <t>EVERDEEN</t>
   </si>
   <si>
     <t>Pool D</t>
@@ -192,7 +195,7 @@
     <t>Team Nu</t>
   </si>
   <si>
-    <t>M. DICK</t>
+    <t>DICK</t>
   </si>
   <si>
     <t>Neville Longbottom</t>
@@ -201,7 +204,7 @@
     <t>Team Xi</t>
   </si>
   <si>
-    <t>N. LONGBOTTOM</t>
+    <t>LONGBOTTOM</t>
   </si>
   <si>
     <t>Pool E</t>
@@ -210,7 +213,7 @@
     <t>Legolas Greenleaf</t>
   </si>
   <si>
-    <t>L. GREENLEAF</t>
+    <t>GREENLEAF</t>
   </si>
   <si>
     <t>Othello</t>
@@ -228,7 +231,7 @@
     <t>Team Pi</t>
   </si>
   <si>
-    <t>P. BAELISH</t>
+    <t>BAELISH</t>
   </si>
   <si>
     <t>Pool F</t>
@@ -240,7 +243,7 @@
     <t>Team Rho</t>
   </si>
   <si>
-    <t>Q. QUIRRELL</t>
+    <t>QUIRRELL</t>
   </si>
   <si>
     <t>Ron Weasley</t>
@@ -249,7 +252,7 @@
     <t>Team Sigma</t>
   </si>
   <si>
-    <t>R. WEASLEY</t>
+    <t>WEASLEY</t>
   </si>
   <si>
     <t>Samwise Gamgee</t>
@@ -258,7 +261,7 @@
     <t>Team Tau</t>
   </si>
   <si>
-    <t>S. GAMGEE</t>
+    <t>GAMGEE</t>
   </si>
   <si>
     <t>Pool G</t>
@@ -270,9 +273,6 @@
     <t>Team Upsilon</t>
   </si>
   <si>
-    <t>T. LANNISTER</t>
-  </si>
-  <si>
     <t>Ulysses</t>
   </si>
   <si>
@@ -300,7 +300,7 @@
     <t>Team Psi</t>
   </si>
   <si>
-    <t>W. WONKA</t>
+    <t>WONKA</t>
   </si>
   <si>
     <t>Xaro Xhoan Daxos</t>
@@ -309,7 +309,7 @@
     <t>Team Omega</t>
   </si>
   <si>
-    <t>X. DAXOS</t>
+    <t>DAXOS</t>
   </si>
   <si>
     <t>Ygritte</t>
@@ -757,7 +757,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
@@ -813,32 +813,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
@@ -872,51 +848,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1137,8 +1068,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="true"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="15"/>
-    <col customWidth="true" max="4" min="2" width="30"/>
-    <col customWidth="true" max="26" min="5" width="10.6640625"/>
+    <col customWidth="true" max="26" min="2" width="30"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="12.75" customHeight="true">
@@ -1154,276 +1084,279 @@
       <c r="D1" t="s">
         <v>14</v>
       </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="2" spans="1:2" ht="12.75" customHeight="true">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="12.75" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="12.75" customHeight="true">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="12.75" customHeight="true">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="12.75" customHeight="true">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="12.75" customHeight="true">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="12.75" customHeight="true">
       <c r="A8" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="12.75" customHeight="true">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="12.75" customHeight="true">
       <c r="A10" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="12.75" customHeight="true">
       <c r="A11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
         <v>45</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="12.75" customHeight="true">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="12.75" customHeight="true">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="12.75" customHeight="true">
       <c r="A14" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="12.75" customHeight="true">
       <c r="A15" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="12.75" customHeight="true">
       <c r="A16" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="12.75" customHeight="true">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="12.75" customHeight="true">
       <c r="A18" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="12.75" customHeight="true">
       <c r="A19" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="12.75" customHeight="true">
       <c r="A20" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="12.75" customHeight="true">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
         <v>76</v>
@@ -1437,7 +1370,7 @@
     </row>
     <row r="22" spans="1:2" ht="12.75" customHeight="true">
       <c r="A22" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>79</v>
@@ -2535,362 +2468,361 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
-      <c r="A2" s="36" t="str">
+      <c r="A2" s="28" t="str">
         <f>data!$A$4</f>
       </c>
-      <c r="C2" s="35" t="str">
+      <c r="C2" s="27" t="str">
         <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G10)</f>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="37" t="str">
+      <c r="A3" s="29" t="str">
         <f>"1. " &amp; data!$B$2</f>
       </c>
-      <c r="D3" s="34"/>
-      <c r="E3" s="33">
+      <c r="D3" s="26"/>
+      <c r="E3" s="25">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="38" t="str">
+      <c r="A4" s="30" t="str">
         <f>"2. " &amp; data!$B$3</f>
       </c>
-      <c r="C4" s="35" t="str">
+      <c r="C4" s="27" t="str">
         <f>CONCATENATE("Pool B.2 ",'Pool Matches'!O11)</f>
       </c>
-      <c r="D4" s="24"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="32"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="24"/>
     </row>
     <row r="5">
-      <c r="A5" s="39" t="str">
+      <c r="A5" s="31" t="str">
         <f>"3. " &amp; data!$B$4</f>
       </c>
-      <c r="G5" s="33">
+      <c r="G5" s="25">
         <v>9</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34"/>
-      <c r="C6" s="35" t="str">
+      <c r="A6" s="26"/>
+      <c r="C6" s="27" t="str">
         <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G21)</f>
       </c>
-      <c r="G6" s="32"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="32"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="24"/>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="str">
+      <c r="A7" s="28" t="str">
         <f>data!$A$7</f>
       </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="33">
+      <c r="D7" s="26"/>
+      <c r="E7" s="25">
         <v>2</v>
       </c>
-      <c r="F7" s="24"/>
-      <c r="G7" s="32"/>
-      <c r="I7" s="32"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="24"/>
+      <c r="I7" s="24"/>
     </row>
     <row r="8">
-      <c r="A8" s="37" t="str">
+      <c r="A8" s="29" t="str">
         <f>"1. " &amp; data!$B$5</f>
       </c>
-      <c r="C8" s="35" t="str">
+      <c r="C8" s="27" t="str">
         <f>CONCATENATE("Pool D.2 ",'Pool Matches'!O22)</f>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="32"/>
-      <c r="I8" s="32"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="24"/>
+      <c r="I8" s="24"/>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="str">
+      <c r="A9" s="30" t="str">
         <f>"2. " &amp; data!$B$6</f>
       </c>
-      <c r="I9" s="33">
+      <c r="I9" s="25">
         <v>13</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="str">
+      <c r="A10" s="31" t="str">
         <f>"3. " &amp; data!$B$7</f>
       </c>
-      <c r="C10" s="35" t="str">
+      <c r="C10" s="27" t="str">
         <f>CONCATENATE("Pool E.1 ",'Pool Matches'!G32)</f>
       </c>
-      <c r="I10" s="32"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="32"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="24"/>
     </row>
     <row r="11">
-      <c r="A11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="33">
+      <c r="A11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="25">
         <v>3</v>
       </c>
-      <c r="I11" s="32"/>
-      <c r="K11" s="32"/>
+      <c r="I11" s="24"/>
+      <c r="K11" s="24"/>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="str">
+      <c r="A12" s="28" t="str">
         <f>data!$A$10</f>
       </c>
-      <c r="C12" s="35" t="str">
+      <c r="C12" s="27" t="str">
         <f>CONCATENATE("Pool F.2 ",'Pool Matches'!O33)</f>
       </c>
-      <c r="D12" s="24"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="K12" s="32"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="K12" s="24"/>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="str">
+      <c r="A13" s="29" t="str">
         <f>"1. " &amp; data!$B$8</f>
       </c>
-      <c r="G13" s="33">
+      <c r="G13" s="25">
         <v>10</v>
       </c>
-      <c r="H13" s="24"/>
-      <c r="I13" s="32"/>
-      <c r="K13" s="32"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="24"/>
+      <c r="K13" s="24"/>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="str">
+      <c r="A14" s="30" t="str">
         <f>"2. " &amp; data!$B$9</f>
       </c>
-      <c r="C14" s="35" t="str">
+      <c r="C14" s="27" t="str">
         <f>CONCATENATE("Pool G.1 ",'Pool Matches'!G43)</f>
       </c>
-      <c r="G14" s="32"/>
-      <c r="K14" s="32"/>
+      <c r="G14" s="24"/>
+      <c r="K14" s="24"/>
     </row>
     <row r="15">
-      <c r="A15" s="39" t="str">
+      <c r="A15" s="31" t="str">
         <f>"3. " &amp; data!$B$10</f>
       </c>
-      <c r="D15" s="34"/>
-      <c r="E15" s="33">
+      <c r="D15" s="26"/>
+      <c r="E15" s="25">
         <v>4</v>
       </c>
-      <c r="F15" s="24"/>
-      <c r="G15" s="32"/>
-      <c r="K15" s="32"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="24"/>
+      <c r="K15" s="24"/>
     </row>
     <row r="16">
-      <c r="A16" s="34"/>
-      <c r="C16" s="35" t="str">
+      <c r="A16" s="26"/>
+      <c r="C16" s="27" t="str">
         <f>CONCATENATE("Pool H.2 ",'Pool Matches'!O44)</f>
       </c>
-      <c r="D16" s="24"/>
-      <c r="E16" s="32"/>
-      <c r="K16" s="32"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="24"/>
+      <c r="K16" s="24"/>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="str">
+      <c r="A17" s="28" t="str">
         <f>data!$A$13</f>
       </c>
-      <c r="K17" s="33">
+      <c r="K17" s="25">
         <v>15</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="37" t="str">
+      <c r="A18" s="29" t="str">
         <f>"1. " &amp; data!$B$11</f>
       </c>
-      <c r="C18" s="35" t="str">
+      <c r="C18" s="27" t="str">
         <f>CONCATENATE("Pool B.1 ",'Pool Matches'!O10)</f>
       </c>
-      <c r="K18" s="32"/>
+      <c r="K18" s="24"/>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="str">
+      <c r="A19" s="30" t="str">
         <f>"2. " &amp; data!$B$12</f>
       </c>
-      <c r="D19" s="34"/>
-      <c r="E19" s="33">
+      <c r="D19" s="26"/>
+      <c r="E19" s="25">
         <v>5</v>
       </c>
-      <c r="K19" s="32"/>
+      <c r="K19" s="24"/>
     </row>
     <row r="20">
-      <c r="A20" s="39" t="str">
+      <c r="A20" s="31" t="str">
         <f>"3. " &amp; data!$B$13</f>
       </c>
-      <c r="C20" s="35" t="str">
+      <c r="C20" s="27" t="str">
         <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G11)</f>
       </c>
-      <c r="D20" s="24"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="32"/>
-      <c r="K20" s="32"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="24"/>
+      <c r="K20" s="24"/>
     </row>
     <row r="21">
-      <c r="A21" s="34"/>
-      <c r="G21" s="33">
+      <c r="A21" s="26"/>
+      <c r="G21" s="25">
         <v>11</v>
       </c>
-      <c r="K21" s="32"/>
+      <c r="K21" s="24"/>
     </row>
     <row r="22">
-      <c r="A22" s="36" t="str">
+      <c r="A22" s="28" t="str">
         <f>data!$A$16</f>
       </c>
-      <c r="C22" s="35" t="str">
+      <c r="C22" s="27" t="str">
         <f>CONCATENATE("Pool D.1 ",'Pool Matches'!O21)</f>
       </c>
-      <c r="G22" s="32"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="32"/>
-      <c r="K22" s="32"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="24"/>
+      <c r="K22" s="24"/>
     </row>
     <row r="23">
-      <c r="A23" s="37" t="str">
+      <c r="A23" s="29" t="str">
         <f>"1. " &amp; data!$B$14</f>
       </c>
-      <c r="D23" s="34"/>
-      <c r="E23" s="33">
+      <c r="D23" s="26"/>
+      <c r="E23" s="25">
         <v>6</v>
       </c>
-      <c r="F23" s="24"/>
-      <c r="G23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="K23" s="32"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="K23" s="24"/>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="str">
+      <c r="A24" s="30" t="str">
         <f>"2. " &amp; data!$B$15</f>
       </c>
-      <c r="C24" s="35" t="str">
+      <c r="C24" s="27" t="str">
         <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G22)</f>
       </c>
-      <c r="D24" s="24"/>
-      <c r="E24" s="32"/>
-      <c r="I24" s="32"/>
-      <c r="K24" s="32"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="K24" s="24"/>
     </row>
     <row r="25">
-      <c r="A25" s="39" t="str">
+      <c r="A25" s="31" t="str">
         <f>"3. " &amp; data!$B$16</f>
       </c>
-      <c r="I25" s="33">
+      <c r="I25" s="25">
         <v>14</v>
       </c>
-      <c r="J25" s="24"/>
-      <c r="K25" s="32"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="24"/>
     </row>
     <row r="26">
-      <c r="A26" s="34"/>
-      <c r="C26" s="35" t="str">
+      <c r="A26" s="26"/>
+      <c r="C26" s="27" t="str">
         <f>CONCATENATE("Pool F.1 ",'Pool Matches'!O32)</f>
       </c>
-      <c r="I26" s="32"/>
+      <c r="I26" s="24"/>
     </row>
     <row r="27">
-      <c r="A27" s="36" t="str">
+      <c r="A27" s="28" t="str">
         <f>data!$A$19</f>
       </c>
-      <c r="D27" s="34"/>
-      <c r="E27" s="33">
+      <c r="D27" s="26"/>
+      <c r="E27" s="25">
         <v>7</v>
       </c>
-      <c r="I27" s="32"/>
+      <c r="I27" s="24"/>
     </row>
     <row r="28">
-      <c r="A28" s="37" t="str">
+      <c r="A28" s="29" t="str">
         <f>"1. " &amp; data!$B$17</f>
       </c>
-      <c r="C28" s="35" t="str">
+      <c r="C28" s="27" t="str">
         <f>CONCATENATE("Pool E.2 ",'Pool Matches'!G33)</f>
       </c>
-      <c r="D28" s="24"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="32"/>
-      <c r="I28" s="32"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="24"/>
+      <c r="I28" s="24"/>
     </row>
     <row r="29">
-      <c r="A29" s="38" t="str">
+      <c r="A29" s="30" t="str">
         <f>"2. " &amp; data!$B$18</f>
       </c>
-      <c r="G29" s="33">
+      <c r="G29" s="25">
         <v>12</v>
       </c>
-      <c r="H29" s="24"/>
-      <c r="I29" s="32"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="24"/>
     </row>
     <row r="30">
-      <c r="A30" s="39" t="str">
+      <c r="A30" s="31" t="str">
         <f>"3. " &amp; data!$B$19</f>
       </c>
-      <c r="C30" s="35" t="str">
+      <c r="C30" s="27" t="str">
         <f>CONCATENATE("Pool H.1 ",'Pool Matches'!O43)</f>
       </c>
-      <c r="G30" s="32"/>
+      <c r="G30" s="24"/>
     </row>
     <row r="31">
-      <c r="A31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="33">
+      <c r="A31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="25">
         <v>8</v>
       </c>
-      <c r="F31" s="24"/>
-      <c r="G31" s="32"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="24"/>
     </row>
     <row r="32">
-      <c r="A32" s="36" t="str">
+      <c r="A32" s="28" t="str">
         <f>data!$A$22</f>
       </c>
-      <c r="C32" s="35" t="str">
+      <c r="C32" s="27" t="str">
         <f>CONCATENATE("Pool G.2 ",'Pool Matches'!G44)</f>
       </c>
-      <c r="D32" s="24"/>
-      <c r="E32" s="32"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="24"/>
     </row>
     <row r="33">
-      <c r="A33" s="37" t="str">
+      <c r="A33" s="29" t="str">
         <f>"1. " &amp; data!$B$20</f>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="38" t="str">
+      <c r="A34" s="30" t="str">
         <f>"2. " &amp; data!$B$21</f>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="39" t="str">
+      <c r="A35" s="31" t="str">
         <f>"3. " &amp; data!$B$22</f>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="34"/>
+      <c r="A36" s="26"/>
     </row>
     <row r="37">
-      <c r="A37" s="36" t="str">
+      <c r="A37" s="28" t="str">
         <f>data!$A$25</f>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="37" t="str">
+      <c r="A38" s="29" t="str">
         <f>"1. " &amp; data!$B$23</f>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="38" t="str">
+      <c r="A39" s="30" t="str">
         <f>"2. " &amp; data!$B$24</f>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="39" t="str">
+      <c r="A40" s="31" t="str">
         <f>"3. " &amp; data!$B$25</f>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="34"/>
+      <c r="A41" s="26"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
@@ -2904,122 +2836,122 @@
   <dimension ref="A1"/>
   <sheetData>
     <row r="1" ht="400" customHeight="true">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="34" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="2" ht="400" customHeight="true">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="34" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="3" ht="400" customHeight="true">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="34" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="4" ht="400" customHeight="true">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="34" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="5" ht="400" customHeight="true">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="34" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="6" ht="400" customHeight="true">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="34" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="7" ht="400" customHeight="true">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="34" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="8" ht="400" customHeight="true">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="34" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="9" ht="400" customHeight="true">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="34" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="10" ht="400" customHeight="true">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="34" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="11" ht="400" customHeight="true">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="34" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="12" ht="400" customHeight="true">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="34" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="13" ht="400" customHeight="true">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="34" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="14" ht="400" customHeight="true">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="34" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="15" ht="400" customHeight="true">
-      <c r="A15" s="42" t="s">
+      <c r="A15" s="34" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="16" ht="400" customHeight="true">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="34" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="17" ht="400" customHeight="true">
-      <c r="A17" s="42" t="s">
+      <c r="A17" s="34" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="18" ht="400" customHeight="true">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="34" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="19" ht="400" customHeight="true">
-      <c r="A19" s="42" t="s">
+      <c r="A19" s="34" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="20" ht="400" customHeight="true">
-      <c r="A20" s="42" t="s">
+      <c r="A20" s="34" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="21" ht="400" customHeight="true">
-      <c r="A21" s="42" t="s">
+      <c r="A21" s="34" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="22" ht="400" customHeight="true">
-      <c r="A22" s="42" t="s">
+      <c r="A22" s="34" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="23" ht="400" customHeight="true">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="34" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="24" ht="400" customHeight="true">
-      <c r="A24" s="42" t="s">
+      <c r="A24" s="34" t="s">
         <v>121</v>
       </c>
     </row>
@@ -3283,7 +3215,6 @@
     <col customWidth="true" max="26" min="11" width="8.83203125"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" spans="1:8" ht="20">
       <c r="A2" s="2"/>
       <c r="B2" s="15" t="s">
@@ -3470,9 +3401,6 @@
     <col max="16384" min="16" style="7" width="10.83203125"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="20" t="str">
         <f>data!$A$4</f>
@@ -3500,7 +3428,7 @@
       <c r="D5" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" t="s">
         <v>94</v>
       </c>
       <c r="I5" s="21" t="s">
@@ -3509,7 +3437,7 @@
       <c r="L5" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="O5" s="25" t="s">
+      <c r="O5" t="s">
         <v>94</v>
       </c>
     </row>
@@ -3585,39 +3513,36 @@
         <f>data!$B$5</f>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="F10" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="G10" s="24"/>
+      <c r="G10" s="23"/>
       <c r="N10" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="O10" s="24"/>
+      <c r="O10" s="23"/>
     </row>
     <row r="11">
       <c r="F11" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="24"/>
+      <c r="G11" s="23"/>
       <c r="N11" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="O11" s="24"/>
+      <c r="O11" s="23"/>
     </row>
     <row r="12">
       <c r="F12" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G12" s="24"/>
+      <c r="G12" s="23"/>
       <c r="N12" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="O12" s="24"/>
-    </row>
-    <row r="13"/>
-    <row r="14"/>
+      <c r="O12" s="23"/>
+    </row>
     <row r="15">
       <c r="A15" s="20" t="str">
         <f>data!$A$10</f>
@@ -3645,7 +3570,7 @@
       <c r="D16" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="G16" s="26" t="s">
+      <c r="G16" t="s">
         <v>94</v>
       </c>
       <c r="I16" s="21" t="s">
@@ -3654,7 +3579,7 @@
       <c r="L16" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="O16" s="27" t="s">
+      <c r="O16" t="s">
         <v>94</v>
       </c>
     </row>
@@ -3730,39 +3655,36 @@
         <f>data!$B$11</f>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="F21" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="G21" s="24"/>
+      <c r="G21" s="23"/>
       <c r="N21" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="O21" s="24"/>
+      <c r="O21" s="23"/>
     </row>
     <row r="22">
       <c r="F22" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="G22" s="24"/>
+      <c r="G22" s="23"/>
       <c r="N22" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="O22" s="24"/>
+      <c r="O22" s="23"/>
     </row>
     <row r="23">
       <c r="F23" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G23" s="24"/>
+      <c r="G23" s="23"/>
       <c r="N23" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="O23" s="24"/>
-    </row>
-    <row r="24"/>
-    <row r="25"/>
+      <c r="O23" s="23"/>
+    </row>
     <row r="26">
       <c r="A26" s="20" t="str">
         <f>data!$A$16</f>
@@ -3790,7 +3712,7 @@
       <c r="D27" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="G27" s="28" t="s">
+      <c r="G27" t="s">
         <v>94</v>
       </c>
       <c r="I27" s="21" t="s">
@@ -3799,7 +3721,7 @@
       <c r="L27" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="O27" s="29" t="s">
+      <c r="O27" t="s">
         <v>94</v>
       </c>
     </row>
@@ -3875,39 +3797,36 @@
         <f>data!$B$17</f>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="F32" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="G32" s="24"/>
+      <c r="G32" s="23"/>
       <c r="N32" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="O32" s="24"/>
+      <c r="O32" s="23"/>
     </row>
     <row r="33">
       <c r="F33" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="G33" s="24"/>
+      <c r="G33" s="23"/>
       <c r="N33" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="O33" s="24"/>
+      <c r="O33" s="23"/>
     </row>
     <row r="34">
       <c r="F34" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G34" s="24"/>
+      <c r="G34" s="23"/>
       <c r="N34" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="O34" s="24"/>
-    </row>
-    <row r="35"/>
-    <row r="36"/>
+      <c r="O34" s="23"/>
+    </row>
     <row r="37">
       <c r="A37" s="20" t="str">
         <f>data!$A$22</f>
@@ -3935,7 +3854,7 @@
       <c r="D38" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="G38" s="30" t="s">
+      <c r="G38" t="s">
         <v>94</v>
       </c>
       <c r="I38" s="21" t="s">
@@ -3944,7 +3863,7 @@
       <c r="L38" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="O38" s="31" t="s">
+      <c r="O38" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4020,36 +3939,35 @@
         <f>data!$B$23</f>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="F43" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="G43" s="24"/>
+      <c r="G43" s="23"/>
       <c r="N43" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="O43" s="24"/>
+      <c r="O43" s="23"/>
     </row>
     <row r="44">
       <c r="F44" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="G44" s="24"/>
+      <c r="G44" s="23"/>
       <c r="N44" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="O44" s="24"/>
+      <c r="O44" s="23"/>
     </row>
     <row r="45">
       <c r="F45" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G45" s="24"/>
+      <c r="G45" s="23"/>
       <c r="N45" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="O45" s="24"/>
+      <c r="O45" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4104,7 +4022,6 @@
       <c r="N1" s="20"/>
       <c r="O1" s="20"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="20" t="s">
         <v>122</v>
@@ -4132,7 +4049,7 @@
       <c r="D4" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="G4" s="43" t="s">
+      <c r="G4" t="s">
         <v>94</v>
       </c>
       <c r="I4" s="21" t="s">
@@ -4141,7 +4058,7 @@
       <c r="L4" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="O4" s="44" t="s">
+      <c r="O4" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4169,29 +4086,26 @@
         <f>CONCATENATE("Pool D.2 ",'Pool Matches'!O22)</f>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="F7" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="G7" s="24"/>
+      <c r="G7" s="23"/>
       <c r="N7" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="O7" s="24"/>
+      <c r="O7" s="23"/>
     </row>
     <row r="8">
       <c r="F8" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G8" s="24"/>
+      <c r="G8" s="23"/>
       <c r="N8" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="O8" s="24"/>
-    </row>
-    <row r="9"/>
-    <row r="10"/>
+      <c r="O8" s="23"/>
+    </row>
     <row r="11">
       <c r="A11" s="20" t="s">
         <v>126</v>
@@ -4219,7 +4133,7 @@
       <c r="D12" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="G12" s="45" t="s">
+      <c r="G12" t="s">
         <v>94</v>
       </c>
       <c r="I12" s="21" t="s">
@@ -4228,7 +4142,7 @@
       <c r="L12" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="O12" s="46" t="s">
+      <c r="O12" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4256,29 +4170,26 @@
         <f>CONCATENATE("Pool H.2 ",'Pool Matches'!O44)</f>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="F15" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="G15" s="24"/>
+      <c r="G15" s="23"/>
       <c r="N15" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="O15" s="24"/>
+      <c r="O15" s="23"/>
     </row>
     <row r="16">
       <c r="F16" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G16" s="24"/>
+      <c r="G16" s="23"/>
       <c r="N16" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="O16" s="24"/>
-    </row>
-    <row r="17"/>
-    <row r="18"/>
+      <c r="O16" s="23"/>
+    </row>
     <row r="19">
       <c r="A19" s="20" t="s">
         <v>128</v>
@@ -4306,7 +4217,7 @@
       <c r="D20" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="G20" s="47" t="s">
+      <c r="G20" t="s">
         <v>94</v>
       </c>
       <c r="I20" s="21" t="s">
@@ -4315,7 +4226,7 @@
       <c r="L20" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="O20" s="48" t="s">
+      <c r="O20" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4343,29 +4254,26 @@
         <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G22)</f>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="F23" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="G23" s="24"/>
+      <c r="G23" s="23"/>
       <c r="N23" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="O23" s="24"/>
+      <c r="O23" s="23"/>
     </row>
     <row r="24">
       <c r="F24" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G24" s="24"/>
+      <c r="G24" s="23"/>
       <c r="N24" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="O24" s="24"/>
-    </row>
-    <row r="25"/>
-    <row r="26"/>
+      <c r="O24" s="23"/>
+    </row>
     <row r="27">
       <c r="A27" s="20" t="s">
         <v>130</v>
@@ -4393,7 +4301,7 @@
       <c r="D28" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="G28" s="49" t="s">
+      <c r="G28" t="s">
         <v>94</v>
       </c>
       <c r="I28" s="21" t="s">
@@ -4402,7 +4310,7 @@
       <c r="L28" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="O28" s="50" t="s">
+      <c r="O28" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4430,34 +4338,26 @@
         <f>CONCATENATE("Pool G.2 ",'Pool Matches'!G44)</f>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="F31" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="G31" s="24"/>
+      <c r="G31" s="23"/>
       <c r="N31" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="O31" s="24"/>
+      <c r="O31" s="23"/>
     </row>
     <row r="32">
       <c r="F32" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G32" s="24"/>
+      <c r="G32" s="23"/>
       <c r="N32" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="O32" s="24"/>
-    </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
+      <c r="O32" s="23"/>
+    </row>
     <row r="40">
       <c r="A40" s="20" t="s">
         <v>132</v>
@@ -4477,7 +4377,6 @@
       <c r="N40" s="20"/>
       <c r="O40" s="20"/>
     </row>
-    <row r="41"/>
     <row r="42">
       <c r="A42" s="20" t="s">
         <v>133</v>
@@ -4505,7 +4404,7 @@
       <c r="D43" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="G43" s="51" t="s">
+      <c r="G43" t="s">
         <v>94</v>
       </c>
       <c r="I43" s="21" t="s">
@@ -4514,7 +4413,7 @@
       <c r="L43" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="O43" s="52" t="s">
+      <c r="O43" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4542,29 +4441,26 @@
         <f>CONCATENATE("M 4 ",'Elimination Matches'!O15)</f>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="F46" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="G46" s="24"/>
+      <c r="G46" s="23"/>
       <c r="N46" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="O46" s="24"/>
+      <c r="O46" s="23"/>
     </row>
     <row r="47">
       <c r="F47" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G47" s="24"/>
+      <c r="G47" s="23"/>
       <c r="N47" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="O47" s="24"/>
-    </row>
-    <row r="48"/>
-    <row r="49"/>
+      <c r="O47" s="23"/>
+    </row>
     <row r="50">
       <c r="A50" s="20" t="s">
         <v>135</v>
@@ -4592,7 +4488,7 @@
       <c r="D51" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="G51" s="53" t="s">
+      <c r="G51" t="s">
         <v>94</v>
       </c>
       <c r="I51" s="21" t="s">
@@ -4601,7 +4497,7 @@
       <c r="L51" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="O51" s="54" t="s">
+      <c r="O51" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4629,34 +4525,26 @@
         <f>CONCATENATE("M 8 ",'Elimination Matches'!O31)</f>
       </c>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="F54" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="G54" s="24"/>
+      <c r="G54" s="23"/>
       <c r="N54" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="O54" s="24"/>
+      <c r="O54" s="23"/>
     </row>
     <row r="55">
       <c r="F55" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G55" s="24"/>
+      <c r="G55" s="23"/>
       <c r="N55" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="O55" s="24"/>
-    </row>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
+      <c r="O55" s="23"/>
+    </row>
     <row r="63">
       <c r="A63" s="20" t="s">
         <v>137</v>
@@ -4676,7 +4564,6 @@
       <c r="N63" s="20"/>
       <c r="O63" s="20"/>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="20" t="s">
         <v>138</v>
@@ -4704,7 +4591,7 @@
       <c r="D66" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="G66" s="55" t="s">
+      <c r="G66" t="s">
         <v>94</v>
       </c>
       <c r="I66" s="21" t="s">
@@ -4713,7 +4600,7 @@
       <c r="L66" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="O66" s="56" t="s">
+      <c r="O66" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4741,34 +4628,26 @@
         <f>CONCATENATE("M 12 ",'Elimination Matches'!O54)</f>
       </c>
     </row>
-    <row r="68"/>
     <row r="69">
       <c r="F69" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="G69" s="24"/>
+      <c r="G69" s="23"/>
       <c r="N69" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="O69" s="24"/>
+      <c r="O69" s="23"/>
     </row>
     <row r="70">
       <c r="F70" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G70" s="24"/>
+      <c r="G70" s="23"/>
       <c r="N70" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="O70" s="24"/>
-    </row>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
+      <c r="O70" s="23"/>
+    </row>
     <row r="78">
       <c r="A78" s="20" t="s">
         <v>140</v>
@@ -4788,7 +4667,6 @@
       <c r="N78" s="20"/>
       <c r="O78" s="20"/>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="20" t="s">
         <v>141</v>
@@ -4807,7 +4685,7 @@
       <c r="D81" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="G81" s="57" t="s">
+      <c r="G81" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4824,18 +4702,17 @@
         <f>CONCATENATE("M 14 ",'Elimination Matches'!O69)</f>
       </c>
     </row>
-    <row r="83"/>
     <row r="84">
       <c r="F84" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="G84" s="24"/>
+      <c r="G84" s="23"/>
     </row>
     <row r="85">
       <c r="F85" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G85" s="24"/>
+      <c r="G85" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -4877,340 +4754,340 @@
   </cols>
   <sheetData>
     <row r="1" ht="110" customHeight="true">
-      <c r="A1" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="41" t="str">
+      <c r="A1" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="33" t="str">
         <f>data!D2</f>
       </c>
     </row>
     <row r="2" ht="115" customHeight="true">
-      <c r="A2" s="40">
+      <c r="A2" s="32">
         <v>1</v>
       </c>
-      <c r="B2" s="41"/>
+      <c r="B2" s="33"/>
     </row>
     <row r="3" ht="110" customHeight="true">
-      <c r="A3" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="41" t="str">
+      <c r="A3" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="33" t="str">
         <f>data!D3</f>
       </c>
     </row>
     <row r="4" ht="115" customHeight="true">
-      <c r="A4" s="40">
+      <c r="A4" s="32">
         <v>2</v>
       </c>
-      <c r="B4" s="41"/>
+      <c r="B4" s="33"/>
     </row>
     <row r="5" ht="110" customHeight="true">
-      <c r="A5" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="41" t="str">
+      <c r="A5" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="33" t="str">
         <f>data!D4</f>
       </c>
     </row>
     <row r="6" ht="115" customHeight="true">
-      <c r="A6" s="40">
+      <c r="A6" s="32">
         <v>3</v>
       </c>
-      <c r="B6" s="41"/>
+      <c r="B6" s="33"/>
     </row>
     <row r="7" ht="110" customHeight="true">
-      <c r="A7" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="41" t="str">
+      <c r="A7" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="33" t="str">
         <f>data!D5</f>
       </c>
     </row>
     <row r="8" ht="115" customHeight="true">
-      <c r="A8" s="40">
+      <c r="A8" s="32">
         <v>1</v>
       </c>
-      <c r="B8" s="41"/>
+      <c r="B8" s="33"/>
     </row>
     <row r="9" ht="110" customHeight="true">
-      <c r="A9" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="41" t="str">
+      <c r="A9" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="33" t="str">
         <f>data!D6</f>
       </c>
     </row>
     <row r="10" ht="115" customHeight="true">
-      <c r="A10" s="40">
+      <c r="A10" s="32">
         <v>2</v>
       </c>
-      <c r="B10" s="41"/>
+      <c r="B10" s="33"/>
     </row>
     <row r="11" ht="110" customHeight="true">
-      <c r="A11" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="41" t="str">
+      <c r="A11" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="33" t="str">
         <f>data!D7</f>
       </c>
     </row>
     <row r="12" ht="115" customHeight="true">
-      <c r="A12" s="40">
+      <c r="A12" s="32">
         <v>3</v>
       </c>
-      <c r="B12" s="41"/>
+      <c r="B12" s="33"/>
     </row>
     <row r="13" ht="110" customHeight="true">
-      <c r="A13" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="41" t="str">
+      <c r="A13" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="33" t="str">
         <f>data!D8</f>
       </c>
     </row>
     <row r="14" ht="115" customHeight="true">
-      <c r="A14" s="40">
+      <c r="A14" s="32">
         <v>1</v>
       </c>
-      <c r="B14" s="41"/>
+      <c r="B14" s="33"/>
     </row>
     <row r="15" ht="110" customHeight="true">
-      <c r="A15" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="41" t="str">
+      <c r="A15" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="33" t="str">
         <f>data!D9</f>
       </c>
     </row>
     <row r="16" ht="115" customHeight="true">
-      <c r="A16" s="40">
+      <c r="A16" s="32">
         <v>2</v>
       </c>
-      <c r="B16" s="41"/>
+      <c r="B16" s="33"/>
     </row>
     <row r="17" ht="110" customHeight="true">
-      <c r="A17" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="41" t="str">
+      <c r="A17" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="33" t="str">
         <f>data!D10</f>
       </c>
     </row>
     <row r="18" ht="115" customHeight="true">
-      <c r="A18" s="40">
+      <c r="A18" s="32">
         <v>3</v>
       </c>
-      <c r="B18" s="41"/>
+      <c r="B18" s="33"/>
     </row>
     <row r="19" ht="110" customHeight="true">
-      <c r="A19" s="40" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="41" t="str">
+      <c r="A19" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="33" t="str">
         <f>data!D11</f>
       </c>
     </row>
     <row r="20" ht="115" customHeight="true">
-      <c r="A20" s="40">
+      <c r="A20" s="32">
         <v>1</v>
       </c>
-      <c r="B20" s="41"/>
+      <c r="B20" s="33"/>
     </row>
     <row r="21" ht="110" customHeight="true">
-      <c r="A21" s="40" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" s="41" t="str">
+      <c r="A21" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="33" t="str">
         <f>data!D12</f>
       </c>
     </row>
     <row r="22" ht="115" customHeight="true">
-      <c r="A22" s="40">
+      <c r="A22" s="32">
         <v>2</v>
       </c>
-      <c r="B22" s="41"/>
+      <c r="B22" s="33"/>
     </row>
     <row r="23" ht="110" customHeight="true">
-      <c r="A23" s="40" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="41" t="str">
+      <c r="A23" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="33" t="str">
         <f>data!D13</f>
       </c>
     </row>
     <row r="24" ht="115" customHeight="true">
-      <c r="A24" s="40">
+      <c r="A24" s="32">
         <v>3</v>
       </c>
-      <c r="B24" s="41"/>
+      <c r="B24" s="33"/>
     </row>
     <row r="25" ht="110" customHeight="true">
-      <c r="A25" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="B25" s="41" t="str">
+      <c r="A25" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="33" t="str">
         <f>data!D14</f>
       </c>
     </row>
     <row r="26" ht="115" customHeight="true">
-      <c r="A26" s="40">
+      <c r="A26" s="32">
         <v>1</v>
       </c>
-      <c r="B26" s="41"/>
+      <c r="B26" s="33"/>
     </row>
     <row r="27" ht="110" customHeight="true">
-      <c r="A27" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="41" t="str">
+      <c r="A27" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="33" t="str">
         <f>data!D15</f>
       </c>
     </row>
     <row r="28" ht="115" customHeight="true">
-      <c r="A28" s="40">
+      <c r="A28" s="32">
         <v>2</v>
       </c>
-      <c r="B28" s="41"/>
+      <c r="B28" s="33"/>
     </row>
     <row r="29" ht="110" customHeight="true">
-      <c r="A29" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="41" t="str">
+      <c r="A29" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="33" t="str">
         <f>data!D16</f>
       </c>
     </row>
     <row r="30" ht="115" customHeight="true">
-      <c r="A30" s="40">
+      <c r="A30" s="32">
         <v>3</v>
       </c>
-      <c r="B30" s="41"/>
+      <c r="B30" s="33"/>
     </row>
     <row r="31" ht="110" customHeight="true">
-      <c r="A31" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="41" t="str">
+      <c r="A31" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="33" t="str">
         <f>data!D17</f>
       </c>
     </row>
     <row r="32" ht="115" customHeight="true">
-      <c r="A32" s="40">
+      <c r="A32" s="32">
         <v>1</v>
       </c>
-      <c r="B32" s="41"/>
+      <c r="B32" s="33"/>
     </row>
     <row r="33" ht="110" customHeight="true">
-      <c r="A33" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="B33" s="41" t="str">
+      <c r="A33" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="33" t="str">
         <f>data!D18</f>
       </c>
     </row>
     <row r="34" ht="115" customHeight="true">
-      <c r="A34" s="40">
+      <c r="A34" s="32">
         <v>2</v>
       </c>
-      <c r="B34" s="41"/>
+      <c r="B34" s="33"/>
     </row>
     <row r="35" ht="110" customHeight="true">
-      <c r="A35" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="B35" s="41" t="str">
+      <c r="A35" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="33" t="str">
         <f>data!D19</f>
       </c>
     </row>
     <row r="36" ht="115" customHeight="true">
-      <c r="A36" s="40">
+      <c r="A36" s="32">
         <v>3</v>
       </c>
-      <c r="B36" s="41"/>
+      <c r="B36" s="33"/>
     </row>
     <row r="37" ht="110" customHeight="true">
-      <c r="A37" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37" s="41" t="str">
+      <c r="A37" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="33" t="str">
         <f>data!D20</f>
       </c>
     </row>
     <row r="38" ht="115" customHeight="true">
-      <c r="A38" s="40">
+      <c r="A38" s="32">
         <v>1</v>
       </c>
-      <c r="B38" s="41"/>
+      <c r="B38" s="33"/>
     </row>
     <row r="39" ht="110" customHeight="true">
-      <c r="A39" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="B39" s="41" t="str">
+      <c r="A39" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" s="33" t="str">
         <f>data!D21</f>
       </c>
     </row>
     <row r="40" ht="115" customHeight="true">
-      <c r="A40" s="40">
+      <c r="A40" s="32">
         <v>2</v>
       </c>
-      <c r="B40" s="41"/>
+      <c r="B40" s="33"/>
     </row>
     <row r="41" ht="110" customHeight="true">
-      <c r="A41" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="B41" s="41" t="str">
+      <c r="A41" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="B41" s="33" t="str">
         <f>data!D22</f>
       </c>
     </row>
     <row r="42" ht="115" customHeight="true">
-      <c r="A42" s="40">
+      <c r="A42" s="32">
         <v>3</v>
       </c>
-      <c r="B42" s="41"/>
+      <c r="B42" s="33"/>
     </row>
     <row r="43" ht="110" customHeight="true">
-      <c r="A43" s="40" t="s">
+      <c r="A43" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="B43" s="41" t="str">
+      <c r="B43" s="33" t="str">
         <f>data!D23</f>
       </c>
     </row>
     <row r="44" ht="115" customHeight="true">
-      <c r="A44" s="40">
+      <c r="A44" s="32">
         <v>1</v>
       </c>
-      <c r="B44" s="41"/>
+      <c r="B44" s="33"/>
     </row>
     <row r="45" ht="110" customHeight="true">
-      <c r="A45" s="40" t="s">
+      <c r="A45" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="B45" s="41" t="str">
+      <c r="B45" s="33" t="str">
         <f>data!D24</f>
       </c>
     </row>
     <row r="46" ht="115" customHeight="true">
-      <c r="A46" s="40">
+      <c r="A46" s="32">
         <v>2</v>
       </c>
-      <c r="B46" s="41"/>
+      <c r="B46" s="33"/>
     </row>
     <row r="47" ht="110" customHeight="true">
-      <c r="A47" s="40" t="s">
+      <c r="A47" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="B47" s="41" t="str">
+      <c r="B47" s="33" t="str">
         <f>data!D25</f>
       </c>
     </row>
     <row r="48" ht="115" customHeight="true">
-      <c r="A48" s="40">
+      <c r="A48" s="32">
         <v>3</v>
       </c>
-      <c r="B48" s="41"/>
+      <c r="B48" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="24">

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -3467,7 +3467,7 @@
     </row>
     <row r="7">
       <c r="A7" s="22" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$2</f>
       </c>
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
@@ -3475,10 +3475,10 @@
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
       <c r="G7" s="22" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$4</f>
       </c>
       <c r="I7" s="22" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$5</f>
       </c>
       <c r="J7" s="22"/>
       <c r="K7" s="22"/>
@@ -3486,12 +3486,12 @@
       <c r="M7" s="22"/>
       <c r="N7" s="22"/>
       <c r="O7" s="22" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$7</f>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="22" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$3</f>
       </c>
       <c r="B8" s="22"/>
       <c r="C8" s="22"/>
@@ -3499,10 +3499,10 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="22" t="str">
-        <f>data!$B$2</f>
+        <f>data!$B$4</f>
       </c>
       <c r="I8" s="22" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$6</f>
       </c>
       <c r="J8" s="22"/>
       <c r="K8" s="22"/>
@@ -3510,7 +3510,7 @@
       <c r="M8" s="22"/>
       <c r="N8" s="22"/>
       <c r="O8" s="22" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$7</f>
       </c>
     </row>
     <row r="10">
@@ -3609,7 +3609,7 @@
     </row>
     <row r="18">
       <c r="A18" s="22" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$8</f>
       </c>
       <c r="B18" s="22"/>
       <c r="C18" s="22"/>
@@ -3617,10 +3617,10 @@
       <c r="E18" s="22"/>
       <c r="F18" s="22"/>
       <c r="G18" s="22" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$10</f>
       </c>
       <c r="I18" s="22" t="str">
-        <f>data!$B$13</f>
+        <f>data!$B$11</f>
       </c>
       <c r="J18" s="22"/>
       <c r="K18" s="22"/>
@@ -3628,12 +3628,12 @@
       <c r="M18" s="22"/>
       <c r="N18" s="22"/>
       <c r="O18" s="22" t="str">
-        <f>data!$B$12</f>
+        <f>data!$B$13</f>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$9</f>
       </c>
       <c r="B19" s="22"/>
       <c r="C19" s="22"/>
@@ -3641,10 +3641,10 @@
       <c r="E19" s="22"/>
       <c r="F19" s="22"/>
       <c r="G19" s="22" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$10</f>
       </c>
       <c r="I19" s="22" t="str">
-        <f>data!$B$13</f>
+        <f>data!$B$12</f>
       </c>
       <c r="J19" s="22"/>
       <c r="K19" s="22"/>
@@ -3652,7 +3652,7 @@
       <c r="M19" s="22"/>
       <c r="N19" s="22"/>
       <c r="O19" s="22" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$13</f>
       </c>
     </row>
     <row r="21">
@@ -3751,7 +3751,7 @@
     </row>
     <row r="29">
       <c r="A29" s="22" t="str">
-        <f>data!$B$16</f>
+        <f>data!$B$14</f>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
@@ -3759,10 +3759,10 @@
       <c r="E29" s="22"/>
       <c r="F29" s="22"/>
       <c r="G29" s="22" t="str">
-        <f>data!$B$15</f>
+        <f>data!$B$16</f>
       </c>
       <c r="I29" s="22" t="str">
-        <f>data!$B$19</f>
+        <f>data!$B$17</f>
       </c>
       <c r="J29" s="22"/>
       <c r="K29" s="22"/>
@@ -3770,12 +3770,12 @@
       <c r="M29" s="22"/>
       <c r="N29" s="22"/>
       <c r="O29" s="22" t="str">
-        <f>data!$B$18</f>
+        <f>data!$B$19</f>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="22" t="str">
-        <f>data!$B$16</f>
+        <f>data!$B$15</f>
       </c>
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
@@ -3783,10 +3783,10 @@
       <c r="E30" s="22"/>
       <c r="F30" s="22"/>
       <c r="G30" s="22" t="str">
-        <f>data!$B$14</f>
+        <f>data!$B$16</f>
       </c>
       <c r="I30" s="22" t="str">
-        <f>data!$B$19</f>
+        <f>data!$B$18</f>
       </c>
       <c r="J30" s="22"/>
       <c r="K30" s="22"/>
@@ -3794,7 +3794,7 @@
       <c r="M30" s="22"/>
       <c r="N30" s="22"/>
       <c r="O30" s="22" t="str">
-        <f>data!$B$17</f>
+        <f>data!$B$19</f>
       </c>
     </row>
     <row r="32">
@@ -3893,7 +3893,7 @@
     </row>
     <row r="40">
       <c r="A40" s="22" t="str">
-        <f>data!$B$22</f>
+        <f>data!$B$20</f>
       </c>
       <c r="B40" s="22"/>
       <c r="C40" s="22"/>
@@ -3901,10 +3901,10 @@
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
       <c r="G40" s="22" t="str">
-        <f>data!$B$21</f>
+        <f>data!$B$22</f>
       </c>
       <c r="I40" s="22" t="str">
-        <f>data!$B$25</f>
+        <f>data!$B$23</f>
       </c>
       <c r="J40" s="22"/>
       <c r="K40" s="22"/>
@@ -3912,12 +3912,12 @@
       <c r="M40" s="22"/>
       <c r="N40" s="22"/>
       <c r="O40" s="22" t="str">
-        <f>data!$B$24</f>
+        <f>data!$B$25</f>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="22" t="str">
-        <f>data!$B$22</f>
+        <f>data!$B$21</f>
       </c>
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
@@ -3925,10 +3925,10 @@
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
       <c r="G41" s="22" t="str">
-        <f>data!$B$20</f>
+        <f>data!$B$22</f>
       </c>
       <c r="I41" s="22" t="str">
-        <f>data!$B$25</f>
+        <f>data!$B$24</f>
       </c>
       <c r="J41" s="22"/>
       <c r="K41" s="22"/>
@@ -3936,7 +3936,7 @@
       <c r="M41" s="22"/>
       <c r="N41" s="22"/>
       <c r="O41" s="22" t="str">
-        <f>data!$B$23</f>
+        <f>data!$B$25</f>
       </c>
     </row>
     <row r="43">

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -21,7 +21,9 @@
     <sheet name="Tree 1" sheetId="10" r:id="rId13"/>
     <sheet name="Tags" sheetId="11" r:id="rId14"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName localSheetId="5" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$48</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -105,6 +107,27 @@
     <t>LANNISTER</t>
   </si>
   <si>
+    <t>Katniss Everdeen</t>
+  </si>
+  <si>
+    <t>Team Lambda</t>
+  </si>
+  <si>
+    <t>EVERDEEN</t>
+  </si>
+  <si>
+    <t>Ron Weasley</t>
+  </si>
+  <si>
+    <t>Team Sigma</t>
+  </si>
+  <si>
+    <t>WEASLEY</t>
+  </si>
+  <si>
+    <t>Pool B</t>
+  </si>
+  <si>
     <t>Daenerys Targaryen</t>
   </si>
   <si>
@@ -114,6 +137,21 @@
     <t>TARGARYEN</t>
   </si>
   <si>
+    <t>Team Mu</t>
+  </si>
+  <si>
+    <t>Samwise Gamgee</t>
+  </si>
+  <si>
+    <t>Team Tau</t>
+  </si>
+  <si>
+    <t>GAMGEE</t>
+  </si>
+  <si>
+    <t>Pool C</t>
+  </si>
+  <si>
     <t>Eddard Stark</t>
   </si>
   <si>
@@ -123,7 +161,19 @@
     <t>STARK</t>
   </si>
   <si>
-    <t>Pool B</t>
+    <t>Legolas Greenleaf</t>
+  </si>
+  <si>
+    <t>GREENLEAF</t>
+  </si>
+  <si>
+    <t>Tyrion Lannister</t>
+  </si>
+  <si>
+    <t>Team Upsilon</t>
+  </si>
+  <si>
+    <t>Pool D</t>
   </si>
   <si>
     <t>Frodo Baggins</t>
@@ -135,6 +185,27 @@
     <t>BAGGINS</t>
   </si>
   <si>
+    <t>Moby Dick</t>
+  </si>
+  <si>
+    <t>Team Nu</t>
+  </si>
+  <si>
+    <t>DICK</t>
+  </si>
+  <si>
+    <t>Ulysses</t>
+  </si>
+  <si>
+    <t>Team Phi</t>
+  </si>
+  <si>
+    <t>ULYSSES</t>
+  </si>
+  <si>
+    <t>Pool E</t>
+  </si>
+  <si>
     <t>Gandalf The Grey</t>
   </si>
   <si>
@@ -144,6 +215,27 @@
     <t>GANDALF</t>
   </si>
   <si>
+    <t>Neville Longbottom</t>
+  </si>
+  <si>
+    <t>Team Xi</t>
+  </si>
+  <si>
+    <t>LONGBOTTOM</t>
+  </si>
+  <si>
+    <t>Voldemort</t>
+  </si>
+  <si>
+    <t>Team Chi</t>
+  </si>
+  <si>
+    <t>VOLDEMORT</t>
+  </si>
+  <si>
+    <t>Pool F</t>
+  </si>
+  <si>
     <t>Hermione Granger</t>
   </si>
   <si>
@@ -153,7 +245,25 @@
     <t>GRANGER</t>
   </si>
   <si>
-    <t>Pool C</t>
+    <t>Othello</t>
+  </si>
+  <si>
+    <t>Team Omicron</t>
+  </si>
+  <si>
+    <t>OTHELLO</t>
+  </si>
+  <si>
+    <t>Willy Wonka</t>
+  </si>
+  <si>
+    <t>Team Psi</t>
+  </si>
+  <si>
+    <t>WONKA</t>
+  </si>
+  <si>
+    <t>Pool G</t>
   </si>
   <si>
     <t>Inigo Montoya</t>
@@ -165,6 +275,27 @@
     <t>MONTOYA</t>
   </si>
   <si>
+    <t>Petyr Baelish</t>
+  </si>
+  <si>
+    <t>Team Pi</t>
+  </si>
+  <si>
+    <t>BAELISH</t>
+  </si>
+  <si>
+    <t>Xaro Xhoan Daxos</t>
+  </si>
+  <si>
+    <t>Team Omega</t>
+  </si>
+  <si>
+    <t>DAXOS</t>
+  </si>
+  <si>
+    <t>Pool H</t>
+  </si>
+  <si>
     <t>Jon Snow</t>
   </si>
   <si>
@@ -174,69 +305,6 @@
     <t>SNOW</t>
   </si>
   <si>
-    <t>Katniss Everdeen</t>
-  </si>
-  <si>
-    <t>Team Lambda</t>
-  </si>
-  <si>
-    <t>EVERDEEN</t>
-  </si>
-  <si>
-    <t>Pool D</t>
-  </si>
-  <si>
-    <t>Team Mu</t>
-  </si>
-  <si>
-    <t>Moby Dick</t>
-  </si>
-  <si>
-    <t>Team Nu</t>
-  </si>
-  <si>
-    <t>DICK</t>
-  </si>
-  <si>
-    <t>Neville Longbottom</t>
-  </si>
-  <si>
-    <t>Team Xi</t>
-  </si>
-  <si>
-    <t>LONGBOTTOM</t>
-  </si>
-  <si>
-    <t>Pool E</t>
-  </si>
-  <si>
-    <t>Legolas Greenleaf</t>
-  </si>
-  <si>
-    <t>GREENLEAF</t>
-  </si>
-  <si>
-    <t>Othello</t>
-  </si>
-  <si>
-    <t>Team Omicron</t>
-  </si>
-  <si>
-    <t>OTHELLO</t>
-  </si>
-  <si>
-    <t>Petyr Baelish</t>
-  </si>
-  <si>
-    <t>Team Pi</t>
-  </si>
-  <si>
-    <t>BAELISH</t>
-  </si>
-  <si>
-    <t>Pool F</t>
-  </si>
-  <si>
     <t>Quirinus Quirrell</t>
   </si>
   <si>
@@ -244,72 +312,6 @@
   </si>
   <si>
     <t>QUIRRELL</t>
-  </si>
-  <si>
-    <t>Ron Weasley</t>
-  </si>
-  <si>
-    <t>Team Sigma</t>
-  </si>
-  <si>
-    <t>WEASLEY</t>
-  </si>
-  <si>
-    <t>Samwise Gamgee</t>
-  </si>
-  <si>
-    <t>Team Tau</t>
-  </si>
-  <si>
-    <t>GAMGEE</t>
-  </si>
-  <si>
-    <t>Pool G</t>
-  </si>
-  <si>
-    <t>Tyrion Lannister</t>
-  </si>
-  <si>
-    <t>Team Upsilon</t>
-  </si>
-  <si>
-    <t>Ulysses</t>
-  </si>
-  <si>
-    <t>Team Phi</t>
-  </si>
-  <si>
-    <t>ULYSSES</t>
-  </si>
-  <si>
-    <t>Voldemort</t>
-  </si>
-  <si>
-    <t>Team Chi</t>
-  </si>
-  <si>
-    <t>VOLDEMORT</t>
-  </si>
-  <si>
-    <t>Pool H</t>
-  </si>
-  <si>
-    <t>Willy Wonka</t>
-  </si>
-  <si>
-    <t>Team Psi</t>
-  </si>
-  <si>
-    <t>WONKA</t>
-  </si>
-  <si>
-    <t>Xaro Xhoan Daxos</t>
-  </si>
-  <si>
-    <t>Team Omega</t>
-  </si>
-  <si>
-    <t>DAXOS</t>
   </si>
   <si>
     <t>Ygritte</t>
@@ -567,13 +569,13 @@
     </font>
     <font>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF000000"/>
       <sz val="12"/>
     </font>
     <font>
       <family val="2"/>
-      <color rgb="FF000000"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
@@ -593,7 +595,7 @@
       <sz val="150"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -609,6 +611,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -757,7 +764,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
@@ -807,19 +814,22 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="true" applyAlignment="false">
@@ -831,13 +841,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -1149,13 +1159,13 @@
         <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
         <v>30</v>
       </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="12.75" customHeight="true">
@@ -1163,66 +1173,66 @@
         <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
         <v>33</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="12.75" customHeight="true">
       <c r="A8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="D8" t="s">
         <v>37</v>
-      </c>
-      <c r="C8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="12.75" customHeight="true">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="12.75" customHeight="true">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="12.75" customHeight="true">
       <c r="A11" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
         <v>45</v>
@@ -1230,133 +1240,133 @@
     </row>
     <row r="12" spans="1:2" ht="12.75" customHeight="true">
       <c r="A12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
         <v>48</v>
-      </c>
-      <c r="C12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="12.75" customHeight="true">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s">
         <v>51</v>
-      </c>
-      <c r="C13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="12.75" customHeight="true">
       <c r="A14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="D14" t="s">
         <v>55</v>
-      </c>
-      <c r="C14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="12.75" customHeight="true">
       <c r="A15" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
         <v>57</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>58</v>
-      </c>
-      <c r="D15" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="12.75" customHeight="true">
       <c r="A16" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" t="s">
         <v>60</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>61</v>
-      </c>
-      <c r="D16" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="12.75" customHeight="true">
       <c r="A17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" t="s">
         <v>63</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>64</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>65</v>
-      </c>
-      <c r="D17" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="12.75" customHeight="true">
       <c r="A18" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" t="s">
         <v>67</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>68</v>
-      </c>
-      <c r="D18" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="12.75" customHeight="true">
       <c r="A19" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" t="s">
         <v>70</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>71</v>
-      </c>
-      <c r="D19" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="12.75" customHeight="true">
       <c r="A20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" t="s">
         <v>74</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>75</v>
-      </c>
-      <c r="D20" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="12.75" customHeight="true">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s">
         <v>76</v>
@@ -1370,7 +1380,7 @@
     </row>
     <row r="22" spans="1:2" ht="12.75" customHeight="true">
       <c r="A22" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>79</v>
@@ -2468,520 +2478,512 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="28" t="str">
+    <row r="4">
+      <c r="A4" s="29" t="str">
         <f>data!$A$4</f>
       </c>
-      <c r="C2" s="27" t="str">
+    </row>
+    <row r="5">
+      <c r="A5" s="30" t="str">
+        <f>"1. " &amp; data!$B$2</f>
+      </c>
+      <c r="C5" s="28" t="str">
         <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G10)</f>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="29" t="str">
-        <f>"1. " &amp; data!$B$2</f>
-      </c>
-      <c r="D3" s="26"/>
-      <c r="E3" s="25">
+    <row r="6">
+      <c r="A6" s="31" t="str">
+        <f>"2. " &amp; data!$B$3</f>
+      </c>
+      <c r="D6" s="27"/>
+      <c r="E6" s="26">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="30" t="str">
-        <f>"2. " &amp; data!$B$3</f>
-      </c>
-      <c r="C4" s="27" t="str">
+    <row r="7">
+      <c r="A7" s="32" t="str">
+        <f>"3. " &amp; data!$B$4</f>
+      </c>
+      <c r="C7" s="28" t="str">
         <f>CONCATENATE("Pool B.2 ",'Pool Matches'!O11)</f>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="24"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="31" t="str">
-        <f>"3. " &amp; data!$B$4</f>
-      </c>
-      <c r="G5" s="25">
+      <c r="D7" s="22"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="25"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="27"/>
+      <c r="G8" s="26">
         <v>9</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="26"/>
-      <c r="C6" s="27" t="str">
+    <row r="9">
+      <c r="A9" s="29" t="str">
+        <f>data!$A$7</f>
+      </c>
+      <c r="C9" s="28" t="str">
         <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G21)</f>
       </c>
-      <c r="G6" s="24"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="24"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="28" t="str">
-        <f>data!$A$7</f>
-      </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="25">
+      <c r="G9" s="25"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="25"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="str">
+        <f>"1. " &amp; data!$B$5</f>
+      </c>
+      <c r="D10" s="27"/>
+      <c r="E10" s="26">
         <v>2</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="24"/>
-      <c r="I7" s="24"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="29" t="str">
-        <f>"1. " &amp; data!$B$5</f>
-      </c>
-      <c r="C8" s="27" t="str">
+      <c r="F10" s="22"/>
+      <c r="G10" s="25"/>
+      <c r="I10" s="25"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="str">
+        <f>"2. " &amp; data!$B$6</f>
+      </c>
+      <c r="C11" s="28" t="str">
         <f>CONCATENATE("Pool D.2 ",'Pool Matches'!O22)</f>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="24"/>
-      <c r="I8" s="24"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="30" t="str">
-        <f>"2. " &amp; data!$B$6</f>
-      </c>
-      <c r="I9" s="25">
+      <c r="D11" s="22"/>
+      <c r="E11" s="25"/>
+      <c r="I11" s="25"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="str">
+        <f>"3. " &amp; data!$B$7</f>
+      </c>
+      <c r="I12" s="26">
         <v>13</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="31" t="str">
-        <f>"3. " &amp; data!$B$7</f>
-      </c>
-      <c r="C10" s="27" t="str">
+    <row r="13">
+      <c r="A13" s="27"/>
+      <c r="C13" s="28" t="str">
         <f>CONCATENATE("Pool E.1 ",'Pool Matches'!G32)</f>
       </c>
-      <c r="I10" s="24"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="24"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="25">
+      <c r="I13" s="25"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="25"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="str">
+        <f>data!$A$10</f>
+      </c>
+      <c r="D14" s="27"/>
+      <c r="E14" s="26">
         <v>3</v>
       </c>
-      <c r="I11" s="24"/>
-      <c r="K11" s="24"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="28" t="str">
-        <f>data!$A$10</f>
-      </c>
-      <c r="C12" s="27" t="str">
+      <c r="I14" s="25"/>
+      <c r="K14" s="25"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="30" t="str">
+        <f>"1. " &amp; data!$B$8</f>
+      </c>
+      <c r="C15" s="28" t="str">
         <f>CONCATENATE("Pool F.2 ",'Pool Matches'!O33)</f>
       </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="K12" s="24"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="29" t="str">
-        <f>"1. " &amp; data!$B$8</f>
-      </c>
-      <c r="G13" s="25">
+      <c r="D15" s="22"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="K15" s="25"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="str">
+        <f>"2. " &amp; data!$B$9</f>
+      </c>
+      <c r="G16" s="26">
         <v>10</v>
       </c>
-      <c r="H13" s="23"/>
-      <c r="I13" s="24"/>
-      <c r="K13" s="24"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="30" t="str">
-        <f>"2. " &amp; data!$B$9</f>
-      </c>
-      <c r="C14" s="27" t="str">
+      <c r="H16" s="22"/>
+      <c r="I16" s="25"/>
+      <c r="K16" s="25"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="32" t="str">
+        <f>"3. " &amp; data!$B$10</f>
+      </c>
+      <c r="C17" s="28" t="str">
         <f>CONCATENATE("Pool G.1 ",'Pool Matches'!G43)</f>
       </c>
-      <c r="G14" s="24"/>
-      <c r="K14" s="24"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="31" t="str">
-        <f>"3. " &amp; data!$B$10</f>
-      </c>
-      <c r="D15" s="26"/>
-      <c r="E15" s="25">
+      <c r="G17" s="25"/>
+      <c r="K17" s="25"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="26">
         <v>4</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="24"/>
-      <c r="K15" s="24"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="26"/>
-      <c r="C16" s="27" t="str">
+      <c r="F18" s="22"/>
+      <c r="G18" s="25"/>
+      <c r="K18" s="25"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="str">
+        <f>data!$A$13</f>
+      </c>
+      <c r="C19" s="28" t="str">
         <f>CONCATENATE("Pool H.2 ",'Pool Matches'!O44)</f>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="24"/>
-      <c r="K16" s="24"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="28" t="str">
-        <f>data!$A$13</f>
-      </c>
-      <c r="K17" s="25">
+      <c r="D19" s="22"/>
+      <c r="E19" s="25"/>
+      <c r="K19" s="25"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="str">
+        <f>"1. " &amp; data!$B$11</f>
+      </c>
+      <c r="K20" s="26">
         <v>15</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="29" t="str">
-        <f>"1. " &amp; data!$B$11</f>
-      </c>
-      <c r="C18" s="27" t="str">
+    <row r="21">
+      <c r="A21" s="31" t="str">
+        <f>"2. " &amp; data!$B$12</f>
+      </c>
+      <c r="C21" s="28" t="str">
         <f>CONCATENATE("Pool B.1 ",'Pool Matches'!O10)</f>
       </c>
-      <c r="K18" s="24"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="30" t="str">
-        <f>"2. " &amp; data!$B$12</f>
-      </c>
-      <c r="D19" s="26"/>
-      <c r="E19" s="25">
+      <c r="K21" s="25"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="32" t="str">
+        <f>"3. " &amp; data!$B$13</f>
+      </c>
+      <c r="D22" s="27"/>
+      <c r="E22" s="26">
         <v>5</v>
       </c>
-      <c r="K19" s="24"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="31" t="str">
-        <f>"3. " &amp; data!$B$13</f>
-      </c>
-      <c r="C20" s="27" t="str">
+      <c r="K22" s="25"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="27"/>
+      <c r="C23" s="28" t="str">
         <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G11)</f>
       </c>
-      <c r="D20" s="23"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="24"/>
-      <c r="K20" s="24"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="26"/>
-      <c r="G21" s="25">
+      <c r="D23" s="22"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="25"/>
+      <c r="K23" s="25"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="str">
+        <f>data!$A$16</f>
+      </c>
+      <c r="G24" s="26">
         <v>11</v>
       </c>
-      <c r="K21" s="24"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="28" t="str">
-        <f>data!$A$16</f>
-      </c>
-      <c r="C22" s="27" t="str">
+      <c r="K24" s="25"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="str">
+        <f>"1. " &amp; data!$B$14</f>
+      </c>
+      <c r="C25" s="28" t="str">
         <f>CONCATENATE("Pool D.1 ",'Pool Matches'!O21)</f>
       </c>
-      <c r="G22" s="24"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="24"/>
-      <c r="K22" s="24"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="29" t="str">
-        <f>"1. " &amp; data!$B$14</f>
-      </c>
-      <c r="D23" s="26"/>
-      <c r="E23" s="25">
+      <c r="G25" s="25"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="25"/>
+      <c r="K25" s="25"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="str">
+        <f>"2. " &amp; data!$B$15</f>
+      </c>
+      <c r="D26" s="27"/>
+      <c r="E26" s="26">
         <v>6</v>
       </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="K23" s="24"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="30" t="str">
-        <f>"2. " &amp; data!$B$15</f>
-      </c>
-      <c r="C24" s="27" t="str">
+      <c r="F26" s="22"/>
+      <c r="G26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="K26" s="25"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="32" t="str">
+        <f>"3. " &amp; data!$B$16</f>
+      </c>
+      <c r="C27" s="28" t="str">
         <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G22)</f>
       </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="K24" s="24"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="31" t="str">
-        <f>"3. " &amp; data!$B$16</f>
-      </c>
-      <c r="I25" s="25">
+      <c r="D27" s="22"/>
+      <c r="E27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="K27" s="25"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="27"/>
+      <c r="I28" s="26">
         <v>14</v>
       </c>
-      <c r="J25" s="23"/>
-      <c r="K25" s="24"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="26"/>
-      <c r="C26" s="27" t="str">
+      <c r="J28" s="22"/>
+      <c r="K28" s="25"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="29" t="str">
+        <f>data!$A$19</f>
+      </c>
+      <c r="C29" s="28" t="str">
         <f>CONCATENATE("Pool F.1 ",'Pool Matches'!O32)</f>
       </c>
-      <c r="I26" s="24"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="28" t="str">
-        <f>data!$A$19</f>
-      </c>
-      <c r="D27" s="26"/>
-      <c r="E27" s="25">
+      <c r="I29" s="25"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="str">
+        <f>"1. " &amp; data!$B$17</f>
+      </c>
+      <c r="D30" s="27"/>
+      <c r="E30" s="26">
         <v>7</v>
       </c>
-      <c r="I27" s="24"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="29" t="str">
-        <f>"1. " &amp; data!$B$17</f>
-      </c>
-      <c r="C28" s="27" t="str">
+      <c r="I30" s="25"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="str">
+        <f>"2. " &amp; data!$B$18</f>
+      </c>
+      <c r="C31" s="28" t="str">
         <f>CONCATENATE("Pool E.2 ",'Pool Matches'!G33)</f>
       </c>
-      <c r="D28" s="23"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="24"/>
-      <c r="I28" s="24"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="30" t="str">
-        <f>"2. " &amp; data!$B$18</f>
-      </c>
-      <c r="G29" s="25">
+      <c r="D31" s="22"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="25"/>
+      <c r="I31" s="25"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="32" t="str">
+        <f>"3. " &amp; data!$B$19</f>
+      </c>
+      <c r="G32" s="26">
         <v>12</v>
       </c>
-      <c r="H29" s="23"/>
-      <c r="I29" s="24"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="31" t="str">
-        <f>"3. " &amp; data!$B$19</f>
-      </c>
-      <c r="C30" s="27" t="str">
+      <c r="H32" s="22"/>
+      <c r="I32" s="25"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="27"/>
+      <c r="C33" s="28" t="str">
         <f>CONCATENATE("Pool H.1 ",'Pool Matches'!O43)</f>
       </c>
-      <c r="G30" s="24"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="25">
+      <c r="G33" s="25"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="29" t="str">
+        <f>data!$A$22</f>
+      </c>
+      <c r="D34" s="27"/>
+      <c r="E34" s="26">
         <v>8</v>
       </c>
-      <c r="F31" s="23"/>
-      <c r="G31" s="24"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="28" t="str">
-        <f>data!$A$22</f>
-      </c>
-      <c r="C32" s="27" t="str">
+      <c r="F34" s="22"/>
+      <c r="G34" s="25"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="30" t="str">
+        <f>"1. " &amp; data!$B$20</f>
+      </c>
+      <c r="C35" s="28" t="str">
         <f>CONCATENATE("Pool G.2 ",'Pool Matches'!G44)</f>
       </c>
-      <c r="D32" s="23"/>
-      <c r="E32" s="24"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="29" t="str">
-        <f>"1. " &amp; data!$B$20</f>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="30" t="str">
+      <c r="D35" s="22"/>
+      <c r="E35" s="25"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="31" t="str">
         <f>"2. " &amp; data!$B$21</f>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="31" t="str">
+    <row r="37">
+      <c r="A37" s="32" t="str">
         <f>"3. " &amp; data!$B$22</f>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="26"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="28" t="str">
+    <row r="38">
+      <c r="A38" s="27"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="29" t="str">
         <f>data!$A$25</f>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="29" t="str">
+    <row r="40">
+      <c r="A40" s="30" t="str">
         <f>"1. " &amp; data!$B$23</f>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="30" t="str">
+    <row r="41">
+      <c r="A41" s="31" t="str">
         <f>"2. " &amp; data!$B$24</f>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="31" t="str">
+    <row r="42">
+      <c r="A42" s="32" t="str">
         <f>"3. " &amp; data!$B$25</f>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="26"/>
+    <row r="43">
+      <c r="A43" s="27"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="90"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="400" customHeight="true">
-      <c r="A1" s="34" t="s">
+    <row r="1" ht="390" customHeight="true">
+      <c r="A1" s="35" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="2" ht="400" customHeight="true">
-      <c r="A2" s="34" t="s">
+    <row r="2" ht="390" customHeight="true">
+      <c r="A2" s="35" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3" ht="400" customHeight="true">
-      <c r="A3" s="34" t="s">
+    <row r="3" ht="390" customHeight="true">
+      <c r="A3" s="35" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="4" ht="400" customHeight="true">
-      <c r="A4" s="34" t="s">
+    <row r="4" ht="390" customHeight="true">
+      <c r="A4" s="35" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="5" ht="400" customHeight="true">
-      <c r="A5" s="34" t="s">
+    <row r="5" ht="390" customHeight="true">
+      <c r="A5" s="35" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="6" ht="400" customHeight="true">
-      <c r="A6" s="34" t="s">
+    <row r="6" ht="390" customHeight="true">
+      <c r="A6" s="35" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="7" ht="400" customHeight="true">
-      <c r="A7" s="34" t="s">
+    <row r="7" ht="390" customHeight="true">
+      <c r="A7" s="35" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="8" ht="400" customHeight="true">
-      <c r="A8" s="34" t="s">
+    <row r="8" ht="390" customHeight="true">
+      <c r="A8" s="35" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="9" ht="400" customHeight="true">
-      <c r="A9" s="34" t="s">
+    <row r="9" ht="390" customHeight="true">
+      <c r="A9" s="35" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="10" ht="400" customHeight="true">
-      <c r="A10" s="34" t="s">
+    <row r="10" ht="390" customHeight="true">
+      <c r="A10" s="35" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="11" ht="400" customHeight="true">
-      <c r="A11" s="34" t="s">
+    <row r="11" ht="390" customHeight="true">
+      <c r="A11" s="35" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="12" ht="400" customHeight="true">
-      <c r="A12" s="34" t="s">
+    <row r="12" ht="390" customHeight="true">
+      <c r="A12" s="35" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="13" ht="400" customHeight="true">
-      <c r="A13" s="34" t="s">
+    <row r="13" ht="390" customHeight="true">
+      <c r="A13" s="35" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="14" ht="400" customHeight="true">
-      <c r="A14" s="34" t="s">
+    <row r="14" ht="390" customHeight="true">
+      <c r="A14" s="35" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="15" ht="400" customHeight="true">
-      <c r="A15" s="34" t="s">
+    <row r="15" ht="390" customHeight="true">
+      <c r="A15" s="35" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="16" ht="400" customHeight="true">
-      <c r="A16" s="34" t="s">
+    <row r="16" ht="390" customHeight="true">
+      <c r="A16" s="35" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="17" ht="400" customHeight="true">
-      <c r="A17" s="34" t="s">
+    <row r="17" ht="390" customHeight="true">
+      <c r="A17" s="35" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="18" ht="400" customHeight="true">
-      <c r="A18" s="34" t="s">
+    <row r="18" ht="390" customHeight="true">
+      <c r="A18" s="35" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="19" ht="400" customHeight="true">
-      <c r="A19" s="34" t="s">
+    <row r="19" ht="390" customHeight="true">
+      <c r="A19" s="35" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="20" ht="400" customHeight="true">
-      <c r="A20" s="34" t="s">
+    <row r="20" ht="390" customHeight="true">
+      <c r="A20" s="35" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="21" ht="400" customHeight="true">
-      <c r="A21" s="34" t="s">
+    <row r="21" ht="390" customHeight="true">
+      <c r="A21" s="35" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="22" ht="400" customHeight="true">
-      <c r="A22" s="34" t="s">
+    <row r="22" ht="390" customHeight="true">
+      <c r="A22" s="35" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="23" ht="400" customHeight="true">
-      <c r="A23" s="34" t="s">
+    <row r="23" ht="390" customHeight="true">
+      <c r="A23" s="35" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="24" ht="400" customHeight="true">
-      <c r="A24" s="34" t="s">
+    <row r="24" ht="390" customHeight="true">
+      <c r="A24" s="35" t="s">
         <v>121</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
-  <pageSetup paperSize="11"/>
-  <rowBreaks count="23" manualBreakCount="23">
-    <brk id="1" max="16383" man="true"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+  <rowBreaks count="12" manualBreakCount="12">
     <brk id="2" max="16383" man="true"/>
-    <brk id="3" max="16383" man="true"/>
     <brk id="4" max="16383" man="true"/>
-    <brk id="5" max="16383" man="true"/>
     <brk id="6" max="16383" man="true"/>
-    <brk id="7" max="16383" man="true"/>
     <brk id="8" max="16383" man="true"/>
-    <brk id="9" max="16383" man="true"/>
     <brk id="10" max="16383" man="true"/>
-    <brk id="11" max="16383" man="true"/>
     <brk id="12" max="16383" man="true"/>
-    <brk id="13" max="16383" man="true"/>
     <brk id="14" max="16383" man="true"/>
-    <brk id="15" max="16383" man="true"/>
     <brk id="16" max="16383" man="true"/>
-    <brk id="17" max="16383" man="true"/>
     <brk id="18" max="16383" man="true"/>
-    <brk id="19" max="16383" man="true"/>
     <brk id="20" max="16383" man="true"/>
-    <brk id="21" max="16383" man="true"/>
     <brk id="22" max="16383" man="true"/>
-    <brk id="23" max="16383" man="true"/>
+    <brk id="24" max="16383" man="true"/>
   </rowBreaks>
   <colBreaks/>
 </worksheet>
@@ -3422,94 +3424,94 @@
       <c r="O4" s="20"/>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="L5" s="22" t="s">
+      <c r="L5" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="O5" t="s">
+      <c r="O5" s="24" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="str">
+      <c r="A6" s="21" t="str">
         <f>data!$B$2</f>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22" t="str">
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21" t="str">
         <f>data!$B$3</f>
       </c>
-      <c r="I6" s="22" t="str">
+      <c r="I6" s="21" t="str">
         <f>data!$B$5</f>
       </c>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22" t="str">
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="21" t="str">
         <f>data!$B$6</f>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="str">
+      <c r="A7" s="21" t="str">
         <f>data!$B$2</f>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22" t="str">
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21" t="str">
         <f>data!$B$4</f>
       </c>
-      <c r="I7" s="22" t="str">
+      <c r="I7" s="21" t="str">
         <f>data!$B$5</f>
       </c>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22" t="str">
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21" t="str">
         <f>data!$B$7</f>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="str">
+      <c r="A8" s="21" t="str">
         <f>data!$B$3</f>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22" t="str">
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21" t="str">
         <f>data!$B$4</f>
       </c>
-      <c r="I8" s="22" t="str">
+      <c r="I8" s="21" t="str">
         <f>data!$B$6</f>
       </c>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22" t="str">
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21" t="str">
         <f>data!$B$7</f>
       </c>
     </row>
@@ -3517,31 +3519,31 @@
       <c r="F10" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="G10" s="23"/>
+      <c r="G10" s="22"/>
       <c r="N10" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="O10" s="23"/>
+      <c r="O10" s="22"/>
     </row>
     <row r="11">
       <c r="F11" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="23"/>
+      <c r="G11" s="22"/>
       <c r="N11" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="O11" s="23"/>
+      <c r="O11" s="22"/>
     </row>
     <row r="12">
       <c r="F12" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G12" s="23"/>
+      <c r="G12" s="22"/>
       <c r="N12" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="O12" s="23"/>
+      <c r="O12" s="22"/>
     </row>
     <row r="15">
       <c r="A15" s="20" t="str">
@@ -3564,94 +3566,94 @@
       <c r="O15" s="20"/>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="I16" s="21" t="s">
+      <c r="I16" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="L16" s="22" t="s">
+      <c r="L16" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="O16" t="s">
+      <c r="O16" s="24" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="str">
+      <c r="A17" s="21" t="str">
         <f>data!$B$8</f>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22" t="str">
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21" t="str">
         <f>data!$B$9</f>
       </c>
-      <c r="I17" s="22" t="str">
+      <c r="I17" s="21" t="str">
         <f>data!$B$11</f>
       </c>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22"/>
-      <c r="O17" s="22" t="str">
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="21" t="str">
         <f>data!$B$12</f>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="str">
+      <c r="A18" s="21" t="str">
         <f>data!$B$8</f>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22" t="str">
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21" t="str">
         <f>data!$B$10</f>
       </c>
-      <c r="I18" s="22" t="str">
+      <c r="I18" s="21" t="str">
         <f>data!$B$11</f>
       </c>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22" t="str">
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21" t="str">
         <f>data!$B$13</f>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="str">
+      <c r="A19" s="21" t="str">
         <f>data!$B$9</f>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22" t="str">
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21" t="str">
         <f>data!$B$10</f>
       </c>
-      <c r="I19" s="22" t="str">
+      <c r="I19" s="21" t="str">
         <f>data!$B$12</f>
       </c>
-      <c r="J19" s="22"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="22"/>
-      <c r="N19" s="22"/>
-      <c r="O19" s="22" t="str">
+      <c r="J19" s="21"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="21"/>
+      <c r="N19" s="21"/>
+      <c r="O19" s="21" t="str">
         <f>data!$B$13</f>
       </c>
     </row>
@@ -3659,31 +3661,31 @@
       <c r="F21" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="G21" s="23"/>
+      <c r="G21" s="22"/>
       <c r="N21" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="O21" s="23"/>
+      <c r="O21" s="22"/>
     </row>
     <row r="22">
       <c r="F22" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="G22" s="23"/>
+      <c r="G22" s="22"/>
       <c r="N22" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="O22" s="23"/>
+      <c r="O22" s="22"/>
     </row>
     <row r="23">
       <c r="F23" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G23" s="23"/>
+      <c r="G23" s="22"/>
       <c r="N23" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="O23" s="23"/>
+      <c r="O23" s="22"/>
     </row>
     <row r="26">
       <c r="A26" s="20" t="str">
@@ -3706,94 +3708,94 @@
       <c r="O26" s="20"/>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="D27" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="I27" s="21" t="s">
+      <c r="I27" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="L27" s="22" t="s">
+      <c r="L27" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="O27" t="s">
+      <c r="O27" s="24" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="str">
+      <c r="A28" s="21" t="str">
         <f>data!$B$14</f>
       </c>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22" t="str">
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21" t="str">
         <f>data!$B$15</f>
       </c>
-      <c r="I28" s="22" t="str">
+      <c r="I28" s="21" t="str">
         <f>data!$B$17</f>
       </c>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="22"/>
-      <c r="O28" s="22" t="str">
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="21"/>
+      <c r="O28" s="21" t="str">
         <f>data!$B$18</f>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="str">
+      <c r="A29" s="21" t="str">
         <f>data!$B$14</f>
       </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22" t="str">
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21" t="str">
         <f>data!$B$16</f>
       </c>
-      <c r="I29" s="22" t="str">
+      <c r="I29" s="21" t="str">
         <f>data!$B$17</f>
       </c>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="22"/>
-      <c r="M29" s="22"/>
-      <c r="N29" s="22"/>
-      <c r="O29" s="22" t="str">
+      <c r="J29" s="21"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="21"/>
+      <c r="M29" s="21"/>
+      <c r="N29" s="21"/>
+      <c r="O29" s="21" t="str">
         <f>data!$B$19</f>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="str">
+      <c r="A30" s="21" t="str">
         <f>data!$B$15</f>
       </c>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22" t="str">
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21" t="str">
         <f>data!$B$16</f>
       </c>
-      <c r="I30" s="22" t="str">
+      <c r="I30" s="21" t="str">
         <f>data!$B$18</f>
       </c>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="22"/>
-      <c r="N30" s="22"/>
-      <c r="O30" s="22" t="str">
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="21"/>
+      <c r="O30" s="21" t="str">
         <f>data!$B$19</f>
       </c>
     </row>
@@ -3801,31 +3803,31 @@
       <c r="F32" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="G32" s="23"/>
+      <c r="G32" s="22"/>
       <c r="N32" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="O32" s="23"/>
+      <c r="O32" s="22"/>
     </row>
     <row r="33">
       <c r="F33" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="G33" s="23"/>
+      <c r="G33" s="22"/>
       <c r="N33" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="O33" s="23"/>
+      <c r="O33" s="22"/>
     </row>
     <row r="34">
       <c r="F34" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G34" s="23"/>
+      <c r="G34" s="22"/>
       <c r="N34" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="O34" s="23"/>
+      <c r="O34" s="22"/>
     </row>
     <row r="37">
       <c r="A37" s="20" t="str">
@@ -3848,94 +3850,94 @@
       <c r="O37" s="20"/>
     </row>
     <row r="38">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D38" s="22" t="s">
+      <c r="D38" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G38" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="I38" s="21" t="s">
+      <c r="I38" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="L38" s="22" t="s">
+      <c r="L38" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="O38" t="s">
+      <c r="O38" s="24" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="str">
+      <c r="A39" s="21" t="str">
         <f>data!$B$20</f>
       </c>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="22" t="str">
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21" t="str">
         <f>data!$B$21</f>
       </c>
-      <c r="I39" s="22" t="str">
+      <c r="I39" s="21" t="str">
         <f>data!$B$23</f>
       </c>
-      <c r="J39" s="22"/>
-      <c r="K39" s="22"/>
-      <c r="L39" s="22"/>
-      <c r="M39" s="22"/>
-      <c r="N39" s="22"/>
-      <c r="O39" s="22" t="str">
+      <c r="J39" s="21"/>
+      <c r="K39" s="21"/>
+      <c r="L39" s="21"/>
+      <c r="M39" s="21"/>
+      <c r="N39" s="21"/>
+      <c r="O39" s="21" t="str">
         <f>data!$B$24</f>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="str">
+      <c r="A40" s="21" t="str">
         <f>data!$B$20</f>
       </c>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22" t="str">
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21" t="str">
         <f>data!$B$22</f>
       </c>
-      <c r="I40" s="22" t="str">
+      <c r="I40" s="21" t="str">
         <f>data!$B$23</f>
       </c>
-      <c r="J40" s="22"/>
-      <c r="K40" s="22"/>
-      <c r="L40" s="22"/>
-      <c r="M40" s="22"/>
-      <c r="N40" s="22"/>
-      <c r="O40" s="22" t="str">
+      <c r="J40" s="21"/>
+      <c r="K40" s="21"/>
+      <c r="L40" s="21"/>
+      <c r="M40" s="21"/>
+      <c r="N40" s="21"/>
+      <c r="O40" s="21" t="str">
         <f>data!$B$25</f>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="22" t="str">
+      <c r="A41" s="21" t="str">
         <f>data!$B$21</f>
       </c>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22" t="str">
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21" t="str">
         <f>data!$B$22</f>
       </c>
-      <c r="I41" s="22" t="str">
+      <c r="I41" s="21" t="str">
         <f>data!$B$24</f>
       </c>
-      <c r="J41" s="22"/>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="22"/>
-      <c r="N41" s="22"/>
-      <c r="O41" s="22" t="str">
+      <c r="J41" s="21"/>
+      <c r="K41" s="21"/>
+      <c r="L41" s="21"/>
+      <c r="M41" s="21"/>
+      <c r="N41" s="21"/>
+      <c r="O41" s="21" t="str">
         <f>data!$B$25</f>
       </c>
     </row>
@@ -3943,31 +3945,31 @@
       <c r="F43" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="G43" s="23"/>
+      <c r="G43" s="22"/>
       <c r="N43" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="O43" s="23"/>
+      <c r="O43" s="22"/>
     </row>
     <row r="44">
       <c r="F44" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="G44" s="23"/>
+      <c r="G44" s="22"/>
       <c r="N44" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="O44" s="23"/>
+      <c r="O44" s="22"/>
     </row>
     <row r="45">
       <c r="F45" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G45" s="23"/>
+      <c r="G45" s="22"/>
       <c r="N45" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="O45" s="23"/>
+      <c r="O45" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4043,46 +4045,46 @@
       <c r="O3" s="20"/>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="L4" s="22" t="s">
+      <c r="L4" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="24" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="str">
+      <c r="A5" s="21" t="str">
         <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G10)</f>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22" t="str">
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21" t="str">
         <f>CONCATENATE("Pool B.2 ",'Pool Matches'!O11)</f>
       </c>
-      <c r="I5" s="22" t="str">
+      <c r="I5" s="21" t="str">
         <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G21)</f>
       </c>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22" t="str">
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="21"/>
+      <c r="N5" s="21"/>
+      <c r="O5" s="21" t="str">
         <f>CONCATENATE("Pool D.2 ",'Pool Matches'!O22)</f>
       </c>
     </row>
@@ -4090,21 +4092,21 @@
       <c r="F7" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="G7" s="23"/>
+      <c r="G7" s="22"/>
       <c r="N7" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="O7" s="23"/>
+      <c r="O7" s="22"/>
     </row>
     <row r="8">
       <c r="F8" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G8" s="23"/>
+      <c r="G8" s="22"/>
       <c r="N8" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="O8" s="23"/>
+      <c r="O8" s="22"/>
     </row>
     <row r="11">
       <c r="A11" s="20" t="s">
@@ -4127,46 +4129,46 @@
       <c r="O11" s="20"/>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="I12" s="21" t="s">
+      <c r="I12" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="L12" s="22" t="s">
+      <c r="L12" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="O12" t="s">
+      <c r="O12" s="24" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="str">
+      <c r="A13" s="21" t="str">
         <f>CONCATENATE("Pool E.1 ",'Pool Matches'!G32)</f>
       </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22" t="str">
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21" t="str">
         <f>CONCATENATE("Pool F.2 ",'Pool Matches'!O33)</f>
       </c>
-      <c r="I13" s="22" t="str">
+      <c r="I13" s="21" t="str">
         <f>CONCATENATE("Pool G.1 ",'Pool Matches'!G43)</f>
       </c>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22" t="str">
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21" t="str">
         <f>CONCATENATE("Pool H.2 ",'Pool Matches'!O44)</f>
       </c>
     </row>
@@ -4174,21 +4176,21 @@
       <c r="F15" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="G15" s="23"/>
+      <c r="G15" s="22"/>
       <c r="N15" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="O15" s="23"/>
+      <c r="O15" s="22"/>
     </row>
     <row r="16">
       <c r="F16" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G16" s="23"/>
+      <c r="G16" s="22"/>
       <c r="N16" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="O16" s="23"/>
+      <c r="O16" s="22"/>
     </row>
     <row r="19">
       <c r="A19" s="20" t="s">
@@ -4211,46 +4213,46 @@
       <c r="O19" s="20"/>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="I20" s="21" t="s">
+      <c r="I20" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="L20" s="22" t="s">
+      <c r="L20" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="O20" t="s">
+      <c r="O20" s="24" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="str">
+      <c r="A21" s="21" t="str">
         <f>CONCATENATE("Pool B.1 ",'Pool Matches'!O10)</f>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22" t="str">
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21" t="str">
         <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G11)</f>
       </c>
-      <c r="I21" s="22" t="str">
+      <c r="I21" s="21" t="str">
         <f>CONCATENATE("Pool D.1 ",'Pool Matches'!O21)</f>
       </c>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="22"/>
-      <c r="N21" s="22"/>
-      <c r="O21" s="22" t="str">
+      <c r="J21" s="21"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="21"/>
+      <c r="M21" s="21"/>
+      <c r="N21" s="21"/>
+      <c r="O21" s="21" t="str">
         <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G22)</f>
       </c>
     </row>
@@ -4258,21 +4260,21 @@
       <c r="F23" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="G23" s="23"/>
+      <c r="G23" s="22"/>
       <c r="N23" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="O23" s="23"/>
+      <c r="O23" s="22"/>
     </row>
     <row r="24">
       <c r="F24" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G24" s="23"/>
+      <c r="G24" s="22"/>
       <c r="N24" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="O24" s="23"/>
+      <c r="O24" s="22"/>
     </row>
     <row r="27">
       <c r="A27" s="20" t="s">
@@ -4295,46 +4297,46 @@
       <c r="O27" s="20"/>
     </row>
     <row r="28">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="D28" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G28" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="I28" s="21" t="s">
+      <c r="I28" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="L28" s="22" t="s">
+      <c r="L28" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="O28" t="s">
+      <c r="O28" s="24" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="str">
+      <c r="A29" s="21" t="str">
         <f>CONCATENATE("Pool F.1 ",'Pool Matches'!O32)</f>
       </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22" t="str">
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21" t="str">
         <f>CONCATENATE("Pool E.2 ",'Pool Matches'!G33)</f>
       </c>
-      <c r="I29" s="22" t="str">
+      <c r="I29" s="21" t="str">
         <f>CONCATENATE("Pool H.1 ",'Pool Matches'!O43)</f>
       </c>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="22"/>
-      <c r="M29" s="22"/>
-      <c r="N29" s="22"/>
-      <c r="O29" s="22" t="str">
+      <c r="J29" s="21"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="21"/>
+      <c r="M29" s="21"/>
+      <c r="N29" s="21"/>
+      <c r="O29" s="21" t="str">
         <f>CONCATENATE("Pool G.2 ",'Pool Matches'!G44)</f>
       </c>
     </row>
@@ -4342,21 +4344,21 @@
       <c r="F31" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="G31" s="23"/>
+      <c r="G31" s="22"/>
       <c r="N31" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="O31" s="23"/>
+      <c r="O31" s="22"/>
     </row>
     <row r="32">
       <c r="F32" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G32" s="23"/>
+      <c r="G32" s="22"/>
       <c r="N32" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="O32" s="23"/>
+      <c r="O32" s="22"/>
     </row>
     <row r="40">
       <c r="A40" s="20" t="s">
@@ -4398,46 +4400,46 @@
       <c r="O42" s="20"/>
     </row>
     <row r="43">
-      <c r="A43" s="21" t="s">
+      <c r="A43" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D43" s="22" t="s">
+      <c r="D43" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="G43" t="s">
+      <c r="G43" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="I43" s="21" t="s">
+      <c r="I43" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="L43" s="22" t="s">
+      <c r="L43" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="O43" t="s">
+      <c r="O43" s="24" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="22" t="str">
+      <c r="A44" s="21" t="str">
         <f>CONCATENATE("M 1 ",'Elimination Matches'!G7)</f>
       </c>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="22" t="str">
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21" t="str">
         <f>CONCATENATE("M 2 ",'Elimination Matches'!O7)</f>
       </c>
-      <c r="I44" s="22" t="str">
+      <c r="I44" s="21" t="str">
         <f>CONCATENATE("M 3 ",'Elimination Matches'!G15)</f>
       </c>
-      <c r="J44" s="22"/>
-      <c r="K44" s="22"/>
-      <c r="L44" s="22"/>
-      <c r="M44" s="22"/>
-      <c r="N44" s="22"/>
-      <c r="O44" s="22" t="str">
+      <c r="J44" s="21"/>
+      <c r="K44" s="21"/>
+      <c r="L44" s="21"/>
+      <c r="M44" s="21"/>
+      <c r="N44" s="21"/>
+      <c r="O44" s="21" t="str">
         <f>CONCATENATE("M 4 ",'Elimination Matches'!O15)</f>
       </c>
     </row>
@@ -4445,21 +4447,21 @@
       <c r="F46" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="G46" s="23"/>
+      <c r="G46" s="22"/>
       <c r="N46" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="O46" s="23"/>
+      <c r="O46" s="22"/>
     </row>
     <row r="47">
       <c r="F47" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G47" s="23"/>
+      <c r="G47" s="22"/>
       <c r="N47" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="O47" s="23"/>
+      <c r="O47" s="22"/>
     </row>
     <row r="50">
       <c r="A50" s="20" t="s">
@@ -4482,46 +4484,46 @@
       <c r="O50" s="20"/>
     </row>
     <row r="51">
-      <c r="A51" s="21" t="s">
+      <c r="A51" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D51" s="22" t="s">
+      <c r="D51" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="G51" t="s">
+      <c r="G51" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="I51" s="21" t="s">
+      <c r="I51" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="L51" s="22" t="s">
+      <c r="L51" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="O51" t="s">
+      <c r="O51" s="24" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="22" t="str">
+      <c r="A52" s="21" t="str">
         <f>CONCATENATE("M 5 ",'Elimination Matches'!G23)</f>
       </c>
-      <c r="B52" s="22"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="22" t="str">
+      <c r="B52" s="21"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="21"/>
+      <c r="G52" s="21" t="str">
         <f>CONCATENATE("M 6 ",'Elimination Matches'!O23)</f>
       </c>
-      <c r="I52" s="22" t="str">
+      <c r="I52" s="21" t="str">
         <f>CONCATENATE("M 7 ",'Elimination Matches'!G31)</f>
       </c>
-      <c r="J52" s="22"/>
-      <c r="K52" s="22"/>
-      <c r="L52" s="22"/>
-      <c r="M52" s="22"/>
-      <c r="N52" s="22"/>
-      <c r="O52" s="22" t="str">
+      <c r="J52" s="21"/>
+      <c r="K52" s="21"/>
+      <c r="L52" s="21"/>
+      <c r="M52" s="21"/>
+      <c r="N52" s="21"/>
+      <c r="O52" s="21" t="str">
         <f>CONCATENATE("M 8 ",'Elimination Matches'!O31)</f>
       </c>
     </row>
@@ -4529,21 +4531,21 @@
       <c r="F54" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="G54" s="23"/>
+      <c r="G54" s="22"/>
       <c r="N54" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="O54" s="23"/>
+      <c r="O54" s="22"/>
     </row>
     <row r="55">
       <c r="F55" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G55" s="23"/>
+      <c r="G55" s="22"/>
       <c r="N55" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="O55" s="23"/>
+      <c r="O55" s="22"/>
     </row>
     <row r="63">
       <c r="A63" s="20" t="s">
@@ -4585,46 +4587,46 @@
       <c r="O65" s="20"/>
     </row>
     <row r="66">
-      <c r="A66" s="21" t="s">
+      <c r="A66" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D66" s="22" t="s">
+      <c r="D66" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="G66" t="s">
+      <c r="G66" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="I66" s="21" t="s">
+      <c r="I66" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="L66" s="22" t="s">
+      <c r="L66" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="O66" t="s">
+      <c r="O66" s="24" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="22" t="str">
+      <c r="A67" s="21" t="str">
         <f>CONCATENATE("M 9 ",'Elimination Matches'!G46)</f>
       </c>
-      <c r="B67" s="22"/>
-      <c r="C67" s="22"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22" t="str">
+      <c r="B67" s="21"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="21"/>
+      <c r="G67" s="21" t="str">
         <f>CONCATENATE("M 10 ",'Elimination Matches'!O46)</f>
       </c>
-      <c r="I67" s="22" t="str">
+      <c r="I67" s="21" t="str">
         <f>CONCATENATE("M 11 ",'Elimination Matches'!G54)</f>
       </c>
-      <c r="J67" s="22"/>
-      <c r="K67" s="22"/>
-      <c r="L67" s="22"/>
-      <c r="M67" s="22"/>
-      <c r="N67" s="22"/>
-      <c r="O67" s="22" t="str">
+      <c r="J67" s="21"/>
+      <c r="K67" s="21"/>
+      <c r="L67" s="21"/>
+      <c r="M67" s="21"/>
+      <c r="N67" s="21"/>
+      <c r="O67" s="21" t="str">
         <f>CONCATENATE("M 12 ",'Elimination Matches'!O54)</f>
       </c>
     </row>
@@ -4632,21 +4634,21 @@
       <c r="F69" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="G69" s="23"/>
+      <c r="G69" s="22"/>
       <c r="N69" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="O69" s="23"/>
+      <c r="O69" s="22"/>
     </row>
     <row r="70">
       <c r="F70" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G70" s="23"/>
+      <c r="G70" s="22"/>
       <c r="N70" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="O70" s="23"/>
+      <c r="O70" s="22"/>
     </row>
     <row r="78">
       <c r="A78" s="20" t="s">
@@ -4679,26 +4681,26 @@
       <c r="G80" s="20"/>
     </row>
     <row r="81">
-      <c r="A81" s="21" t="s">
+      <c r="A81" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D81" s="22" t="s">
+      <c r="D81" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="G81" t="s">
+      <c r="G81" s="24" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="22" t="str">
+      <c r="A82" s="21" t="str">
         <f>CONCATENATE("M 13 ",'Elimination Matches'!G69)</f>
       </c>
-      <c r="B82" s="22"/>
-      <c r="C82" s="22"/>
-      <c r="D82" s="22"/>
-      <c r="E82" s="22"/>
-      <c r="F82" s="22"/>
-      <c r="G82" s="22" t="str">
+      <c r="B82" s="21"/>
+      <c r="C82" s="21"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="21"/>
+      <c r="F82" s="21"/>
+      <c r="G82" s="21" t="str">
         <f>CONCATENATE("M 14 ",'Elimination Matches'!O69)</f>
       </c>
     </row>
@@ -4706,13 +4708,13 @@
       <c r="F84" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="G84" s="23"/>
+      <c r="G84" s="22"/>
     </row>
     <row r="85">
       <c r="F85" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G85" s="23"/>
+      <c r="G85" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -4748,346 +4750,346 @@
   <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="115" customHeight="true"/>
   <cols>
-    <col customWidth="true" max="1" min="1" style="10" width="21.6640625"/>
-    <col customWidth="true" max="2" min="2" style="9" width="170.6640625"/>
+    <col customWidth="true" max="1" min="1" style="10" width="20"/>
+    <col customWidth="true" max="2" min="2" style="9" width="170"/>
     <col max="16384" min="3" style="8" width="10.83203125"/>
   </cols>
   <sheetData>
     <row r="1" ht="110" customHeight="true">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="33" t="str">
+      <c r="B1" s="34" t="str">
         <f>data!D2</f>
       </c>
     </row>
     <row r="2" ht="115" customHeight="true">
-      <c r="A2" s="32">
+      <c r="A2" s="33">
         <v>1</v>
       </c>
-      <c r="B2" s="33"/>
+      <c r="B2" s="34"/>
     </row>
     <row r="3" ht="110" customHeight="true">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="33" t="str">
+      <c r="B3" s="34" t="str">
         <f>data!D3</f>
       </c>
     </row>
     <row r="4" ht="115" customHeight="true">
-      <c r="A4" s="32">
+      <c r="A4" s="33">
         <v>2</v>
       </c>
-      <c r="B4" s="33"/>
+      <c r="B4" s="34"/>
     </row>
     <row r="5" ht="110" customHeight="true">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="33" t="str">
+      <c r="B5" s="34" t="str">
         <f>data!D4</f>
       </c>
     </row>
     <row r="6" ht="115" customHeight="true">
-      <c r="A6" s="32">
+      <c r="A6" s="33">
         <v>3</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="34"/>
     </row>
     <row r="7" ht="110" customHeight="true">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="33" t="str">
+      <c r="B7" s="34" t="str">
         <f>data!D5</f>
       </c>
     </row>
     <row r="8" ht="115" customHeight="true">
-      <c r="A8" s="32">
+      <c r="A8" s="33">
         <v>1</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="34"/>
     </row>
     <row r="9" ht="110" customHeight="true">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="33" t="str">
+      <c r="B9" s="34" t="str">
         <f>data!D6</f>
       </c>
     </row>
     <row r="10" ht="115" customHeight="true">
-      <c r="A10" s="32">
+      <c r="A10" s="33">
         <v>2</v>
       </c>
-      <c r="B10" s="33"/>
+      <c r="B10" s="34"/>
     </row>
     <row r="11" ht="110" customHeight="true">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="33" t="str">
+      <c r="B11" s="34" t="str">
         <f>data!D7</f>
       </c>
     </row>
     <row r="12" ht="115" customHeight="true">
-      <c r="A12" s="32">
+      <c r="A12" s="33">
         <v>3</v>
       </c>
-      <c r="B12" s="33"/>
+      <c r="B12" s="34"/>
     </row>
     <row r="13" ht="110" customHeight="true">
-      <c r="A13" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="33" t="str">
+      <c r="A13" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="34" t="str">
         <f>data!D8</f>
       </c>
     </row>
     <row r="14" ht="115" customHeight="true">
-      <c r="A14" s="32">
+      <c r="A14" s="33">
         <v>1</v>
       </c>
-      <c r="B14" s="33"/>
+      <c r="B14" s="34"/>
     </row>
     <row r="15" ht="110" customHeight="true">
-      <c r="A15" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="33" t="str">
+      <c r="A15" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="34" t="str">
         <f>data!D9</f>
       </c>
     </row>
     <row r="16" ht="115" customHeight="true">
-      <c r="A16" s="32">
+      <c r="A16" s="33">
         <v>2</v>
       </c>
-      <c r="B16" s="33"/>
+      <c r="B16" s="34"/>
     </row>
     <row r="17" ht="110" customHeight="true">
-      <c r="A17" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="33" t="str">
+      <c r="A17" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="34" t="str">
         <f>data!D10</f>
       </c>
     </row>
     <row r="18" ht="115" customHeight="true">
-      <c r="A18" s="32">
+      <c r="A18" s="33">
         <v>3</v>
       </c>
-      <c r="B18" s="33"/>
+      <c r="B18" s="34"/>
     </row>
     <row r="19" ht="110" customHeight="true">
-      <c r="A19" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="33" t="str">
+      <c r="A19" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="34" t="str">
         <f>data!D11</f>
       </c>
     </row>
     <row r="20" ht="115" customHeight="true">
-      <c r="A20" s="32">
+      <c r="A20" s="33">
         <v>1</v>
       </c>
-      <c r="B20" s="33"/>
+      <c r="B20" s="34"/>
     </row>
     <row r="21" ht="110" customHeight="true">
-      <c r="A21" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="33" t="str">
+      <c r="A21" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="34" t="str">
         <f>data!D12</f>
       </c>
     </row>
     <row r="22" ht="115" customHeight="true">
-      <c r="A22" s="32">
+      <c r="A22" s="33">
         <v>2</v>
       </c>
-      <c r="B22" s="33"/>
+      <c r="B22" s="34"/>
     </row>
     <row r="23" ht="110" customHeight="true">
-      <c r="A23" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="33" t="str">
+      <c r="A23" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="34" t="str">
         <f>data!D13</f>
       </c>
     </row>
     <row r="24" ht="115" customHeight="true">
-      <c r="A24" s="32">
+      <c r="A24" s="33">
         <v>3</v>
       </c>
-      <c r="B24" s="33"/>
+      <c r="B24" s="34"/>
     </row>
     <row r="25" ht="110" customHeight="true">
-      <c r="A25" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" s="33" t="str">
+      <c r="A25" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="34" t="str">
         <f>data!D14</f>
       </c>
     </row>
     <row r="26" ht="115" customHeight="true">
-      <c r="A26" s="32">
+      <c r="A26" s="33">
         <v>1</v>
       </c>
-      <c r="B26" s="33"/>
+      <c r="B26" s="34"/>
     </row>
     <row r="27" ht="110" customHeight="true">
-      <c r="A27" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27" s="33" t="str">
+      <c r="A27" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="34" t="str">
         <f>data!D15</f>
       </c>
     </row>
     <row r="28" ht="115" customHeight="true">
-      <c r="A28" s="32">
+      <c r="A28" s="33">
         <v>2</v>
       </c>
-      <c r="B28" s="33"/>
+      <c r="B28" s="34"/>
     </row>
     <row r="29" ht="110" customHeight="true">
-      <c r="A29" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="B29" s="33" t="str">
+      <c r="A29" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="34" t="str">
         <f>data!D16</f>
       </c>
     </row>
     <row r="30" ht="115" customHeight="true">
-      <c r="A30" s="32">
+      <c r="A30" s="33">
         <v>3</v>
       </c>
-      <c r="B30" s="33"/>
+      <c r="B30" s="34"/>
     </row>
     <row r="31" ht="110" customHeight="true">
-      <c r="A31" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="33" t="str">
+      <c r="A31" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="34" t="str">
         <f>data!D17</f>
       </c>
     </row>
     <row r="32" ht="115" customHeight="true">
-      <c r="A32" s="32">
+      <c r="A32" s="33">
         <v>1</v>
       </c>
-      <c r="B32" s="33"/>
+      <c r="B32" s="34"/>
     </row>
     <row r="33" ht="110" customHeight="true">
-      <c r="A33" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="B33" s="33" t="str">
+      <c r="A33" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="34" t="str">
         <f>data!D18</f>
       </c>
     </row>
     <row r="34" ht="115" customHeight="true">
-      <c r="A34" s="32">
+      <c r="A34" s="33">
         <v>2</v>
       </c>
-      <c r="B34" s="33"/>
+      <c r="B34" s="34"/>
     </row>
     <row r="35" ht="110" customHeight="true">
-      <c r="A35" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="B35" s="33" t="str">
+      <c r="A35" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" s="34" t="str">
         <f>data!D19</f>
       </c>
     </row>
     <row r="36" ht="115" customHeight="true">
-      <c r="A36" s="32">
+      <c r="A36" s="33">
         <v>3</v>
       </c>
-      <c r="B36" s="33"/>
+      <c r="B36" s="34"/>
     </row>
     <row r="37" ht="110" customHeight="true">
-      <c r="A37" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" s="33" t="str">
+      <c r="A37" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" s="34" t="str">
         <f>data!D20</f>
       </c>
     </row>
     <row r="38" ht="115" customHeight="true">
-      <c r="A38" s="32">
+      <c r="A38" s="33">
         <v>1</v>
       </c>
-      <c r="B38" s="33"/>
+      <c r="B38" s="34"/>
     </row>
     <row r="39" ht="110" customHeight="true">
-      <c r="A39" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="B39" s="33" t="str">
+      <c r="A39" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" s="34" t="str">
         <f>data!D21</f>
       </c>
     </row>
     <row r="40" ht="115" customHeight="true">
-      <c r="A40" s="32">
+      <c r="A40" s="33">
         <v>2</v>
       </c>
-      <c r="B40" s="33"/>
+      <c r="B40" s="34"/>
     </row>
     <row r="41" ht="110" customHeight="true">
-      <c r="A41" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="B41" s="33" t="str">
+      <c r="A41" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" s="34" t="str">
         <f>data!D22</f>
       </c>
     </row>
     <row r="42" ht="115" customHeight="true">
-      <c r="A42" s="32">
+      <c r="A42" s="33">
         <v>3</v>
       </c>
-      <c r="B42" s="33"/>
+      <c r="B42" s="34"/>
     </row>
     <row r="43" ht="110" customHeight="true">
-      <c r="A43" s="32" t="s">
+      <c r="A43" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="B43" s="33" t="str">
+      <c r="B43" s="34" t="str">
         <f>data!D23</f>
       </c>
     </row>
     <row r="44" ht="115" customHeight="true">
-      <c r="A44" s="32">
+      <c r="A44" s="33">
         <v>1</v>
       </c>
-      <c r="B44" s="33"/>
+      <c r="B44" s="34"/>
     </row>
     <row r="45" ht="110" customHeight="true">
-      <c r="A45" s="32" t="s">
+      <c r="A45" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="B45" s="33" t="str">
+      <c r="B45" s="34" t="str">
         <f>data!D24</f>
       </c>
     </row>
     <row r="46" ht="115" customHeight="true">
-      <c r="A46" s="32">
+      <c r="A46" s="33">
         <v>2</v>
       </c>
-      <c r="B46" s="33"/>
+      <c r="B46" s="34"/>
     </row>
     <row r="47" ht="110" customHeight="true">
-      <c r="A47" s="32" t="s">
+      <c r="A47" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="B47" s="33" t="str">
+      <c r="B47" s="34" t="str">
         <f>data!D25</f>
       </c>
     </row>
     <row r="48" ht="115" customHeight="true">
-      <c r="A48" s="32">
+      <c r="A48" s="33">
         <v>3</v>
       </c>
-      <c r="B48" s="33"/>
+      <c r="B48" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -5118,7 +5120,7 @@
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" horizontalDpi="0" orientation="landscape" paperSize="8" verticalDpi="0"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" horizontalDpi="0" orientation="landscape" paperSize="8" verticalDpi="0"/>
   <rowBreaks count="8" manualBreakCount="8">
     <brk id="6" max="16383" man="true"/>
     <brk id="12" max="16383" man="true"/>

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="26060" windowHeight="21580" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="26060" windowHeight="21580" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="Elimination Matches" sheetId="7" r:id="rId5"/>
     <sheet name="Names to Print" sheetId="8" r:id="rId6"/>
     <sheet name="Tree 1" sheetId="10" r:id="rId13"/>
-    <sheet name="Tags" sheetId="11" r:id="rId14"/>
+    <sheet name="Tree 2" sheetId="11" r:id="rId14"/>
+    <sheet name="Tags" sheetId="12" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName localSheetId="5" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$48</definedName>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
   <si>
     <t>Elimination Round 1</t>
   </si>
@@ -80,6 +81,9 @@
     <t>Number of Elimination Matches</t>
   </si>
   <si>
+    <t>Title prefix:</t>
+  </si>
+  <si>
     <t>Pool</t>
   </si>
   <si>
@@ -128,6 +132,93 @@
     <t>Pool B</t>
   </si>
   <si>
+    <t>Eddard Stark</t>
+  </si>
+  <si>
+    <t>Team Epsilon</t>
+  </si>
+  <si>
+    <t>STARK</t>
+  </si>
+  <si>
+    <t>Legolas Greenleaf</t>
+  </si>
+  <si>
+    <t>Team Mu</t>
+  </si>
+  <si>
+    <t>GREENLEAF</t>
+  </si>
+  <si>
+    <t>Tyrion Lannister</t>
+  </si>
+  <si>
+    <t>Team Upsilon</t>
+  </si>
+  <si>
+    <t>Pool C</t>
+  </si>
+  <si>
+    <t>Gandalf The Grey</t>
+  </si>
+  <si>
+    <t>Team Eta</t>
+  </si>
+  <si>
+    <t>GANDALF</t>
+  </si>
+  <si>
+    <t>Neville Longbottom</t>
+  </si>
+  <si>
+    <t>Team Xi</t>
+  </si>
+  <si>
+    <t>LONGBOTTOM</t>
+  </si>
+  <si>
+    <t>Voldemort</t>
+  </si>
+  <si>
+    <t>Team Chi</t>
+  </si>
+  <si>
+    <t>VOLDEMORT</t>
+  </si>
+  <si>
+    <t>Pool D</t>
+  </si>
+  <si>
+    <t>Inigo Montoya</t>
+  </si>
+  <si>
+    <t>Team Iota</t>
+  </si>
+  <si>
+    <t>MONTOYA</t>
+  </si>
+  <si>
+    <t>Petyr Baelish</t>
+  </si>
+  <si>
+    <t>Team Pi</t>
+  </si>
+  <si>
+    <t>BAELISH</t>
+  </si>
+  <si>
+    <t>Xaro Xhoan Daxos</t>
+  </si>
+  <si>
+    <t>Team Omega</t>
+  </si>
+  <si>
+    <t>DAXOS</t>
+  </si>
+  <si>
+    <t>Pool E</t>
+  </si>
+  <si>
     <t>Daenerys Targaryen</t>
   </si>
   <si>
@@ -137,9 +228,6 @@
     <t>TARGARYEN</t>
   </si>
   <si>
-    <t>Team Mu</t>
-  </si>
-  <si>
     <t>Samwise Gamgee</t>
   </si>
   <si>
@@ -149,31 +237,7 @@
     <t>GAMGEE</t>
   </si>
   <si>
-    <t>Pool C</t>
-  </si>
-  <si>
-    <t>Eddard Stark</t>
-  </si>
-  <si>
-    <t>Team Epsilon</t>
-  </si>
-  <si>
-    <t>STARK</t>
-  </si>
-  <si>
-    <t>Legolas Greenleaf</t>
-  </si>
-  <si>
-    <t>GREENLEAF</t>
-  </si>
-  <si>
-    <t>Tyrion Lannister</t>
-  </si>
-  <si>
-    <t>Team Upsilon</t>
-  </si>
-  <si>
-    <t>Pool D</t>
+    <t>Pool F</t>
   </si>
   <si>
     <t>Frodo Baggins</t>
@@ -203,37 +267,7 @@
     <t>ULYSSES</t>
   </si>
   <si>
-    <t>Pool E</t>
-  </si>
-  <si>
-    <t>Gandalf The Grey</t>
-  </si>
-  <si>
-    <t>Team Eta</t>
-  </si>
-  <si>
-    <t>GANDALF</t>
-  </si>
-  <si>
-    <t>Neville Longbottom</t>
-  </si>
-  <si>
-    <t>Team Xi</t>
-  </si>
-  <si>
-    <t>LONGBOTTOM</t>
-  </si>
-  <si>
-    <t>Voldemort</t>
-  </si>
-  <si>
-    <t>Team Chi</t>
-  </si>
-  <si>
-    <t>VOLDEMORT</t>
-  </si>
-  <si>
-    <t>Pool F</t>
+    <t>Pool G</t>
   </si>
   <si>
     <t>Hermione Granger</t>
@@ -263,36 +297,6 @@
     <t>WONKA</t>
   </si>
   <si>
-    <t>Pool G</t>
-  </si>
-  <si>
-    <t>Inigo Montoya</t>
-  </si>
-  <si>
-    <t>Team Iota</t>
-  </si>
-  <si>
-    <t>MONTOYA</t>
-  </si>
-  <si>
-    <t>Petyr Baelish</t>
-  </si>
-  <si>
-    <t>Team Pi</t>
-  </si>
-  <si>
-    <t>BAELISH</t>
-  </si>
-  <si>
-    <t>Xaro Xhoan Daxos</t>
-  </si>
-  <si>
-    <t>Team Omega</t>
-  </si>
-  <si>
-    <t>DAXOS</t>
-  </si>
-  <si>
     <t>Pool H</t>
   </si>
   <si>
@@ -323,6 +327,12 @@
     <t>YGRITTE</t>
   </si>
   <si>
+    <t>Shiaijo A</t>
+  </si>
+  <si>
+    <t>Shiaijo B</t>
+  </si>
+  <si>
     <t>Red</t>
   </si>
   <si>
@@ -470,7 +480,7 @@
     <t>Elimination Round 4</t>
   </si>
   <si>
-    <t>Match 15</t>
+    <t>Match 0</t>
   </si>
 </sst>
 </file>
@@ -1085,92 +1095,84 @@
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" t="s">
-        <v>15</v>
-      </c>
+      <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2" ht="12.75" customHeight="true">
       <c r="A2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
         <v>16</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="12.75" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
         <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="12.75" customHeight="true">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
         <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="12.75" customHeight="true">
       <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
         <v>26</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="12.75" customHeight="true">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
         <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="12.75" customHeight="true">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>31</v>
@@ -1184,27 +1186,27 @@
     </row>
     <row r="8" spans="1:2" ht="12.75" customHeight="true">
       <c r="A8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" t="s">
         <v>35</v>
       </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="12.75" customHeight="true">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
         <v>38</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
       </c>
       <c r="D9" t="s">
         <v>39</v>
@@ -1212,7 +1214,7 @@
     </row>
     <row r="10" spans="1:2" ht="12.75" customHeight="true">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>40</v>
@@ -1221,12 +1223,12 @@
         <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="12.75" customHeight="true">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>43</v>
@@ -1240,35 +1242,35 @@
     </row>
     <row r="12" spans="1:2" ht="12.75" customHeight="true">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="12.75" customHeight="true">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="12.75" customHeight="true">
       <c r="A14" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>53</v>
@@ -1282,161 +1284,171 @@
     </row>
     <row r="15" spans="1:2" ht="12.75" customHeight="true">
       <c r="A15" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="12.75" customHeight="true">
       <c r="A16" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="12.75" customHeight="true">
       <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" t="s">
         <v>62</v>
-      </c>
-      <c r="B17" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="12.75" customHeight="true">
       <c r="A18" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" t="s">
         <v>66</v>
-      </c>
-      <c r="C18" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="12.75" customHeight="true">
       <c r="A19" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
         <v>69</v>
-      </c>
-      <c r="C19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="12.75" customHeight="true">
       <c r="A20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" t="s">
         <v>72</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="12.75" customHeight="true">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" t="s">
         <v>76</v>
-      </c>
-      <c r="C21" t="s">
-        <v>77</v>
-      </c>
-      <c r="D21" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="12.75" customHeight="true">
       <c r="A22" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" t="s">
         <v>79</v>
-      </c>
-      <c r="C22" t="s">
-        <v>80</v>
-      </c>
-      <c r="D22" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="12.75" customHeight="true">
       <c r="A23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" t="s">
         <v>82</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="12.75" customHeight="true">
       <c r="A24" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" t="s">
         <v>86</v>
-      </c>
-      <c r="C24" t="s">
-        <v>87</v>
-      </c>
-      <c r="D24" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="12.75" customHeight="true">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" t="s">
         <v>89</v>
       </c>
-      <c r="C25" t="s">
+    </row>
+    <row r="26" spans="1:2" ht="12.75" customHeight="true">
+      <c r="A26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D25" t="s">
+      <c r="C26" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="12.75" customHeight="true">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
+      <c r="D26" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="27" spans="1:2" ht="12.75" customHeight="true">
       <c r="A27" s="1"/>
@@ -2478,14 +2490,34 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="str">
+        <f>IF(data!$B$1="","Shiaijo A",data!$B$1&amp;" - Shiaijo A")</f>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+    </row>
     <row r="4">
       <c r="A4" s="29" t="str">
-        <f>data!$A$4</f>
+        <f>data!$A$5</f>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="30" t="str">
-        <f>"1. " &amp; data!$B$2</f>
+        <f>"1. " &amp; data!$B$3</f>
       </c>
       <c r="C5" s="28" t="str">
         <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G10)</f>
@@ -2493,7 +2525,7 @@
     </row>
     <row r="6">
       <c r="A6" s="31" t="str">
-        <f>"2. " &amp; data!$B$3</f>
+        <f>"2. " &amp; data!$B$4</f>
       </c>
       <c r="D6" s="27"/>
       <c r="E6" s="26">
@@ -2502,10 +2534,10 @@
     </row>
     <row r="7">
       <c r="A7" s="32" t="str">
-        <f>"3. " &amp; data!$B$4</f>
+        <f>"3. " &amp; data!$B$5</f>
       </c>
       <c r="C7" s="28" t="str">
-        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!O11)</f>
+        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G22)</f>
       </c>
       <c r="D7" s="22"/>
       <c r="E7" s="25"/>
@@ -2520,10 +2552,10 @@
     </row>
     <row r="9">
       <c r="A9" s="29" t="str">
-        <f>data!$A$7</f>
+        <f>data!$A$8</f>
       </c>
       <c r="C9" s="28" t="str">
-        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G21)</f>
+        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G32)</f>
       </c>
       <c r="G9" s="25"/>
       <c r="H9" s="27"/>
@@ -2531,7 +2563,7 @@
     </row>
     <row r="10">
       <c r="A10" s="30" t="str">
-        <f>"1. " &amp; data!$B$5</f>
+        <f>"1. " &amp; data!$B$6</f>
       </c>
       <c r="D10" s="27"/>
       <c r="E10" s="26">
@@ -2543,10 +2575,10 @@
     </row>
     <row r="11">
       <c r="A11" s="31" t="str">
-        <f>"2. " &amp; data!$B$6</f>
+        <f>"2. " &amp; data!$B$7</f>
       </c>
       <c r="C11" s="28" t="str">
-        <f>CONCATENATE("Pool D.2 ",'Pool Matches'!O22)</f>
+        <f>CONCATENATE("Pool D.2 ",'Pool Matches'!G44)</f>
       </c>
       <c r="D11" s="22"/>
       <c r="E11" s="25"/>
@@ -2554,7 +2586,7 @@
     </row>
     <row r="12">
       <c r="A12" s="32" t="str">
-        <f>"3. " &amp; data!$B$7</f>
+        <f>"3. " &amp; data!$B$8</f>
       </c>
       <c r="I12" s="26">
         <v>13</v>
@@ -2563,57 +2595,51 @@
     <row r="13">
       <c r="A13" s="27"/>
       <c r="C13" s="28" t="str">
-        <f>CONCATENATE("Pool E.1 ",'Pool Matches'!G32)</f>
+        <f>CONCATENATE("Pool E.1 ",'Pool Matches'!O10)</f>
       </c>
       <c r="I13" s="25"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="25"/>
     </row>
     <row r="14">
       <c r="A14" s="29" t="str">
-        <f>data!$A$10</f>
+        <f>data!$A$11</f>
       </c>
       <c r="D14" s="27"/>
       <c r="E14" s="26">
         <v>3</v>
       </c>
       <c r="I14" s="25"/>
-      <c r="K14" s="25"/>
     </row>
     <row r="15">
       <c r="A15" s="30" t="str">
-        <f>"1. " &amp; data!$B$8</f>
+        <f>"1. " &amp; data!$B$9</f>
       </c>
       <c r="C15" s="28" t="str">
-        <f>CONCATENATE("Pool F.2 ",'Pool Matches'!O33)</f>
+        <f>CONCATENATE("Pool F.2 ",'Pool Matches'!O22)</f>
       </c>
       <c r="D15" s="22"/>
       <c r="E15" s="25"/>
       <c r="F15" s="27"/>
       <c r="G15" s="25"/>
       <c r="I15" s="25"/>
-      <c r="K15" s="25"/>
     </row>
     <row r="16">
       <c r="A16" s="31" t="str">
-        <f>"2. " &amp; data!$B$9</f>
+        <f>"2. " &amp; data!$B$10</f>
       </c>
       <c r="G16" s="26">
         <v>10</v>
       </c>
       <c r="H16" s="22"/>
       <c r="I16" s="25"/>
-      <c r="K16" s="25"/>
     </row>
     <row r="17">
       <c r="A17" s="32" t="str">
-        <f>"3. " &amp; data!$B$10</f>
+        <f>"3. " &amp; data!$B$11</f>
       </c>
       <c r="C17" s="28" t="str">
-        <f>CONCATENATE("Pool G.1 ",'Pool Matches'!G43)</f>
+        <f>CONCATENATE("Pool G.1 ",'Pool Matches'!O32)</f>
       </c>
       <c r="G17" s="25"/>
-      <c r="K17" s="25"/>
     </row>
     <row r="18">
       <c r="A18" s="27"/>
@@ -2623,218 +2649,39 @@
       </c>
       <c r="F18" s="22"/>
       <c r="G18" s="25"/>
-      <c r="K18" s="25"/>
     </row>
     <row r="19">
       <c r="A19" s="29" t="str">
-        <f>data!$A$13</f>
+        <f>data!$A$14</f>
       </c>
       <c r="C19" s="28" t="str">
         <f>CONCATENATE("Pool H.2 ",'Pool Matches'!O44)</f>
       </c>
       <c r="D19" s="22"/>
       <c r="E19" s="25"/>
-      <c r="K19" s="25"/>
     </row>
     <row r="20">
       <c r="A20" s="30" t="str">
-        <f>"1. " &amp; data!$B$11</f>
-      </c>
-      <c r="K20" s="26">
-        <v>15</v>
+        <f>"1. " &amp; data!$B$12</f>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="31" t="str">
-        <f>"2. " &amp; data!$B$12</f>
-      </c>
-      <c r="C21" s="28" t="str">
-        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!O10)</f>
-      </c>
-      <c r="K21" s="25"/>
+        <f>"2. " &amp; data!$B$13</f>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="32" t="str">
-        <f>"3. " &amp; data!$B$13</f>
-      </c>
-      <c r="D22" s="27"/>
-      <c r="E22" s="26">
-        <v>5</v>
-      </c>
-      <c r="K22" s="25"/>
+        <f>"3. " &amp; data!$B$14</f>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="27"/>
-      <c r="C23" s="28" t="str">
-        <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G11)</f>
-      </c>
-      <c r="D23" s="22"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="25"/>
-      <c r="K23" s="25"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="29" t="str">
-        <f>data!$A$16</f>
-      </c>
-      <c r="G24" s="26">
-        <v>11</v>
-      </c>
-      <c r="K24" s="25"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="30" t="str">
-        <f>"1. " &amp; data!$B$14</f>
-      </c>
-      <c r="C25" s="28" t="str">
-        <f>CONCATENATE("Pool D.1 ",'Pool Matches'!O21)</f>
-      </c>
-      <c r="G25" s="25"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="25"/>
-      <c r="K25" s="25"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="31" t="str">
-        <f>"2. " &amp; data!$B$15</f>
-      </c>
-      <c r="D26" s="27"/>
-      <c r="E26" s="26">
-        <v>6</v>
-      </c>
-      <c r="F26" s="22"/>
-      <c r="G26" s="25"/>
-      <c r="I26" s="25"/>
-      <c r="K26" s="25"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="32" t="str">
-        <f>"3. " &amp; data!$B$16</f>
-      </c>
-      <c r="C27" s="28" t="str">
-        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G22)</f>
-      </c>
-      <c r="D27" s="22"/>
-      <c r="E27" s="25"/>
-      <c r="I27" s="25"/>
-      <c r="K27" s="25"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="27"/>
-      <c r="I28" s="26">
-        <v>14</v>
-      </c>
-      <c r="J28" s="22"/>
-      <c r="K28" s="25"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="29" t="str">
-        <f>data!$A$19</f>
-      </c>
-      <c r="C29" s="28" t="str">
-        <f>CONCATENATE("Pool F.1 ",'Pool Matches'!O32)</f>
-      </c>
-      <c r="I29" s="25"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="30" t="str">
-        <f>"1. " &amp; data!$B$17</f>
-      </c>
-      <c r="D30" s="27"/>
-      <c r="E30" s="26">
-        <v>7</v>
-      </c>
-      <c r="I30" s="25"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="31" t="str">
-        <f>"2. " &amp; data!$B$18</f>
-      </c>
-      <c r="C31" s="28" t="str">
-        <f>CONCATENATE("Pool E.2 ",'Pool Matches'!G33)</f>
-      </c>
-      <c r="D31" s="22"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="25"/>
-      <c r="I31" s="25"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="32" t="str">
-        <f>"3. " &amp; data!$B$19</f>
-      </c>
-      <c r="G32" s="26">
-        <v>12</v>
-      </c>
-      <c r="H32" s="22"/>
-      <c r="I32" s="25"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="27"/>
-      <c r="C33" s="28" t="str">
-        <f>CONCATENATE("Pool H.1 ",'Pool Matches'!O43)</f>
-      </c>
-      <c r="G33" s="25"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="29" t="str">
-        <f>data!$A$22</f>
-      </c>
-      <c r="D34" s="27"/>
-      <c r="E34" s="26">
-        <v>8</v>
-      </c>
-      <c r="F34" s="22"/>
-      <c r="G34" s="25"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="30" t="str">
-        <f>"1. " &amp; data!$B$20</f>
-      </c>
-      <c r="C35" s="28" t="str">
-        <f>CONCATENATE("Pool G.2 ",'Pool Matches'!G44)</f>
-      </c>
-      <c r="D35" s="22"/>
-      <c r="E35" s="25"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="31" t="str">
-        <f>"2. " &amp; data!$B$21</f>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="32" t="str">
-        <f>"3. " &amp; data!$B$22</f>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="27"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="29" t="str">
-        <f>data!$A$25</f>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="30" t="str">
-        <f>"1. " &amp; data!$B$23</f>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="31" t="str">
-        <f>"2. " &amp; data!$B$24</f>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="32" t="str">
-        <f>"3. " &amp; data!$B$25</f>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="27"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:P1"/>
+  </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -2842,6 +2689,216 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4065E12-1BC4-BF48-9DCD-AFB9407081DC}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="3.5" defaultRowHeight="13"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="20.83203125"/>
+    <col customWidth="true" max="2" min="2" width="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="str">
+        <f>IF(data!$B$1="","Shiaijo B",data!$B$1&amp;" - Shiaijo B")</f>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="str">
+        <f>data!$A$17</f>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="30" t="str">
+        <f>"1. " &amp; data!$B$15</f>
+      </c>
+      <c r="C5" s="28" t="str">
+        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G21)</f>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="str">
+        <f>"2. " &amp; data!$B$16</f>
+      </c>
+      <c r="D6" s="27"/>
+      <c r="E6" s="26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="32" t="str">
+        <f>"3. " &amp; data!$B$17</f>
+      </c>
+      <c r="C7" s="28" t="str">
+        <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G11)</f>
+      </c>
+      <c r="D7" s="22"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="25"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="27"/>
+      <c r="G8" s="26">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="str">
+        <f>data!$A$20</f>
+      </c>
+      <c r="C9" s="28" t="str">
+        <f>CONCATENATE("Pool D.1 ",'Pool Matches'!G43)</f>
+      </c>
+      <c r="G9" s="25"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="25"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="str">
+        <f>"1. " &amp; data!$B$18</f>
+      </c>
+      <c r="D10" s="27"/>
+      <c r="E10" s="26">
+        <v>6</v>
+      </c>
+      <c r="F10" s="22"/>
+      <c r="G10" s="25"/>
+      <c r="I10" s="25"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="str">
+        <f>"2. " &amp; data!$B$19</f>
+      </c>
+      <c r="C11" s="28" t="str">
+        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G33)</f>
+      </c>
+      <c r="D11" s="22"/>
+      <c r="E11" s="25"/>
+      <c r="I11" s="25"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="str">
+        <f>"3. " &amp; data!$B$20</f>
+      </c>
+      <c r="I12" s="26">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27"/>
+      <c r="C13" s="28" t="str">
+        <f>CONCATENATE("Pool F.1 ",'Pool Matches'!O21)</f>
+      </c>
+      <c r="I13" s="25"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="str">
+        <f>data!$A$23</f>
+      </c>
+      <c r="D14" s="27"/>
+      <c r="E14" s="26">
+        <v>7</v>
+      </c>
+      <c r="I14" s="25"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="30" t="str">
+        <f>"1. " &amp; data!$B$21</f>
+      </c>
+      <c r="C15" s="28" t="str">
+        <f>CONCATENATE("Pool E.2 ",'Pool Matches'!O11)</f>
+      </c>
+      <c r="D15" s="22"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="25"/>
+      <c r="I15" s="25"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="str">
+        <f>"2. " &amp; data!$B$22</f>
+      </c>
+      <c r="G16" s="26">
+        <v>12</v>
+      </c>
+      <c r="H16" s="22"/>
+      <c r="I16" s="25"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="32" t="str">
+        <f>"3. " &amp; data!$B$23</f>
+      </c>
+      <c r="C17" s="28" t="str">
+        <f>CONCATENATE("Pool H.1 ",'Pool Matches'!O43)</f>
+      </c>
+      <c r="G17" s="25"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="26">
+        <v>8</v>
+      </c>
+      <c r="F18" s="22"/>
+      <c r="G18" s="25"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="str">
+        <f>data!$A$26</f>
+      </c>
+      <c r="C19" s="28" t="str">
+        <f>CONCATENATE("Pool G.2 ",'Pool Matches'!O33)</f>
+      </c>
+      <c r="D19" s="22"/>
+      <c r="E19" s="25"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="str">
+        <f>"1. " &amp; data!$B$24</f>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="str">
+        <f>"2. " &amp; data!$B$25</f>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="32" t="str">
+        <f>"3. " &amp; data!$B$26</f>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="27"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:P1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageMargins left="0.25" right="0.25" top="0" bottom="0" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
@@ -2850,122 +2907,122 @@
   <sheetData>
     <row r="1" ht="390" customHeight="true">
       <c r="A1" s="35" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" ht="390" customHeight="true">
       <c r="A2" s="35" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" ht="390" customHeight="true">
       <c r="A3" s="35" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" ht="390" customHeight="true">
       <c r="A4" s="35" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" ht="390" customHeight="true">
       <c r="A5" s="35" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" ht="390" customHeight="true">
       <c r="A6" s="35" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" ht="390" customHeight="true">
       <c r="A7" s="35" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" ht="390" customHeight="true">
       <c r="A8" s="35" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" ht="390" customHeight="true">
       <c r="A9" s="35" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" ht="390" customHeight="true">
       <c r="A10" s="35" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" ht="390" customHeight="true">
       <c r="A11" s="35" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" ht="390" customHeight="true">
       <c r="A12" s="35" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" ht="390" customHeight="true">
       <c r="A13" s="35" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" ht="390" customHeight="true">
       <c r="A14" s="35" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" ht="390" customHeight="true">
       <c r="A15" s="35" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" ht="390" customHeight="true">
       <c r="A16" s="35" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" ht="390" customHeight="true">
       <c r="A17" s="35" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" ht="390" customHeight="true">
       <c r="A18" s="35" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" ht="390" customHeight="true">
       <c r="A19" s="35" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" ht="390" customHeight="true">
       <c r="A20" s="35" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" ht="390" customHeight="true">
       <c r="A21" s="35" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" ht="390" customHeight="true">
       <c r="A22" s="35" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" ht="390" customHeight="true">
       <c r="A23" s="35" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" ht="390" customHeight="true">
       <c r="A24" s="35" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -3219,7 +3276,8 @@
   <sheetData>
     <row r="2" spans="1:8" ht="20">
       <c r="A2" s="2"/>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="15" t="str">
+        <f>IF(data!$B$1="","Tournament Pools",data!$B$1&amp;" - Tournament Pools")</f>
         <v>1</v>
       </c>
       <c r="C2" s="16"/>
@@ -3248,130 +3306,130 @@
     </row>
     <row r="5" spans="1:8" ht="17" customHeight="true" thickBot="true">
       <c r="B5" s="6" t="str">
-        <f>data!$A$4</f>
+        <f>data!$A$5</f>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="6" t="str">
-        <f>data!$A$13</f>
+        <f>data!$A$14</f>
       </c>
       <c r="F5" s="6" t="str">
-        <f>data!$A$22</f>
+        <f>data!$A$23</f>
       </c>
     </row>
     <row r="6" spans="1:8" ht="17" customHeight="true" thickBot="true">
       <c r="B6" s="5" t="str">
-        <f>"1. " &amp; data!$B$2</f>
+        <f>"1. " &amp; data!$B$3</f>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="5" t="str">
-        <f>"1. " &amp; data!$B$11</f>
+        <f>"1. " &amp; data!$B$12</f>
       </c>
       <c r="F6" s="5" t="str">
-        <f>"1. " &amp; data!$B$20</f>
+        <f>"1. " &amp; data!$B$21</f>
       </c>
     </row>
     <row r="7" spans="1:8" ht="17" customHeight="true" thickBot="true">
       <c r="B7" s="5" t="str">
-        <f>"2. " &amp; data!$B$3</f>
+        <f>"2. " &amp; data!$B$4</f>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="5" t="str">
-        <f>"2. " &amp; data!$B$12</f>
+        <f>"2. " &amp; data!$B$13</f>
       </c>
       <c r="F7" s="5" t="str">
-        <f>"2. " &amp; data!$B$21</f>
+        <f>"2. " &amp; data!$B$22</f>
       </c>
     </row>
     <row r="8" spans="1:8" ht="17" customHeight="true" thickBot="true">
       <c r="B8" s="5" t="str">
-        <f>"3. " &amp; data!$B$4</f>
+        <f>"3. " &amp; data!$B$5</f>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="5" t="str">
-        <f>"3. " &amp; data!$B$13</f>
+        <f>"3. " &amp; data!$B$14</f>
       </c>
       <c r="F8" s="5" t="str">
-        <f>"3. " &amp; data!$B$22</f>
+        <f>"3. " &amp; data!$B$23</f>
       </c>
     </row>
     <row r="9" ht="17" customHeight="true"/>
     <row r="10" ht="17" customHeight="true"/>
     <row r="11" ht="17" customHeight="true">
       <c r="B11" s="6" t="str">
-        <f>data!$A$7</f>
+        <f>data!$A$8</f>
       </c>
       <c r="D11" s="6" t="str">
-        <f>data!$A$16</f>
+        <f>data!$A$17</f>
       </c>
       <c r="F11" s="6" t="str">
-        <f>data!$A$25</f>
+        <f>data!$A$26</f>
       </c>
     </row>
     <row r="12" ht="17" customHeight="true">
       <c r="B12" s="5" t="str">
-        <f>"1. " &amp; data!$B$5</f>
+        <f>"1. " &amp; data!$B$6</f>
       </c>
       <c r="D12" s="5" t="str">
-        <f>"1. " &amp; data!$B$14</f>
+        <f>"1. " &amp; data!$B$15</f>
       </c>
       <c r="F12" s="5" t="str">
-        <f>"1. " &amp; data!$B$23</f>
+        <f>"1. " &amp; data!$B$24</f>
       </c>
     </row>
     <row r="13" ht="17" customHeight="true">
       <c r="B13" s="5" t="str">
-        <f>"2. " &amp; data!$B$6</f>
+        <f>"2. " &amp; data!$B$7</f>
       </c>
       <c r="D13" s="5" t="str">
-        <f>"2. " &amp; data!$B$15</f>
+        <f>"2. " &amp; data!$B$16</f>
       </c>
       <c r="F13" s="5" t="str">
-        <f>"2. " &amp; data!$B$24</f>
+        <f>"2. " &amp; data!$B$25</f>
       </c>
     </row>
     <row r="14" ht="17" customHeight="true">
       <c r="B14" s="5" t="str">
-        <f>"3. " &amp; data!$B$7</f>
+        <f>"3. " &amp; data!$B$8</f>
       </c>
       <c r="D14" s="5" t="str">
-        <f>"3. " &amp; data!$B$16</f>
+        <f>"3. " &amp; data!$B$17</f>
       </c>
       <c r="F14" s="5" t="str">
-        <f>"3. " &amp; data!$B$25</f>
+        <f>"3. " &amp; data!$B$26</f>
       </c>
     </row>
     <row r="15" ht="17" customHeight="true"/>
     <row r="16" ht="17" customHeight="true"/>
     <row r="17" ht="17" customHeight="true">
       <c r="B17" s="6" t="str">
-        <f>data!$A$10</f>
+        <f>data!$A$11</f>
       </c>
       <c r="D17" s="6" t="str">
-        <f>data!$A$19</f>
+        <f>data!$A$20</f>
       </c>
     </row>
     <row r="18" ht="17" customHeight="true">
       <c r="B18" s="5" t="str">
-        <f>"1. " &amp; data!$B$8</f>
+        <f>"1. " &amp; data!$B$9</f>
       </c>
       <c r="D18" s="5" t="str">
-        <f>"1. " &amp; data!$B$17</f>
+        <f>"1. " &amp; data!$B$18</f>
       </c>
     </row>
     <row r="19" ht="17" customHeight="true">
       <c r="B19" s="5" t="str">
-        <f>"2. " &amp; data!$B$9</f>
+        <f>"2. " &amp; data!$B$10</f>
       </c>
       <c r="D19" s="5" t="str">
-        <f>"2. " &amp; data!$B$18</f>
+        <f>"2. " &amp; data!$B$19</f>
       </c>
     </row>
     <row r="20" ht="17" customHeight="true">
       <c r="B20" s="5" t="str">
-        <f>"3. " &amp; data!$B$10</f>
+        <f>"3. " &amp; data!$B$11</f>
       </c>
       <c r="D20" s="5" t="str">
-        <f>"3. " &amp; data!$B$19</f>
+        <f>"3. " &amp; data!$B$20</f>
       </c>
     </row>
   </sheetData>
@@ -3403,9 +3461,29 @@
     <col max="16384" min="16" style="7" width="10.83203125"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="I1" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+    </row>
     <row r="4">
       <c r="A4" s="20" t="str">
-        <f>data!$A$4</f>
+        <f>data!$A$5</f>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -3414,7 +3492,7 @@
       <c r="F4" s="20"/>
       <c r="G4" s="20"/>
       <c r="I4" s="20" t="str">
-        <f>data!$A$7</f>
+        <f>data!$A$17</f>
       </c>
       <c r="J4" s="20"/>
       <c r="K4" s="20"/>
@@ -3425,27 +3503,27 @@
     </row>
     <row r="5">
       <c r="A5" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L5" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="O5" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="21" t="str">
-        <f>data!$B$2</f>
+        <f>data!$B$3</f>
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
@@ -3453,10 +3531,10 @@
       <c r="E6" s="21"/>
       <c r="F6" s="21"/>
       <c r="G6" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$4</f>
       </c>
       <c r="I6" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$15</f>
       </c>
       <c r="J6" s="21"/>
       <c r="K6" s="21"/>
@@ -3464,12 +3542,12 @@
       <c r="M6" s="21"/>
       <c r="N6" s="21"/>
       <c r="O6" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$16</f>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="21" t="str">
-        <f>data!$B$2</f>
+        <f>data!$B$3</f>
       </c>
       <c r="B7" s="21"/>
       <c r="C7" s="21"/>
@@ -3477,10 +3555,10 @@
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
       <c r="G7" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$5</f>
       </c>
       <c r="I7" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$15</f>
       </c>
       <c r="J7" s="21"/>
       <c r="K7" s="21"/>
@@ -3488,12 +3566,12 @@
       <c r="M7" s="21"/>
       <c r="N7" s="21"/>
       <c r="O7" s="21" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$17</f>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$4</f>
       </c>
       <c r="B8" s="21"/>
       <c r="C8" s="21"/>
@@ -3501,10 +3579,10 @@
       <c r="E8" s="21"/>
       <c r="F8" s="21"/>
       <c r="G8" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$5</f>
       </c>
       <c r="I8" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$16</f>
       </c>
       <c r="J8" s="21"/>
       <c r="K8" s="21"/>
@@ -3512,42 +3590,42 @@
       <c r="M8" s="21"/>
       <c r="N8" s="21"/>
       <c r="O8" s="21" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$17</f>
       </c>
     </row>
     <row r="10">
       <c r="F10" s="7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G10" s="22"/>
       <c r="N10" s="7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="O10" s="22"/>
     </row>
     <row r="11">
       <c r="F11" s="7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G11" s="22"/>
       <c r="N11" s="7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O11" s="22"/>
     </row>
     <row r="12">
       <c r="F12" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G12" s="22"/>
       <c r="N12" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="O12" s="22"/>
     </row>
     <row r="15">
       <c r="A15" s="20" t="str">
-        <f>data!$A$10</f>
+        <f>data!$A$8</f>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -3556,7 +3634,7 @@
       <c r="F15" s="20"/>
       <c r="G15" s="20"/>
       <c r="I15" s="20" t="str">
-        <f>data!$A$13</f>
+        <f>data!$A$20</f>
       </c>
       <c r="J15" s="20"/>
       <c r="K15" s="20"/>
@@ -3567,27 +3645,27 @@
     </row>
     <row r="16">
       <c r="A16" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I16" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="O16" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$6</f>
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
@@ -3595,10 +3673,10 @@
       <c r="E17" s="21"/>
       <c r="F17" s="21"/>
       <c r="G17" s="21" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$7</f>
       </c>
       <c r="I17" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$18</f>
       </c>
       <c r="J17" s="21"/>
       <c r="K17" s="21"/>
@@ -3606,12 +3684,12 @@
       <c r="M17" s="21"/>
       <c r="N17" s="21"/>
       <c r="O17" s="21" t="str">
-        <f>data!$B$12</f>
+        <f>data!$B$19</f>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$6</f>
       </c>
       <c r="B18" s="21"/>
       <c r="C18" s="21"/>
@@ -3619,10 +3697,10 @@
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
       <c r="G18" s="21" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$8</f>
       </c>
       <c r="I18" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$18</f>
       </c>
       <c r="J18" s="21"/>
       <c r="K18" s="21"/>
@@ -3630,12 +3708,12 @@
       <c r="M18" s="21"/>
       <c r="N18" s="21"/>
       <c r="O18" s="21" t="str">
-        <f>data!$B$13</f>
+        <f>data!$B$20</f>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="21" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$7</f>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
@@ -3643,10 +3721,10 @@
       <c r="E19" s="21"/>
       <c r="F19" s="21"/>
       <c r="G19" s="21" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$8</f>
       </c>
       <c r="I19" s="21" t="str">
-        <f>data!$B$12</f>
+        <f>data!$B$19</f>
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21"/>
@@ -3654,42 +3732,42 @@
       <c r="M19" s="21"/>
       <c r="N19" s="21"/>
       <c r="O19" s="21" t="str">
-        <f>data!$B$13</f>
+        <f>data!$B$20</f>
       </c>
     </row>
     <row r="21">
       <c r="F21" s="7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G21" s="22"/>
       <c r="N21" s="7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="O21" s="22"/>
     </row>
     <row r="22">
       <c r="F22" s="7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G22" s="22"/>
       <c r="N22" s="7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O22" s="22"/>
     </row>
     <row r="23">
       <c r="F23" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G23" s="22"/>
       <c r="N23" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="O23" s="22"/>
     </row>
     <row r="26">
       <c r="A26" s="20" t="str">
-        <f>data!$A$16</f>
+        <f>data!$A$11</f>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -3698,7 +3776,7 @@
       <c r="F26" s="20"/>
       <c r="G26" s="20"/>
       <c r="I26" s="20" t="str">
-        <f>data!$A$19</f>
+        <f>data!$A$23</f>
       </c>
       <c r="J26" s="20"/>
       <c r="K26" s="20"/>
@@ -3709,27 +3787,27 @@
     </row>
     <row r="27">
       <c r="A27" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G27" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I27" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L27" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="O27" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="21" t="str">
-        <f>data!$B$14</f>
+        <f>data!$B$9</f>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -3737,10 +3815,10 @@
       <c r="E28" s="21"/>
       <c r="F28" s="21"/>
       <c r="G28" s="21" t="str">
-        <f>data!$B$15</f>
+        <f>data!$B$10</f>
       </c>
       <c r="I28" s="21" t="str">
-        <f>data!$B$17</f>
+        <f>data!$B$21</f>
       </c>
       <c r="J28" s="21"/>
       <c r="K28" s="21"/>
@@ -3748,12 +3826,12 @@
       <c r="M28" s="21"/>
       <c r="N28" s="21"/>
       <c r="O28" s="21" t="str">
-        <f>data!$B$18</f>
+        <f>data!$B$22</f>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="21" t="str">
-        <f>data!$B$14</f>
+        <f>data!$B$9</f>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -3761,10 +3839,10 @@
       <c r="E29" s="21"/>
       <c r="F29" s="21"/>
       <c r="G29" s="21" t="str">
-        <f>data!$B$16</f>
+        <f>data!$B$11</f>
       </c>
       <c r="I29" s="21" t="str">
-        <f>data!$B$17</f>
+        <f>data!$B$21</f>
       </c>
       <c r="J29" s="21"/>
       <c r="K29" s="21"/>
@@ -3772,12 +3850,12 @@
       <c r="M29" s="21"/>
       <c r="N29" s="21"/>
       <c r="O29" s="21" t="str">
-        <f>data!$B$19</f>
+        <f>data!$B$23</f>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="21" t="str">
-        <f>data!$B$15</f>
+        <f>data!$B$10</f>
       </c>
       <c r="B30" s="21"/>
       <c r="C30" s="21"/>
@@ -3785,10 +3863,10 @@
       <c r="E30" s="21"/>
       <c r="F30" s="21"/>
       <c r="G30" s="21" t="str">
-        <f>data!$B$16</f>
+        <f>data!$B$11</f>
       </c>
       <c r="I30" s="21" t="str">
-        <f>data!$B$18</f>
+        <f>data!$B$22</f>
       </c>
       <c r="J30" s="21"/>
       <c r="K30" s="21"/>
@@ -3796,42 +3874,42 @@
       <c r="M30" s="21"/>
       <c r="N30" s="21"/>
       <c r="O30" s="21" t="str">
-        <f>data!$B$19</f>
+        <f>data!$B$23</f>
       </c>
     </row>
     <row r="32">
       <c r="F32" s="7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G32" s="22"/>
       <c r="N32" s="7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="O32" s="22"/>
     </row>
     <row r="33">
       <c r="F33" s="7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G33" s="22"/>
       <c r="N33" s="7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O33" s="22"/>
     </row>
     <row r="34">
       <c r="F34" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G34" s="22"/>
       <c r="N34" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="O34" s="22"/>
     </row>
     <row r="37">
       <c r="A37" s="20" t="str">
-        <f>data!$A$22</f>
+        <f>data!$A$14</f>
       </c>
       <c r="B37" s="20"/>
       <c r="C37" s="20"/>
@@ -3840,7 +3918,7 @@
       <c r="F37" s="20"/>
       <c r="G37" s="20"/>
       <c r="I37" s="20" t="str">
-        <f>data!$A$25</f>
+        <f>data!$A$26</f>
       </c>
       <c r="J37" s="20"/>
       <c r="K37" s="20"/>
@@ -3851,27 +3929,27 @@
     </row>
     <row r="38">
       <c r="A38" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G38" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I38" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L38" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="O38" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="str">
-        <f>data!$B$20</f>
+        <f>data!$B$12</f>
       </c>
       <c r="B39" s="21"/>
       <c r="C39" s="21"/>
@@ -3879,10 +3957,10 @@
       <c r="E39" s="21"/>
       <c r="F39" s="21"/>
       <c r="G39" s="21" t="str">
-        <f>data!$B$21</f>
+        <f>data!$B$13</f>
       </c>
       <c r="I39" s="21" t="str">
-        <f>data!$B$23</f>
+        <f>data!$B$24</f>
       </c>
       <c r="J39" s="21"/>
       <c r="K39" s="21"/>
@@ -3890,12 +3968,12 @@
       <c r="M39" s="21"/>
       <c r="N39" s="21"/>
       <c r="O39" s="21" t="str">
-        <f>data!$B$24</f>
+        <f>data!$B$25</f>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="str">
-        <f>data!$B$20</f>
+        <f>data!$B$12</f>
       </c>
       <c r="B40" s="21"/>
       <c r="C40" s="21"/>
@@ -3903,10 +3981,10 @@
       <c r="E40" s="21"/>
       <c r="F40" s="21"/>
       <c r="G40" s="21" t="str">
-        <f>data!$B$22</f>
+        <f>data!$B$14</f>
       </c>
       <c r="I40" s="21" t="str">
-        <f>data!$B$23</f>
+        <f>data!$B$24</f>
       </c>
       <c r="J40" s="21"/>
       <c r="K40" s="21"/>
@@ -3914,12 +3992,12 @@
       <c r="M40" s="21"/>
       <c r="N40" s="21"/>
       <c r="O40" s="21" t="str">
-        <f>data!$B$25</f>
+        <f>data!$B$26</f>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="str">
-        <f>data!$B$21</f>
+        <f>data!$B$13</f>
       </c>
       <c r="B41" s="21"/>
       <c r="C41" s="21"/>
@@ -3927,10 +4005,10 @@
       <c r="E41" s="21"/>
       <c r="F41" s="21"/>
       <c r="G41" s="21" t="str">
-        <f>data!$B$22</f>
+        <f>data!$B$14</f>
       </c>
       <c r="I41" s="21" t="str">
-        <f>data!$B$24</f>
+        <f>data!$B$25</f>
       </c>
       <c r="J41" s="21"/>
       <c r="K41" s="21"/>
@@ -3938,48 +4016,50 @@
       <c r="M41" s="21"/>
       <c r="N41" s="21"/>
       <c r="O41" s="21" t="str">
-        <f>data!$B$25</f>
+        <f>data!$B$26</f>
       </c>
     </row>
     <row r="43">
       <c r="F43" s="7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G43" s="22"/>
       <c r="N43" s="7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="O43" s="22"/>
     </row>
     <row r="44">
       <c r="F44" s="7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G44" s="22"/>
       <c r="N44" s="7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O44" s="22"/>
     </row>
     <row r="45">
       <c r="F45" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G45" s="22"/>
       <c r="N45" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="O45" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="I1:O1"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A37:G37"/>
     <mergeCell ref="I4:O4"/>
-    <mergeCell ref="A15:G15"/>
     <mergeCell ref="I15:O15"/>
-    <mergeCell ref="A26:G26"/>
     <mergeCell ref="I26:O26"/>
-    <mergeCell ref="A37:G37"/>
     <mergeCell ref="I37:O37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4026,7 +4106,7 @@
     </row>
     <row r="3">
       <c r="A3" s="20" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
@@ -4035,7 +4115,7 @@
       <c r="F3" s="20"/>
       <c r="G3" s="20"/>
       <c r="I3" s="20" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J3" s="20"/>
       <c r="K3" s="20"/>
@@ -4046,22 +4126,22 @@
     </row>
     <row r="4">
       <c r="A4" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="O4" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5">
@@ -4074,10 +4154,10 @@
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
       <c r="G5" s="21" t="str">
-        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!O11)</f>
+        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G22)</f>
       </c>
       <c r="I5" s="21" t="str">
-        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G21)</f>
+        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G32)</f>
       </c>
       <c r="J5" s="21"/>
       <c r="K5" s="21"/>
@@ -4085,32 +4165,32 @@
       <c r="M5" s="21"/>
       <c r="N5" s="21"/>
       <c r="O5" s="21" t="str">
-        <f>CONCATENATE("Pool D.2 ",'Pool Matches'!O22)</f>
+        <f>CONCATENATE("Pool D.2 ",'Pool Matches'!G44)</f>
       </c>
     </row>
     <row r="7">
       <c r="F7" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G7" s="22"/>
       <c r="N7" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O7" s="22"/>
     </row>
     <row r="8">
       <c r="F8" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G8" s="22"/>
       <c r="N8" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="O8" s="22"/>
     </row>
     <row r="11">
       <c r="A11" s="20" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
@@ -4119,7 +4199,7 @@
       <c r="F11" s="20"/>
       <c r="G11" s="20"/>
       <c r="I11" s="20" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J11" s="20"/>
       <c r="K11" s="20"/>
@@ -4130,27 +4210,27 @@
     </row>
     <row r="12">
       <c r="A12" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I12" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="O12" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="21" t="str">
-        <f>CONCATENATE("Pool E.1 ",'Pool Matches'!G32)</f>
+        <f>CONCATENATE("Pool E.1 ",'Pool Matches'!O10)</f>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
@@ -4158,10 +4238,10 @@
       <c r="E13" s="21"/>
       <c r="F13" s="21"/>
       <c r="G13" s="21" t="str">
-        <f>CONCATENATE("Pool F.2 ",'Pool Matches'!O33)</f>
+        <f>CONCATENATE("Pool F.2 ",'Pool Matches'!O22)</f>
       </c>
       <c r="I13" s="21" t="str">
-        <f>CONCATENATE("Pool G.1 ",'Pool Matches'!G43)</f>
+        <f>CONCATENATE("Pool G.1 ",'Pool Matches'!O32)</f>
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21"/>
@@ -4174,27 +4254,27 @@
     </row>
     <row r="15">
       <c r="F15" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G15" s="22"/>
       <c r="N15" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O15" s="22"/>
     </row>
     <row r="16">
       <c r="F16" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G16" s="22"/>
       <c r="N16" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="O16" s="22"/>
     </row>
     <row r="19">
       <c r="A19" s="20" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
@@ -4203,7 +4283,7 @@
       <c r="F19" s="20"/>
       <c r="G19" s="20"/>
       <c r="I19" s="20" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J19" s="20"/>
       <c r="K19" s="20"/>
@@ -4214,27 +4294,27 @@
     </row>
     <row r="20">
       <c r="A20" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="O20" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="21" t="str">
-        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!O10)</f>
+        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G21)</f>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -4245,7 +4325,7 @@
         <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G11)</f>
       </c>
       <c r="I21" s="21" t="str">
-        <f>CONCATENATE("Pool D.1 ",'Pool Matches'!O21)</f>
+        <f>CONCATENATE("Pool D.1 ",'Pool Matches'!G43)</f>
       </c>
       <c r="J21" s="21"/>
       <c r="K21" s="21"/>
@@ -4253,32 +4333,32 @@
       <c r="M21" s="21"/>
       <c r="N21" s="21"/>
       <c r="O21" s="21" t="str">
-        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G22)</f>
+        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G33)</f>
       </c>
     </row>
     <row r="23">
       <c r="F23" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G23" s="22"/>
       <c r="N23" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O23" s="22"/>
     </row>
     <row r="24">
       <c r="F24" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G24" s="22"/>
       <c r="N24" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="O24" s="22"/>
     </row>
     <row r="27">
       <c r="A27" s="20" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
@@ -4287,7 +4367,7 @@
       <c r="F27" s="20"/>
       <c r="G27" s="20"/>
       <c r="I27" s="20" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J27" s="20"/>
       <c r="K27" s="20"/>
@@ -4298,27 +4378,27 @@
     </row>
     <row r="28">
       <c r="A28" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G28" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I28" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L28" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="O28" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="21" t="str">
-        <f>CONCATENATE("Pool F.1 ",'Pool Matches'!O32)</f>
+        <f>CONCATENATE("Pool F.1 ",'Pool Matches'!O21)</f>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -4326,7 +4406,7 @@
       <c r="E29" s="21"/>
       <c r="F29" s="21"/>
       <c r="G29" s="21" t="str">
-        <f>CONCATENATE("Pool E.2 ",'Pool Matches'!G33)</f>
+        <f>CONCATENATE("Pool E.2 ",'Pool Matches'!O11)</f>
       </c>
       <c r="I29" s="21" t="str">
         <f>CONCATENATE("Pool H.1 ",'Pool Matches'!O43)</f>
@@ -4337,32 +4417,32 @@
       <c r="M29" s="21"/>
       <c r="N29" s="21"/>
       <c r="O29" s="21" t="str">
-        <f>CONCATENATE("Pool G.2 ",'Pool Matches'!G44)</f>
+        <f>CONCATENATE("Pool G.2 ",'Pool Matches'!O33)</f>
       </c>
     </row>
     <row r="31">
       <c r="F31" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G31" s="22"/>
       <c r="N31" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O31" s="22"/>
     </row>
     <row r="32">
       <c r="F32" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G32" s="22"/>
       <c r="N32" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="O32" s="22"/>
     </row>
     <row r="40">
       <c r="A40" s="20" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B40" s="20"/>
       <c r="C40" s="20"/>
@@ -4381,7 +4461,7 @@
     </row>
     <row r="42">
       <c r="A42" s="20" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
@@ -4390,7 +4470,7 @@
       <c r="F42" s="20"/>
       <c r="G42" s="20"/>
       <c r="I42" s="20" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J42" s="20"/>
       <c r="K42" s="20"/>
@@ -4401,22 +4481,22 @@
     </row>
     <row r="43">
       <c r="A43" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G43" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I43" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L43" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="O43" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44">
@@ -4445,27 +4525,27 @@
     </row>
     <row r="46">
       <c r="F46" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G46" s="22"/>
       <c r="N46" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O46" s="22"/>
     </row>
     <row r="47">
       <c r="F47" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G47" s="22"/>
       <c r="N47" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="O47" s="22"/>
     </row>
     <row r="50">
       <c r="A50" s="20" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B50" s="20"/>
       <c r="C50" s="20"/>
@@ -4474,7 +4554,7 @@
       <c r="F50" s="20"/>
       <c r="G50" s="20"/>
       <c r="I50" s="20" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="J50" s="20"/>
       <c r="K50" s="20"/>
@@ -4485,22 +4565,22 @@
     </row>
     <row r="51">
       <c r="A51" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G51" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I51" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L51" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="O51" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52">
@@ -4529,27 +4609,27 @@
     </row>
     <row r="54">
       <c r="F54" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G54" s="22"/>
       <c r="N54" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O54" s="22"/>
     </row>
     <row r="55">
       <c r="F55" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G55" s="22"/>
       <c r="N55" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="O55" s="22"/>
     </row>
     <row r="63">
       <c r="A63" s="20" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
@@ -4568,7 +4648,7 @@
     </row>
     <row r="65">
       <c r="A65" s="20" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
@@ -4577,7 +4657,7 @@
       <c r="F65" s="20"/>
       <c r="G65" s="20"/>
       <c r="I65" s="20" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J65" s="20"/>
       <c r="K65" s="20"/>
@@ -4588,22 +4668,22 @@
     </row>
     <row r="66">
       <c r="A66" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G66" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I66" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L66" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="O66" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="67">
@@ -4632,27 +4712,27 @@
     </row>
     <row r="69">
       <c r="F69" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G69" s="22"/>
       <c r="N69" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O69" s="22"/>
     </row>
     <row r="70">
       <c r="F70" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G70" s="22"/>
       <c r="N70" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="O70" s="22"/>
     </row>
     <row r="78">
       <c r="A78" s="20" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B78" s="20"/>
       <c r="C78" s="20"/>
@@ -4671,7 +4751,7 @@
     </row>
     <row r="80">
       <c r="A80" s="20" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B80" s="20"/>
       <c r="C80" s="20"/>
@@ -4682,13 +4762,13 @@
     </row>
     <row r="81">
       <c r="A81" s="23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D81" s="21" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G81" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="82">
@@ -4706,13 +4786,13 @@
     </row>
     <row r="84">
       <c r="F84" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G84" s="22"/>
     </row>
     <row r="85">
       <c r="F85" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G85" s="22"/>
     </row>
@@ -4757,10 +4837,10 @@
   <sheetData>
     <row r="1" ht="110" customHeight="true">
       <c r="A1" s="33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="34" t="str">
-        <f>data!D2</f>
+        <f>data!D3</f>
       </c>
     </row>
     <row r="2" ht="115" customHeight="true">
@@ -4771,10 +4851,10 @@
     </row>
     <row r="3" ht="110" customHeight="true">
       <c r="A3" s="33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="34" t="str">
-        <f>data!D3</f>
+        <f>data!D4</f>
       </c>
     </row>
     <row r="4" ht="115" customHeight="true">
@@ -4785,10 +4865,10 @@
     </row>
     <row r="5" ht="110" customHeight="true">
       <c r="A5" s="33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" s="34" t="str">
-        <f>data!D4</f>
+        <f>data!D5</f>
       </c>
     </row>
     <row r="6" ht="115" customHeight="true">
@@ -4799,10 +4879,10 @@
     </row>
     <row r="7" ht="110" customHeight="true">
       <c r="A7" s="33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="34" t="str">
-        <f>data!D5</f>
+        <f>data!D6</f>
       </c>
     </row>
     <row r="8" ht="115" customHeight="true">
@@ -4813,10 +4893,10 @@
     </row>
     <row r="9" ht="110" customHeight="true">
       <c r="A9" s="33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" s="34" t="str">
-        <f>data!D6</f>
+        <f>data!D7</f>
       </c>
     </row>
     <row r="10" ht="115" customHeight="true">
@@ -4827,10 +4907,10 @@
     </row>
     <row r="11" ht="110" customHeight="true">
       <c r="A11" s="33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11" s="34" t="str">
-        <f>data!D7</f>
+        <f>data!D8</f>
       </c>
     </row>
     <row r="12" ht="115" customHeight="true">
@@ -4841,10 +4921,10 @@
     </row>
     <row r="13" ht="110" customHeight="true">
       <c r="A13" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="34" t="str">
-        <f>data!D8</f>
+        <f>data!D9</f>
       </c>
     </row>
     <row r="14" ht="115" customHeight="true">
@@ -4855,10 +4935,10 @@
     </row>
     <row r="15" ht="110" customHeight="true">
       <c r="A15" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15" s="34" t="str">
-        <f>data!D9</f>
+        <f>data!D10</f>
       </c>
     </row>
     <row r="16" ht="115" customHeight="true">
@@ -4869,10 +4949,10 @@
     </row>
     <row r="17" ht="110" customHeight="true">
       <c r="A17" s="33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B17" s="34" t="str">
-        <f>data!D10</f>
+        <f>data!D11</f>
       </c>
     </row>
     <row r="18" ht="115" customHeight="true">
@@ -4883,10 +4963,10 @@
     </row>
     <row r="19" ht="110" customHeight="true">
       <c r="A19" s="33" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B19" s="34" t="str">
-        <f>data!D11</f>
+        <f>data!D12</f>
       </c>
     </row>
     <row r="20" ht="115" customHeight="true">
@@ -4897,10 +4977,10 @@
     </row>
     <row r="21" ht="110" customHeight="true">
       <c r="A21" s="33" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B21" s="34" t="str">
-        <f>data!D12</f>
+        <f>data!D13</f>
       </c>
     </row>
     <row r="22" ht="115" customHeight="true">
@@ -4911,10 +4991,10 @@
     </row>
     <row r="23" ht="110" customHeight="true">
       <c r="A23" s="33" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B23" s="34" t="str">
-        <f>data!D13</f>
+        <f>data!D14</f>
       </c>
     </row>
     <row r="24" ht="115" customHeight="true">
@@ -4925,10 +5005,10 @@
     </row>
     <row r="25" ht="110" customHeight="true">
       <c r="A25" s="33" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B25" s="34" t="str">
-        <f>data!D14</f>
+        <f>data!D15</f>
       </c>
     </row>
     <row r="26" ht="115" customHeight="true">
@@ -4939,10 +5019,10 @@
     </row>
     <row r="27" ht="110" customHeight="true">
       <c r="A27" s="33" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B27" s="34" t="str">
-        <f>data!D15</f>
+        <f>data!D16</f>
       </c>
     </row>
     <row r="28" ht="115" customHeight="true">
@@ -4953,10 +5033,10 @@
     </row>
     <row r="29" ht="110" customHeight="true">
       <c r="A29" s="33" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B29" s="34" t="str">
-        <f>data!D16</f>
+        <f>data!D17</f>
       </c>
     </row>
     <row r="30" ht="115" customHeight="true">
@@ -4967,10 +5047,10 @@
     </row>
     <row r="31" ht="110" customHeight="true">
       <c r="A31" s="33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B31" s="34" t="str">
-        <f>data!D17</f>
+        <f>data!D18</f>
       </c>
     </row>
     <row r="32" ht="115" customHeight="true">
@@ -4981,10 +5061,10 @@
     </row>
     <row r="33" ht="110" customHeight="true">
       <c r="A33" s="33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B33" s="34" t="str">
-        <f>data!D18</f>
+        <f>data!D19</f>
       </c>
     </row>
     <row r="34" ht="115" customHeight="true">
@@ -4995,10 +5075,10 @@
     </row>
     <row r="35" ht="110" customHeight="true">
       <c r="A35" s="33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B35" s="34" t="str">
-        <f>data!D19</f>
+        <f>data!D20</f>
       </c>
     </row>
     <row r="36" ht="115" customHeight="true">
@@ -5009,10 +5089,10 @@
     </row>
     <row r="37" ht="110" customHeight="true">
       <c r="A37" s="33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B37" s="34" t="str">
-        <f>data!D20</f>
+        <f>data!D21</f>
       </c>
     </row>
     <row r="38" ht="115" customHeight="true">
@@ -5023,10 +5103,10 @@
     </row>
     <row r="39" ht="110" customHeight="true">
       <c r="A39" s="33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B39" s="34" t="str">
-        <f>data!D21</f>
+        <f>data!D22</f>
       </c>
     </row>
     <row r="40" ht="115" customHeight="true">
@@ -5037,10 +5117,10 @@
     </row>
     <row r="41" ht="110" customHeight="true">
       <c r="A41" s="33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B41" s="34" t="str">
-        <f>data!D22</f>
+        <f>data!D23</f>
       </c>
     </row>
     <row r="42" ht="115" customHeight="true">
@@ -5051,10 +5131,10 @@
     </row>
     <row r="43" ht="110" customHeight="true">
       <c r="A43" s="33" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B43" s="34" t="str">
-        <f>data!D23</f>
+        <f>data!D24</f>
       </c>
     </row>
     <row r="44" ht="115" customHeight="true">
@@ -5065,10 +5145,10 @@
     </row>
     <row r="45" ht="110" customHeight="true">
       <c r="A45" s="33" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B45" s="34" t="str">
-        <f>data!D24</f>
+        <f>data!D25</f>
       </c>
     </row>
     <row r="46" ht="115" customHeight="true">
@@ -5079,10 +5159,10 @@
     </row>
     <row r="47" ht="110" customHeight="true">
       <c r="A47" s="33" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B47" s="34" t="str">
-        <f>data!D25</f>
+        <f>data!D26</f>
       </c>
     </row>
     <row r="48" ht="115" customHeight="true">

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -23,6 +23,8 @@
     <sheet name="Tags" sheetId="12" r:id="rId15"/>
   </sheets>
   <definedNames>
+    <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$21</definedName>
+    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$O$47</definedName>
     <definedName localSheetId="5" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$48</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -3444,21 +3446,25 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02F663BF-AB57-994A-845A-DBCD1B560412}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col customWidth="true" max="1" min="1" style="7" width="34"/>
-    <col customWidth="true" max="3" min="2" style="7" width="3.83203125"/>
+    <col customWidth="true" max="1" min="1" style="7" width="30"/>
+    <col customWidth="true" max="3" min="2" style="7" width="5"/>
     <col customWidth="true" max="4" min="4" style="7" width="3"/>
-    <col customWidth="true" max="6" min="5" style="7" width="3.83203125"/>
-    <col customWidth="true" max="7" min="7" style="7" width="34"/>
-    <col customWidth="true" max="8" min="8" style="7" width="3.83203125"/>
-    <col customWidth="true" max="9" min="9" style="7" width="34"/>
-    <col customWidth="true" max="11" min="10" style="7" width="3.83203125"/>
+    <col customWidth="true" max="6" min="5" style="7" width="5"/>
+    <col customWidth="true" max="7" min="7" style="7" width="30"/>
+    <col customWidth="true" max="8" min="8" style="7" width="2"/>
+    <col customWidth="true" max="9" min="9" style="7" width="30"/>
+    <col customWidth="true" max="11" min="10" style="7" width="5"/>
     <col customWidth="true" max="12" min="12" style="7" width="3"/>
-    <col customWidth="true" max="14" min="13" style="7" width="3.83203125"/>
-    <col customWidth="true" max="15" min="15" style="7" width="34"/>
-    <col max="16384" min="16" style="7" width="10.83203125"/>
+    <col customWidth="true" max="14" min="13" style="7" width="5"/>
+    <col customWidth="true" max="15" min="15" style="7" width="30"/>
+    <col customWidth="true" max="16" min="16" style="7" width="2"/>
+    <col max="16384" min="17" style="7" width="10.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4054,15 +4060,23 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="I4:O4"/>
     <mergeCell ref="A15:G15"/>
+    <mergeCell ref="I15:O15"/>
     <mergeCell ref="A26:G26"/>
+    <mergeCell ref="I26:O26"/>
     <mergeCell ref="A37:G37"/>
-    <mergeCell ref="I4:O4"/>
-    <mergeCell ref="I15:O15"/>
-    <mergeCell ref="I26:O26"/>
     <mergeCell ref="I37:O37"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" fitToWidth="2" orientation="portrait" pageOrder="downThenOver" paperSize="9"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="41" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="8" max="1048575" man="true"/>
+  </colBreaks>
 </worksheet>
 </file>
 
@@ -4071,18 +4085,19 @@
   <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col customWidth="true" max="1" min="1" style="7" width="34"/>
-    <col customWidth="true" max="3" min="2" style="7" width="3.83203125"/>
+    <col customWidth="true" max="1" min="1" style="7" width="30"/>
+    <col customWidth="true" max="3" min="2" style="7" width="5"/>
     <col customWidth="true" max="4" min="4" style="7" width="3"/>
-    <col customWidth="true" max="6" min="5" style="7" width="3.83203125"/>
-    <col customWidth="true" max="7" min="7" style="7" width="34"/>
-    <col customWidth="true" max="8" min="8" style="7" width="3.83203125"/>
-    <col customWidth="true" max="9" min="9" style="7" width="34"/>
-    <col customWidth="true" max="11" min="10" style="7" width="3.83203125"/>
+    <col customWidth="true" max="6" min="5" style="7" width="5"/>
+    <col customWidth="true" max="7" min="7" style="7" width="30"/>
+    <col customWidth="true" max="8" min="8" style="7" width="2"/>
+    <col customWidth="true" max="9" min="9" style="7" width="30"/>
+    <col customWidth="true" max="11" min="10" style="7" width="5"/>
     <col customWidth="true" max="12" min="12" style="7" width="3"/>
-    <col customWidth="true" max="14" min="13" style="7" width="3.83203125"/>
-    <col customWidth="true" max="15" min="15" style="7" width="34"/>
-    <col max="16384" min="16" style="7" width="10.83203125"/>
+    <col customWidth="true" max="14" min="13" style="7" width="5"/>
+    <col customWidth="true" max="15" min="15" style="7" width="30"/>
+    <col customWidth="true" max="16" min="16" style="7" width="2"/>
+    <col max="16384" min="17" style="7" width="10.83203125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17" thickBot="true">

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -335,13 +335,13 @@
     <t>Shiaijo B</t>
   </si>
   <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>vs</t>
+  </si>
+  <si>
     <t>Red</t>
-  </si>
-  <si>
-    <t>vs</t>
-  </si>
-  <si>
-    <t>White</t>
   </si>
   <si>
     <t xml:space="preserve">1. </t>
@@ -3508,28 +3508,28 @@
       <c r="O4" s="20"/>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="24" t="s">
         <v>95</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="24" t="s">
         <v>95</v>
       </c>
       <c r="L5" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="O5" s="24" t="s">
+      <c r="O5" s="23" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$4</f>
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
@@ -3537,10 +3537,10 @@
       <c r="E6" s="21"/>
       <c r="F6" s="21"/>
       <c r="G6" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$3</f>
       </c>
       <c r="I6" s="21" t="str">
-        <f>data!$B$15</f>
+        <f>data!$B$16</f>
       </c>
       <c r="J6" s="21"/>
       <c r="K6" s="21"/>
@@ -3548,12 +3548,12 @@
       <c r="M6" s="21"/>
       <c r="N6" s="21"/>
       <c r="O6" s="21" t="str">
-        <f>data!$B$16</f>
+        <f>data!$B$15</f>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$5</f>
       </c>
       <c r="B7" s="21"/>
       <c r="C7" s="21"/>
@@ -3561,10 +3561,10 @@
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
       <c r="G7" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$3</f>
       </c>
       <c r="I7" s="21" t="str">
-        <f>data!$B$15</f>
+        <f>data!$B$17</f>
       </c>
       <c r="J7" s="21"/>
       <c r="K7" s="21"/>
@@ -3572,12 +3572,12 @@
       <c r="M7" s="21"/>
       <c r="N7" s="21"/>
       <c r="O7" s="21" t="str">
-        <f>data!$B$17</f>
+        <f>data!$B$15</f>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$5</f>
       </c>
       <c r="B8" s="21"/>
       <c r="C8" s="21"/>
@@ -3585,10 +3585,10 @@
       <c r="E8" s="21"/>
       <c r="F8" s="21"/>
       <c r="G8" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$4</f>
       </c>
       <c r="I8" s="21" t="str">
-        <f>data!$B$16</f>
+        <f>data!$B$17</f>
       </c>
       <c r="J8" s="21"/>
       <c r="K8" s="21"/>
@@ -3596,7 +3596,7 @@
       <c r="M8" s="21"/>
       <c r="N8" s="21"/>
       <c r="O8" s="21" t="str">
-        <f>data!$B$17</f>
+        <f>data!$B$16</f>
       </c>
     </row>
     <row r="10">
@@ -3650,28 +3650,28 @@
       <c r="O15" s="20"/>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="24" t="s">
         <v>95</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G16" s="24" t="s">
+      <c r="G16" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="I16" s="23" t="s">
+      <c r="I16" s="24" t="s">
         <v>95</v>
       </c>
       <c r="L16" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="O16" s="24" t="s">
+      <c r="O16" s="23" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$7</f>
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="21"/>
@@ -3679,10 +3679,10 @@
       <c r="E17" s="21"/>
       <c r="F17" s="21"/>
       <c r="G17" s="21" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$6</f>
       </c>
       <c r="I17" s="21" t="str">
-        <f>data!$B$18</f>
+        <f>data!$B$19</f>
       </c>
       <c r="J17" s="21"/>
       <c r="K17" s="21"/>
@@ -3690,12 +3690,12 @@
       <c r="M17" s="21"/>
       <c r="N17" s="21"/>
       <c r="O17" s="21" t="str">
-        <f>data!$B$19</f>
+        <f>data!$B$18</f>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$8</f>
       </c>
       <c r="B18" s="21"/>
       <c r="C18" s="21"/>
@@ -3703,10 +3703,10 @@
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
       <c r="G18" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$6</f>
       </c>
       <c r="I18" s="21" t="str">
-        <f>data!$B$18</f>
+        <f>data!$B$20</f>
       </c>
       <c r="J18" s="21"/>
       <c r="K18" s="21"/>
@@ -3714,12 +3714,12 @@
       <c r="M18" s="21"/>
       <c r="N18" s="21"/>
       <c r="O18" s="21" t="str">
-        <f>data!$B$20</f>
+        <f>data!$B$18</f>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="21" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$8</f>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
@@ -3727,10 +3727,10 @@
       <c r="E19" s="21"/>
       <c r="F19" s="21"/>
       <c r="G19" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$7</f>
       </c>
       <c r="I19" s="21" t="str">
-        <f>data!$B$19</f>
+        <f>data!$B$20</f>
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21"/>
@@ -3738,7 +3738,7 @@
       <c r="M19" s="21"/>
       <c r="N19" s="21"/>
       <c r="O19" s="21" t="str">
-        <f>data!$B$20</f>
+        <f>data!$B$19</f>
       </c>
     </row>
     <row r="21">
@@ -3792,28 +3792,28 @@
       <c r="O26" s="20"/>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="24" t="s">
         <v>95</v>
       </c>
       <c r="D27" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G27" s="24" t="s">
+      <c r="G27" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="I27" s="23" t="s">
+      <c r="I27" s="24" t="s">
         <v>95</v>
       </c>
       <c r="L27" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="O27" s="24" t="s">
+      <c r="O27" s="23" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="21" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$10</f>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -3821,10 +3821,10 @@
       <c r="E28" s="21"/>
       <c r="F28" s="21"/>
       <c r="G28" s="21" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$9</f>
       </c>
       <c r="I28" s="21" t="str">
-        <f>data!$B$21</f>
+        <f>data!$B$22</f>
       </c>
       <c r="J28" s="21"/>
       <c r="K28" s="21"/>
@@ -3832,12 +3832,12 @@
       <c r="M28" s="21"/>
       <c r="N28" s="21"/>
       <c r="O28" s="21" t="str">
-        <f>data!$B$22</f>
+        <f>data!$B$21</f>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="21" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$11</f>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -3845,10 +3845,10 @@
       <c r="E29" s="21"/>
       <c r="F29" s="21"/>
       <c r="G29" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$9</f>
       </c>
       <c r="I29" s="21" t="str">
-        <f>data!$B$21</f>
+        <f>data!$B$23</f>
       </c>
       <c r="J29" s="21"/>
       <c r="K29" s="21"/>
@@ -3856,12 +3856,12 @@
       <c r="M29" s="21"/>
       <c r="N29" s="21"/>
       <c r="O29" s="21" t="str">
-        <f>data!$B$23</f>
+        <f>data!$B$21</f>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="21" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$11</f>
       </c>
       <c r="B30" s="21"/>
       <c r="C30" s="21"/>
@@ -3869,10 +3869,10 @@
       <c r="E30" s="21"/>
       <c r="F30" s="21"/>
       <c r="G30" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$10</f>
       </c>
       <c r="I30" s="21" t="str">
-        <f>data!$B$22</f>
+        <f>data!$B$23</f>
       </c>
       <c r="J30" s="21"/>
       <c r="K30" s="21"/>
@@ -3880,7 +3880,7 @@
       <c r="M30" s="21"/>
       <c r="N30" s="21"/>
       <c r="O30" s="21" t="str">
-        <f>data!$B$23</f>
+        <f>data!$B$22</f>
       </c>
     </row>
     <row r="32">
@@ -3934,28 +3934,28 @@
       <c r="O37" s="20"/>
     </row>
     <row r="38">
-      <c r="A38" s="23" t="s">
+      <c r="A38" s="24" t="s">
         <v>95</v>
       </c>
       <c r="D38" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G38" s="24" t="s">
+      <c r="G38" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="I38" s="23" t="s">
+      <c r="I38" s="24" t="s">
         <v>95</v>
       </c>
       <c r="L38" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="O38" s="24" t="s">
+      <c r="O38" s="23" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="str">
-        <f>data!$B$12</f>
+        <f>data!$B$13</f>
       </c>
       <c r="B39" s="21"/>
       <c r="C39" s="21"/>
@@ -3963,10 +3963,10 @@
       <c r="E39" s="21"/>
       <c r="F39" s="21"/>
       <c r="G39" s="21" t="str">
-        <f>data!$B$13</f>
+        <f>data!$B$12</f>
       </c>
       <c r="I39" s="21" t="str">
-        <f>data!$B$24</f>
+        <f>data!$B$25</f>
       </c>
       <c r="J39" s="21"/>
       <c r="K39" s="21"/>
@@ -3974,12 +3974,12 @@
       <c r="M39" s="21"/>
       <c r="N39" s="21"/>
       <c r="O39" s="21" t="str">
-        <f>data!$B$25</f>
+        <f>data!$B$24</f>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="str">
-        <f>data!$B$12</f>
+        <f>data!$B$14</f>
       </c>
       <c r="B40" s="21"/>
       <c r="C40" s="21"/>
@@ -3987,10 +3987,10 @@
       <c r="E40" s="21"/>
       <c r="F40" s="21"/>
       <c r="G40" s="21" t="str">
-        <f>data!$B$14</f>
+        <f>data!$B$12</f>
       </c>
       <c r="I40" s="21" t="str">
-        <f>data!$B$24</f>
+        <f>data!$B$26</f>
       </c>
       <c r="J40" s="21"/>
       <c r="K40" s="21"/>
@@ -3998,12 +3998,12 @@
       <c r="M40" s="21"/>
       <c r="N40" s="21"/>
       <c r="O40" s="21" t="str">
-        <f>data!$B$26</f>
+        <f>data!$B$24</f>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="str">
-        <f>data!$B$13</f>
+        <f>data!$B$14</f>
       </c>
       <c r="B41" s="21"/>
       <c r="C41" s="21"/>
@@ -4011,10 +4011,10 @@
       <c r="E41" s="21"/>
       <c r="F41" s="21"/>
       <c r="G41" s="21" t="str">
-        <f>data!$B$14</f>
+        <f>data!$B$13</f>
       </c>
       <c r="I41" s="21" t="str">
-        <f>data!$B$25</f>
+        <f>data!$B$26</f>
       </c>
       <c r="J41" s="21"/>
       <c r="K41" s="21"/>
@@ -4022,7 +4022,7 @@
       <c r="M41" s="21"/>
       <c r="N41" s="21"/>
       <c r="O41" s="21" t="str">
-        <f>data!$B$26</f>
+        <f>data!$B$25</f>
       </c>
     </row>
     <row r="43">
@@ -4140,28 +4140,28 @@
       <c r="O3" s="20"/>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="24" t="s">
         <v>95</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="24" t="s">
         <v>95</v>
       </c>
       <c r="L4" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="O4" s="24" t="s">
+      <c r="O4" s="23" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="21" t="str">
-        <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G10)</f>
+        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G22)</f>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="21"/>
@@ -4169,10 +4169,10 @@
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
       <c r="G5" s="21" t="str">
-        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G22)</f>
+        <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G10)</f>
       </c>
       <c r="I5" s="21" t="str">
-        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G32)</f>
+        <f>CONCATENATE("Pool D.2 ",'Pool Matches'!G44)</f>
       </c>
       <c r="J5" s="21"/>
       <c r="K5" s="21"/>
@@ -4180,7 +4180,7 @@
       <c r="M5" s="21"/>
       <c r="N5" s="21"/>
       <c r="O5" s="21" t="str">
-        <f>CONCATENATE("Pool D.2 ",'Pool Matches'!G44)</f>
+        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G32)</f>
       </c>
     </row>
     <row r="7">
@@ -4224,28 +4224,28 @@
       <c r="O11" s="20"/>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="24" t="s">
         <v>95</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="I12" s="23" t="s">
+      <c r="I12" s="24" t="s">
         <v>95</v>
       </c>
       <c r="L12" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="O12" s="24" t="s">
+      <c r="O12" s="23" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="21" t="str">
-        <f>CONCATENATE("Pool E.1 ",'Pool Matches'!O10)</f>
+        <f>CONCATENATE("Pool F.2 ",'Pool Matches'!O22)</f>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
@@ -4253,10 +4253,10 @@
       <c r="E13" s="21"/>
       <c r="F13" s="21"/>
       <c r="G13" s="21" t="str">
-        <f>CONCATENATE("Pool F.2 ",'Pool Matches'!O22)</f>
+        <f>CONCATENATE("Pool E.1 ",'Pool Matches'!O10)</f>
       </c>
       <c r="I13" s="21" t="str">
-        <f>CONCATENATE("Pool G.1 ",'Pool Matches'!O32)</f>
+        <f>CONCATENATE("Pool H.2 ",'Pool Matches'!O44)</f>
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21"/>
@@ -4264,7 +4264,7 @@
       <c r="M13" s="21"/>
       <c r="N13" s="21"/>
       <c r="O13" s="21" t="str">
-        <f>CONCATENATE("Pool H.2 ",'Pool Matches'!O44)</f>
+        <f>CONCATENATE("Pool G.1 ",'Pool Matches'!O32)</f>
       </c>
     </row>
     <row r="15">
@@ -4308,28 +4308,28 @@
       <c r="O19" s="20"/>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="24" t="s">
         <v>95</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G20" s="24" t="s">
+      <c r="G20" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="I20" s="23" t="s">
+      <c r="I20" s="24" t="s">
         <v>95</v>
       </c>
       <c r="L20" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="O20" s="24" t="s">
+      <c r="O20" s="23" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="21" t="str">
-        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G21)</f>
+        <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G11)</f>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -4337,10 +4337,10 @@
       <c r="E21" s="21"/>
       <c r="F21" s="21"/>
       <c r="G21" s="21" t="str">
-        <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G11)</f>
+        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G21)</f>
       </c>
       <c r="I21" s="21" t="str">
-        <f>CONCATENATE("Pool D.1 ",'Pool Matches'!G43)</f>
+        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G33)</f>
       </c>
       <c r="J21" s="21"/>
       <c r="K21" s="21"/>
@@ -4348,7 +4348,7 @@
       <c r="M21" s="21"/>
       <c r="N21" s="21"/>
       <c r="O21" s="21" t="str">
-        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G33)</f>
+        <f>CONCATENATE("Pool D.1 ",'Pool Matches'!G43)</f>
       </c>
     </row>
     <row r="23">
@@ -4392,28 +4392,28 @@
       <c r="O27" s="20"/>
     </row>
     <row r="28">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="24" t="s">
         <v>95</v>
       </c>
       <c r="D28" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G28" s="24" t="s">
+      <c r="G28" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="I28" s="23" t="s">
+      <c r="I28" s="24" t="s">
         <v>95</v>
       </c>
       <c r="L28" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="O28" s="24" t="s">
+      <c r="O28" s="23" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="21" t="str">
-        <f>CONCATENATE("Pool F.1 ",'Pool Matches'!O21)</f>
+        <f>CONCATENATE("Pool E.2 ",'Pool Matches'!O11)</f>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -4421,10 +4421,10 @@
       <c r="E29" s="21"/>
       <c r="F29" s="21"/>
       <c r="G29" s="21" t="str">
-        <f>CONCATENATE("Pool E.2 ",'Pool Matches'!O11)</f>
+        <f>CONCATENATE("Pool F.1 ",'Pool Matches'!O21)</f>
       </c>
       <c r="I29" s="21" t="str">
-        <f>CONCATENATE("Pool H.1 ",'Pool Matches'!O43)</f>
+        <f>CONCATENATE("Pool G.2 ",'Pool Matches'!O33)</f>
       </c>
       <c r="J29" s="21"/>
       <c r="K29" s="21"/>
@@ -4432,7 +4432,7 @@
       <c r="M29" s="21"/>
       <c r="N29" s="21"/>
       <c r="O29" s="21" t="str">
-        <f>CONCATENATE("Pool G.2 ",'Pool Matches'!O33)</f>
+        <f>CONCATENATE("Pool H.1 ",'Pool Matches'!O43)</f>
       </c>
     </row>
     <row r="31">
@@ -4495,28 +4495,28 @@
       <c r="O42" s="20"/>
     </row>
     <row r="43">
-      <c r="A43" s="23" t="s">
+      <c r="A43" s="24" t="s">
         <v>95</v>
       </c>
       <c r="D43" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G43" s="24" t="s">
+      <c r="G43" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="I43" s="23" t="s">
+      <c r="I43" s="24" t="s">
         <v>95</v>
       </c>
       <c r="L43" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="O43" s="24" t="s">
+      <c r="O43" s="23" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="str">
-        <f>CONCATENATE("M 1 ",'Elimination Matches'!G7)</f>
+        <f>CONCATENATE("M 2 ",'Elimination Matches'!O7)</f>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
@@ -4524,10 +4524,10 @@
       <c r="E44" s="21"/>
       <c r="F44" s="21"/>
       <c r="G44" s="21" t="str">
-        <f>CONCATENATE("M 2 ",'Elimination Matches'!O7)</f>
+        <f>CONCATENATE("M 1 ",'Elimination Matches'!G7)</f>
       </c>
       <c r="I44" s="21" t="str">
-        <f>CONCATENATE("M 3 ",'Elimination Matches'!G15)</f>
+        <f>CONCATENATE("M 4 ",'Elimination Matches'!O15)</f>
       </c>
       <c r="J44" s="21"/>
       <c r="K44" s="21"/>
@@ -4535,7 +4535,7 @@
       <c r="M44" s="21"/>
       <c r="N44" s="21"/>
       <c r="O44" s="21" t="str">
-        <f>CONCATENATE("M 4 ",'Elimination Matches'!O15)</f>
+        <f>CONCATENATE("M 3 ",'Elimination Matches'!G15)</f>
       </c>
     </row>
     <row r="46">
@@ -4579,28 +4579,28 @@
       <c r="O50" s="20"/>
     </row>
     <row r="51">
-      <c r="A51" s="23" t="s">
+      <c r="A51" s="24" t="s">
         <v>95</v>
       </c>
       <c r="D51" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G51" s="24" t="s">
+      <c r="G51" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="I51" s="23" t="s">
+      <c r="I51" s="24" t="s">
         <v>95</v>
       </c>
       <c r="L51" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="O51" s="24" t="s">
+      <c r="O51" s="23" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="21" t="str">
-        <f>CONCATENATE("M 5 ",'Elimination Matches'!G23)</f>
+        <f>CONCATENATE("M 6 ",'Elimination Matches'!O23)</f>
       </c>
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
@@ -4608,10 +4608,10 @@
       <c r="E52" s="21"/>
       <c r="F52" s="21"/>
       <c r="G52" s="21" t="str">
-        <f>CONCATENATE("M 6 ",'Elimination Matches'!O23)</f>
+        <f>CONCATENATE("M 5 ",'Elimination Matches'!G23)</f>
       </c>
       <c r="I52" s="21" t="str">
-        <f>CONCATENATE("M 7 ",'Elimination Matches'!G31)</f>
+        <f>CONCATENATE("M 8 ",'Elimination Matches'!O31)</f>
       </c>
       <c r="J52" s="21"/>
       <c r="K52" s="21"/>
@@ -4619,7 +4619,7 @@
       <c r="M52" s="21"/>
       <c r="N52" s="21"/>
       <c r="O52" s="21" t="str">
-        <f>CONCATENATE("M 8 ",'Elimination Matches'!O31)</f>
+        <f>CONCATENATE("M 7 ",'Elimination Matches'!G31)</f>
       </c>
     </row>
     <row r="54">
@@ -4682,28 +4682,28 @@
       <c r="O65" s="20"/>
     </row>
     <row r="66">
-      <c r="A66" s="23" t="s">
+      <c r="A66" s="24" t="s">
         <v>95</v>
       </c>
       <c r="D66" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G66" s="24" t="s">
+      <c r="G66" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="I66" s="23" t="s">
+      <c r="I66" s="24" t="s">
         <v>95</v>
       </c>
       <c r="L66" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="O66" s="24" t="s">
+      <c r="O66" s="23" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="21" t="str">
-        <f>CONCATENATE("M 9 ",'Elimination Matches'!G46)</f>
+        <f>CONCATENATE("M 10 ",'Elimination Matches'!O46)</f>
       </c>
       <c r="B67" s="21"/>
       <c r="C67" s="21"/>
@@ -4711,10 +4711,10 @@
       <c r="E67" s="21"/>
       <c r="F67" s="21"/>
       <c r="G67" s="21" t="str">
-        <f>CONCATENATE("M 10 ",'Elimination Matches'!O46)</f>
+        <f>CONCATENATE("M 9 ",'Elimination Matches'!G46)</f>
       </c>
       <c r="I67" s="21" t="str">
-        <f>CONCATENATE("M 11 ",'Elimination Matches'!G54)</f>
+        <f>CONCATENATE("M 12 ",'Elimination Matches'!O54)</f>
       </c>
       <c r="J67" s="21"/>
       <c r="K67" s="21"/>
@@ -4722,7 +4722,7 @@
       <c r="M67" s="21"/>
       <c r="N67" s="21"/>
       <c r="O67" s="21" t="str">
-        <f>CONCATENATE("M 12 ",'Elimination Matches'!O54)</f>
+        <f>CONCATENATE("M 11 ",'Elimination Matches'!G54)</f>
       </c>
     </row>
     <row r="69">
@@ -4776,19 +4776,19 @@
       <c r="G80" s="20"/>
     </row>
     <row r="81">
-      <c r="A81" s="23" t="s">
+      <c r="A81" s="24" t="s">
         <v>95</v>
       </c>
       <c r="D81" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G81" s="24" t="s">
+      <c r="G81" s="23" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="21" t="str">
-        <f>CONCATENATE("M 13 ",'Elimination Matches'!G69)</f>
+        <f>CONCATENATE("M 14 ",'Elimination Matches'!O69)</f>
       </c>
       <c r="B82" s="21"/>
       <c r="C82" s="21"/>
@@ -4796,7 +4796,7 @@
       <c r="E82" s="21"/>
       <c r="F82" s="21"/>
       <c r="G82" s="21" t="str">
-        <f>CONCATENATE("M 14 ",'Elimination Matches'!O69)</f>
+        <f>CONCATENATE("M 13 ",'Elimination Matches'!G69)</f>
       </c>
     </row>
     <row r="84">

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="26060" windowHeight="21580" activeTab="8"/>
+    <workbookView xWindow="34720" yWindow="1400" windowWidth="38080" windowHeight="20800" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -23,9 +23,10 @@
     <sheet name="Tags" sheetId="12" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$21</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$O$47</definedName>
+    <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$39</definedName>
+    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$O$41</definedName>
     <definedName localSheetId="5" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$48</definedName>
+    <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,10 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
-  <si>
-    <t>Elimination Round 1</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
   <si>
     <t>Tournament Pools</t>
   </si>
@@ -425,7 +423,7 @@
     <t>H3</t>
   </si>
   <si>
-    <t>Match 1</t>
+    <t>Round 1 - Match 1</t>
   </si>
   <si>
     <t>1.</t>
@@ -434,55 +432,67 @@
     <t>2.</t>
   </si>
   <si>
-    <t>Match 2</t>
-  </si>
-  <si>
-    <t>Match 3</t>
-  </si>
-  <si>
-    <t>Match 4</t>
-  </si>
-  <si>
-    <t>Match 5</t>
-  </si>
-  <si>
-    <t>Match 6</t>
-  </si>
-  <si>
-    <t>Match 7</t>
-  </si>
-  <si>
-    <t>Match 8</t>
-  </si>
-  <si>
-    <t>Elimination Round 2</t>
-  </si>
-  <si>
-    <t>Match 9</t>
-  </si>
-  <si>
-    <t>Match 10</t>
-  </si>
-  <si>
-    <t>Match 11</t>
-  </si>
-  <si>
-    <t>Match 12</t>
-  </si>
-  <si>
-    <t>Elimination Round 3</t>
-  </si>
-  <si>
-    <t>Match 13</t>
-  </si>
-  <si>
-    <t>Match 14</t>
-  </si>
-  <si>
-    <t>Elimination Round 4</t>
-  </si>
-  <si>
-    <t>Match 0</t>
+    <t>Round 1 - Match 5</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 2</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 6</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 3</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 7</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 4</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 8</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 9</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 11</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 10</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 12</t>
+  </si>
+  <si>
+    <t>Round 3 - Match 13</t>
+  </si>
+  <si>
+    <t>Round 3 - Match 14</t>
+  </si>
+  <si>
+    <t>Round 4 - Match 0</t>
+  </si>
+  <si>
+    <t>Tournament Summary</t>
+  </si>
+  <si>
+    <t>Total Pool Time</t>
+  </si>
+  <si>
+    <t>Total Elimination Time</t>
+  </si>
+  <si>
+    <t>Grand Total (Sequential)</t>
+  </si>
+  <si>
+    <t>Grand Total (Parallel across Courts)</t>
+  </si>
+  <si>
+    <t>Start Time:</t>
+  </si>
+  <si>
+    <t>Estimated Finish Time</t>
   </si>
 </sst>
 </file>
@@ -631,7 +641,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -651,43 +661,6 @@
       </top>
       <bottom style="medium">
         <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -776,7 +749,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
@@ -814,62 +787,57 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="false">
+      <alignment/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="false">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="true" applyAlignment="false">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1095,361 +1063,361 @@
   <sheetData>
     <row r="1" spans="1:2" ht="12.75" customHeight="true">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2" ht="12.75" customHeight="true">
       <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="12.75" customHeight="true">
       <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="12.75" customHeight="true">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="12.75" customHeight="true">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="12.75" customHeight="true">
       <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="12.75" customHeight="true">
       <c r="A7" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
         <v>31</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="12.75" customHeight="true">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
         <v>34</v>
       </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="12.75" customHeight="true">
       <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
         <v>36</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="12.75" customHeight="true">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
         <v>40</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>41</v>
-      </c>
-      <c r="D10" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="12.75" customHeight="true">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
         <v>43</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>44</v>
-      </c>
-      <c r="D11" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="12.75" customHeight="true">
       <c r="A12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" t="s">
         <v>47</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>48</v>
-      </c>
-      <c r="D12" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="12.75" customHeight="true">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
         <v>50</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>51</v>
-      </c>
-      <c r="D13" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="12.75" customHeight="true">
       <c r="A14" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" t="s">
         <v>53</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>54</v>
-      </c>
-      <c r="D14" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="12.75" customHeight="true">
       <c r="A15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" t="s">
         <v>57</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>58</v>
-      </c>
-      <c r="D15" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="12.75" customHeight="true">
       <c r="A16" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="12.75" customHeight="true">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s">
         <v>60</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>61</v>
-      </c>
-      <c r="D17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="12.75" customHeight="true">
       <c r="A18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" t="s">
         <v>64</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>65</v>
-      </c>
-      <c r="D18" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="12.75" customHeight="true">
       <c r="A19" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" t="s">
         <v>67</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>68</v>
-      </c>
-      <c r="D19" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="12.75" customHeight="true">
       <c r="A20" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" t="s">
         <v>70</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>71</v>
-      </c>
-      <c r="D20" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="12.75" customHeight="true">
       <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" t="s">
         <v>73</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>74</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>75</v>
-      </c>
-      <c r="D21" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="12.75" customHeight="true">
       <c r="A22" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" t="s">
         <v>77</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>78</v>
-      </c>
-      <c r="D22" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="12.75" customHeight="true">
       <c r="A23" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" t="s">
         <v>80</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>81</v>
-      </c>
-      <c r="D23" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="12.75" customHeight="true">
       <c r="A24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" t="s">
         <v>84</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>85</v>
-      </c>
-      <c r="D24" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="12.75" customHeight="true">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" t="s">
         <v>87</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>88</v>
-      </c>
-      <c r="D25" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="12.75" customHeight="true">
       <c r="A26" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C26" t="s">
         <v>90</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>91</v>
-      </c>
-      <c r="D26" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="12.75" customHeight="true">
@@ -2493,192 +2461,192 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="str">
+      <c r="A1" s="18" t="str">
         <f>IF(data!$B$1="","Shiaijo A",data!$B$1&amp;" - Shiaijo A")</f>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="str">
+      <c r="A4" s="27" t="str">
         <f>data!$A$5</f>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="str">
+      <c r="A5" s="28" t="str">
         <f>"1. " &amp; data!$B$3</f>
       </c>
-      <c r="C5" s="28" t="str">
-        <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G10)</f>
+      <c r="C5" s="26" t="str">
+        <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G8)</f>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="31" t="str">
+      <c r="A6" s="29" t="str">
         <f>"2. " &amp; data!$B$4</f>
       </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="26">
+      <c r="D6" s="25"/>
+      <c r="E6" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="str">
+      <c r="A7" s="30" t="str">
         <f>"3. " &amp; data!$B$5</f>
       </c>
-      <c r="C7" s="28" t="str">
-        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G22)</f>
-      </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="25"/>
+      <c r="C7" s="26" t="str">
+        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G19)</f>
+      </c>
+      <c r="D7" s="20"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="23"/>
     </row>
     <row r="8">
-      <c r="A8" s="27"/>
-      <c r="G8" s="26">
+      <c r="A8" s="25"/>
+      <c r="G8" s="24">
         <v>9</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="str">
+      <c r="A9" s="27" t="str">
         <f>data!$A$8</f>
       </c>
-      <c r="C9" s="28" t="str">
-        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G32)</f>
-      </c>
-      <c r="G9" s="25"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="25"/>
+      <c r="C9" s="26" t="str">
+        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G28)</f>
+      </c>
+      <c r="G9" s="23"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="23"/>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="str">
+      <c r="A10" s="28" t="str">
         <f>"1. " &amp; data!$B$6</f>
       </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="26">
+      <c r="D10" s="25"/>
+      <c r="E10" s="24">
         <v>2</v>
       </c>
-      <c r="F10" s="22"/>
-      <c r="G10" s="25"/>
-      <c r="I10" s="25"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="23"/>
+      <c r="I10" s="23"/>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="str">
+      <c r="A11" s="29" t="str">
         <f>"2. " &amp; data!$B$7</f>
       </c>
-      <c r="C11" s="28" t="str">
-        <f>CONCATENATE("Pool D.2 ",'Pool Matches'!G44)</f>
-      </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="25"/>
-      <c r="I11" s="25"/>
+      <c r="C11" s="26" t="str">
+        <f>CONCATENATE("Pool D.2 ",'Pool Matches'!G39)</f>
+      </c>
+      <c r="D11" s="20"/>
+      <c r="E11" s="23"/>
+      <c r="I11" s="23"/>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="str">
+      <c r="A12" s="30" t="str">
         <f>"3. " &amp; data!$B$8</f>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="24">
         <v>13</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27"/>
-      <c r="C13" s="28" t="str">
-        <f>CONCATENATE("Pool E.1 ",'Pool Matches'!O10)</f>
-      </c>
-      <c r="I13" s="25"/>
+      <c r="A13" s="25"/>
+      <c r="C13" s="26" t="str">
+        <f>CONCATENATE("Pool E.1 ",'Pool Matches'!O8)</f>
+      </c>
+      <c r="I13" s="23"/>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="str">
+      <c r="A14" s="27" t="str">
         <f>data!$A$11</f>
       </c>
-      <c r="D14" s="27"/>
-      <c r="E14" s="26">
+      <c r="D14" s="25"/>
+      <c r="E14" s="24">
         <v>3</v>
       </c>
-      <c r="I14" s="25"/>
+      <c r="I14" s="23"/>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="str">
+      <c r="A15" s="28" t="str">
         <f>"1. " &amp; data!$B$9</f>
       </c>
-      <c r="C15" s="28" t="str">
-        <f>CONCATENATE("Pool F.2 ",'Pool Matches'!O22)</f>
-      </c>
-      <c r="D15" s="22"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="25"/>
-      <c r="I15" s="25"/>
+      <c r="C15" s="26" t="str">
+        <f>CONCATENATE("Pool F.2 ",'Pool Matches'!O19)</f>
+      </c>
+      <c r="D15" s="20"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="23"/>
+      <c r="I15" s="23"/>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="str">
+      <c r="A16" s="29" t="str">
         <f>"2. " &amp; data!$B$10</f>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="24">
         <v>10</v>
       </c>
-      <c r="H16" s="22"/>
-      <c r="I16" s="25"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="23"/>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="str">
+      <c r="A17" s="30" t="str">
         <f>"3. " &amp; data!$B$11</f>
       </c>
-      <c r="C17" s="28" t="str">
-        <f>CONCATENATE("Pool G.1 ",'Pool Matches'!O32)</f>
-      </c>
-      <c r="G17" s="25"/>
+      <c r="C17" s="26" t="str">
+        <f>CONCATENATE("Pool G.1 ",'Pool Matches'!O28)</f>
+      </c>
+      <c r="G17" s="23"/>
     </row>
     <row r="18">
-      <c r="A18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="26">
+      <c r="A18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="24">
         <v>4</v>
       </c>
-      <c r="F18" s="22"/>
-      <c r="G18" s="25"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="23"/>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="str">
+      <c r="A19" s="27" t="str">
         <f>data!$A$14</f>
       </c>
-      <c r="C19" s="28" t="str">
-        <f>CONCATENATE("Pool H.2 ",'Pool Matches'!O44)</f>
-      </c>
-      <c r="D19" s="22"/>
-      <c r="E19" s="25"/>
+      <c r="C19" s="26" t="str">
+        <f>CONCATENATE("Pool H.2 ",'Pool Matches'!O39)</f>
+      </c>
+      <c r="D19" s="20"/>
+      <c r="E19" s="23"/>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="str">
+      <c r="A20" s="28" t="str">
         <f>"1. " &amp; data!$B$12</f>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="31" t="str">
+      <c r="A21" s="29" t="str">
         <f>"2. " &amp; data!$B$13</f>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="32" t="str">
+      <c r="A22" s="30" t="str">
         <f>"3. " &amp; data!$B$14</f>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="27"/>
+      <c r="A23" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2703,192 +2671,192 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="str">
+      <c r="A1" s="18" t="str">
         <f>IF(data!$B$1="","Shiaijo B",data!$B$1&amp;" - Shiaijo B")</f>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="str">
+      <c r="A4" s="27" t="str">
         <f>data!$A$17</f>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="str">
+      <c r="A5" s="28" t="str">
         <f>"1. " &amp; data!$B$15</f>
       </c>
-      <c r="C5" s="28" t="str">
-        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G21)</f>
+      <c r="C5" s="26" t="str">
+        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G18)</f>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="31" t="str">
+      <c r="A6" s="29" t="str">
         <f>"2. " &amp; data!$B$16</f>
       </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="26">
+      <c r="D6" s="25"/>
+      <c r="E6" s="24">
         <v>5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="str">
+      <c r="A7" s="30" t="str">
         <f>"3. " &amp; data!$B$17</f>
       </c>
-      <c r="C7" s="28" t="str">
-        <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G11)</f>
-      </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="25"/>
+      <c r="C7" s="26" t="str">
+        <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G9)</f>
+      </c>
+      <c r="D7" s="20"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="23"/>
     </row>
     <row r="8">
-      <c r="A8" s="27"/>
-      <c r="G8" s="26">
+      <c r="A8" s="25"/>
+      <c r="G8" s="24">
         <v>11</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="str">
+      <c r="A9" s="27" t="str">
         <f>data!$A$20</f>
       </c>
-      <c r="C9" s="28" t="str">
-        <f>CONCATENATE("Pool D.1 ",'Pool Matches'!G43)</f>
-      </c>
-      <c r="G9" s="25"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="25"/>
+      <c r="C9" s="26" t="str">
+        <f>CONCATENATE("Pool D.1 ",'Pool Matches'!G38)</f>
+      </c>
+      <c r="G9" s="23"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="23"/>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="str">
+      <c r="A10" s="28" t="str">
         <f>"1. " &amp; data!$B$18</f>
       </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="26">
+      <c r="D10" s="25"/>
+      <c r="E10" s="24">
         <v>6</v>
       </c>
-      <c r="F10" s="22"/>
-      <c r="G10" s="25"/>
-      <c r="I10" s="25"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="23"/>
+      <c r="I10" s="23"/>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="str">
+      <c r="A11" s="29" t="str">
         <f>"2. " &amp; data!$B$19</f>
       </c>
-      <c r="C11" s="28" t="str">
-        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G33)</f>
-      </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="25"/>
-      <c r="I11" s="25"/>
+      <c r="C11" s="26" t="str">
+        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G29)</f>
+      </c>
+      <c r="D11" s="20"/>
+      <c r="E11" s="23"/>
+      <c r="I11" s="23"/>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="str">
+      <c r="A12" s="30" t="str">
         <f>"3. " &amp; data!$B$20</f>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="24">
         <v>14</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27"/>
-      <c r="C13" s="28" t="str">
-        <f>CONCATENATE("Pool F.1 ",'Pool Matches'!O21)</f>
-      </c>
-      <c r="I13" s="25"/>
+      <c r="A13" s="25"/>
+      <c r="C13" s="26" t="str">
+        <f>CONCATENATE("Pool F.1 ",'Pool Matches'!O18)</f>
+      </c>
+      <c r="I13" s="23"/>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="str">
+      <c r="A14" s="27" t="str">
         <f>data!$A$23</f>
       </c>
-      <c r="D14" s="27"/>
-      <c r="E14" s="26">
+      <c r="D14" s="25"/>
+      <c r="E14" s="24">
         <v>7</v>
       </c>
-      <c r="I14" s="25"/>
+      <c r="I14" s="23"/>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="str">
+      <c r="A15" s="28" t="str">
         <f>"1. " &amp; data!$B$21</f>
       </c>
-      <c r="C15" s="28" t="str">
-        <f>CONCATENATE("Pool E.2 ",'Pool Matches'!O11)</f>
-      </c>
-      <c r="D15" s="22"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="25"/>
-      <c r="I15" s="25"/>
+      <c r="C15" s="26" t="str">
+        <f>CONCATENATE("Pool E.2 ",'Pool Matches'!O9)</f>
+      </c>
+      <c r="D15" s="20"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="23"/>
+      <c r="I15" s="23"/>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="str">
+      <c r="A16" s="29" t="str">
         <f>"2. " &amp; data!$B$22</f>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="24">
         <v>12</v>
       </c>
-      <c r="H16" s="22"/>
-      <c r="I16" s="25"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="23"/>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="str">
+      <c r="A17" s="30" t="str">
         <f>"3. " &amp; data!$B$23</f>
       </c>
-      <c r="C17" s="28" t="str">
-        <f>CONCATENATE("Pool H.1 ",'Pool Matches'!O43)</f>
-      </c>
-      <c r="G17" s="25"/>
+      <c r="C17" s="26" t="str">
+        <f>CONCATENATE("Pool H.1 ",'Pool Matches'!O38)</f>
+      </c>
+      <c r="G17" s="23"/>
     </row>
     <row r="18">
-      <c r="A18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="26">
+      <c r="A18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="24">
         <v>8</v>
       </c>
-      <c r="F18" s="22"/>
-      <c r="G18" s="25"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="23"/>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="str">
+      <c r="A19" s="27" t="str">
         <f>data!$A$26</f>
       </c>
-      <c r="C19" s="28" t="str">
-        <f>CONCATENATE("Pool G.2 ",'Pool Matches'!O33)</f>
-      </c>
-      <c r="D19" s="22"/>
-      <c r="E19" s="25"/>
+      <c r="C19" s="26" t="str">
+        <f>CONCATENATE("Pool G.2 ",'Pool Matches'!O29)</f>
+      </c>
+      <c r="D19" s="20"/>
+      <c r="E19" s="23"/>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="str">
+      <c r="A20" s="28" t="str">
         <f>"1. " &amp; data!$B$24</f>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="31" t="str">
+      <c r="A21" s="29" t="str">
         <f>"2. " &amp; data!$B$25</f>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="32" t="str">
+      <c r="A22" s="30" t="str">
         <f>"3. " &amp; data!$B$26</f>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="27"/>
+      <c r="A23" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2908,123 +2876,123 @@
   </cols>
   <sheetData>
     <row r="1" ht="390" customHeight="true">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" ht="390" customHeight="true">
+      <c r="A2" s="33" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="2" ht="390" customHeight="true">
-      <c r="A2" s="35" t="s">
+    <row r="3" ht="390" customHeight="true">
+      <c r="A3" s="33" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="3" ht="390" customHeight="true">
-      <c r="A3" s="35" t="s">
+    <row r="4" ht="390" customHeight="true">
+      <c r="A4" s="33" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="4" ht="390" customHeight="true">
-      <c r="A4" s="35" t="s">
+    <row r="5" ht="390" customHeight="true">
+      <c r="A5" s="33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="5" ht="390" customHeight="true">
-      <c r="A5" s="35" t="s">
+    <row r="6" ht="390" customHeight="true">
+      <c r="A6" s="33" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="6" ht="390" customHeight="true">
-      <c r="A6" s="35" t="s">
+    <row r="7" ht="390" customHeight="true">
+      <c r="A7" s="33" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="7" ht="390" customHeight="true">
-      <c r="A7" s="35" t="s">
+    <row r="8" ht="390" customHeight="true">
+      <c r="A8" s="33" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="8" ht="390" customHeight="true">
-      <c r="A8" s="35" t="s">
+    <row r="9" ht="390" customHeight="true">
+      <c r="A9" s="33" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="9" ht="390" customHeight="true">
-      <c r="A9" s="35" t="s">
+    <row r="10" ht="390" customHeight="true">
+      <c r="A10" s="33" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="10" ht="390" customHeight="true">
-      <c r="A10" s="35" t="s">
+    <row r="11" ht="390" customHeight="true">
+      <c r="A11" s="33" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="11" ht="390" customHeight="true">
-      <c r="A11" s="35" t="s">
+    <row r="12" ht="390" customHeight="true">
+      <c r="A12" s="33" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="12" ht="390" customHeight="true">
-      <c r="A12" s="35" t="s">
+    <row r="13" ht="390" customHeight="true">
+      <c r="A13" s="33" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="13" ht="390" customHeight="true">
-      <c r="A13" s="35" t="s">
+    <row r="14" ht="390" customHeight="true">
+      <c r="A14" s="33" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="14" ht="390" customHeight="true">
-      <c r="A14" s="35" t="s">
+    <row r="15" ht="390" customHeight="true">
+      <c r="A15" s="33" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="15" ht="390" customHeight="true">
-      <c r="A15" s="35" t="s">
+    <row r="16" ht="390" customHeight="true">
+      <c r="A16" s="33" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="16" ht="390" customHeight="true">
-      <c r="A16" s="35" t="s">
+    <row r="17" ht="390" customHeight="true">
+      <c r="A17" s="33" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="17" ht="390" customHeight="true">
-      <c r="A17" s="35" t="s">
+    <row r="18" ht="390" customHeight="true">
+      <c r="A18" s="33" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="18" ht="390" customHeight="true">
-      <c r="A18" s="35" t="s">
+    <row r="19" ht="390" customHeight="true">
+      <c r="A19" s="33" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="19" ht="390" customHeight="true">
-      <c r="A19" s="35" t="s">
+    <row r="20" ht="390" customHeight="true">
+      <c r="A20" s="33" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="20" ht="390" customHeight="true">
-      <c r="A20" s="35" t="s">
+    <row r="21" ht="390" customHeight="true">
+      <c r="A21" s="33" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="21" ht="390" customHeight="true">
-      <c r="A21" s="35" t="s">
+    <row r="22" ht="390" customHeight="true">
+      <c r="A22" s="33" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="22" ht="390" customHeight="true">
-      <c r="A22" s="35" t="s">
+    <row r="23" ht="390" customHeight="true">
+      <c r="A23" s="33" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="23" ht="390" customHeight="true">
-      <c r="A23" s="35" t="s">
+    <row r="24" ht="390" customHeight="true">
+      <c r="A24" s="33" t="s">
         <v>123</v>
-      </c>
-    </row>
-    <row r="24" ht="390" customHeight="true">
-      <c r="A24" s="35" t="s">
-        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -3061,28 +3029,28 @@
   <sheetData>
     <row r="1" spans="1:8" ht="51">
       <c r="A1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="C1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="H1" s="13" t="s">
         <v>8</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="11" customFormat="true" ht="16">
@@ -3093,7 +3061,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="11">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D2" s="12">
         <v>2.0833333333333333E-3</v>
@@ -3108,8 +3076,8 @@
       <c r="G2" s="12">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="H2" s="12">
-        <f>E2+(A2*C2*F2)+G2</f>
+      <c r="H2" s="12" t="str">
+        <f>C2*I2+J2</f>
         <v>6.041666666666666E-2</v>
       </c>
     </row>
@@ -3173,26 +3141,26 @@
     </row>
     <row r="7" spans="1:8" ht="51">
       <c r="A7" s="13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="F7" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="G7" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="H7" s="13" t="s">
         <v>8</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="true" ht="16">
@@ -3250,7 +3218,81 @@
       <c r="G11" s="14"/>
       <c r="H11" s="14"/>
     </row>
+    <row r="13">
+      <c r="E13" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19" t="str">
+        <f>H2</f>
+      </c>
+    </row>
+    <row r="15">
+      <c r="E15" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19" t="str">
+        <f>H8</f>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19" t="str">
+        <f>H14+H15</f>
+      </c>
+    </row>
+    <row r="17">
+      <c r="E17" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19" t="str">
+        <f>H16/A14</f>
+      </c>
+    </row>
+    <row r="18">
+      <c r="E18" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="34">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="E19" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="34" t="str">
+        <f>H18+H17</f>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E13:H13"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3268,7 +3310,7 @@
     <col customWidth="true" max="3" min="3" width="8.83203125"/>
     <col customWidth="true" max="4" min="4" width="30"/>
     <col customWidth="true" max="5" min="5" width="8.83203125"/>
-    <col customWidth="true" max="6" min="6" width="30"/>
+    <col customWidth="true" max="6" min="6" width="32.6640625"/>
     <col customWidth="true" max="7" min="7" width="8.83203125"/>
     <col customWidth="true" max="8" min="8" width="33"/>
     <col customWidth="true" max="9" min="9" width="8.83203125"/>
@@ -3280,7 +3322,7 @@
       <c r="A2" s="2"/>
       <c r="B2" s="15" t="str">
         <f>IF(data!$B$1="","Tournament Pools",data!$B$1&amp;" - Tournament Pools")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
@@ -3312,9 +3354,6 @@
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="6" t="str">
-        <f>data!$A$14</f>
-      </c>
-      <c r="F5" s="6" t="str">
         <f>data!$A$23</f>
       </c>
     </row>
@@ -3324,9 +3363,6 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="5" t="str">
-        <f>"1. " &amp; data!$B$12</f>
-      </c>
-      <c r="F6" s="5" t="str">
         <f>"1. " &amp; data!$B$21</f>
       </c>
     </row>
@@ -3336,9 +3372,6 @@
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="5" t="str">
-        <f>"2. " &amp; data!$B$13</f>
-      </c>
-      <c r="F7" s="5" t="str">
         <f>"2. " &amp; data!$B$22</f>
       </c>
     </row>
@@ -3348,9 +3381,6 @@
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="5" t="str">
-        <f>"3. " &amp; data!$B$14</f>
-      </c>
-      <c r="F8" s="5" t="str">
         <f>"3. " &amp; data!$B$23</f>
       </c>
     </row>
@@ -3361,9 +3391,6 @@
         <f>data!$A$8</f>
       </c>
       <c r="D11" s="6" t="str">
-        <f>data!$A$17</f>
-      </c>
-      <c r="F11" s="6" t="str">
         <f>data!$A$26</f>
       </c>
     </row>
@@ -3372,9 +3399,6 @@
         <f>"1. " &amp; data!$B$6</f>
       </c>
       <c r="D12" s="5" t="str">
-        <f>"1. " &amp; data!$B$15</f>
-      </c>
-      <c r="F12" s="5" t="str">
         <f>"1. " &amp; data!$B$24</f>
       </c>
     </row>
@@ -3383,9 +3407,6 @@
         <f>"2. " &amp; data!$B$7</f>
       </c>
       <c r="D13" s="5" t="str">
-        <f>"2. " &amp; data!$B$16</f>
-      </c>
-      <c r="F13" s="5" t="str">
         <f>"2. " &amp; data!$B$25</f>
       </c>
     </row>
@@ -3394,9 +3415,6 @@
         <f>"3. " &amp; data!$B$8</f>
       </c>
       <c r="D14" s="5" t="str">
-        <f>"3. " &amp; data!$B$17</f>
-      </c>
-      <c r="F14" s="5" t="str">
         <f>"3. " &amp; data!$B$26</f>
       </c>
     </row>
@@ -3406,31 +3424,85 @@
       <c r="B17" s="6" t="str">
         <f>data!$A$11</f>
       </c>
-      <c r="D17" s="6" t="str">
-        <f>data!$A$20</f>
-      </c>
     </row>
     <row r="18" ht="17" customHeight="true">
       <c r="B18" s="5" t="str">
         <f>"1. " &amp; data!$B$9</f>
       </c>
-      <c r="D18" s="5" t="str">
-        <f>"1. " &amp; data!$B$18</f>
-      </c>
     </row>
     <row r="19" ht="17" customHeight="true">
       <c r="B19" s="5" t="str">
         <f>"2. " &amp; data!$B$10</f>
       </c>
-      <c r="D19" s="5" t="str">
-        <f>"2. " &amp; data!$B$19</f>
-      </c>
     </row>
     <row r="20" ht="17" customHeight="true">
       <c r="B20" s="5" t="str">
         <f>"3. " &amp; data!$B$11</f>
       </c>
-      <c r="D20" s="5" t="str">
+    </row>
+    <row r="21" ht="17" customHeight="true"/>
+    <row r="22" ht="17" customHeight="true"/>
+    <row r="23" ht="17" customHeight="true">
+      <c r="B23" s="6" t="str">
+        <f>data!$A$14</f>
+      </c>
+    </row>
+    <row r="24" ht="17" customHeight="true">
+      <c r="B24" s="5" t="str">
+        <f>"1. " &amp; data!$B$12</f>
+      </c>
+    </row>
+    <row r="25" ht="17" customHeight="true">
+      <c r="B25" s="5" t="str">
+        <f>"2. " &amp; data!$B$13</f>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="true">
+      <c r="B26" s="5" t="str">
+        <f>"3. " &amp; data!$B$14</f>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="true"/>
+    <row r="28" ht="17" customHeight="true"/>
+    <row r="29" ht="17" customHeight="true">
+      <c r="B29" s="6" t="str">
+        <f>data!$A$17</f>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="true">
+      <c r="B30" s="5" t="str">
+        <f>"1. " &amp; data!$B$15</f>
+      </c>
+    </row>
+    <row r="31" ht="17" customHeight="true">
+      <c r="B31" s="5" t="str">
+        <f>"2. " &amp; data!$B$16</f>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="true">
+      <c r="B32" s="5" t="str">
+        <f>"3. " &amp; data!$B$17</f>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="true"/>
+    <row r="34" ht="17" customHeight="true"/>
+    <row r="35" ht="17" customHeight="true">
+      <c r="B35" s="6" t="str">
+        <f>data!$A$20</f>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="true">
+      <c r="B36" s="5" t="str">
+        <f>"1. " &amp; data!$B$18</f>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="true">
+      <c r="B37" s="5" t="str">
+        <f>"2. " &amp; data!$B$19</f>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="true">
+      <c r="B38" s="5" t="str">
         <f>"3. " &amp; data!$B$20</f>
       </c>
     </row>
@@ -3468,611 +3540,611 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="I1" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="I1" s="20" t="s">
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="str">
+        <f>data!$A$5</f>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="I2" s="18" t="str">
+        <f>data!$A$17</f>
+      </c>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
+      <c r="D3" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="str">
-        <f>data!$A$5</f>
-      </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="I4" s="20" t="str">
-        <f>data!$A$17</f>
-      </c>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
+      <c r="A4" s="19" t="str">
+        <f>data!$B$4</f>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19" t="str">
+        <f>data!$B$3</f>
+      </c>
+      <c r="I4" s="19" t="str">
+        <f>data!$B$16</f>
+      </c>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19" t="str">
+        <f>data!$B$15</f>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="G5" s="23" t="s">
+      <c r="A5" s="19" t="str">
+        <f>data!$B$5</f>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19" t="str">
+        <f>data!$B$3</f>
+      </c>
+      <c r="I5" s="19" t="str">
+        <f>data!$B$17</f>
+      </c>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19" t="str">
+        <f>data!$B$15</f>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="str">
+        <f>data!$B$5</f>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19" t="str">
+        <f>data!$B$4</f>
+      </c>
+      <c r="I6" s="19" t="str">
+        <f>data!$B$17</f>
+      </c>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19" t="str">
+        <f>data!$B$16</f>
+      </c>
+    </row>
+    <row r="8">
+      <c r="F8" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="I5" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="L5" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="O5" s="23" t="s">
+      <c r="G8" s="20"/>
+      <c r="N8" s="7" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="21" t="str">
-        <f>data!$B$4</f>
-      </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21" t="str">
-        <f>data!$B$3</f>
-      </c>
-      <c r="I6" s="21" t="str">
-        <f>data!$B$16</f>
-      </c>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="21" t="str">
-        <f>data!$B$15</f>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="21" t="str">
-        <f>data!$B$5</f>
-      </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21" t="str">
-        <f>data!$B$3</f>
-      </c>
-      <c r="I7" s="21" t="str">
-        <f>data!$B$17</f>
-      </c>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="21"/>
-      <c r="O7" s="21" t="str">
-        <f>data!$B$15</f>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="21" t="str">
-        <f>data!$B$5</f>
-      </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21" t="str">
-        <f>data!$B$4</f>
-      </c>
-      <c r="I8" s="21" t="str">
-        <f>data!$B$17</f>
-      </c>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="21"/>
-      <c r="O8" s="21" t="str">
-        <f>data!$B$16</f>
-      </c>
+      <c r="O8" s="20"/>
+    </row>
+    <row r="9">
+      <c r="F9" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G9" s="20"/>
+      <c r="N9" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="O9" s="20"/>
     </row>
     <row r="10">
       <c r="F10" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="G10" s="20"/>
+      <c r="N10" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="O10" s="20"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="str">
+        <f>data!$A$8</f>
+      </c>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="I12" s="18" t="str">
+        <f>data!$A$20</f>
+      </c>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="O13" s="21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="str">
+        <f>data!$B$7</f>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19" t="str">
+        <f>data!$B$6</f>
+      </c>
+      <c r="I14" s="19" t="str">
+        <f>data!$B$19</f>
+      </c>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19" t="str">
+        <f>data!$B$18</f>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="str">
+        <f>data!$B$8</f>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19" t="str">
+        <f>data!$B$6</f>
+      </c>
+      <c r="I15" s="19" t="str">
+        <f>data!$B$20</f>
+      </c>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19" t="str">
+        <f>data!$B$18</f>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="str">
+        <f>data!$B$8</f>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19" t="str">
+        <f>data!$B$7</f>
+      </c>
+      <c r="I16" s="19" t="str">
+        <f>data!$B$20</f>
+      </c>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19" t="str">
+        <f>data!$B$19</f>
+      </c>
+    </row>
+    <row r="18">
+      <c r="F18" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G18" s="20"/>
+      <c r="N18" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="O18" s="20"/>
+    </row>
+    <row r="19">
+      <c r="F19" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="G10" s="22"/>
-      <c r="N10" s="7" t="s">
+      <c r="G19" s="20"/>
+      <c r="N19" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="O10" s="22"/>
-    </row>
-    <row r="11">
-      <c r="F11" s="7" t="s">
+      <c r="O19" s="20"/>
+    </row>
+    <row r="20">
+      <c r="F20" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="G11" s="22"/>
-      <c r="N11" s="7" t="s">
+      <c r="G20" s="20"/>
+      <c r="N20" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="O11" s="22"/>
-    </row>
-    <row r="12">
-      <c r="F12" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="G12" s="22"/>
-      <c r="N12" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="O12" s="22"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="str">
-        <f>data!$A$8</f>
-      </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="I15" s="20" t="str">
-        <f>data!$A$20</f>
-      </c>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="s">
+      <c r="O20" s="20"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="str">
+        <f>data!$A$11</f>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="I22" s="18" t="str">
+        <f>data!$A$23</f>
+      </c>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="G23" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G16" s="23" t="s">
+      <c r="I23" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="L23" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="O23" s="21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="str">
+        <f>data!$B$10</f>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19" t="str">
+        <f>data!$B$9</f>
+      </c>
+      <c r="I24" s="19" t="str">
+        <f>data!$B$22</f>
+      </c>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19" t="str">
+        <f>data!$B$21</f>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="str">
+        <f>data!$B$11</f>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19" t="str">
+        <f>data!$B$9</f>
+      </c>
+      <c r="I25" s="19" t="str">
+        <f>data!$B$23</f>
+      </c>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19" t="str">
+        <f>data!$B$21</f>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="str">
+        <f>data!$B$11</f>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19" t="str">
+        <f>data!$B$10</f>
+      </c>
+      <c r="I26" s="19" t="str">
+        <f>data!$B$23</f>
+      </c>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19" t="str">
+        <f>data!$B$22</f>
+      </c>
+    </row>
+    <row r="28">
+      <c r="F28" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="I16" s="24" t="s">
+      <c r="G28" s="20"/>
+      <c r="N28" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="O28" s="20"/>
+    </row>
+    <row r="29">
+      <c r="F29" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G29" s="20"/>
+      <c r="N29" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="O29" s="20"/>
+    </row>
+    <row r="30">
+      <c r="F30" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="G30" s="20"/>
+      <c r="N30" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="O30" s="20"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="str">
+        <f>data!$A$14</f>
+      </c>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="I32" s="18" t="str">
+        <f>data!$A$26</f>
+      </c>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="L16" s="21" t="s">
+      <c r="G33" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="O16" s="23" t="s">
+      <c r="I33" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="L33" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="O33" s="21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="str">
+        <f>data!$B$13</f>
+      </c>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19" t="str">
+        <f>data!$B$12</f>
+      </c>
+      <c r="I34" s="19" t="str">
+        <f>data!$B$25</f>
+      </c>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
+      <c r="O34" s="19" t="str">
+        <f>data!$B$24</f>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="str">
+        <f>data!$B$14</f>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19" t="str">
+        <f>data!$B$12</f>
+      </c>
+      <c r="I35" s="19" t="str">
+        <f>data!$B$26</f>
+      </c>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="19"/>
+      <c r="O35" s="19" t="str">
+        <f>data!$B$24</f>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="str">
+        <f>data!$B$14</f>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19" t="str">
+        <f>data!$B$13</f>
+      </c>
+      <c r="I36" s="19" t="str">
+        <f>data!$B$26</f>
+      </c>
+      <c r="J36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+      <c r="M36" s="19"/>
+      <c r="N36" s="19"/>
+      <c r="O36" s="19" t="str">
+        <f>data!$B$25</f>
+      </c>
+    </row>
+    <row r="38">
+      <c r="F38" s="7" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="str">
-        <f>data!$B$7</f>
-      </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21" t="str">
-        <f>data!$B$6</f>
-      </c>
-      <c r="I17" s="21" t="str">
-        <f>data!$B$19</f>
-      </c>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
-      <c r="N17" s="21"/>
-      <c r="O17" s="21" t="str">
-        <f>data!$B$18</f>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="21" t="str">
-        <f>data!$B$8</f>
-      </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21" t="str">
-        <f>data!$B$6</f>
-      </c>
-      <c r="I18" s="21" t="str">
-        <f>data!$B$20</f>
-      </c>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21" t="str">
-        <f>data!$B$18</f>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="str">
-        <f>data!$B$8</f>
-      </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21" t="str">
-        <f>data!$B$7</f>
-      </c>
-      <c r="I19" s="21" t="str">
-        <f>data!$B$20</f>
-      </c>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="21"/>
-      <c r="N19" s="21"/>
-      <c r="O19" s="21" t="str">
-        <f>data!$B$19</f>
-      </c>
-    </row>
-    <row r="21">
-      <c r="F21" s="7" t="s">
+      <c r="G38" s="20"/>
+      <c r="N38" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="O38" s="20"/>
+    </row>
+    <row r="39">
+      <c r="F39" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="G21" s="22"/>
-      <c r="N21" s="7" t="s">
+      <c r="G39" s="20"/>
+      <c r="N39" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="O21" s="22"/>
-    </row>
-    <row r="22">
-      <c r="F22" s="7" t="s">
+      <c r="O39" s="20"/>
+    </row>
+    <row r="40">
+      <c r="F40" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="G22" s="22"/>
-      <c r="N22" s="7" t="s">
+      <c r="G40" s="20"/>
+      <c r="N40" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="O22" s="22"/>
-    </row>
-    <row r="23">
-      <c r="F23" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="G23" s="22"/>
-      <c r="N23" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="O23" s="22"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="20" t="str">
-        <f>data!$A$11</f>
-      </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="I26" s="20" t="str">
-        <f>data!$A$23</f>
-      </c>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="G27" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="I27" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="L27" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="O27" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="21" t="str">
-        <f>data!$B$10</f>
-      </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21" t="str">
-        <f>data!$B$9</f>
-      </c>
-      <c r="I28" s="21" t="str">
-        <f>data!$B$22</f>
-      </c>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
-      <c r="O28" s="21" t="str">
-        <f>data!$B$21</f>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="21" t="str">
-        <f>data!$B$11</f>
-      </c>
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21" t="str">
-        <f>data!$B$9</f>
-      </c>
-      <c r="I29" s="21" t="str">
-        <f>data!$B$23</f>
-      </c>
-      <c r="J29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="21"/>
-      <c r="N29" s="21"/>
-      <c r="O29" s="21" t="str">
-        <f>data!$B$21</f>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="21" t="str">
-        <f>data!$B$11</f>
-      </c>
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21" t="str">
-        <f>data!$B$10</f>
-      </c>
-      <c r="I30" s="21" t="str">
-        <f>data!$B$23</f>
-      </c>
-      <c r="J30" s="21"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
-      <c r="O30" s="21" t="str">
-        <f>data!$B$22</f>
-      </c>
-    </row>
-    <row r="32">
-      <c r="F32" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G32" s="22"/>
-      <c r="N32" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="O32" s="22"/>
-    </row>
-    <row r="33">
-      <c r="F33" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="G33" s="22"/>
-      <c r="N33" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="O33" s="22"/>
-    </row>
-    <row r="34">
-      <c r="F34" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="G34" s="22"/>
-      <c r="N34" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="O34" s="22"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="20" t="str">
-        <f>data!$A$14</f>
-      </c>
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="I37" s="20" t="str">
-        <f>data!$A$26</f>
-      </c>
-      <c r="J37" s="20"/>
-      <c r="K37" s="20"/>
-      <c r="L37" s="20"/>
-      <c r="M37" s="20"/>
-      <c r="N37" s="20"/>
-      <c r="O37" s="20"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D38" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="G38" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="I38" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="L38" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="O38" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="21" t="str">
-        <f>data!$B$13</f>
-      </c>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21" t="str">
-        <f>data!$B$12</f>
-      </c>
-      <c r="I39" s="21" t="str">
-        <f>data!$B$25</f>
-      </c>
-      <c r="J39" s="21"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
-      <c r="M39" s="21"/>
-      <c r="N39" s="21"/>
-      <c r="O39" s="21" t="str">
-        <f>data!$B$24</f>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="21" t="str">
-        <f>data!$B$14</f>
-      </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="21" t="str">
-        <f>data!$B$12</f>
-      </c>
-      <c r="I40" s="21" t="str">
-        <f>data!$B$26</f>
-      </c>
-      <c r="J40" s="21"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
-      <c r="M40" s="21"/>
-      <c r="N40" s="21"/>
-      <c r="O40" s="21" t="str">
-        <f>data!$B$24</f>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="21" t="str">
-        <f>data!$B$14</f>
-      </c>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21" t="str">
-        <f>data!$B$13</f>
-      </c>
-      <c r="I41" s="21" t="str">
-        <f>data!$B$26</f>
-      </c>
-      <c r="J41" s="21"/>
-      <c r="K41" s="21"/>
-      <c r="L41" s="21"/>
-      <c r="M41" s="21"/>
-      <c r="N41" s="21"/>
-      <c r="O41" s="21" t="str">
-        <f>data!$B$25</f>
-      </c>
-    </row>
-    <row r="43">
-      <c r="F43" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G43" s="22"/>
-      <c r="N43" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="O43" s="22"/>
-    </row>
-    <row r="44">
-      <c r="F44" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="G44" s="22"/>
-      <c r="N44" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="O44" s="22"/>
-    </row>
-    <row r="45">
-      <c r="F45" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="G45" s="22"/>
-      <c r="N45" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="O45" s="22"/>
+      <c r="O40" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:O1"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="I4:O4"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="I15:O15"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="I26:O26"/>
-    <mergeCell ref="A37:G37"/>
-    <mergeCell ref="I37:O37"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="I2:O2"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="I12:O12"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="I22:O22"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="I32:O32"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" fitToWidth="2" orientation="portrait" pageOrder="downThenOver" paperSize="9"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="41" max="16383" man="true"/>
+    <brk id="21" max="16383" man="true"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="8" max="1048575" man="true"/>
@@ -4082,6 +4154,9 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3D4E4C4-15C1-724B-94C9-DD9C94F4D3CF}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
@@ -4100,740 +4175,691 @@
     <col max="16384" min="17" style="7" width="10.83203125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="17" thickBot="true">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
+    <row r="1" spans="1:15">
+      <c r="A1" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="I2" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="O3" s="21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="str">
+        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G19)</f>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19" t="str">
+        <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G8)</f>
+      </c>
+      <c r="I4" s="19" t="str">
+        <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G9)</f>
+      </c>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19" t="str">
+        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G18)</f>
+      </c>
+    </row>
+    <row r="6">
+      <c r="F6" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="I3" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="L4" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="O4" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="21" t="str">
-        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G22)</f>
-      </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21" t="str">
-        <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G10)</f>
-      </c>
-      <c r="I5" s="21" t="str">
-        <f>CONCATENATE("Pool D.2 ",'Pool Matches'!G44)</f>
-      </c>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="21"/>
-      <c r="O5" s="21" t="str">
-        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G32)</f>
-      </c>
+      <c r="G6" s="20"/>
+      <c r="N6" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="O6" s="20"/>
     </row>
     <row r="7">
       <c r="F7" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G7" s="22"/>
+      <c r="G7" s="20"/>
       <c r="N7" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O7" s="22"/>
-    </row>
-    <row r="8">
-      <c r="F8" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="G8" s="22"/>
-      <c r="N8" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="O8" s="22"/>
+      <c r="O7" s="20"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="I10" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="I11" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
+      <c r="A11" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="I11" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="O11" s="21" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="G12" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="L12" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="O12" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="str">
-        <f>CONCATENATE("Pool F.2 ",'Pool Matches'!O22)</f>
-      </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21" t="str">
-        <f>CONCATENATE("Pool E.1 ",'Pool Matches'!O10)</f>
-      </c>
-      <c r="I13" s="21" t="str">
-        <f>CONCATENATE("Pool H.2 ",'Pool Matches'!O44)</f>
-      </c>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21" t="str">
-        <f>CONCATENATE("Pool G.1 ",'Pool Matches'!O32)</f>
-      </c>
+      <c r="A12" s="19" t="str">
+        <f>CONCATENATE("Pool D.2 ",'Pool Matches'!G39)</f>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19" t="str">
+        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G28)</f>
+      </c>
+      <c r="I12" s="19" t="str">
+        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G29)</f>
+      </c>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19" t="str">
+        <f>CONCATENATE("Pool D.1 ",'Pool Matches'!G38)</f>
+      </c>
+    </row>
+    <row r="14">
+      <c r="F14" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G14" s="20"/>
+      <c r="N14" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="O14" s="20"/>
     </row>
     <row r="15">
       <c r="F15" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G15" s="22"/>
+      <c r="G15" s="20"/>
       <c r="N15" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O15" s="22"/>
-    </row>
-    <row r="16">
-      <c r="F16" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="G16" s="22"/>
-      <c r="N16" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="O16" s="22"/>
+      <c r="O15" s="20"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="I18" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="I19" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
+      <c r="A19" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="I19" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="O19" s="21" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="G20" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="I20" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="L20" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="O20" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="str">
-        <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G11)</f>
-      </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21" t="str">
-        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G21)</f>
-      </c>
-      <c r="I21" s="21" t="str">
-        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G33)</f>
-      </c>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="21"/>
-      <c r="N21" s="21"/>
-      <c r="O21" s="21" t="str">
-        <f>CONCATENATE("Pool D.1 ",'Pool Matches'!G43)</f>
-      </c>
+      <c r="A20" s="19" t="str">
+        <f>CONCATENATE("Pool F.2 ",'Pool Matches'!O19)</f>
+      </c>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19" t="str">
+        <f>CONCATENATE("Pool E.1 ",'Pool Matches'!O8)</f>
+      </c>
+      <c r="I20" s="19" t="str">
+        <f>CONCATENATE("Pool E.2 ",'Pool Matches'!O9)</f>
+      </c>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19" t="str">
+        <f>CONCATENATE("Pool F.1 ",'Pool Matches'!O18)</f>
+      </c>
+    </row>
+    <row r="22">
+      <c r="F22" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G22" s="20"/>
+      <c r="N22" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="O22" s="20"/>
     </row>
     <row r="23">
       <c r="F23" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G23" s="22"/>
+      <c r="G23" s="20"/>
       <c r="N23" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O23" s="22"/>
-    </row>
-    <row r="24">
-      <c r="F24" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="G24" s="22"/>
-      <c r="N24" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="O24" s="22"/>
+      <c r="O23" s="20"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="I26" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="I27" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="20"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="20"/>
+      <c r="A27" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="I27" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="L27" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="O27" s="21" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="G28" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="I28" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="L28" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="O28" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="21" t="str">
-        <f>CONCATENATE("Pool E.2 ",'Pool Matches'!O11)</f>
-      </c>
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21" t="str">
-        <f>CONCATENATE("Pool F.1 ",'Pool Matches'!O21)</f>
-      </c>
-      <c r="I29" s="21" t="str">
-        <f>CONCATENATE("Pool G.2 ",'Pool Matches'!O33)</f>
-      </c>
-      <c r="J29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="21"/>
-      <c r="N29" s="21"/>
-      <c r="O29" s="21" t="str">
-        <f>CONCATENATE("Pool H.1 ",'Pool Matches'!O43)</f>
-      </c>
+      <c r="A28" s="19" t="str">
+        <f>CONCATENATE("Pool H.2 ",'Pool Matches'!O39)</f>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19" t="str">
+        <f>CONCATENATE("Pool G.1 ",'Pool Matches'!O28)</f>
+      </c>
+      <c r="I28" s="19" t="str">
+        <f>CONCATENATE("Pool G.2 ",'Pool Matches'!O29)</f>
+      </c>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19" t="str">
+        <f>CONCATENATE("Pool H.1 ",'Pool Matches'!O38)</f>
+      </c>
+    </row>
+    <row r="30">
+      <c r="F30" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G30" s="20"/>
+      <c r="N30" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="O30" s="20"/>
     </row>
     <row r="31">
       <c r="F31" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G31" s="22"/>
+      <c r="G31" s="20"/>
       <c r="N31" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O31" s="22"/>
-    </row>
-    <row r="32">
-      <c r="F32" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="G32" s="22"/>
-      <c r="N32" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="O32" s="22"/>
+      <c r="O31" s="20"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="I39" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="18"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="18"/>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="B40" s="20"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="20"/>
-      <c r="K40" s="20"/>
-      <c r="L40" s="20"/>
-      <c r="M40" s="20"/>
-      <c r="N40" s="20"/>
-      <c r="O40" s="20"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="20" t="s">
+      <c r="A40" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="G40" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="I40" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="L40" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="O40" s="21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="str">
+        <f>CONCATENATE("M 2 ",'Elimination Matches'!G14)</f>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19" t="str">
+        <f>CONCATENATE("M 1 ",'Elimination Matches'!G6)</f>
+      </c>
+      <c r="I41" s="19" t="str">
+        <f>CONCATENATE("M 6 ",'Elimination Matches'!O14)</f>
+      </c>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="19"/>
+      <c r="O41" s="19" t="str">
+        <f>CONCATENATE("M 5 ",'Elimination Matches'!O6)</f>
+      </c>
+    </row>
+    <row r="43">
+      <c r="F43" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G43" s="20"/>
+      <c r="N43" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="O43" s="20"/>
+    </row>
+    <row r="44">
+      <c r="F44" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="G44" s="20"/>
+      <c r="N44" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="O44" s="20"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="B42" s="20"/>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
-      <c r="I42" s="20" t="s">
+      <c r="B47" s="18"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
+      <c r="I47" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="J42" s="20"/>
-      <c r="K42" s="20"/>
-      <c r="L42" s="20"/>
-      <c r="M42" s="20"/>
-      <c r="N42" s="20"/>
-      <c r="O42" s="20"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="24" t="s">
+      <c r="J47" s="18"/>
+      <c r="K47" s="18"/>
+      <c r="L47" s="18"/>
+      <c r="M47" s="18"/>
+      <c r="N47" s="18"/>
+      <c r="O47" s="18"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="D43" s="21" t="s">
+      <c r="G48" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G43" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="I43" s="24" t="s">
+      <c r="I48" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="L48" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="L43" s="21" t="s">
+      <c r="O48" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="O43" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="21" t="str">
-        <f>CONCATENATE("M 2 ",'Elimination Matches'!O7)</f>
-      </c>
-      <c r="B44" s="21"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21"/>
-      <c r="G44" s="21" t="str">
-        <f>CONCATENATE("M 1 ",'Elimination Matches'!G7)</f>
-      </c>
-      <c r="I44" s="21" t="str">
-        <f>CONCATENATE("M 4 ",'Elimination Matches'!O15)</f>
-      </c>
-      <c r="J44" s="21"/>
-      <c r="K44" s="21"/>
-      <c r="L44" s="21"/>
-      <c r="M44" s="21"/>
-      <c r="N44" s="21"/>
-      <c r="O44" s="21" t="str">
-        <f>CONCATENATE("M 3 ",'Elimination Matches'!G15)</f>
-      </c>
-    </row>
-    <row r="46">
-      <c r="F46" s="7" t="s">
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="str">
+        <f>CONCATENATE("M 4 ",'Elimination Matches'!G30)</f>
+      </c>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19" t="str">
+        <f>CONCATENATE("M 3 ",'Elimination Matches'!G22)</f>
+      </c>
+      <c r="I49" s="19" t="str">
+        <f>CONCATENATE("M 8 ",'Elimination Matches'!O30)</f>
+      </c>
+      <c r="J49" s="19"/>
+      <c r="K49" s="19"/>
+      <c r="L49" s="19"/>
+      <c r="M49" s="19"/>
+      <c r="N49" s="19"/>
+      <c r="O49" s="19" t="str">
+        <f>CONCATENATE("M 7 ",'Elimination Matches'!O22)</f>
+      </c>
+    </row>
+    <row r="51">
+      <c r="F51" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G51" s="20"/>
+      <c r="N51" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="O51" s="20"/>
+    </row>
+    <row r="52">
+      <c r="F52" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G46" s="22"/>
-      <c r="N46" s="7" t="s">
+      <c r="G52" s="20"/>
+      <c r="N52" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O46" s="22"/>
-    </row>
-    <row r="47">
-      <c r="F47" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="G47" s="22"/>
-      <c r="N47" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="O47" s="22"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="20" t="s">
+      <c r="O52" s="20"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="B50" s="20"/>
-      <c r="C50" s="20"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="20"/>
-      <c r="I50" s="20" t="s">
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="I60" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="J50" s="20"/>
-      <c r="K50" s="20"/>
-      <c r="L50" s="20"/>
-      <c r="M50" s="20"/>
-      <c r="N50" s="20"/>
-      <c r="O50" s="20"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="24" t="s">
+      <c r="J60" s="18"/>
+      <c r="K60" s="18"/>
+      <c r="L60" s="18"/>
+      <c r="M60" s="18"/>
+      <c r="N60" s="18"/>
+      <c r="O60" s="18"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D61" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="D51" s="21" t="s">
+      <c r="G61" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G51" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="I51" s="24" t="s">
+      <c r="I61" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="L61" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="L51" s="21" t="s">
+      <c r="O61" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="O51" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="21" t="str">
-        <f>CONCATENATE("M 6 ",'Elimination Matches'!O23)</f>
-      </c>
-      <c r="B52" s="21"/>
-      <c r="C52" s="21"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
-      <c r="G52" s="21" t="str">
-        <f>CONCATENATE("M 5 ",'Elimination Matches'!G23)</f>
-      </c>
-      <c r="I52" s="21" t="str">
-        <f>CONCATENATE("M 8 ",'Elimination Matches'!O31)</f>
-      </c>
-      <c r="J52" s="21"/>
-      <c r="K52" s="21"/>
-      <c r="L52" s="21"/>
-      <c r="M52" s="21"/>
-      <c r="N52" s="21"/>
-      <c r="O52" s="21" t="str">
-        <f>CONCATENATE("M 7 ",'Elimination Matches'!G31)</f>
-      </c>
-    </row>
-    <row r="54">
-      <c r="F54" s="7" t="s">
+    </row>
+    <row r="62">
+      <c r="A62" s="19" t="str">
+        <f>CONCATENATE("M 10 ",'Elimination Matches'!G51)</f>
+      </c>
+      <c r="B62" s="19"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="19"/>
+      <c r="F62" s="19"/>
+      <c r="G62" s="19" t="str">
+        <f>CONCATENATE("M 9 ",'Elimination Matches'!G43)</f>
+      </c>
+      <c r="I62" s="19" t="str">
+        <f>CONCATENATE("M 12 ",'Elimination Matches'!O51)</f>
+      </c>
+      <c r="J62" s="19"/>
+      <c r="K62" s="19"/>
+      <c r="L62" s="19"/>
+      <c r="M62" s="19"/>
+      <c r="N62" s="19"/>
+      <c r="O62" s="19" t="str">
+        <f>CONCATENATE("M 11 ",'Elimination Matches'!O43)</f>
+      </c>
+    </row>
+    <row r="64">
+      <c r="F64" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G64" s="20"/>
+      <c r="N64" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="O64" s="20"/>
+    </row>
+    <row r="65">
+      <c r="F65" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G54" s="22"/>
-      <c r="N54" s="7" t="s">
+      <c r="G65" s="20"/>
+      <c r="N65" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="O54" s="22"/>
-    </row>
-    <row r="55">
-      <c r="F55" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="G55" s="22"/>
-      <c r="N55" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="O55" s="22"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="20" t="s">
+      <c r="O65" s="20"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="B63" s="20"/>
-      <c r="C63" s="20"/>
-      <c r="D63" s="20"/>
-      <c r="E63" s="20"/>
-      <c r="F63" s="20"/>
-      <c r="G63" s="20"/>
-      <c r="H63" s="20"/>
-      <c r="I63" s="20"/>
-      <c r="J63" s="20"/>
-      <c r="K63" s="20"/>
-      <c r="L63" s="20"/>
-      <c r="M63" s="20"/>
-      <c r="N63" s="20"/>
-      <c r="O63" s="20"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="B65" s="20"/>
-      <c r="C65" s="20"/>
-      <c r="D65" s="20"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="20"/>
-      <c r="G65" s="20"/>
-      <c r="I65" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="J65" s="20"/>
-      <c r="K65" s="20"/>
-      <c r="L65" s="20"/>
-      <c r="M65" s="20"/>
-      <c r="N65" s="20"/>
-      <c r="O65" s="20"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="24" t="s">
+      <c r="B73" s="18"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="18"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D74" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="D66" s="21" t="s">
+      <c r="G74" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G66" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="I66" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="L66" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="O66" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="21" t="str">
-        <f>CONCATENATE("M 10 ",'Elimination Matches'!O46)</f>
-      </c>
-      <c r="B67" s="21"/>
-      <c r="C67" s="21"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="21"/>
-      <c r="G67" s="21" t="str">
-        <f>CONCATENATE("M 9 ",'Elimination Matches'!G46)</f>
-      </c>
-      <c r="I67" s="21" t="str">
-        <f>CONCATENATE("M 12 ",'Elimination Matches'!O54)</f>
-      </c>
-      <c r="J67" s="21"/>
-      <c r="K67" s="21"/>
-      <c r="L67" s="21"/>
-      <c r="M67" s="21"/>
-      <c r="N67" s="21"/>
-      <c r="O67" s="21" t="str">
-        <f>CONCATENATE("M 11 ",'Elimination Matches'!G54)</f>
-      </c>
-    </row>
-    <row r="69">
-      <c r="F69" s="7" t="s">
+    </row>
+    <row r="75">
+      <c r="A75" s="19" t="str">
+        <f>CONCATENATE("M 14 ",'Elimination Matches'!O64)</f>
+      </c>
+      <c r="B75" s="19"/>
+      <c r="C75" s="19"/>
+      <c r="D75" s="19"/>
+      <c r="E75" s="19"/>
+      <c r="F75" s="19"/>
+      <c r="G75" s="19" t="str">
+        <f>CONCATENATE("M 13 ",'Elimination Matches'!G64)</f>
+      </c>
+    </row>
+    <row r="77">
+      <c r="F77" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G77" s="20"/>
+    </row>
+    <row r="78">
+      <c r="F78" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G69" s="22"/>
-      <c r="N69" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="O69" s="22"/>
-    </row>
-    <row r="70">
-      <c r="F70" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="G70" s="22"/>
-      <c r="N70" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="O70" s="22"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="B78" s="20"/>
-      <c r="C78" s="20"/>
-      <c r="D78" s="20"/>
-      <c r="E78" s="20"/>
-      <c r="F78" s="20"/>
       <c r="G78" s="20"/>
-      <c r="H78" s="20"/>
-      <c r="I78" s="20"/>
-      <c r="J78" s="20"/>
-      <c r="K78" s="20"/>
-      <c r="L78" s="20"/>
-      <c r="M78" s="20"/>
-      <c r="N78" s="20"/>
-      <c r="O78" s="20"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="B80" s="20"/>
-      <c r="C80" s="20"/>
-      <c r="D80" s="20"/>
-      <c r="E80" s="20"/>
-      <c r="F80" s="20"/>
-      <c r="G80" s="20"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D81" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="G81" s="23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="21" t="str">
-        <f>CONCATENATE("M 14 ",'Elimination Matches'!O69)</f>
-      </c>
-      <c r="B82" s="21"/>
-      <c r="C82" s="21"/>
-      <c r="D82" s="21"/>
-      <c r="E82" s="21"/>
-      <c r="F82" s="21"/>
-      <c r="G82" s="21" t="str">
-        <f>CONCATENATE("M 13 ",'Elimination Matches'!G69)</f>
-      </c>
-    </row>
-    <row r="84">
-      <c r="F84" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="G84" s="22"/>
-    </row>
-    <row r="85">
-      <c r="F85" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="G85" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="I3:O3"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="I11:O11"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="I19:O19"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="I27:O27"/>
-    <mergeCell ref="A40:O40"/>
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="I42:O42"/>
-    <mergeCell ref="A50:G50"/>
-    <mergeCell ref="I50:O50"/>
-    <mergeCell ref="A63:O63"/>
-    <mergeCell ref="A65:G65"/>
-    <mergeCell ref="I65:O65"/>
-    <mergeCell ref="A78:O78"/>
-    <mergeCell ref="A80:G80"/>
+  <mergeCells count="17">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="I2:O2"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="I10:O10"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="I18:O18"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="I26:O26"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="I39:O39"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="I47:O47"/>
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="I60:O60"/>
+    <mergeCell ref="A73:G73"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" fitToWidth="2" orientation="portrait" pageOrder="downThenOver" paperSize="9"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="38" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="8" max="1048575" man="true"/>
+  </colBreaks>
 </worksheet>
 </file>
 
@@ -4851,340 +4877,340 @@
   </cols>
   <sheetData>
     <row r="1" ht="110" customHeight="true">
-      <c r="A1" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="34" t="str">
+      <c r="A1" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="32" t="str">
         <f>data!D3</f>
       </c>
     </row>
     <row r="2" ht="115" customHeight="true">
-      <c r="A2" s="33">
+      <c r="A2" s="31">
         <v>1</v>
       </c>
-      <c r="B2" s="34"/>
+      <c r="B2" s="32"/>
     </row>
     <row r="3" ht="110" customHeight="true">
-      <c r="A3" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="34" t="str">
+      <c r="A3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="32" t="str">
         <f>data!D4</f>
       </c>
     </row>
     <row r="4" ht="115" customHeight="true">
-      <c r="A4" s="33">
+      <c r="A4" s="31">
         <v>2</v>
       </c>
-      <c r="B4" s="34"/>
+      <c r="B4" s="32"/>
     </row>
     <row r="5" ht="110" customHeight="true">
-      <c r="A5" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="34" t="str">
+      <c r="A5" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="32" t="str">
         <f>data!D5</f>
       </c>
     </row>
     <row r="6" ht="115" customHeight="true">
-      <c r="A6" s="33">
+      <c r="A6" s="31">
         <v>3</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="32"/>
     </row>
     <row r="7" ht="110" customHeight="true">
-      <c r="A7" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="34" t="str">
+      <c r="A7" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="32" t="str">
         <f>data!D6</f>
       </c>
     </row>
     <row r="8" ht="115" customHeight="true">
-      <c r="A8" s="33">
+      <c r="A8" s="31">
         <v>1</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="32"/>
     </row>
     <row r="9" ht="110" customHeight="true">
-      <c r="A9" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="34" t="str">
+      <c r="A9" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="32" t="str">
         <f>data!D7</f>
       </c>
     </row>
     <row r="10" ht="115" customHeight="true">
-      <c r="A10" s="33">
+      <c r="A10" s="31">
         <v>2</v>
       </c>
-      <c r="B10" s="34"/>
+      <c r="B10" s="32"/>
     </row>
     <row r="11" ht="110" customHeight="true">
-      <c r="A11" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="34" t="str">
+      <c r="A11" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="32" t="str">
         <f>data!D8</f>
       </c>
     </row>
     <row r="12" ht="115" customHeight="true">
-      <c r="A12" s="33">
+      <c r="A12" s="31">
         <v>3</v>
       </c>
-      <c r="B12" s="34"/>
+      <c r="B12" s="32"/>
     </row>
     <row r="13" ht="110" customHeight="true">
-      <c r="A13" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="34" t="str">
+      <c r="A13" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="32" t="str">
         <f>data!D9</f>
       </c>
     </row>
     <row r="14" ht="115" customHeight="true">
-      <c r="A14" s="33">
+      <c r="A14" s="31">
         <v>1</v>
       </c>
-      <c r="B14" s="34"/>
+      <c r="B14" s="32"/>
     </row>
     <row r="15" ht="110" customHeight="true">
-      <c r="A15" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="34" t="str">
+      <c r="A15" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="32" t="str">
         <f>data!D10</f>
       </c>
     </row>
     <row r="16" ht="115" customHeight="true">
-      <c r="A16" s="33">
+      <c r="A16" s="31">
         <v>2</v>
       </c>
-      <c r="B16" s="34"/>
+      <c r="B16" s="32"/>
     </row>
     <row r="17" ht="110" customHeight="true">
-      <c r="A17" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="34" t="str">
+      <c r="A17" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="32" t="str">
         <f>data!D11</f>
       </c>
     </row>
     <row r="18" ht="115" customHeight="true">
-      <c r="A18" s="33">
+      <c r="A18" s="31">
         <v>3</v>
       </c>
-      <c r="B18" s="34"/>
+      <c r="B18" s="32"/>
     </row>
     <row r="19" ht="110" customHeight="true">
-      <c r="A19" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="34" t="str">
+      <c r="A19" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="32" t="str">
         <f>data!D12</f>
       </c>
     </row>
     <row r="20" ht="115" customHeight="true">
-      <c r="A20" s="33">
+      <c r="A20" s="31">
         <v>1</v>
       </c>
-      <c r="B20" s="34"/>
+      <c r="B20" s="32"/>
     </row>
     <row r="21" ht="110" customHeight="true">
-      <c r="A21" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="34" t="str">
+      <c r="A21" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="32" t="str">
         <f>data!D13</f>
       </c>
     </row>
     <row r="22" ht="115" customHeight="true">
-      <c r="A22" s="33">
+      <c r="A22" s="31">
         <v>2</v>
       </c>
-      <c r="B22" s="34"/>
+      <c r="B22" s="32"/>
     </row>
     <row r="23" ht="110" customHeight="true">
-      <c r="A23" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="34" t="str">
+      <c r="A23" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="32" t="str">
         <f>data!D14</f>
       </c>
     </row>
     <row r="24" ht="115" customHeight="true">
-      <c r="A24" s="33">
+      <c r="A24" s="31">
         <v>3</v>
       </c>
-      <c r="B24" s="34"/>
+      <c r="B24" s="32"/>
     </row>
     <row r="25" ht="110" customHeight="true">
-      <c r="A25" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="34" t="str">
+      <c r="A25" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="32" t="str">
         <f>data!D15</f>
       </c>
     </row>
     <row r="26" ht="115" customHeight="true">
-      <c r="A26" s="33">
+      <c r="A26" s="31">
         <v>1</v>
       </c>
-      <c r="B26" s="34"/>
+      <c r="B26" s="32"/>
     </row>
     <row r="27" ht="110" customHeight="true">
-      <c r="A27" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="34" t="str">
+      <c r="A27" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="32" t="str">
         <f>data!D16</f>
       </c>
     </row>
     <row r="28" ht="115" customHeight="true">
-      <c r="A28" s="33">
+      <c r="A28" s="31">
         <v>2</v>
       </c>
-      <c r="B28" s="34"/>
+      <c r="B28" s="32"/>
     </row>
     <row r="29" ht="110" customHeight="true">
-      <c r="A29" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="34" t="str">
+      <c r="A29" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="32" t="str">
         <f>data!D17</f>
       </c>
     </row>
     <row r="30" ht="115" customHeight="true">
-      <c r="A30" s="33">
+      <c r="A30" s="31">
         <v>3</v>
       </c>
-      <c r="B30" s="34"/>
+      <c r="B30" s="32"/>
     </row>
     <row r="31" ht="110" customHeight="true">
-      <c r="A31" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="34" t="str">
+      <c r="A31" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="32" t="str">
         <f>data!D18</f>
       </c>
     </row>
     <row r="32" ht="115" customHeight="true">
-      <c r="A32" s="33">
+      <c r="A32" s="31">
         <v>1</v>
       </c>
-      <c r="B32" s="34"/>
+      <c r="B32" s="32"/>
     </row>
     <row r="33" ht="110" customHeight="true">
-      <c r="A33" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="B33" s="34" t="str">
+      <c r="A33" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="32" t="str">
         <f>data!D19</f>
       </c>
     </row>
     <row r="34" ht="115" customHeight="true">
-      <c r="A34" s="33">
+      <c r="A34" s="31">
         <v>2</v>
       </c>
-      <c r="B34" s="34"/>
+      <c r="B34" s="32"/>
     </row>
     <row r="35" ht="110" customHeight="true">
-      <c r="A35" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="B35" s="34" t="str">
+      <c r="A35" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" s="32" t="str">
         <f>data!D20</f>
       </c>
     </row>
     <row r="36" ht="115" customHeight="true">
-      <c r="A36" s="33">
+      <c r="A36" s="31">
         <v>3</v>
       </c>
-      <c r="B36" s="34"/>
+      <c r="B36" s="32"/>
     </row>
     <row r="37" ht="110" customHeight="true">
-      <c r="A37" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" s="34" t="str">
+      <c r="A37" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" s="32" t="str">
         <f>data!D21</f>
       </c>
     </row>
     <row r="38" ht="115" customHeight="true">
-      <c r="A38" s="33">
+      <c r="A38" s="31">
         <v>1</v>
       </c>
-      <c r="B38" s="34"/>
+      <c r="B38" s="32"/>
     </row>
     <row r="39" ht="110" customHeight="true">
-      <c r="A39" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="B39" s="34" t="str">
+      <c r="A39" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" s="32" t="str">
         <f>data!D22</f>
       </c>
     </row>
     <row r="40" ht="115" customHeight="true">
-      <c r="A40" s="33">
+      <c r="A40" s="31">
         <v>2</v>
       </c>
-      <c r="B40" s="34"/>
+      <c r="B40" s="32"/>
     </row>
     <row r="41" ht="110" customHeight="true">
-      <c r="A41" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="B41" s="34" t="str">
+      <c r="A41" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" s="32" t="str">
         <f>data!D23</f>
       </c>
     </row>
     <row r="42" ht="115" customHeight="true">
-      <c r="A42" s="33">
+      <c r="A42" s="31">
         <v>3</v>
       </c>
-      <c r="B42" s="34"/>
+      <c r="B42" s="32"/>
     </row>
     <row r="43" ht="110" customHeight="true">
-      <c r="A43" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="B43" s="34" t="str">
+      <c r="A43" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="32" t="str">
         <f>data!D24</f>
       </c>
     </row>
     <row r="44" ht="115" customHeight="true">
-      <c r="A44" s="33">
+      <c r="A44" s="31">
         <v>1</v>
       </c>
-      <c r="B44" s="34"/>
+      <c r="B44" s="32"/>
     </row>
     <row r="45" ht="110" customHeight="true">
-      <c r="A45" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="B45" s="34" t="str">
+      <c r="A45" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" s="32" t="str">
         <f>data!D25</f>
       </c>
     </row>
     <row r="46" ht="115" customHeight="true">
-      <c r="A46" s="33">
+      <c r="A46" s="31">
         <v>2</v>
       </c>
-      <c r="B46" s="34"/>
+      <c r="B46" s="32"/>
     </row>
     <row r="47" ht="110" customHeight="true">
-      <c r="A47" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="B47" s="34" t="str">
+      <c r="A47" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="B47" s="32" t="str">
         <f>data!D26</f>
       </c>
     </row>
     <row r="48" ht="115" customHeight="true">
-      <c r="A48" s="33">
+      <c r="A48" s="31">
         <v>3</v>
       </c>
-      <c r="B48" s="34"/>
+      <c r="B48" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="24">

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -1049,11 +1049,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="15"/>
-    <col customWidth="true" max="26" min="2" width="30"/>
+    <col customWidth="true" max="1" min="1" width="9"/>
+    <col customWidth="true" max="3" min="2" width="20"/>
+    <col customWidth="true" max="26" min="4" width="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1418,7 +1422,8 @@
       </c>
     </row>
   </sheetData>
-  <pageSetup orientation="landscape"/>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -3715,7 +3720,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -3921,7 +3926,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -12,15 +12,17 @@
     <sheet name="Pool Draw" sheetId="3" r:id="rId5"/>
     <sheet name="Pool Matches" sheetId="4" r:id="rId6"/>
     <sheet name="Elimination Matches" sheetId="5" r:id="rId7"/>
-    <sheet name="Names to Print" sheetId="6" r:id="rId8"/>
     <sheet name="Tree 1" sheetId="8" r:id="rId11"/>
     <sheet name="Tree 2" sheetId="9" r:id="rId12"/>
-    <sheet name="Tags" sheetId="10" r:id="rId13"/>
+    <sheet name="Names to Print A" sheetId="10" r:id="rId13"/>
+    <sheet name="Names to Print B" sheetId="11" r:id="rId14"/>
+    <sheet name="Tags" sheetId="12" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$23</definedName>
     <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$O$41</definedName>
-    <definedName localSheetId="5" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$24</definedName>
+    <definedName localSheetId="7" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$12</definedName>
+    <definedName localSheetId="8" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$12</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
@@ -450,7 +452,7 @@
     <t>Round 3 - Match 14</t>
   </si>
   <si>
-    <t>Round 4 - Match 0</t>
+    <t>Round 4 - Match 15</t>
   </si>
   <si>
     <t>Tournament Summary</t>
@@ -1431,6 +1433,240 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="27" t="str">
+        <f>data!D3</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="27" t="str">
+        <f>data!D4</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="27" t="str">
+        <f>data!D5</f>
+      </c>
+    </row>
+    <row r="4" ht="270" customHeight="true">
+      <c r="A4" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="27" t="str">
+        <f>data!D6</f>
+      </c>
+    </row>
+    <row r="5" ht="270" customHeight="true">
+      <c r="A5" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="27" t="str">
+        <f>data!D7</f>
+      </c>
+    </row>
+    <row r="6" ht="270" customHeight="true">
+      <c r="A6" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="27" t="str">
+        <f>data!D8</f>
+      </c>
+    </row>
+    <row r="7" ht="270" customHeight="true">
+      <c r="A7" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="27" t="str">
+        <f>data!D9</f>
+      </c>
+    </row>
+    <row r="8" ht="270" customHeight="true">
+      <c r="A8" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="27" t="str">
+        <f>data!D10</f>
+      </c>
+    </row>
+    <row r="9" ht="270" customHeight="true">
+      <c r="A9" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="27" t="str">
+        <f>data!D11</f>
+      </c>
+    </row>
+    <row r="10" ht="270" customHeight="true">
+      <c r="A10" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="27" t="str">
+        <f>data!D12</f>
+      </c>
+    </row>
+    <row r="11" ht="270" customHeight="true">
+      <c r="A11" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="27" t="str">
+        <f>data!D13</f>
+      </c>
+    </row>
+    <row r="12" ht="270" customHeight="true">
+      <c r="A12" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" s="27" t="str">
+        <f>data!D14</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="4" manualBreakCount="4">
+    <brk id="3" max="16383" man="true"/>
+    <brk id="6" max="16383" man="true"/>
+    <brk id="9" max="16383" man="true"/>
+    <brk id="12" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="27" t="str">
+        <f>data!D15</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="27" t="str">
+        <f>data!D16</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="27" t="str">
+        <f>data!D17</f>
+      </c>
+    </row>
+    <row r="4" ht="270" customHeight="true">
+      <c r="A4" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="27" t="str">
+        <f>data!D18</f>
+      </c>
+    </row>
+    <row r="5" ht="270" customHeight="true">
+      <c r="A5" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="B5" s="27" t="str">
+        <f>data!D19</f>
+      </c>
+    </row>
+    <row r="6" ht="270" customHeight="true">
+      <c r="A6" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="27" t="str">
+        <f>data!D20</f>
+      </c>
+    </row>
+    <row r="7" ht="270" customHeight="true">
+      <c r="A7" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" s="27" t="str">
+        <f>data!D21</f>
+      </c>
+    </row>
+    <row r="8" ht="270" customHeight="true">
+      <c r="A8" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" s="27" t="str">
+        <f>data!D22</f>
+      </c>
+    </row>
+    <row r="9" ht="270" customHeight="true">
+      <c r="A9" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B9" s="27" t="str">
+        <f>data!D23</f>
+      </c>
+    </row>
+    <row r="10" ht="270" customHeight="true">
+      <c r="A10" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="27" t="str">
+        <f>data!D24</f>
+      </c>
+    </row>
+    <row r="11" ht="270" customHeight="true">
+      <c r="A11" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" s="27" t="str">
+        <f>data!D25</f>
+      </c>
+    </row>
+    <row r="12" ht="270" customHeight="true">
+      <c r="A12" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="27" t="str">
+        <f>data!D26</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="4" manualBreakCount="4">
+    <brk id="3" max="16383" man="true"/>
+    <brk id="6" max="16383" man="true"/>
+    <brk id="9" max="16383" man="true"/>
+    <brk id="12" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
     <col customWidth="true" max="1" min="1" width="90"/>
   </cols>
   <sheetData>
@@ -3499,223 +3735,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="1" min="1" style="9" width="30"/>
-    <col customWidth="true" max="2" min="2" style="10" width="160"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="27" t="str">
-        <f>data!D3</f>
-      </c>
-    </row>
-    <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" s="27" t="str">
-        <f>data!D4</f>
-      </c>
-    </row>
-    <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" s="27" t="str">
-        <f>data!D5</f>
-      </c>
-    </row>
-    <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="B4" s="27" t="str">
-        <f>data!D6</f>
-      </c>
-    </row>
-    <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" s="27" t="str">
-        <f>data!D7</f>
-      </c>
-    </row>
-    <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="B6" s="27" t="str">
-        <f>data!D8</f>
-      </c>
-    </row>
-    <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" s="27" t="str">
-        <f>data!D9</f>
-      </c>
-    </row>
-    <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" s="27" t="str">
-        <f>data!D10</f>
-      </c>
-    </row>
-    <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" s="27" t="str">
-        <f>data!D11</f>
-      </c>
-    </row>
-    <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="B10" s="27" t="str">
-        <f>data!D12</f>
-      </c>
-    </row>
-    <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="B11" s="27" t="str">
-        <f>data!D13</f>
-      </c>
-    </row>
-    <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="B12" s="27" t="str">
-        <f>data!D14</f>
-      </c>
-    </row>
-    <row r="13" ht="270" customHeight="true">
-      <c r="A13" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="B13" s="27" t="str">
-        <f>data!D15</f>
-      </c>
-    </row>
-    <row r="14" ht="270" customHeight="true">
-      <c r="A14" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="B14" s="27" t="str">
-        <f>data!D16</f>
-      </c>
-    </row>
-    <row r="15" ht="270" customHeight="true">
-      <c r="A15" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="B15" s="27" t="str">
-        <f>data!D17</f>
-      </c>
-    </row>
-    <row r="16" ht="270" customHeight="true">
-      <c r="A16" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="B16" s="27" t="str">
-        <f>data!D18</f>
-      </c>
-    </row>
-    <row r="17" ht="270" customHeight="true">
-      <c r="A17" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="B17" s="27" t="str">
-        <f>data!D19</f>
-      </c>
-    </row>
-    <row r="18" ht="270" customHeight="true">
-      <c r="A18" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="B18" s="27" t="str">
-        <f>data!D20</f>
-      </c>
-    </row>
-    <row r="19" ht="270" customHeight="true">
-      <c r="A19" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="B19" s="27" t="str">
-        <f>data!D21</f>
-      </c>
-    </row>
-    <row r="20" ht="270" customHeight="true">
-      <c r="A20" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="B20" s="27" t="str">
-        <f>data!D22</f>
-      </c>
-    </row>
-    <row r="21" ht="270" customHeight="true">
-      <c r="A21" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="B21" s="27" t="str">
-        <f>data!D23</f>
-      </c>
-    </row>
-    <row r="22" ht="270" customHeight="true">
-      <c r="A22" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="B22" s="27" t="str">
-        <f>data!D24</f>
-      </c>
-    </row>
-    <row r="23" ht="270" customHeight="true">
-      <c r="A23" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="B23" s="27" t="str">
-        <f>data!D25</f>
-      </c>
-    </row>
-    <row r="24" ht="270" customHeight="true">
-      <c r="A24" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="B24" s="27" t="str">
-        <f>data!D26</f>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="8"/>
-  <rowBreaks count="8" manualBreakCount="8">
-    <brk id="3" max="16383" man="true"/>
-    <brk id="6" max="16383" man="true"/>
-    <brk id="9" max="16383" man="true"/>
-    <brk id="12" max="16383" man="true"/>
-    <brk id="15" max="16383" man="true"/>
-    <brk id="18" max="16383" man="true"/>
-    <brk id="21" max="16383" man="true"/>
-    <brk id="24" max="16383" man="true"/>
-  </rowBreaks>
-  <colBreaks/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$23</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$O$41</definedName>
+    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$O$65</definedName>
     <definedName localSheetId="7" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$12</definedName>
     <definedName localSheetId="8" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$12</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$O$85</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="154">
   <si>
     <t>Number of pools</t>
   </si>
@@ -321,6 +321,24 @@
   </si>
   <si>
     <t>Red</t>
+  </si>
+  <si>
+    <t>Results</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>PW</t>
+  </si>
+  <si>
+    <t>PL</t>
   </si>
   <si>
     <t xml:space="preserve">1. </t>
@@ -576,7 +594,7 @@
       <sz val="150"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -586,6 +604,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFEFEF"/>
       </patternFill>
     </fill>
     <fill>
@@ -692,7 +715,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -733,17 +756,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center"/>
+      <protection hidden="false" locked="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment/>
+      <protection hidden="false" locked="false"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
@@ -754,10 +785,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
@@ -779,6 +810,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -1438,102 +1472,103 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="27" t="str">
+      <c r="A1" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="29" t="str">
         <f>data!D3</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" s="27" t="str">
+      <c r="A2" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="29" t="str">
         <f>data!D4</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" s="27" t="str">
+      <c r="A3" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="29" t="str">
         <f>data!D5</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="B4" s="27" t="str">
+      <c r="A4" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="29" t="str">
         <f>data!D6</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" s="27" t="str">
+      <c r="A5" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" s="29" t="str">
         <f>data!D7</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="B6" s="27" t="str">
+      <c r="A6" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" s="29" t="str">
         <f>data!D8</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" s="27" t="str">
+      <c r="A7" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="29" t="str">
         <f>data!D9</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" s="27" t="str">
+      <c r="A8" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="29" t="str">
         <f>data!D10</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" s="27" t="str">
+      <c r="A9" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" s="29" t="str">
         <f>data!D11</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="B10" s="27" t="str">
+      <c r="A10" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="29" t="str">
         <f>data!D12</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="B11" s="27" t="str">
+      <c r="A11" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" s="29" t="str">
         <f>data!D13</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="B12" s="27" t="str">
+      <c r="A12" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" s="29" t="str">
         <f>data!D14</f>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="8"/>
   <rowBreaks count="4" manualBreakCount="4">
@@ -1555,102 +1590,103 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="B1" s="27" t="str">
+      <c r="A1" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="29" t="str">
         <f>data!D15</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="B2" s="27" t="str">
+      <c r="A2" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="29" t="str">
         <f>data!D16</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" s="27" t="str">
+      <c r="A3" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="29" t="str">
         <f>data!D17</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" s="27" t="str">
+      <c r="A4" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="29" t="str">
         <f>data!D18</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="B5" s="27" t="str">
+      <c r="A5" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="29" t="str">
         <f>data!D19</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="B6" s="27" t="str">
+      <c r="A6" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="29" t="str">
         <f>data!D20</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="B7" s="27" t="str">
+      <c r="A7" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="29" t="str">
         <f>data!D21</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="B8" s="27" t="str">
+      <c r="A8" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="29" t="str">
         <f>data!D22</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="B9" s="27" t="str">
+      <c r="A9" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="29" t="str">
         <f>data!D23</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="B10" s="27" t="str">
+      <c r="A10" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="29" t="str">
         <f>data!D24</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="B11" s="27" t="str">
+      <c r="A11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="29" t="str">
         <f>data!D25</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="B12" s="27" t="str">
+      <c r="A12" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="29" t="str">
         <f>data!D26</f>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="8"/>
   <rowBreaks count="4" manualBreakCount="4">
@@ -1671,246 +1707,247 @@
   </cols>
   <sheetData>
     <row r="1" ht="390" customHeight="true">
-      <c r="A1" s="28" t="s">
-        <v>100</v>
+      <c r="A1" s="30" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="2" ht="390" customHeight="true">
-      <c r="A2" s="28" t="s">
-        <v>100</v>
+      <c r="A2" s="30" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="3" ht="390" customHeight="true">
-      <c r="A3" s="28" t="s">
-        <v>101</v>
+      <c r="A3" s="30" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="4" ht="390" customHeight="true">
-      <c r="A4" s="28" t="s">
-        <v>101</v>
+      <c r="A4" s="30" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="5" ht="390" customHeight="true">
-      <c r="A5" s="28" t="s">
-        <v>102</v>
+      <c r="A5" s="30" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="6" ht="390" customHeight="true">
-      <c r="A6" s="28" t="s">
-        <v>102</v>
+      <c r="A6" s="30" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="7" ht="390" customHeight="true">
-      <c r="A7" s="28" t="s">
-        <v>103</v>
+      <c r="A7" s="30" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="8" ht="390" customHeight="true">
-      <c r="A8" s="28" t="s">
-        <v>103</v>
+      <c r="A8" s="30" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="9" ht="390" customHeight="true">
-      <c r="A9" s="28" t="s">
-        <v>104</v>
+      <c r="A9" s="30" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="10" ht="390" customHeight="true">
-      <c r="A10" s="28" t="s">
-        <v>104</v>
+      <c r="A10" s="30" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="11" ht="390" customHeight="true">
-      <c r="A11" s="28" t="s">
-        <v>105</v>
+      <c r="A11" s="30" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="12" ht="390" customHeight="true">
-      <c r="A12" s="28" t="s">
-        <v>105</v>
+      <c r="A12" s="30" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="13" ht="390" customHeight="true">
-      <c r="A13" s="28" t="s">
-        <v>106</v>
+      <c r="A13" s="30" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="14" ht="390" customHeight="true">
-      <c r="A14" s="28" t="s">
-        <v>106</v>
+      <c r="A14" s="30" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="15" ht="390" customHeight="true">
-      <c r="A15" s="28" t="s">
-        <v>107</v>
+      <c r="A15" s="30" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="16" ht="390" customHeight="true">
-      <c r="A16" s="28" t="s">
-        <v>107</v>
+      <c r="A16" s="30" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="17" ht="390" customHeight="true">
-      <c r="A17" s="28" t="s">
-        <v>108</v>
+      <c r="A17" s="30" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="18" ht="390" customHeight="true">
-      <c r="A18" s="28" t="s">
-        <v>108</v>
+      <c r="A18" s="30" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="19" ht="390" customHeight="true">
-      <c r="A19" s="28" t="s">
-        <v>109</v>
+      <c r="A19" s="30" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="20" ht="390" customHeight="true">
-      <c r="A20" s="28" t="s">
-        <v>109</v>
+      <c r="A20" s="30" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="21" ht="390" customHeight="true">
-      <c r="A21" s="28" t="s">
-        <v>110</v>
+      <c r="A21" s="30" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="22" ht="390" customHeight="true">
-      <c r="A22" s="28" t="s">
-        <v>110</v>
+      <c r="A22" s="30" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="23" ht="390" customHeight="true">
-      <c r="A23" s="28" t="s">
-        <v>111</v>
+      <c r="A23" s="30" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="24" ht="390" customHeight="true">
-      <c r="A24" s="28" t="s">
-        <v>111</v>
+      <c r="A24" s="30" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="25" ht="390" customHeight="true">
-      <c r="A25" s="28" t="s">
-        <v>112</v>
+      <c r="A25" s="30" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="26" ht="390" customHeight="true">
-      <c r="A26" s="28" t="s">
-        <v>112</v>
+      <c r="A26" s="30" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="27" ht="390" customHeight="true">
-      <c r="A27" s="28" t="s">
-        <v>113</v>
+      <c r="A27" s="30" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="28" ht="390" customHeight="true">
-      <c r="A28" s="28" t="s">
-        <v>113</v>
+      <c r="A28" s="30" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="29" ht="390" customHeight="true">
-      <c r="A29" s="28" t="s">
-        <v>114</v>
+      <c r="A29" s="30" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="30" ht="390" customHeight="true">
-      <c r="A30" s="28" t="s">
-        <v>114</v>
+      <c r="A30" s="30" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="31" ht="390" customHeight="true">
-      <c r="A31" s="28" t="s">
-        <v>115</v>
+      <c r="A31" s="30" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="32" ht="390" customHeight="true">
-      <c r="A32" s="28" t="s">
-        <v>115</v>
+      <c r="A32" s="30" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="33" ht="390" customHeight="true">
-      <c r="A33" s="28" t="s">
-        <v>116</v>
+      <c r="A33" s="30" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="34" ht="390" customHeight="true">
-      <c r="A34" s="28" t="s">
-        <v>116</v>
+      <c r="A34" s="30" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="35" ht="390" customHeight="true">
-      <c r="A35" s="28" t="s">
-        <v>117</v>
+      <c r="A35" s="30" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="36" ht="390" customHeight="true">
-      <c r="A36" s="28" t="s">
-        <v>117</v>
+      <c r="A36" s="30" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="37" ht="390" customHeight="true">
-      <c r="A37" s="28" t="s">
-        <v>118</v>
+      <c r="A37" s="30" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="38" ht="390" customHeight="true">
-      <c r="A38" s="28" t="s">
-        <v>118</v>
+      <c r="A38" s="30" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="39" ht="390" customHeight="true">
-      <c r="A39" s="28" t="s">
-        <v>119</v>
+      <c r="A39" s="30" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="40" ht="390" customHeight="true">
-      <c r="A40" s="28" t="s">
-        <v>119</v>
+      <c r="A40" s="30" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="41" ht="390" customHeight="true">
-      <c r="A41" s="28" t="s">
-        <v>120</v>
+      <c r="A41" s="30" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="42" ht="390" customHeight="true">
-      <c r="A42" s="28" t="s">
-        <v>120</v>
+      <c r="A42" s="30" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="43" ht="390" customHeight="true">
-      <c r="A43" s="28" t="s">
-        <v>121</v>
+      <c r="A43" s="30" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="44" ht="390" customHeight="true">
-      <c r="A44" s="28" t="s">
-        <v>121</v>
+      <c r="A44" s="30" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="45" ht="390" customHeight="true">
-      <c r="A45" s="28" t="s">
-        <v>122</v>
+      <c r="A45" s="30" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="46" ht="390" customHeight="true">
-      <c r="A46" s="28" t="s">
-        <v>122</v>
+      <c r="A46" s="30" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="47" ht="390" customHeight="true">
-      <c r="A47" s="28" t="s">
-        <v>123</v>
+      <c r="A47" s="30" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="48" ht="390" customHeight="true">
-      <c r="A48" s="28" t="s">
-        <v>123</v>
+      <c r="A48" s="30" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9"/>
   <rowBreaks count="24" manualBreakCount="24">
@@ -2003,7 +2040,7 @@
       <c r="G2" s="3">
         <v>0.020833333333333332</v>
       </c>
-      <c r="H2" s="29" t="str">
+      <c r="H2" s="31" t="str">
         <f>C2*I2+J2</f>
       </c>
     </row>
@@ -2107,7 +2144,7 @@
       <c r="G8" s="3">
         <v>0.020833333333333332</v>
       </c>
-      <c r="H8" s="29" t="str">
+      <c r="H8" s="31" t="str">
         <f>E8+(A8*F8)+G8</f>
       </c>
     </row>
@@ -2143,7 +2180,7 @@
     </row>
     <row r="13">
       <c r="E13" s="13" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
@@ -2153,62 +2190,62 @@
       <c r="A14">
         <v>2</v>
       </c>
-      <c r="E14" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="29" t="str">
+      <c r="E14" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="31" t="str">
         <f>H2</f>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="29" t="str">
+      <c r="E15" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="31" t="str">
         <f>H8</f>
       </c>
     </row>
     <row r="16">
-      <c r="E16" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="29" t="str">
+      <c r="E16" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="str">
         <f>H14+H15</f>
       </c>
     </row>
     <row r="17">
-      <c r="E17" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="29" t="str">
+      <c r="E17" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="31" t="str">
         <f>H16/A14</f>
       </c>
     </row>
     <row r="18">
       <c r="E18" s="13" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
-      <c r="H18" s="30">
+      <c r="H18" s="33">
         <v>0.375</v>
       </c>
     </row>
     <row r="19">
       <c r="E19" s="13" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
-      <c r="H19" s="30" t="str">
+      <c r="H19" s="33" t="str">
         <f>H18+H17</f>
       </c>
     </row>
@@ -2406,14 +2443,15 @@
     <col customWidth="true" max="4" min="4" width="3"/>
     <col customWidth="true" max="6" min="5" width="5"/>
     <col customWidth="true" max="7" min="7" width="30"/>
-    <col customWidth="true" max="8" min="8" width="2"/>
+    <col customWidth="true" max="8" min="8" width="5"/>
     <col customWidth="true" max="9" min="9" width="30"/>
     <col customWidth="true" max="11" min="10" width="5"/>
     <col customWidth="true" max="12" min="12" width="3"/>
     <col customWidth="true" max="14" min="13" width="5"/>
     <col customWidth="true" max="15" min="15" width="30"/>
-    <col customWidth="true" max="16" min="16" width="2"/>
-    <col customWidth="true" max="20" min="17" width="10.83"/>
+    <col customWidth="true" max="18" min="16" width="5"/>
+    <col customWidth="true" max="19" min="19" width="30"/>
+    <col customWidth="true" max="20" min="20" width="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2480,22 +2518,22 @@
       <c r="A4" s="14" t="str">
         <f>data!$B$4</f>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="14" t="str">
         <f>data!$B$3</f>
       </c>
       <c r="I4" s="14" t="str">
         <f>data!$B$16</f>
       </c>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
       <c r="O4" s="14" t="str">
         <f>data!$B$15</f>
       </c>
@@ -2504,22 +2542,22 @@
       <c r="A5" s="14" t="str">
         <f>data!$B$5</f>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
       <c r="G5" s="14" t="str">
         <f>data!$B$3</f>
       </c>
       <c r="I5" s="14" t="str">
         <f>data!$B$17</f>
       </c>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
       <c r="O5" s="14" t="str">
         <f>data!$B$15</f>
       </c>
@@ -2528,498 +2566,1109 @@
       <c r="A6" s="14" t="str">
         <f>data!$B$5</f>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
       <c r="G6" s="14" t="str">
         <f>data!$B$4</f>
       </c>
       <c r="I6" s="14" t="str">
         <f>data!$B$17</f>
       </c>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
       <c r="O6" s="14" t="str">
         <f>data!$B$16</f>
       </c>
     </row>
     <row r="8">
-      <c r="F8" t="s">
+      <c r="A8" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="G8" s="15"/>
-      <c r="N8" t="s">
+      <c r="B8" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I8" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="O8" s="15"/>
+      <c r="J8" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="M8" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="9">
-      <c r="F9" t="s">
+      <c r="A9" s="14" t="str">
+        <f>data!$B$3</f>
+      </c>
+      <c r="B9" s="14" t="str">
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C9" s="14" t="str">
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D9" s="14" t="str">
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),1,0),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),1,0),0)</f>
+      </c>
+      <c r="E9" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F9" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="I9" s="14" t="str">
+        <f>data!$B$15</f>
+      </c>
+      <c r="J9" s="14" t="str">
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K9" s="14" t="str">
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L9" s="14" t="str">
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),1,0),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),1,0),0)</f>
+      </c>
+      <c r="M9" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N9" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))</f>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="str">
+        <f>data!$B$4</f>
+      </c>
+      <c r="B10" s="14" t="str">
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C10" s="14" t="str">
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D10" s="14" t="str">
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),1,0),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),1,0),0)</f>
+      </c>
+      <c r="E10" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F10" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="I10" s="14" t="str">
+        <f>data!$B$16</f>
+      </c>
+      <c r="J10" s="14" t="str">
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K10" s="14" t="str">
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L10" s="14" t="str">
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),1,0),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),1,0),0)</f>
+      </c>
+      <c r="M10" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N10" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))</f>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="str">
+        <f>data!$B$5</f>
+      </c>
+      <c r="B11" s="14" t="str">
+        <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C11" s="14" t="str">
+        <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D11" s="14" t="str">
+        <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),1,0),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),1,0),0)</f>
+      </c>
+      <c r="E11" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F11" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="I11" s="14" t="str">
+        <f>data!$B$17</f>
+      </c>
+      <c r="J11" s="14" t="str">
+        <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K11" s="14" t="str">
+        <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L11" s="14" t="str">
+        <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),1,0),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),1,0),0)</f>
+      </c>
+      <c r="M11" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N11" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))</f>
+      </c>
+    </row>
+    <row r="13">
+      <c r="F13" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" s="19"/>
+      <c r="N13" t="s">
+        <v>103</v>
+      </c>
+      <c r="O13" s="19"/>
+    </row>
+    <row r="14">
+      <c r="F14" t="s">
+        <v>104</v>
+      </c>
+      <c r="G14" s="19"/>
+      <c r="N14" t="s">
+        <v>104</v>
+      </c>
+      <c r="O14" s="19"/>
+    </row>
+    <row r="15">
+      <c r="F15" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" s="19"/>
+      <c r="N15" t="s">
+        <v>105</v>
+      </c>
+      <c r="O15" s="19"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="str">
+        <f>data!$A$8</f>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="I18" s="13" t="str">
+        <f>data!$A$20</f>
+      </c>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="O19" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="str">
+        <f>data!$B$7</f>
+      </c>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="14" t="str">
+        <f>data!$B$6</f>
+      </c>
+      <c r="I20" s="14" t="str">
+        <f>data!$B$19</f>
+      </c>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="14" t="str">
+        <f>data!$B$18</f>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="str">
+        <f>data!$B$8</f>
+      </c>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="14" t="str">
+        <f>data!$B$6</f>
+      </c>
+      <c r="I21" s="14" t="str">
+        <f>data!$B$20</f>
+      </c>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="14" t="str">
+        <f>data!$B$18</f>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="str">
+        <f>data!$B$8</f>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="14" t="str">
+        <f>data!$B$7</f>
+      </c>
+      <c r="I22" s="14" t="str">
+        <f>data!$B$20</f>
+      </c>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="14" t="str">
+        <f>data!$B$19</f>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="G9" s="15"/>
-      <c r="N9" t="s">
+      <c r="C24" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="J24" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="O9" s="15"/>
-    </row>
-    <row r="10">
-      <c r="F10" t="s">
+      <c r="K24" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="G10" s="15"/>
-      <c r="N10" t="s">
-        <v>99</v>
-      </c>
-      <c r="O10" s="15"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="str">
-        <f>data!$A$8</f>
-      </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="I12" s="13" t="str">
-        <f>data!$A$20</f>
-      </c>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="G13" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="O13" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="str">
-        <f>data!$B$7</f>
-      </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14" t="str">
-        <f>data!$B$6</f>
-      </c>
-      <c r="I14" s="14" t="str">
-        <f>data!$B$19</f>
-      </c>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14" t="str">
-        <f>data!$B$18</f>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="str">
-        <f>data!$B$8</f>
-      </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14" t="str">
-        <f>data!$B$6</f>
-      </c>
-      <c r="I15" s="14" t="str">
-        <f>data!$B$20</f>
-      </c>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14" t="str">
-        <f>data!$B$18</f>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="str">
-        <f>data!$B$8</f>
-      </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14" t="str">
-        <f>data!$B$7</f>
-      </c>
-      <c r="I16" s="14" t="str">
-        <f>data!$B$20</f>
-      </c>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14" t="str">
-        <f>data!$B$19</f>
-      </c>
-    </row>
-    <row r="18">
-      <c r="F18" t="s">
-        <v>97</v>
-      </c>
-      <c r="G18" s="15"/>
-      <c r="N18" t="s">
-        <v>97</v>
-      </c>
-      <c r="O18" s="15"/>
-    </row>
-    <row r="19">
-      <c r="F19" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" s="15"/>
-      <c r="N19" t="s">
-        <v>98</v>
-      </c>
-      <c r="O19" s="15"/>
-    </row>
-    <row r="20">
-      <c r="F20" t="s">
-        <v>99</v>
-      </c>
-      <c r="G20" s="15"/>
-      <c r="N20" t="s">
-        <v>99</v>
-      </c>
-      <c r="O20" s="15"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="str">
-        <f>data!$A$11</f>
-      </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="I22" s="13" t="str">
-        <f>data!$A$23</f>
-      </c>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="13"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="G23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="I23" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="L23" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="O23" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="str">
-        <f>data!$B$10</f>
-      </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14" t="str">
-        <f>data!$B$9</f>
-      </c>
-      <c r="I24" s="14" t="str">
-        <f>data!$B$22</f>
-      </c>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14" t="str">
-        <f>data!$B$21</f>
+      <c r="L24" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="M24" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="N24" s="13" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="str">
-        <f>data!$B$11</f>
-      </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$6</f>
+      </c>
+      <c r="B25" s="14" t="str">
+        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C25" s="14" t="str">
+        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D25" s="14" t="str">
+        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),1,0),0)+IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),1,0),0)</f>
+      </c>
+      <c r="E25" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F25" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))</f>
       </c>
       <c r="I25" s="14" t="str">
-        <f>data!$B$23</f>
-      </c>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14" t="str">
-        <f>data!$B$21</f>
+        <f>data!$B$18</f>
+      </c>
+      <c r="J25" s="14" t="str">
+        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K25" s="14" t="str">
+        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L25" s="14" t="str">
+        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),1,0),0)+IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),1,0),0)</f>
+      </c>
+      <c r="M25" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N25" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))</f>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="str">
-        <f>data!$B$11</f>
-      </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$7</f>
+      </c>
+      <c r="B26" s="14" t="str">
+        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C26" s="14" t="str">
+        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D26" s="14" t="str">
+        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),1,0),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),1,0),0)</f>
+      </c>
+      <c r="E26" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F26" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))</f>
       </c>
       <c r="I26" s="14" t="str">
-        <f>data!$B$23</f>
-      </c>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14" t="str">
-        <f>data!$B$22</f>
-      </c>
-    </row>
-    <row r="28">
-      <c r="F28" t="s">
-        <v>97</v>
-      </c>
-      <c r="G28" s="15"/>
-      <c r="N28" t="s">
-        <v>97</v>
-      </c>
-      <c r="O28" s="15"/>
+        <f>data!$B$19</f>
+      </c>
+      <c r="J26" s="14" t="str">
+        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K26" s="14" t="str">
+        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L26" s="14" t="str">
+        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),1,0),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),1,0),0)</f>
+      </c>
+      <c r="M26" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N26" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))</f>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="str">
+        <f>data!$B$8</f>
+      </c>
+      <c r="B27" s="14" t="str">
+        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C27" s="14" t="str">
+        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D27" s="14" t="str">
+        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),1,0),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),1,0),0)</f>
+      </c>
+      <c r="E27" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F27" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="I27" s="14" t="str">
+        <f>data!$B$20</f>
+      </c>
+      <c r="J27" s="14" t="str">
+        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K27" s="14" t="str">
+        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L27" s="14" t="str">
+        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),1,0),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),1,0),0)</f>
+      </c>
+      <c r="M27" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N27" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))</f>
+      </c>
     </row>
     <row r="29">
       <c r="F29" t="s">
-        <v>98</v>
-      </c>
-      <c r="G29" s="15"/>
+        <v>103</v>
+      </c>
+      <c r="G29" s="19"/>
       <c r="N29" t="s">
-        <v>98</v>
-      </c>
-      <c r="O29" s="15"/>
+        <v>103</v>
+      </c>
+      <c r="O29" s="19"/>
     </row>
     <row r="30">
       <c r="F30" t="s">
-        <v>99</v>
-      </c>
-      <c r="G30" s="15"/>
+        <v>104</v>
+      </c>
+      <c r="G30" s="19"/>
       <c r="N30" t="s">
-        <v>99</v>
-      </c>
-      <c r="O30" s="15"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="str">
-        <f>data!$A$14</f>
-      </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="I32" s="13" t="str">
-        <f>data!$A$26</f>
-      </c>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
-      <c r="M32" s="13"/>
-      <c r="N32" s="13"/>
-      <c r="O32" s="13"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="O30" s="19"/>
+    </row>
+    <row r="31">
+      <c r="F31" t="s">
+        <v>105</v>
+      </c>
+      <c r="G31" s="19"/>
+      <c r="N31" t="s">
+        <v>105</v>
+      </c>
+      <c r="O31" s="19"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="str">
+        <f>data!$A$11</f>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="I34" s="13" t="str">
+        <f>data!$A$23</f>
+      </c>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D35" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="G33" s="16" t="s">
+      <c r="G35" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="I33" s="17" t="s">
+      <c r="I35" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="L33" s="14" t="s">
+      <c r="L35" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="O33" s="16" t="s">
+      <c r="O35" s="16" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="str">
-        <f>data!$B$13</f>
-      </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14" t="str">
-        <f>data!$B$12</f>
-      </c>
-      <c r="I34" s="14" t="str">
-        <f>data!$B$25</f>
-      </c>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="14" t="str">
-        <f>data!$B$24</f>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="str">
-        <f>data!$B$14</f>
-      </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14" t="str">
-        <f>data!$B$12</f>
-      </c>
-      <c r="I35" s="14" t="str">
-        <f>data!$B$26</f>
-      </c>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="14" t="str">
-        <f>data!$B$24</f>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="str">
+        <f>data!$B$10</f>
+      </c>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="14" t="str">
+        <f>data!$B$9</f>
+      </c>
+      <c r="I36" s="14" t="str">
+        <f>data!$B$22</f>
+      </c>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="14" t="str">
+        <f>data!$B$21</f>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="str">
+        <f>data!$B$11</f>
+      </c>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="14" t="str">
+        <f>data!$B$9</f>
+      </c>
+      <c r="I37" s="14" t="str">
+        <f>data!$B$23</f>
+      </c>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="14" t="str">
+        <f>data!$B$21</f>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="str">
+        <f>data!$B$11</f>
+      </c>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="14" t="str">
+        <f>data!$B$10</f>
+      </c>
+      <c r="I38" s="14" t="str">
+        <f>data!$B$23</f>
+      </c>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="14" t="str">
+        <f>data!$B$22</f>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="J40" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="K40" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="L40" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="M40" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="N40" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="str">
+        <f>data!$B$9</f>
+      </c>
+      <c r="B41" s="14" t="str">
+        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C41" s="14" t="str">
+        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D41" s="14" t="str">
+        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),1,0),0)+IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),1,0),0)</f>
+      </c>
+      <c r="E41" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F41" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="I41" s="14" t="str">
+        <f>data!$B$21</f>
+      </c>
+      <c r="J41" s="14" t="str">
+        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K41" s="14" t="str">
+        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L41" s="14" t="str">
+        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),1,0),0)+IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),1,0),0)</f>
+      </c>
+      <c r="M41" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N41" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-",""))</f>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="str">
+        <f>data!$B$10</f>
+      </c>
+      <c r="B42" s="14" t="str">
+        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C42" s="14" t="str">
+        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D42" s="14" t="str">
+        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),1,0),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),1,0),0)</f>
+      </c>
+      <c r="E42" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F42" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="I42" s="14" t="str">
+        <f>data!$B$22</f>
+      </c>
+      <c r="J42" s="14" t="str">
+        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K42" s="14" t="str">
+        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L42" s="14" t="str">
+        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),1,0),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),1,0),0)</f>
+      </c>
+      <c r="M42" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N42" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))</f>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="str">
+        <f>data!$B$11</f>
+      </c>
+      <c r="B43" s="14" t="str">
+        <f>IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C43" s="14" t="str">
+        <f>IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D43" s="14" t="str">
+        <f>IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),1,0),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),1,0),0)</f>
+      </c>
+      <c r="E43" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F43" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="I43" s="14" t="str">
+        <f>data!$B$23</f>
+      </c>
+      <c r="J43" s="14" t="str">
+        <f>IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K43" s="14" t="str">
+        <f>IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L43" s="14" t="str">
+        <f>IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),1,0),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),1,0),0)</f>
+      </c>
+      <c r="M43" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N43" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))</f>
+      </c>
+    </row>
+    <row r="45">
+      <c r="F45" t="s">
+        <v>103</v>
+      </c>
+      <c r="G45" s="19"/>
+      <c r="N45" t="s">
+        <v>103</v>
+      </c>
+      <c r="O45" s="19"/>
+    </row>
+    <row r="46">
+      <c r="F46" t="s">
+        <v>104</v>
+      </c>
+      <c r="G46" s="19"/>
+      <c r="N46" t="s">
+        <v>104</v>
+      </c>
+      <c r="O46" s="19"/>
+    </row>
+    <row r="47">
+      <c r="F47" t="s">
+        <v>105</v>
+      </c>
+      <c r="G47" s="19"/>
+      <c r="N47" t="s">
+        <v>105</v>
+      </c>
+      <c r="O47" s="19"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="str">
+        <f>data!$A$14</f>
+      </c>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="I50" s="13" t="str">
+        <f>data!$A$26</f>
+      </c>
+      <c r="J50" s="13"/>
+      <c r="K50" s="13"/>
+      <c r="L50" s="13"/>
+      <c r="M50" s="13"/>
+      <c r="N50" s="13"/>
+      <c r="O50" s="13"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="G51" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="I51" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="L51" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="O51" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="str">
+        <f>data!$B$13</f>
+      </c>
+      <c r="B52" s="18"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="14" t="str">
+        <f>data!$B$12</f>
+      </c>
+      <c r="I52" s="14" t="str">
+        <f>data!$B$25</f>
+      </c>
+      <c r="J52" s="18"/>
+      <c r="K52" s="18"/>
+      <c r="L52" s="18"/>
+      <c r="M52" s="18"/>
+      <c r="N52" s="18"/>
+      <c r="O52" s="14" t="str">
+        <f>data!$B$24</f>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="str">
         <f>data!$B$14</f>
       </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14" t="str">
+      <c r="B53" s="18"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="14" t="str">
+        <f>data!$B$12</f>
+      </c>
+      <c r="I53" s="14" t="str">
+        <f>data!$B$26</f>
+      </c>
+      <c r="J53" s="18"/>
+      <c r="K53" s="18"/>
+      <c r="L53" s="18"/>
+      <c r="M53" s="18"/>
+      <c r="N53" s="18"/>
+      <c r="O53" s="14" t="str">
+        <f>data!$B$24</f>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="str">
+        <f>data!$B$14</f>
+      </c>
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="14" t="str">
         <f>data!$B$13</f>
       </c>
-      <c r="I36" s="14" t="str">
+      <c r="I54" s="14" t="str">
         <f>data!$B$26</f>
       </c>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="14" t="str">
+      <c r="J54" s="18"/>
+      <c r="K54" s="18"/>
+      <c r="L54" s="18"/>
+      <c r="M54" s="18"/>
+      <c r="N54" s="18"/>
+      <c r="O54" s="14" t="str">
         <f>data!$B$25</f>
       </c>
     </row>
-    <row r="38">
-      <c r="F38" t="s">
+    <row r="56">
+      <c r="A56" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="G38" s="15"/>
-      <c r="N38" t="s">
+      <c r="B56" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F56" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I56" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="O38" s="15"/>
-    </row>
-    <row r="39">
-      <c r="F39" t="s">
+      <c r="J56" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="G39" s="15"/>
-      <c r="N39" t="s">
-        <v>98</v>
-      </c>
-      <c r="O39" s="15"/>
-    </row>
-    <row r="40">
-      <c r="F40" t="s">
+      <c r="K56" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="G40" s="15"/>
-      <c r="N40" t="s">
-        <v>99</v>
-      </c>
-      <c r="O40" s="15"/>
+      <c r="L56" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="M56" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="N56" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="str">
+        <f>data!$B$12</f>
+      </c>
+      <c r="B57" s="14" t="str">
+        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C57" s="14" t="str">
+        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D57" s="14" t="str">
+        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),1,0),0)+IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),1,0),0)</f>
+      </c>
+      <c r="E57" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F57" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="I57" s="14" t="str">
+        <f>data!$B$24</f>
+      </c>
+      <c r="J57" s="14" t="str">
+        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K57" s="14" t="str">
+        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L57" s="14" t="str">
+        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),1,0),0)+IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),1,0),0)</f>
+      </c>
+      <c r="M57" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N57" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-",""))</f>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="str">
+        <f>data!$B$13</f>
+      </c>
+      <c r="B58" s="14" t="str">
+        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C58" s="14" t="str">
+        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D58" s="14" t="str">
+        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),1,0),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),1,0),0)</f>
+      </c>
+      <c r="E58" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F58" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="I58" s="14" t="str">
+        <f>data!$B$25</f>
+      </c>
+      <c r="J58" s="14" t="str">
+        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K58" s="14" t="str">
+        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L58" s="14" t="str">
+        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),1,0),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),1,0),0)</f>
+      </c>
+      <c r="M58" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N58" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-",""))</f>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="str">
+        <f>data!$B$14</f>
+      </c>
+      <c r="B59" s="14" t="str">
+        <f>IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C59" s="14" t="str">
+        <f>IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D59" s="14" t="str">
+        <f>IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),1,0),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),1,0),0)</f>
+      </c>
+      <c r="E59" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F59" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="I59" s="14" t="str">
+        <f>data!$B$26</f>
+      </c>
+      <c r="J59" s="14" t="str">
+        <f>IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K59" s="14" t="str">
+        <f>IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L59" s="14" t="str">
+        <f>IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),1,0),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),1,0),0)</f>
+      </c>
+      <c r="M59" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N59" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-",""))</f>
+      </c>
+    </row>
+    <row r="61">
+      <c r="F61" t="s">
+        <v>103</v>
+      </c>
+      <c r="G61" s="19"/>
+      <c r="N61" t="s">
+        <v>103</v>
+      </c>
+      <c r="O61" s="19"/>
+    </row>
+    <row r="62">
+      <c r="F62" t="s">
+        <v>104</v>
+      </c>
+      <c r="G62" s="19"/>
+      <c r="N62" t="s">
+        <v>104</v>
+      </c>
+      <c r="O62" s="19"/>
+    </row>
+    <row r="63">
+      <c r="F63" t="s">
+        <v>105</v>
+      </c>
+      <c r="G63" s="19"/>
+      <c r="N63" t="s">
+        <v>105</v>
+      </c>
+      <c r="O63" s="19"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="10">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="I2:O2"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="I12:O12"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="I22:O22"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="I32:O32"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="I18:O18"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="I34:O34"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="I50:O50"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageSetup fitToHeight="0" fitToWidth="2" orientation="portrait" pageOrder="downThenOver" paperSize="9"/>
-  <rowBreaks/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="33" max="16383" man="true"/>
+  </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="8" max="1048575" man="true"/>
   </colBreaks>
@@ -3039,14 +3688,15 @@
     <col customWidth="true" max="4" min="4" width="3"/>
     <col customWidth="true" max="6" min="5" width="5"/>
     <col customWidth="true" max="7" min="7" width="30"/>
-    <col customWidth="true" max="8" min="8" width="2"/>
+    <col customWidth="true" max="8" min="8" width="5"/>
     <col customWidth="true" max="9" min="9" width="30"/>
     <col customWidth="true" max="11" min="10" width="5"/>
     <col customWidth="true" max="12" min="12" width="3"/>
     <col customWidth="true" max="14" min="13" width="5"/>
     <col customWidth="true" max="15" min="15" width="30"/>
-    <col customWidth="true" max="16" min="16" width="2"/>
-    <col customWidth="true" max="20" min="17" width="10.83"/>
+    <col customWidth="true" max="18" min="16" width="5"/>
+    <col customWidth="true" max="19" min="19" width="30"/>
+    <col customWidth="true" max="20" min="20" width="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3071,7 +3721,7 @@
     </row>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -3080,7 +3730,7 @@
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
       <c r="I2" s="13" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
@@ -3111,51 +3761,51 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G19)</f>
-      </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G30)</f>
+      </c>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G8)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G13)</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G9)</f>
-      </c>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G14)</f>
+      </c>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
       <c r="O4" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G18)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G29)</f>
       </c>
     </row>
     <row r="6">
       <c r="F6" t="s">
-        <v>125</v>
-      </c>
-      <c r="G6" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="G6" s="19"/>
       <c r="N6" t="s">
-        <v>125</v>
-      </c>
-      <c r="O6" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="O6" s="19"/>
     </row>
     <row r="7">
       <c r="F7" t="s">
-        <v>126</v>
-      </c>
-      <c r="G7" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="G7" s="19"/>
       <c r="N7" t="s">
-        <v>126</v>
-      </c>
-      <c r="O7" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="O7" s="19"/>
     </row>
     <row r="10">
       <c r="A10" s="13" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -3164,7 +3814,7 @@
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="I10" s="13" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
@@ -3195,51 +3845,51 @@
     </row>
     <row r="12">
       <c r="A12" s="14" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G39)</f>
-      </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G62)</f>
+      </c>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G28)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G45)</f>
       </c>
       <c r="I12" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G29)</f>
-      </c>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G46)</f>
+      </c>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
       <c r="O12" s="14" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G38)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G61)</f>
       </c>
     </row>
     <row r="14">
       <c r="F14" t="s">
-        <v>125</v>
-      </c>
-      <c r="G14" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="G14" s="19"/>
       <c r="N14" t="s">
-        <v>125</v>
-      </c>
-      <c r="O14" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="O14" s="19"/>
     </row>
     <row r="15">
       <c r="F15" t="s">
-        <v>126</v>
-      </c>
-      <c r="G15" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="G15" s="19"/>
       <c r="N15" t="s">
-        <v>126</v>
-      </c>
-      <c r="O15" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="O15" s="19"/>
     </row>
     <row r="18">
       <c r="A18" s="13" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -3248,7 +3898,7 @@
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
       <c r="I18" s="13" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
@@ -3279,51 +3929,51 @@
     </row>
     <row r="20">
       <c r="A20" s="14" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O19)</f>
-      </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O30)</f>
+      </c>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
       <c r="G20" s="14" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O8)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O13)</f>
       </c>
       <c r="I20" s="14" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O9)</f>
-      </c>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O14)</f>
+      </c>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
       <c r="O20" s="14" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O18)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O29)</f>
       </c>
     </row>
     <row r="22">
       <c r="F22" t="s">
-        <v>125</v>
-      </c>
-      <c r="G22" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="G22" s="19"/>
       <c r="N22" t="s">
-        <v>125</v>
-      </c>
-      <c r="O22" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="O22" s="19"/>
     </row>
     <row r="23">
       <c r="F23" t="s">
-        <v>126</v>
-      </c>
-      <c r="G23" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="G23" s="19"/>
       <c r="N23" t="s">
-        <v>126</v>
-      </c>
-      <c r="O23" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="O23" s="19"/>
     </row>
     <row r="26">
       <c r="A26" s="13" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
@@ -3332,7 +3982,7 @@
       <c r="F26" s="13"/>
       <c r="G26" s="13"/>
       <c r="I26" s="13" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="J26" s="13"/>
       <c r="K26" s="13"/>
@@ -3363,51 +4013,51 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O39)</f>
-      </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O62)</f>
+      </c>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="14" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O28)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O45)</f>
       </c>
       <c r="I28" s="14" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O29)</f>
-      </c>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O46)</f>
+      </c>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
       <c r="O28" s="14" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O38)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O61)</f>
       </c>
     </row>
     <row r="30">
       <c r="F30" t="s">
-        <v>125</v>
-      </c>
-      <c r="G30" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="G30" s="19"/>
       <c r="N30" t="s">
-        <v>125</v>
-      </c>
-      <c r="O30" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="O30" s="19"/>
     </row>
     <row r="31">
       <c r="F31" t="s">
-        <v>126</v>
-      </c>
-      <c r="G31" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="G31" s="19"/>
       <c r="N31" t="s">
-        <v>126</v>
-      </c>
-      <c r="O31" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="O31" s="19"/>
     </row>
     <row r="39">
       <c r="A39" s="13" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B39" s="13"/>
       <c r="C39" s="13"/>
@@ -3416,7 +4066,7 @@
       <c r="F39" s="13"/>
       <c r="G39" s="13"/>
       <c r="I39" s="13" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J39" s="13"/>
       <c r="K39" s="13"/>
@@ -3449,49 +4099,49 @@
       <c r="A41" s="14" t="str">
         <f>CONCATENATE("M 2 ",G14)</f>
       </c>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
       <c r="G41" s="14" t="str">
         <f>CONCATENATE("M 1 ",G6)</f>
       </c>
       <c r="I41" s="14" t="str">
         <f>CONCATENATE("M 6 ",O14)</f>
       </c>
-      <c r="J41" s="14"/>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="14"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="18"/>
+      <c r="N41" s="18"/>
       <c r="O41" s="14" t="str">
         <f>CONCATENATE("M 5 ",O6)</f>
       </c>
     </row>
     <row r="43">
       <c r="F43" t="s">
-        <v>125</v>
-      </c>
-      <c r="G43" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="G43" s="19"/>
       <c r="N43" t="s">
-        <v>125</v>
-      </c>
-      <c r="O43" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="O43" s="19"/>
     </row>
     <row r="44">
       <c r="F44" t="s">
-        <v>126</v>
-      </c>
-      <c r="G44" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="G44" s="19"/>
       <c r="N44" t="s">
-        <v>126</v>
-      </c>
-      <c r="O44" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="O44" s="19"/>
     </row>
     <row r="47">
       <c r="A47" s="13" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B47" s="13"/>
       <c r="C47" s="13"/>
@@ -3500,7 +4150,7 @@
       <c r="F47" s="13"/>
       <c r="G47" s="13"/>
       <c r="I47" s="13" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="J47" s="13"/>
       <c r="K47" s="13"/>
@@ -3533,49 +4183,49 @@
       <c r="A49" s="14" t="str">
         <f>CONCATENATE("M 4 ",G30)</f>
       </c>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
       <c r="G49" s="14" t="str">
         <f>CONCATENATE("M 3 ",G22)</f>
       </c>
       <c r="I49" s="14" t="str">
         <f>CONCATENATE("M 8 ",O30)</f>
       </c>
-      <c r="J49" s="14"/>
-      <c r="K49" s="14"/>
-      <c r="L49" s="14"/>
-      <c r="M49" s="14"/>
-      <c r="N49" s="14"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="18"/>
+      <c r="M49" s="18"/>
+      <c r="N49" s="18"/>
       <c r="O49" s="14" t="str">
         <f>CONCATENATE("M 7 ",O22)</f>
       </c>
     </row>
     <row r="51">
       <c r="F51" t="s">
-        <v>125</v>
-      </c>
-      <c r="G51" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="G51" s="19"/>
       <c r="N51" t="s">
-        <v>125</v>
-      </c>
-      <c r="O51" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="O51" s="19"/>
     </row>
     <row r="52">
       <c r="F52" t="s">
-        <v>126</v>
-      </c>
-      <c r="G52" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="G52" s="19"/>
       <c r="N52" t="s">
-        <v>126</v>
-      </c>
-      <c r="O52" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="O52" s="19"/>
     </row>
     <row r="60">
       <c r="A60" s="13" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B60" s="13"/>
       <c r="C60" s="13"/>
@@ -3584,7 +4234,7 @@
       <c r="F60" s="13"/>
       <c r="G60" s="13"/>
       <c r="I60" s="13" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J60" s="13"/>
       <c r="K60" s="13"/>
@@ -3617,49 +4267,49 @@
       <c r="A62" s="14" t="str">
         <f>CONCATENATE("M 10 ",G51)</f>
       </c>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
       <c r="G62" s="14" t="str">
         <f>CONCATENATE("M 9 ",G43)</f>
       </c>
       <c r="I62" s="14" t="str">
         <f>CONCATENATE("M 12 ",O51)</f>
       </c>
-      <c r="J62" s="14"/>
-      <c r="K62" s="14"/>
-      <c r="L62" s="14"/>
-      <c r="M62" s="14"/>
-      <c r="N62" s="14"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="18"/>
+      <c r="L62" s="18"/>
+      <c r="M62" s="18"/>
+      <c r="N62" s="18"/>
       <c r="O62" s="14" t="str">
         <f>CONCATENATE("M 11 ",O43)</f>
       </c>
     </row>
     <row r="64">
       <c r="F64" t="s">
-        <v>125</v>
-      </c>
-      <c r="G64" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="G64" s="19"/>
       <c r="N64" t="s">
-        <v>125</v>
-      </c>
-      <c r="O64" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="O64" s="19"/>
     </row>
     <row r="65">
       <c r="F65" t="s">
-        <v>126</v>
-      </c>
-      <c r="G65" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="G65" s="19"/>
       <c r="N65" t="s">
-        <v>126</v>
-      </c>
-      <c r="O65" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="O65" s="19"/>
     </row>
     <row r="73">
       <c r="A73" s="13" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B73" s="13"/>
       <c r="C73" s="13"/>
@@ -3683,28 +4333,29 @@
       <c r="A75" s="14" t="str">
         <f>CONCATENATE("M 14 ",O64)</f>
       </c>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="18"/>
+      <c r="F75" s="18"/>
       <c r="G75" s="14" t="str">
         <f>CONCATENATE("M 13 ",G64)</f>
       </c>
     </row>
     <row r="77">
       <c r="F77" t="s">
-        <v>125</v>
-      </c>
-      <c r="G77" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="G77" s="19"/>
     </row>
     <row r="78">
       <c r="F78" t="s">
-        <v>126</v>
-      </c>
-      <c r="G78" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="G78" s="19"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="17">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:O1"/>
@@ -3765,174 +4416,175 @@
       <c r="P1" s="13"/>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="str">
+      <c r="A4" s="24" t="str">
         <f>data!$A$5</f>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="str">
+      <c r="A5" s="25" t="str">
         <f>"1. " &amp; data!$B$3</f>
       </c>
-      <c r="C5" s="21" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G8)</f>
+      <c r="C5" s="23" t="str">
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G13)</f>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="str">
+      <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$4</f>
       </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="19">
+      <c r="D6" s="22"/>
+      <c r="E6" s="21">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="str">
+      <c r="A7" s="27" t="str">
         <f>"3. " &amp; data!$B$5</f>
       </c>
-      <c r="C7" s="21" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G19)</f>
+      <c r="C7" s="23" t="str">
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G30)</f>
       </c>
       <c r="D7" s="15"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="18"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8">
-      <c r="A8" s="20"/>
-      <c r="G8" s="19">
+      <c r="A8" s="22"/>
+      <c r="G8" s="21">
         <v>9</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="str">
+      <c r="A9" s="24" t="str">
         <f>data!$A$8</f>
       </c>
-      <c r="C9" s="21" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G28)</f>
-      </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="18"/>
+      <c r="C9" s="23" t="str">
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G45)</f>
+      </c>
+      <c r="G9" s="20"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="20"/>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="str">
+      <c r="A10" s="25" t="str">
         <f>"1. " &amp; data!$B$6</f>
       </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="19">
+      <c r="D10" s="22"/>
+      <c r="E10" s="21">
         <v>2</v>
       </c>
       <c r="F10" s="15"/>
-      <c r="G10" s="18"/>
-      <c r="I10" s="18"/>
+      <c r="G10" s="20"/>
+      <c r="I10" s="20"/>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="str">
+      <c r="A11" s="26" t="str">
         <f>"2. " &amp; data!$B$7</f>
       </c>
-      <c r="C11" s="21" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G39)</f>
+      <c r="C11" s="23" t="str">
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G62)</f>
       </c>
       <c r="D11" s="15"/>
-      <c r="E11" s="18"/>
-      <c r="I11" s="18"/>
+      <c r="E11" s="20"/>
+      <c r="I11" s="20"/>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="str">
+      <c r="A12" s="27" t="str">
         <f>"3. " &amp; data!$B$8</f>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="21">
         <v>13</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20"/>
-      <c r="C13" s="21" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O8)</f>
-      </c>
-      <c r="I13" s="18"/>
+      <c r="A13" s="22"/>
+      <c r="C13" s="23" t="str">
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O13)</f>
+      </c>
+      <c r="I13" s="20"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="str">
+      <c r="A14" s="24" t="str">
         <f>data!$A$11</f>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="19">
+      <c r="D14" s="22"/>
+      <c r="E14" s="21">
         <v>3</v>
       </c>
-      <c r="I14" s="18"/>
+      <c r="I14" s="20"/>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="str">
+      <c r="A15" s="25" t="str">
         <f>"1. " &amp; data!$B$9</f>
       </c>
-      <c r="C15" s="21" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O19)</f>
+      <c r="C15" s="23" t="str">
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O30)</f>
       </c>
       <c r="D15" s="15"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="18"/>
-      <c r="I15" s="18"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="20"/>
+      <c r="I15" s="20"/>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="str">
+      <c r="A16" s="26" t="str">
         <f>"2. " &amp; data!$B$10</f>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="21">
         <v>10</v>
       </c>
       <c r="H16" s="15"/>
-      <c r="I16" s="18"/>
+      <c r="I16" s="20"/>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="str">
+      <c r="A17" s="27" t="str">
         <f>"3. " &amp; data!$B$11</f>
       </c>
-      <c r="C17" s="21" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O28)</f>
-      </c>
-      <c r="G17" s="18"/>
+      <c r="C17" s="23" t="str">
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O45)</f>
+      </c>
+      <c r="G17" s="20"/>
     </row>
     <row r="18">
-      <c r="A18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="19">
+      <c r="A18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="21">
         <v>4</v>
       </c>
       <c r="F18" s="15"/>
-      <c r="G18" s="18"/>
+      <c r="G18" s="20"/>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="str">
+      <c r="A19" s="24" t="str">
         <f>data!$A$14</f>
       </c>
-      <c r="C19" s="21" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O39)</f>
+      <c r="C19" s="23" t="str">
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O62)</f>
       </c>
       <c r="D19" s="15"/>
-      <c r="E19" s="18"/>
+      <c r="E19" s="20"/>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="str">
+      <c r="A20" s="25" t="str">
         <f>"1. " &amp; data!$B$12</f>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="str">
+      <c r="A21" s="26" t="str">
         <f>"2. " &amp; data!$B$13</f>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="str">
+      <c r="A22" s="27" t="str">
         <f>"3. " &amp; data!$B$14</f>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20"/>
+      <c r="A23" s="22"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -3971,174 +4623,175 @@
       <c r="P1" s="13"/>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="str">
+      <c r="A4" s="24" t="str">
         <f>data!$A$17</f>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="str">
+      <c r="A5" s="25" t="str">
         <f>"1. " &amp; data!$B$15</f>
       </c>
-      <c r="C5" s="21" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G18)</f>
+      <c r="C5" s="23" t="str">
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G29)</f>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="str">
+      <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$16</f>
       </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="19">
+      <c r="D6" s="22"/>
+      <c r="E6" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="str">
+      <c r="A7" s="27" t="str">
         <f>"3. " &amp; data!$B$17</f>
       </c>
-      <c r="C7" s="21" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G9)</f>
+      <c r="C7" s="23" t="str">
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G14)</f>
       </c>
       <c r="D7" s="15"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="18"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8">
-      <c r="A8" s="20"/>
-      <c r="G8" s="19">
+      <c r="A8" s="22"/>
+      <c r="G8" s="21">
         <v>11</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="str">
+      <c r="A9" s="24" t="str">
         <f>data!$A$20</f>
       </c>
-      <c r="C9" s="21" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G38)</f>
-      </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="18"/>
+      <c r="C9" s="23" t="str">
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G61)</f>
+      </c>
+      <c r="G9" s="20"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="20"/>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="str">
+      <c r="A10" s="25" t="str">
         <f>"1. " &amp; data!$B$18</f>
       </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="19">
+      <c r="D10" s="22"/>
+      <c r="E10" s="21">
         <v>6</v>
       </c>
       <c r="F10" s="15"/>
-      <c r="G10" s="18"/>
-      <c r="I10" s="18"/>
+      <c r="G10" s="20"/>
+      <c r="I10" s="20"/>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="str">
+      <c r="A11" s="26" t="str">
         <f>"2. " &amp; data!$B$19</f>
       </c>
-      <c r="C11" s="21" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G29)</f>
+      <c r="C11" s="23" t="str">
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G46)</f>
       </c>
       <c r="D11" s="15"/>
-      <c r="E11" s="18"/>
-      <c r="I11" s="18"/>
+      <c r="E11" s="20"/>
+      <c r="I11" s="20"/>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="str">
+      <c r="A12" s="27" t="str">
         <f>"3. " &amp; data!$B$20</f>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="21">
         <v>14</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20"/>
-      <c r="C13" s="21" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O18)</f>
-      </c>
-      <c r="I13" s="18"/>
+      <c r="A13" s="22"/>
+      <c r="C13" s="23" t="str">
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O29)</f>
+      </c>
+      <c r="I13" s="20"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="str">
+      <c r="A14" s="24" t="str">
         <f>data!$A$23</f>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="19">
+      <c r="D14" s="22"/>
+      <c r="E14" s="21">
         <v>7</v>
       </c>
-      <c r="I14" s="18"/>
+      <c r="I14" s="20"/>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="str">
+      <c r="A15" s="25" t="str">
         <f>"1. " &amp; data!$B$21</f>
       </c>
-      <c r="C15" s="21" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O9)</f>
+      <c r="C15" s="23" t="str">
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O14)</f>
       </c>
       <c r="D15" s="15"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="18"/>
-      <c r="I15" s="18"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="20"/>
+      <c r="I15" s="20"/>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="str">
+      <c r="A16" s="26" t="str">
         <f>"2. " &amp; data!$B$22</f>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="21">
         <v>12</v>
       </c>
       <c r="H16" s="15"/>
-      <c r="I16" s="18"/>
+      <c r="I16" s="20"/>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="str">
+      <c r="A17" s="27" t="str">
         <f>"3. " &amp; data!$B$23</f>
       </c>
-      <c r="C17" s="21" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O38)</f>
-      </c>
-      <c r="G17" s="18"/>
+      <c r="C17" s="23" t="str">
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O61)</f>
+      </c>
+      <c r="G17" s="20"/>
     </row>
     <row r="18">
-      <c r="A18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="19">
+      <c r="A18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="21">
         <v>8</v>
       </c>
       <c r="F18" s="15"/>
-      <c r="G18" s="18"/>
+      <c r="G18" s="20"/>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="str">
+      <c r="A19" s="24" t="str">
         <f>data!$A$26</f>
       </c>
-      <c r="C19" s="21" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O29)</f>
+      <c r="C19" s="23" t="str">
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O46)</f>
       </c>
       <c r="D19" s="15"/>
-      <c r="E19" s="18"/>
+      <c r="E19" s="20"/>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="str">
+      <c r="A20" s="25" t="str">
         <f>"1. " &amp; data!$B$24</f>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="str">
+      <c r="A21" s="26" t="str">
         <f>"2. " &amp; data!$B$25</f>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="str">
+      <c r="A22" s="27" t="str">
         <f>"3. " &amp; data!$B$26</f>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20"/>
+      <c r="A23" s="22"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -20,10 +20,10 @@
   </sheets>
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$23</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$O$65</definedName>
+    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$P$69</definedName>
     <definedName localSheetId="7" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$12</definedName>
     <definedName localSheetId="8" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$12</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$O$85</definedName>
+    <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$P$85</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
@@ -341,13 +341,19 @@
     <t>PL</t>
   </si>
   <si>
-    <t xml:space="preserve">1. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. </t>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Ranking</t>
+  </si>
+  <si>
+    <t>1.</t>
+  </si>
+  <si>
+    <t>2.</t>
+  </si>
+  <si>
+    <t>3.</t>
   </si>
   <si>
     <t>A1</t>
@@ -423,12 +429,6 @@
   </si>
   <si>
     <t>Round 1 - Match 1</t>
-  </si>
-  <si>
-    <t>1.</t>
-  </si>
-  <si>
-    <t>2.</t>
   </si>
   <si>
     <t>Round 1 - Match 5</t>
@@ -1473,98 +1473,98 @@
   <sheetData>
     <row r="1" ht="270" customHeight="true">
       <c r="A1" s="28" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B1" s="29" t="str">
-        <f>data!D3</f>
+        <f>'data'!D3</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
       <c r="A2" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B2" s="29" t="str">
-        <f>data!D4</f>
+        <f>'data'!D4</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
       <c r="A3" s="28" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B3" s="29" t="str">
-        <f>data!D5</f>
+        <f>'data'!D5</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
       <c r="A4" s="28" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B4" s="29" t="str">
-        <f>data!D6</f>
+        <f>'data'!D6</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
       <c r="A5" s="28" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B5" s="29" t="str">
-        <f>data!D7</f>
+        <f>'data'!D7</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
       <c r="A6" s="28" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B6" s="29" t="str">
-        <f>data!D8</f>
+        <f>'data'!D8</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
       <c r="A7" s="28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B7" s="29" t="str">
-        <f>data!D9</f>
+        <f>'data'!D9</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
       <c r="A8" s="28" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B8" s="29" t="str">
-        <f>data!D10</f>
+        <f>'data'!D10</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
       <c r="A9" s="28" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B9" s="29" t="str">
-        <f>data!D11</f>
+        <f>'data'!D11</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
       <c r="A10" s="28" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B10" s="29" t="str">
-        <f>data!D12</f>
+        <f>'data'!D12</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
       <c r="A11" s="28" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B11" s="29" t="str">
-        <f>data!D13</f>
+        <f>'data'!D13</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
       <c r="A12" s="28" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B12" s="29" t="str">
-        <f>data!D14</f>
+        <f>'data'!D14</f>
       </c>
     </row>
   </sheetData>
@@ -1591,98 +1591,98 @@
   <sheetData>
     <row r="1" ht="270" customHeight="true">
       <c r="A1" s="28" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B1" s="29" t="str">
-        <f>data!D15</f>
+        <f>'data'!D15</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
       <c r="A2" s="28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B2" s="29" t="str">
-        <f>data!D16</f>
+        <f>'data'!D16</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
       <c r="A3" s="28" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B3" s="29" t="str">
-        <f>data!D17</f>
+        <f>'data'!D17</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
       <c r="A4" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B4" s="29" t="str">
-        <f>data!D18</f>
+        <f>'data'!D18</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
       <c r="A5" s="28" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B5" s="29" t="str">
-        <f>data!D19</f>
+        <f>'data'!D19</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
       <c r="A6" s="28" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B6" s="29" t="str">
-        <f>data!D20</f>
+        <f>'data'!D20</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
       <c r="A7" s="28" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B7" s="29" t="str">
-        <f>data!D21</f>
+        <f>'data'!D21</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
       <c r="A8" s="28" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B8" s="29" t="str">
-        <f>data!D22</f>
+        <f>'data'!D22</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
       <c r="A9" s="28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B9" s="29" t="str">
-        <f>data!D23</f>
+        <f>'data'!D23</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
       <c r="A10" s="28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B10" s="29" t="str">
-        <f>data!D24</f>
+        <f>'data'!D24</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
       <c r="A11" s="28" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B11" s="29" t="str">
-        <f>data!D25</f>
+        <f>'data'!D25</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
       <c r="A12" s="28" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B12" s="29" t="str">
-        <f>data!D26</f>
+        <f>'data'!D26</f>
       </c>
     </row>
   </sheetData>
@@ -1708,242 +1708,242 @@
   <sheetData>
     <row r="1" ht="390" customHeight="true">
       <c r="A1" s="30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" ht="390" customHeight="true">
       <c r="A2" s="30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" ht="390" customHeight="true">
       <c r="A3" s="30" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" ht="390" customHeight="true">
       <c r="A4" s="30" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" ht="390" customHeight="true">
       <c r="A5" s="30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" ht="390" customHeight="true">
       <c r="A6" s="30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" ht="390" customHeight="true">
       <c r="A7" s="30" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" ht="390" customHeight="true">
       <c r="A8" s="30" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" ht="390" customHeight="true">
       <c r="A9" s="30" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" ht="390" customHeight="true">
       <c r="A10" s="30" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" ht="390" customHeight="true">
       <c r="A11" s="30" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" ht="390" customHeight="true">
       <c r="A12" s="30" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" ht="390" customHeight="true">
       <c r="A13" s="30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" ht="390" customHeight="true">
       <c r="A14" s="30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" ht="390" customHeight="true">
       <c r="A15" s="30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" ht="390" customHeight="true">
       <c r="A16" s="30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" ht="390" customHeight="true">
       <c r="A17" s="30" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" ht="390" customHeight="true">
       <c r="A18" s="30" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" ht="390" customHeight="true">
       <c r="A19" s="30" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" ht="390" customHeight="true">
       <c r="A20" s="30" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" ht="390" customHeight="true">
       <c r="A21" s="30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" ht="390" customHeight="true">
       <c r="A22" s="30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" ht="390" customHeight="true">
       <c r="A23" s="30" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" ht="390" customHeight="true">
       <c r="A24" s="30" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" ht="390" customHeight="true">
       <c r="A25" s="30" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" ht="390" customHeight="true">
       <c r="A26" s="30" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" ht="390" customHeight="true">
       <c r="A27" s="30" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" ht="390" customHeight="true">
       <c r="A28" s="30" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" ht="390" customHeight="true">
       <c r="A29" s="30" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" ht="390" customHeight="true">
       <c r="A30" s="30" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" ht="390" customHeight="true">
       <c r="A31" s="30" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" ht="390" customHeight="true">
       <c r="A32" s="30" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" ht="390" customHeight="true">
       <c r="A33" s="30" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" ht="390" customHeight="true">
       <c r="A34" s="30" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" ht="390" customHeight="true">
       <c r="A35" s="30" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" ht="390" customHeight="true">
       <c r="A36" s="30" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" ht="390" customHeight="true">
       <c r="A37" s="30" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" ht="390" customHeight="true">
       <c r="A38" s="30" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" ht="390" customHeight="true">
       <c r="A39" s="30" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40" ht="390" customHeight="true">
       <c r="A40" s="30" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" ht="390" customHeight="true">
       <c r="A41" s="30" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" ht="390" customHeight="true">
       <c r="A42" s="30" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" ht="390" customHeight="true">
       <c r="A43" s="30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44" ht="390" customHeight="true">
       <c r="A44" s="30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45" ht="390" customHeight="true">
       <c r="A45" s="30" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="46" ht="390" customHeight="true">
       <c r="A46" s="30" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="47" ht="390" customHeight="true">
       <c r="A47" s="30" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="48" ht="390" customHeight="true">
       <c r="A48" s="30" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2303,13 +2303,13 @@
     </row>
     <row r="5" ht="17" customHeight="true">
       <c r="B5" s="11" t="str">
-        <f>data!$A$5</f>
+        <f>'data'!$A$5</f>
       </c>
       <c r="D5" s="11" t="str">
-        <f>data!$A$14</f>
+        <f>'data'!$A$14</f>
       </c>
       <c r="F5" s="11" t="str">
-        <f>data!$A$23</f>
+        <f>'data'!$A$23</f>
       </c>
     </row>
     <row r="6" ht="17" customHeight="true">
@@ -2347,13 +2347,13 @@
     </row>
     <row r="11">
       <c r="B11" s="11" t="str">
-        <f>data!$A$8</f>
+        <f>'data'!$A$8</f>
       </c>
       <c r="D11" s="11" t="str">
-        <f>data!$A$17</f>
+        <f>'data'!$A$17</f>
       </c>
       <c r="F11" s="11" t="str">
-        <f>data!$A$26</f>
+        <f>'data'!$A$26</f>
       </c>
     </row>
     <row r="12">
@@ -2391,10 +2391,10 @@
     </row>
     <row r="17">
       <c r="B17" s="11" t="str">
-        <f>data!$A$11</f>
+        <f>'data'!$A$11</f>
       </c>
       <c r="D17" s="11" t="str">
-        <f>data!$A$20</f>
+        <f>'data'!$A$20</f>
       </c>
     </row>
     <row r="18">
@@ -2439,19 +2439,16 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="3" min="2" width="5"/>
-    <col customWidth="true" max="4" min="4" width="3"/>
-    <col customWidth="true" max="6" min="5" width="5"/>
+    <col customWidth="true" max="6" min="2" width="5"/>
     <col customWidth="true" max="7" min="7" width="30"/>
     <col customWidth="true" max="8" min="8" width="5"/>
     <col customWidth="true" max="9" min="9" width="30"/>
-    <col customWidth="true" max="11" min="10" width="5"/>
-    <col customWidth="true" max="12" min="12" width="3"/>
-    <col customWidth="true" max="14" min="13" width="5"/>
+    <col customWidth="true" max="14" min="10" width="5"/>
     <col customWidth="true" max="15" min="15" width="30"/>
-    <col customWidth="true" max="18" min="16" width="5"/>
-    <col customWidth="true" max="19" min="19" width="30"/>
-    <col customWidth="true" max="20" min="20" width="2"/>
+    <col customWidth="true" max="16" min="16" width="5"/>
+    <col customWidth="true" max="20" min="17" width="10.83"/>
+    <col customWidth="true" hidden="true" max="21" min="21" width="9.140625"/>
+    <col customWidth="true" hidden="true" max="29" min="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2476,7 +2473,7 @@
     </row>
     <row r="2">
       <c r="A2" s="13" t="str">
-        <f>data!$A$5</f>
+        <f>'data'!$A$5</f>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -2485,7 +2482,7 @@
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
       <c r="I2" s="13" t="str">
-        <f>data!$A$17</f>
+        <f>'data'!$A$17</f>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
@@ -2516,7 +2513,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>data!$B$4</f>
+        <f>'data'!$B$4</f>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -2524,10 +2521,10 @@
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
       <c r="G4" s="14" t="str">
-        <f>data!$B$3</f>
+        <f>'data'!$B$3</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>data!$B$16</f>
+        <f>'data'!$B$16</f>
       </c>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
@@ -2535,12 +2532,12 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
       <c r="O4" s="14" t="str">
-        <f>data!$B$15</f>
+        <f>'data'!$B$15</f>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="str">
-        <f>data!$B$5</f>
+        <f>'data'!$B$5</f>
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
@@ -2548,10 +2545,10 @@
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
       <c r="G5" s="14" t="str">
-        <f>data!$B$3</f>
+        <f>'data'!$B$3</f>
       </c>
       <c r="I5" s="14" t="str">
-        <f>data!$B$17</f>
+        <f>'data'!$B$17</f>
       </c>
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>
@@ -2559,12 +2556,12 @@
       <c r="M5" s="18"/>
       <c r="N5" s="18"/>
       <c r="O5" s="14" t="str">
-        <f>data!$B$15</f>
+        <f>'data'!$B$15</f>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="str">
-        <f>data!$B$5</f>
+        <f>'data'!$B$5</f>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -2572,10 +2569,10 @@
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="G6" s="14" t="str">
-        <f>data!$B$4</f>
+        <f>'data'!$B$4</f>
       </c>
       <c r="I6" s="14" t="str">
-        <f>data!$B$17</f>
+        <f>'data'!$B$17</f>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
@@ -2583,7 +2580,7 @@
       <c r="M6" s="18"/>
       <c r="N6" s="18"/>
       <c r="O6" s="14" t="str">
-        <f>data!$B$16</f>
+        <f>'data'!$B$16</f>
       </c>
     </row>
     <row r="8">
@@ -2605,6 +2602,9 @@
       <c r="F8" s="13" t="s">
         <v>102</v>
       </c>
+      <c r="G8" s="13" t="s">
+        <v>103</v>
+      </c>
       <c r="I8" s="13" t="s">
         <v>97</v>
       </c>
@@ -2623,19 +2623,22 @@
       <c r="N8" s="13" t="s">
         <v>102</v>
       </c>
+      <c r="O8" s="13" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="str">
-        <f>data!$B$3</f>
+        <f>'data'!$B$3</f>
       </c>
       <c r="B9" s="14" t="str">
-        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x",AND(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x",AND(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="C9" s="14" t="str">
-        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x",AND(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x",AND(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="D9" s="14" t="str">
-        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),1,0),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x",AND(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x",AND(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="E9" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))</f>
@@ -2643,17 +2646,20 @@
       <c r="F9" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))</f>
       </c>
+      <c r="G9" s="18" t="str">
+        <f>RANK(U9,$U$9:$U$11)+COUNTIF($U$8:U8,U9)</f>
+      </c>
       <c r="I9" s="14" t="str">
-        <f>data!$B$15</f>
+        <f>'data'!$B$15</f>
       </c>
       <c r="J9" s="14" t="str">
-        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x",AND(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x",AND(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="K9" s="14" t="str">
-        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x",AND(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x",AND(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="L9" s="14" t="str">
-        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),1,0),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x",AND(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x",AND(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="M9" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))</f>
@@ -2661,19 +2667,28 @@
       <c r="N9" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))</f>
       </c>
+      <c r="O9" s="18" t="str">
+        <f>RANK(AC9,$AC$9:$AC$11)+COUNTIF($AC$8:AC8,AC9)</f>
+      </c>
+      <c r="U9" t="str">
+        <f>=(B9*1000000)-(C9*10000)+(D9*100)+(E9*1)-(F9*0.01)</f>
+      </c>
+      <c r="AC9" t="str">
+        <f>=(J9*1000000)-(K9*10000)+(L9*100)+(M9*1)-(N9*0.01)</f>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="str">
-        <f>data!$B$4</f>
+        <f>'data'!$B$4</f>
       </c>
       <c r="B10" s="14" t="str">
-        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x",AND(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x",AND(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="C10" s="14" t="str">
-        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x",AND(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x",AND(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="D10" s="14" t="str">
-        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),1,0),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x",AND(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x",AND(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="E10" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))</f>
@@ -2681,17 +2696,20 @@
       <c r="F10" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))</f>
       </c>
+      <c r="G10" s="18" t="str">
+        <f>RANK(U10,$U$9:$U$11)+COUNTIF($U$8:U9,U10)</f>
+      </c>
       <c r="I10" s="14" t="str">
-        <f>data!$B$16</f>
+        <f>'data'!$B$16</f>
       </c>
       <c r="J10" s="14" t="str">
-        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x",AND(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x",AND(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="K10" s="14" t="str">
-        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x",AND(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x",AND(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="L10" s="14" t="str">
-        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),1,0),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x",AND(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x",AND(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="M10" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))</f>
@@ -2699,19 +2717,28 @@
       <c r="N10" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))</f>
       </c>
+      <c r="O10" s="18" t="str">
+        <f>RANK(AC10,$AC$9:$AC$11)+COUNTIF($AC$8:AC9,AC10)</f>
+      </c>
+      <c r="U10" t="str">
+        <f>=(B10*1000000)-(C10*10000)+(D10*100)+(E10*1)-(F10*0.01)</f>
+      </c>
+      <c r="AC10" t="str">
+        <f>=(J10*1000000)-(K10*10000)+(L10*100)+(M10*1)-(N10*0.01)</f>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="str">
-        <f>data!$B$5</f>
+        <f>'data'!$B$5</f>
       </c>
       <c r="B11" s="14" t="str">
-        <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x",AND(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x",AND(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="C11" s="14" t="str">
-        <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x",AND(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x",AND(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="D11" s="14" t="str">
-        <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),1,0),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x",AND(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x",AND(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="E11" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))</f>
@@ -2719,17 +2746,20 @@
       <c r="F11" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))</f>
       </c>
+      <c r="G11" s="18" t="str">
+        <f>RANK(U11,$U$9:$U$11)+COUNTIF($U$8:U10,U11)</f>
+      </c>
       <c r="I11" s="14" t="str">
-        <f>data!$B$17</f>
+        <f>'data'!$B$17</f>
       </c>
       <c r="J11" s="14" t="str">
-        <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x",AND(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x",AND(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="K11" s="14" t="str">
-        <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x",AND(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x",AND(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="L11" s="14" t="str">
-        <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),1,0),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x",AND(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x",AND(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="M11" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))</f>
@@ -2737,104 +2767,111 @@
       <c r="N11" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))</f>
       </c>
-    </row>
-    <row r="13">
-      <c r="F13" t="s">
-        <v>103</v>
-      </c>
-      <c r="G13" s="19"/>
-      <c r="N13" t="s">
-        <v>103</v>
-      </c>
-      <c r="O13" s="19"/>
+      <c r="O11" s="18" t="str">
+        <f>RANK(AC11,$AC$9:$AC$11)+COUNTIF($AC$8:AC10,AC11)</f>
+      </c>
+      <c r="U11" t="str">
+        <f>=(B11*1000000)-(C11*10000)+(D11*100)+(E11*1)-(F11*0.01)</f>
+      </c>
+      <c r="AC11" t="str">
+        <f>=(J11*1000000)-(K11*10000)+(L11*100)+(M11*1)-(N11*0.01)</f>
+      </c>
     </row>
     <row r="14">
-      <c r="F14" t="s">
+      <c r="F14" s="13"/>
+      <c r="G14" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="G14" s="19"/>
-      <c r="N14" t="s">
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="O14" s="19"/>
     </row>
     <row r="15">
       <c r="F15" t="s">
         <v>105</v>
       </c>
-      <c r="G15" s="19"/>
+      <c r="G15" s="19" t="str">
+        <f>IFERROR(INDEX($A$9:$A$11, MATCH(1, $G$9:$G$11, 0)), "-")</f>
+      </c>
       <c r="N15" t="s">
         <v>105</v>
       </c>
-      <c r="O15" s="19"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="str">
-        <f>data!$A$8</f>
-      </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="I18" s="13" t="str">
-        <f>data!$A$20</f>
-      </c>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
+      <c r="O15" s="19" t="str">
+        <f>IFERROR(INDEX($I$9:$I$11, MATCH(1, $O$9:$O$11, 0)), "-")</f>
+      </c>
+    </row>
+    <row r="16">
+      <c r="F16" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" s="19" t="str">
+        <f>IFERROR(INDEX($A$9:$A$11, MATCH(2, $G$9:$G$11, 0)), "-")</f>
+      </c>
+      <c r="N16" t="s">
+        <v>106</v>
+      </c>
+      <c r="O16" s="19" t="str">
+        <f>IFERROR(INDEX($I$9:$I$11, MATCH(2, $O$9:$O$11, 0)), "-")</f>
+      </c>
+    </row>
+    <row r="17">
+      <c r="F17" t="s">
+        <v>107</v>
+      </c>
+      <c r="G17" s="19" t="str">
+        <f>IFERROR(INDEX($A$9:$A$11, MATCH(3, $G$9:$G$11, 0)), "-")</f>
+      </c>
+      <c r="N17" t="s">
+        <v>107</v>
+      </c>
+      <c r="O17" s="19" t="str">
+        <f>IFERROR(INDEX($I$9:$I$11, MATCH(3, $O$9:$O$11, 0)), "-")</f>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="13" t="str">
+        <f>'data'!$A$8</f>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="I19" s="13" t="str">
+        <f>'data'!$A$20</f>
+      </c>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D20" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="16" t="s">
+      <c r="G20" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="I19" s="17" t="s">
+      <c r="I20" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="L19" s="14" t="s">
+      <c r="L20" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="O19" s="16" t="s">
+      <c r="O20" s="16" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="str">
-        <f>data!$B$7</f>
-      </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="14" t="str">
-        <f>data!$B$6</f>
-      </c>
-      <c r="I20" s="14" t="str">
-        <f>data!$B$19</f>
-      </c>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18"/>
-      <c r="M20" s="18"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="14" t="str">
-        <f>data!$B$18</f>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="str">
-        <f>data!$B$8</f>
+        <f>'data'!$B$7</f>
       </c>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -2842,10 +2879,10 @@
       <c r="E21" s="18"/>
       <c r="F21" s="18"/>
       <c r="G21" s="14" t="str">
-        <f>data!$B$6</f>
+        <f>'data'!$B$6</f>
       </c>
       <c r="I21" s="14" t="str">
-        <f>data!$B$20</f>
+        <f>'data'!$B$19</f>
       </c>
       <c r="J21" s="18"/>
       <c r="K21" s="18"/>
@@ -2853,12 +2890,12 @@
       <c r="M21" s="18"/>
       <c r="N21" s="18"/>
       <c r="O21" s="14" t="str">
-        <f>data!$B$18</f>
+        <f>'data'!$B$18</f>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="str">
-        <f>data!$B$8</f>
+        <f>'data'!$B$8</f>
       </c>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -2866,10 +2903,10 @@
       <c r="E22" s="18"/>
       <c r="F22" s="18"/>
       <c r="G22" s="14" t="str">
-        <f>data!$B$7</f>
+        <f>'data'!$B$6</f>
       </c>
       <c r="I22" s="14" t="str">
-        <f>data!$B$20</f>
+        <f>'data'!$B$20</f>
       </c>
       <c r="J22" s="18"/>
       <c r="K22" s="18"/>
@@ -2877,282 +2914,322 @@
       <c r="M22" s="18"/>
       <c r="N22" s="18"/>
       <c r="O22" s="14" t="str">
-        <f>data!$B$19</f>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="s">
+        <f>'data'!$B$18</f>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="str">
+        <f>'data'!$B$8</f>
+      </c>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="14" t="str">
+        <f>'data'!$B$7</f>
+      </c>
+      <c r="I23" s="14" t="str">
+        <f>'data'!$B$20</f>
+      </c>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="14" t="str">
+        <f>'data'!$B$19</f>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B25" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C25" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D25" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E25" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="F24" s="13" t="s">
+      <c r="F25" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="I24" s="13" t="s">
+      <c r="G25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="I25" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="J24" s="13" t="s">
+      <c r="J25" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="K24" s="13" t="s">
+      <c r="K25" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L24" s="13" t="s">
+      <c r="L25" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="M24" s="13" t="s">
+      <c r="M25" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="N24" s="13" t="s">
+      <c r="N25" s="13" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="str">
-        <f>data!$B$6</f>
-      </c>
-      <c r="B25" s="14" t="str">
-        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="C25" s="14" t="str">
-        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="D25" s="14" t="str">
-        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),1,0),0)+IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),1,0),0)</f>
-      </c>
-      <c r="E25" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F25" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="I25" s="14" t="str">
-        <f>data!$B$18</f>
-      </c>
-      <c r="J25" s="14" t="str">
-        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="K25" s="14" t="str">
-        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="L25" s="14" t="str">
-        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),1,0),0)+IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),1,0),0)</f>
-      </c>
-      <c r="M25" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="N25" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))</f>
+      <c r="O25" s="13" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="str">
-        <f>data!$B$7</f>
+        <f>'data'!$B$6</f>
       </c>
       <c r="B26" s="14" t="str">
-        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x",AND(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x",AND(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="C26" s="14" t="str">
-        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x",AND(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x",AND(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="D26" s="14" t="str">
-        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),1,0),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x",AND(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x",AND(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="E26" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F26" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="G26" s="18" t="str">
+        <f>RANK(U26,$U$26:$U$28)+COUNTIF($U$25:U25,U26)</f>
       </c>
       <c r="I26" s="14" t="str">
-        <f>data!$B$19</f>
+        <f>'data'!$B$18</f>
       </c>
       <c r="J26" s="14" t="str">
-        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x",AND(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x",AND(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="K26" s="14" t="str">
-        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x",AND(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x",AND(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="L26" s="14" t="str">
-        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),1,0),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x",AND(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x",AND(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="M26" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N26" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="O26" s="18" t="str">
+        <f>RANK(AC26,$AC$26:$AC$28)+COUNTIF($AC$25:AC25,AC26)</f>
+      </c>
+      <c r="U26" t="str">
+        <f>=(B26*1000000)-(C26*10000)+(D26*100)+(E26*1)-(F26*0.01)</f>
+      </c>
+      <c r="AC26" t="str">
+        <f>=(J26*1000000)-(K26*10000)+(L26*100)+(M26*1)-(N26*0.01)</f>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="str">
-        <f>data!$B$8</f>
+        <f>'data'!$B$7</f>
       </c>
       <c r="B27" s="14" t="str">
-        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x",AND(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),IF(OR(D23="X",D23="x",AND(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="C27" s="14" t="str">
-        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x",AND(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),IF(OR(D23="X",D23="x",AND(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="D27" s="14" t="str">
-        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),1,0),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x",AND(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),IF(OR(D23="X",D23="x",AND(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="E27" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F27" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="G27" s="18" t="str">
+        <f>RANK(U27,$U$26:$U$28)+COUNTIF($U$25:U26,U27)</f>
       </c>
       <c r="I27" s="14" t="str">
-        <f>data!$B$20</f>
+        <f>'data'!$B$19</f>
       </c>
       <c r="J27" s="14" t="str">
-        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x",AND(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),IF(OR(L23="X",L23="x",AND(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="K27" s="14" t="str">
-        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x",AND(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),IF(OR(L23="X",L23="x",AND(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="L27" s="14" t="str">
-        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),1,0),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x",AND(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),IF(OR(L23="X",L23="x",AND(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="M27" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N27" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))</f>
-      </c>
-    </row>
-    <row r="29">
-      <c r="F29" t="s">
-        <v>103</v>
-      </c>
-      <c r="G29" s="19"/>
-      <c r="N29" t="s">
-        <v>103</v>
-      </c>
-      <c r="O29" s="19"/>
-    </row>
-    <row r="30">
-      <c r="F30" t="s">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="O27" s="18" t="str">
+        <f>RANK(AC27,$AC$26:$AC$28)+COUNTIF($AC$25:AC26,AC27)</f>
+      </c>
+      <c r="U27" t="str">
+        <f>=(B27*1000000)-(C27*10000)+(D27*100)+(E27*1)-(F27*0.01)</f>
+      </c>
+      <c r="AC27" t="str">
+        <f>=(J27*1000000)-(K27*10000)+(L27*100)+(M27*1)-(N27*0.01)</f>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="str">
+        <f>'data'!$B$8</f>
+      </c>
+      <c r="B28" s="14" t="str">
+        <f>IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x",AND(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),IF(OR(D23="X",D23="x",AND(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C28" s="14" t="str">
+        <f>IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x",AND(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),IF(OR(D23="X",D23="x",AND(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D28" s="14" t="str">
+        <f>IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x",AND(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),IF(OR(D23="X",D23="x",AND(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="E28" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F28" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="G28" s="18" t="str">
+        <f>RANK(U28,$U$26:$U$28)+COUNTIF($U$25:U27,U28)</f>
+      </c>
+      <c r="I28" s="14" t="str">
+        <f>'data'!$B$20</f>
+      </c>
+      <c r="J28" s="14" t="str">
+        <f>IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x",AND(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),IF(OR(L23="X",L23="x",AND(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K28" s="14" t="str">
+        <f>IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x",AND(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),IF(OR(L23="X",L23="x",AND(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L28" s="14" t="str">
+        <f>IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x",AND(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),IF(OR(L23="X",L23="x",AND(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="M28" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N28" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="O28" s="18" t="str">
+        <f>RANK(AC28,$AC$26:$AC$28)+COUNTIF($AC$25:AC27,AC28)</f>
+      </c>
+      <c r="U28" t="str">
+        <f>=(B28*1000000)-(C28*10000)+(D28*100)+(E28*1)-(F28*0.01)</f>
+      </c>
+      <c r="AC28" t="str">
+        <f>=(J28*1000000)-(K28*10000)+(L28*100)+(M28*1)-(N28*0.01)</f>
+      </c>
+    </row>
+    <row r="31">
+      <c r="F31" s="13"/>
+      <c r="G31" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="G30" s="19"/>
-      <c r="N30" t="s">
+      <c r="N31" s="13"/>
+      <c r="O31" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="O30" s="19"/>
-    </row>
-    <row r="31">
-      <c r="F31" t="s">
+    </row>
+    <row r="32">
+      <c r="F32" t="s">
         <v>105</v>
       </c>
-      <c r="G31" s="19"/>
-      <c r="N31" t="s">
+      <c r="G32" s="19" t="str">
+        <f>IFERROR(INDEX($A$26:$A$28, MATCH(1, $G$26:$G$28, 0)), "-")</f>
+      </c>
+      <c r="N32" t="s">
         <v>105</v>
       </c>
-      <c r="O31" s="19"/>
+      <c r="O32" s="19" t="str">
+        <f>IFERROR(INDEX($I$26:$I$28, MATCH(1, $O$26:$O$28, 0)), "-")</f>
+      </c>
+    </row>
+    <row r="33">
+      <c r="F33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G33" s="19" t="str">
+        <f>IFERROR(INDEX($A$26:$A$28, MATCH(2, $G$26:$G$28, 0)), "-")</f>
+      </c>
+      <c r="N33" t="s">
+        <v>106</v>
+      </c>
+      <c r="O33" s="19" t="str">
+        <f>IFERROR(INDEX($I$26:$I$28, MATCH(2, $O$26:$O$28, 0)), "-")</f>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="str">
-        <f>data!$A$11</f>
-      </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="I34" s="13" t="str">
-        <f>data!$A$23</f>
-      </c>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="13"/>
-      <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="13"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="17" t="s">
+      <c r="F34" t="s">
+        <v>107</v>
+      </c>
+      <c r="G34" s="19" t="str">
+        <f>IFERROR(INDEX($A$26:$A$28, MATCH(3, $G$26:$G$28, 0)), "-")</f>
+      </c>
+      <c r="N34" t="s">
+        <v>107</v>
+      </c>
+      <c r="O34" s="19" t="str">
+        <f>IFERROR(INDEX($I$26:$I$28, MATCH(3, $O$26:$O$28, 0)), "-")</f>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="str">
+        <f>'data'!$A$11</f>
+      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="I36" s="13" t="str">
+        <f>'data'!$A$23</f>
+      </c>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D37" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="G35" s="16" t="s">
+      <c r="G37" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="I35" s="17" t="s">
+      <c r="I37" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="L35" s="14" t="s">
+      <c r="L37" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="O35" s="16" t="s">
+      <c r="O37" s="16" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="str">
-        <f>data!$B$10</f>
-      </c>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="14" t="str">
-        <f>data!$B$9</f>
-      </c>
-      <c r="I36" s="14" t="str">
-        <f>data!$B$22</f>
-      </c>
-      <c r="J36" s="18"/>
-      <c r="K36" s="18"/>
-      <c r="L36" s="18"/>
-      <c r="M36" s="18"/>
-      <c r="N36" s="18"/>
-      <c r="O36" s="14" t="str">
-        <f>data!$B$21</f>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="str">
-        <f>data!$B$11</f>
-      </c>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="14" t="str">
-        <f>data!$B$9</f>
-      </c>
-      <c r="I37" s="14" t="str">
-        <f>data!$B$23</f>
-      </c>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="18"/>
-      <c r="M37" s="18"/>
-      <c r="N37" s="18"/>
-      <c r="O37" s="14" t="str">
-        <f>data!$B$21</f>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="str">
-        <f>data!$B$11</f>
+        <f>'data'!$B$10</f>
       </c>
       <c r="B38" s="18"/>
       <c r="C38" s="18"/>
@@ -3160,10 +3237,10 @@
       <c r="E38" s="18"/>
       <c r="F38" s="18"/>
       <c r="G38" s="14" t="str">
-        <f>data!$B$10</f>
+        <f>'data'!$B$9</f>
       </c>
       <c r="I38" s="14" t="str">
-        <f>data!$B$23</f>
+        <f>'data'!$B$22</f>
       </c>
       <c r="J38" s="18"/>
       <c r="K38" s="18"/>
@@ -3171,484 +3248,660 @@
       <c r="M38" s="18"/>
       <c r="N38" s="18"/>
       <c r="O38" s="14" t="str">
-        <f>data!$B$22</f>
+        <f>'data'!$B$21</f>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="str">
+        <f>'data'!$B$11</f>
+      </c>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="14" t="str">
+        <f>'data'!$B$9</f>
+      </c>
+      <c r="I39" s="14" t="str">
+        <f>'data'!$B$23</f>
+      </c>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="18"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="14" t="str">
+        <f>'data'!$B$21</f>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="14" t="str">
+        <f>'data'!$B$11</f>
+      </c>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="14" t="str">
+        <f>'data'!$B$10</f>
+      </c>
+      <c r="I40" s="14" t="str">
+        <f>'data'!$B$23</f>
+      </c>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="18"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="14" t="str">
+        <f>'data'!$B$22</f>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B42" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C42" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D42" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="E40" s="13" t="s">
+      <c r="E42" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="F40" s="13" t="s">
+      <c r="F42" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="I40" s="13" t="s">
+      <c r="G42" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="I42" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="J40" s="13" t="s">
+      <c r="J42" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="K40" s="13" t="s">
+      <c r="K42" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L40" s="13" t="s">
+      <c r="L42" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="M40" s="13" t="s">
+      <c r="M42" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="N40" s="13" t="s">
+      <c r="N42" s="13" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="14" t="str">
-        <f>data!$B$9</f>
-      </c>
-      <c r="B41" s="14" t="str">
-        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="C41" s="14" t="str">
-        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="D41" s="14" t="str">
-        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),1,0),0)+IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),1,0),0)</f>
-      </c>
-      <c r="E41" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F41" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="I41" s="14" t="str">
-        <f>data!$B$21</f>
-      </c>
-      <c r="J41" s="14" t="str">
-        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="K41" s="14" t="str">
-        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="L41" s="14" t="str">
-        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),1,0),0)+IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),1,0),0)</f>
-      </c>
-      <c r="M41" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="N41" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-",""))</f>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="str">
-        <f>data!$B$10</f>
-      </c>
-      <c r="B42" s="14" t="str">
-        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="C42" s="14" t="str">
-        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="D42" s="14" t="str">
-        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),1,0),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),1,0),0)</f>
-      </c>
-      <c r="E42" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F42" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="I42" s="14" t="str">
-        <f>data!$B$22</f>
-      </c>
-      <c r="J42" s="14" t="str">
-        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="K42" s="14" t="str">
-        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="L42" s="14" t="str">
-        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),1,0),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),1,0),0)</f>
-      </c>
-      <c r="M42" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="N42" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))</f>
+      <c r="O42" s="13" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="str">
-        <f>data!$B$11</f>
+        <f>'data'!$B$9</f>
       </c>
       <c r="B43" s="14" t="str">
-        <f>IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x",AND(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),IF(OR(D39="X",D39="x",AND(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="C43" s="14" t="str">
-        <f>IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x",AND(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),IF(OR(D39="X",D39="x",AND(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="D43" s="14" t="str">
-        <f>IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),1,0),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x",AND(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),IF(OR(D39="X",D39="x",AND(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="E43" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F43" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="G43" s="18" t="str">
+        <f>RANK(U43,$U$43:$U$45)+COUNTIF($U$42:U42,U43)</f>
       </c>
       <c r="I43" s="14" t="str">
-        <f>data!$B$23</f>
+        <f>'data'!$B$21</f>
       </c>
       <c r="J43" s="14" t="str">
-        <f>IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x",AND(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),IF(OR(L39="X",L39="x",AND(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="K43" s="14" t="str">
-        <f>IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x",AND(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),IF(OR(L39="X",L39="x",AND(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="L43" s="14" t="str">
-        <f>IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),1,0),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x",AND(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),IF(OR(L39="X",L39="x",AND(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="M43" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N43" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="O43" s="18" t="str">
+        <f>RANK(AC43,$AC$43:$AC$45)+COUNTIF($AC$42:AC42,AC43)</f>
+      </c>
+      <c r="U43" t="str">
+        <f>=(B43*1000000)-(C43*10000)+(D43*100)+(E43*1)-(F43*0.01)</f>
+      </c>
+      <c r="AC43" t="str">
+        <f>=(J43*1000000)-(K43*10000)+(L43*100)+(M43*1)-(N43*0.01)</f>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="str">
+        <f>'data'!$B$10</f>
+      </c>
+      <c r="B44" s="14" t="str">
+        <f>IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x",AND(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),IF(OR(D40="X",D40="x",AND(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C44" s="14" t="str">
+        <f>IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x",AND(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),IF(OR(D40="X",D40="x",AND(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D44" s="14" t="str">
+        <f>IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x",AND(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),IF(OR(D40="X",D40="x",AND(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="E44" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F44" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="G44" s="18" t="str">
+        <f>RANK(U44,$U$43:$U$45)+COUNTIF($U$42:U43,U44)</f>
+      </c>
+      <c r="I44" s="14" t="str">
+        <f>'data'!$B$22</f>
+      </c>
+      <c r="J44" s="14" t="str">
+        <f>IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x",AND(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),IF(OR(L40="X",L40="x",AND(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K44" s="14" t="str">
+        <f>IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x",AND(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),IF(OR(L40="X",L40="x",AND(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L44" s="14" t="str">
+        <f>IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x",AND(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),IF(OR(L40="X",L40="x",AND(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="M44" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N44" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="O44" s="18" t="str">
+        <f>RANK(AC44,$AC$43:$AC$45)+COUNTIF($AC$42:AC43,AC44)</f>
+      </c>
+      <c r="U44" t="str">
+        <f>=(B44*1000000)-(C44*10000)+(D44*100)+(E44*1)-(F44*0.01)</f>
+      </c>
+      <c r="AC44" t="str">
+        <f>=(J44*1000000)-(K44*10000)+(L44*100)+(M44*1)-(N44*0.01)</f>
       </c>
     </row>
     <row r="45">
-      <c r="F45" t="s">
-        <v>103</v>
-      </c>
-      <c r="G45" s="19"/>
-      <c r="N45" t="s">
-        <v>103</v>
-      </c>
-      <c r="O45" s="19"/>
-    </row>
-    <row r="46">
-      <c r="F46" t="s">
+      <c r="A45" s="14" t="str">
+        <f>'data'!$B$11</f>
+      </c>
+      <c r="B45" s="14" t="str">
+        <f>IF(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),IF(OR(D39="X",D39="x",AND(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),IF(OR(D40="X",D40="x",AND(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C45" s="14" t="str">
+        <f>IF(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),IF(OR(D39="X",D39="x",AND(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),IF(OR(D40="X",D40="x",AND(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D45" s="14" t="str">
+        <f>IF(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),IF(OR(D39="X",D39="x",AND(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),IF(OR(D40="X",D40="x",AND(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="E45" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F45" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="G45" s="18" t="str">
+        <f>RANK(U45,$U$43:$U$45)+COUNTIF($U$42:U44,U45)</f>
+      </c>
+      <c r="I45" s="14" t="str">
+        <f>'data'!$B$23</f>
+      </c>
+      <c r="J45" s="14" t="str">
+        <f>IF(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),IF(OR(L39="X",L39="x",AND(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),IF(OR(L40="X",L40="x",AND(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K45" s="14" t="str">
+        <f>IF(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),IF(OR(L39="X",L39="x",AND(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),IF(OR(L40="X",L40="x",AND(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L45" s="14" t="str">
+        <f>IF(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),IF(OR(L39="X",L39="x",AND(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),IF(OR(L40="X",L40="x",AND(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="M45" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N45" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="O45" s="18" t="str">
+        <f>RANK(AC45,$AC$43:$AC$45)+COUNTIF($AC$42:AC44,AC45)</f>
+      </c>
+      <c r="U45" t="str">
+        <f>=(B45*1000000)-(C45*10000)+(D45*100)+(E45*1)-(F45*0.01)</f>
+      </c>
+      <c r="AC45" t="str">
+        <f>=(J45*1000000)-(K45*10000)+(L45*100)+(M45*1)-(N45*0.01)</f>
+      </c>
+    </row>
+    <row r="48">
+      <c r="F48" s="13"/>
+      <c r="G48" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="G46" s="19"/>
-      <c r="N46" t="s">
+      <c r="N48" s="13"/>
+      <c r="O48" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="O46" s="19"/>
-    </row>
-    <row r="47">
-      <c r="F47" t="s">
+    </row>
+    <row r="49">
+      <c r="F49" t="s">
         <v>105</v>
       </c>
-      <c r="G47" s="19"/>
-      <c r="N47" t="s">
+      <c r="G49" s="19" t="str">
+        <f>IFERROR(INDEX($A$43:$A$45, MATCH(1, $G$43:$G$45, 0)), "-")</f>
+      </c>
+      <c r="N49" t="s">
         <v>105</v>
       </c>
-      <c r="O47" s="19"/>
+      <c r="O49" s="19" t="str">
+        <f>IFERROR(INDEX($I$43:$I$45, MATCH(1, $O$43:$O$45, 0)), "-")</f>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="13" t="str">
-        <f>data!$A$14</f>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="I50" s="13" t="str">
-        <f>data!$A$26</f>
-      </c>
-      <c r="J50" s="13"/>
-      <c r="K50" s="13"/>
-      <c r="L50" s="13"/>
-      <c r="M50" s="13"/>
-      <c r="N50" s="13"/>
-      <c r="O50" s="13"/>
+      <c r="F50" t="s">
+        <v>106</v>
+      </c>
+      <c r="G50" s="19" t="str">
+        <f>IFERROR(INDEX($A$43:$A$45, MATCH(2, $G$43:$G$45, 0)), "-")</f>
+      </c>
+      <c r="N50" t="s">
+        <v>106</v>
+      </c>
+      <c r="O50" s="19" t="str">
+        <f>IFERROR(INDEX($I$43:$I$45, MATCH(2, $O$43:$O$45, 0)), "-")</f>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="s">
+      <c r="F51" t="s">
+        <v>107</v>
+      </c>
+      <c r="G51" s="19" t="str">
+        <f>IFERROR(INDEX($A$43:$A$45, MATCH(3, $G$43:$G$45, 0)), "-")</f>
+      </c>
+      <c r="N51" t="s">
+        <v>107</v>
+      </c>
+      <c r="O51" s="19" t="str">
+        <f>IFERROR(INDEX($I$43:$I$45, MATCH(3, $O$43:$O$45, 0)), "-")</f>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="str">
+        <f>'data'!$A$14</f>
+      </c>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="I53" s="13" t="str">
+        <f>'data'!$A$26</f>
+      </c>
+      <c r="J53" s="13"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="13"/>
+      <c r="M53" s="13"/>
+      <c r="N53" s="13"/>
+      <c r="O53" s="13"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D54" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="G51" s="16" t="s">
+      <c r="G54" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="I51" s="17" t="s">
+      <c r="I54" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="L51" s="14" t="s">
+      <c r="L54" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="O51" s="16" t="s">
+      <c r="O54" s="16" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="14" t="str">
-        <f>data!$B$13</f>
-      </c>
-      <c r="B52" s="18"/>
-      <c r="C52" s="18"/>
-      <c r="D52" s="18"/>
-      <c r="E52" s="18"/>
-      <c r="F52" s="18"/>
-      <c r="G52" s="14" t="str">
-        <f>data!$B$12</f>
-      </c>
-      <c r="I52" s="14" t="str">
-        <f>data!$B$25</f>
-      </c>
-      <c r="J52" s="18"/>
-      <c r="K52" s="18"/>
-      <c r="L52" s="18"/>
-      <c r="M52" s="18"/>
-      <c r="N52" s="18"/>
-      <c r="O52" s="14" t="str">
-        <f>data!$B$24</f>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="14" t="str">
-        <f>data!$B$14</f>
-      </c>
-      <c r="B53" s="18"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="18"/>
-      <c r="G53" s="14" t="str">
-        <f>data!$B$12</f>
-      </c>
-      <c r="I53" s="14" t="str">
-        <f>data!$B$26</f>
-      </c>
-      <c r="J53" s="18"/>
-      <c r="K53" s="18"/>
-      <c r="L53" s="18"/>
-      <c r="M53" s="18"/>
-      <c r="N53" s="18"/>
-      <c r="O53" s="14" t="str">
-        <f>data!$B$24</f>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="14" t="str">
-        <f>data!$B$14</f>
-      </c>
-      <c r="B54" s="18"/>
-      <c r="C54" s="18"/>
-      <c r="D54" s="18"/>
-      <c r="E54" s="18"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="14" t="str">
-        <f>data!$B$13</f>
-      </c>
-      <c r="I54" s="14" t="str">
-        <f>data!$B$26</f>
-      </c>
-      <c r="J54" s="18"/>
-      <c r="K54" s="18"/>
-      <c r="L54" s="18"/>
-      <c r="M54" s="18"/>
-      <c r="N54" s="18"/>
-      <c r="O54" s="14" t="str">
-        <f>data!$B$25</f>
+    <row r="55">
+      <c r="A55" s="14" t="str">
+        <f>'data'!$B$13</f>
+      </c>
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="14" t="str">
+        <f>'data'!$B$12</f>
+      </c>
+      <c r="I55" s="14" t="str">
+        <f>'data'!$B$25</f>
+      </c>
+      <c r="J55" s="18"/>
+      <c r="K55" s="18"/>
+      <c r="L55" s="18"/>
+      <c r="M55" s="18"/>
+      <c r="N55" s="18"/>
+      <c r="O55" s="14" t="str">
+        <f>'data'!$B$24</f>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="D56" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E56" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="F56" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="I56" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="J56" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="K56" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="L56" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="M56" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="N56" s="13" t="s">
-        <v>102</v>
+      <c r="A56" s="14" t="str">
+        <f>'data'!$B$14</f>
+      </c>
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="14" t="str">
+        <f>'data'!$B$12</f>
+      </c>
+      <c r="I56" s="14" t="str">
+        <f>'data'!$B$26</f>
+      </c>
+      <c r="J56" s="18"/>
+      <c r="K56" s="18"/>
+      <c r="L56" s="18"/>
+      <c r="M56" s="18"/>
+      <c r="N56" s="18"/>
+      <c r="O56" s="14" t="str">
+        <f>'data'!$B$24</f>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="str">
-        <f>data!$B$12</f>
-      </c>
-      <c r="B57" s="14" t="str">
-        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="C57" s="14" t="str">
-        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="D57" s="14" t="str">
-        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),1,0),0)+IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),1,0),0)</f>
-      </c>
-      <c r="E57" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F57" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))</f>
+        <f>'data'!$B$14</f>
+      </c>
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="14" t="str">
+        <f>'data'!$B$13</f>
       </c>
       <c r="I57" s="14" t="str">
-        <f>data!$B$24</f>
-      </c>
-      <c r="J57" s="14" t="str">
-        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="K57" s="14" t="str">
-        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="L57" s="14" t="str">
-        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),1,0),0)+IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),1,0),0)</f>
-      </c>
-      <c r="M57" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="N57" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-",""))</f>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="14" t="str">
-        <f>data!$B$13</f>
-      </c>
-      <c r="B58" s="14" t="str">
-        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="C58" s="14" t="str">
-        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="D58" s="14" t="str">
-        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),1,0),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),1,0),0)</f>
-      </c>
-      <c r="E58" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F58" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="I58" s="14" t="str">
-        <f>data!$B$25</f>
-      </c>
-      <c r="J58" s="14" t="str">
-        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="K58" s="14" t="str">
-        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="L58" s="14" t="str">
-        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),1,0),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),1,0),0)</f>
-      </c>
-      <c r="M58" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="N58" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-",""))</f>
+        <f>'data'!$B$26</f>
+      </c>
+      <c r="J57" s="18"/>
+      <c r="K57" s="18"/>
+      <c r="L57" s="18"/>
+      <c r="M57" s="18"/>
+      <c r="N57" s="18"/>
+      <c r="O57" s="14" t="str">
+        <f>'data'!$B$25</f>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="14" t="str">
-        <f>data!$B$14</f>
-      </c>
-      <c r="B59" s="14" t="str">
-        <f>IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="C59" s="14" t="str">
-        <f>IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="D59" s="14" t="str">
-        <f>IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),1,0),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),1,0),0)</f>
-      </c>
-      <c r="E59" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F59" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="I59" s="14" t="str">
-        <f>data!$B$26</f>
-      </c>
-      <c r="J59" s="14" t="str">
-        <f>IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="K59" s="14" t="str">
-        <f>IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="L59" s="14" t="str">
-        <f>IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),1,0),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),1,0),0)</f>
-      </c>
-      <c r="M59" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="N59" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-",""))</f>
+      <c r="A59" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F59" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="G59" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="I59" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="J59" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="K59" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="L59" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="M59" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="N59" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="O59" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="str">
+        <f>'data'!$B$12</f>
+      </c>
+      <c r="B60" s="14" t="str">
+        <f>IF(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),IF(OR(D55="X",D55="x",AND(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),IF(OR(D56="X",D56="x",AND(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C60" s="14" t="str">
+        <f>IF(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),IF(OR(D55="X",D55="x",AND(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),IF(OR(D56="X",D56="x",AND(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D60" s="14" t="str">
+        <f>IF(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),IF(OR(D55="X",D55="x",AND(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),IF(OR(D56="X",D56="x",AND(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="E60" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F60" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="G60" s="18" t="str">
+        <f>RANK(U60,$U$60:$U$62)+COUNTIF($U$59:U59,U60)</f>
+      </c>
+      <c r="I60" s="14" t="str">
+        <f>'data'!$B$24</f>
+      </c>
+      <c r="J60" s="14" t="str">
+        <f>IF(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),IF(OR(L55="X",L55="x",AND(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),IF(OR(L56="X",L56="x",AND(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K60" s="14" t="str">
+        <f>IF(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),IF(OR(L55="X",L55="x",AND(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),IF(OR(L56="X",L56="x",AND(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L60" s="14" t="str">
+        <f>IF(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),IF(OR(L55="X",L55="x",AND(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),IF(OR(L56="X",L56="x",AND(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="M60" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N60" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="O60" s="18" t="str">
+        <f>RANK(AC60,$AC$60:$AC$62)+COUNTIF($AC$59:AC59,AC60)</f>
+      </c>
+      <c r="U60" t="str">
+        <f>=(B60*1000000)-(C60*10000)+(D60*100)+(E60*1)-(F60*0.01)</f>
+      </c>
+      <c r="AC60" t="str">
+        <f>=(J60*1000000)-(K60*10000)+(L60*100)+(M60*1)-(N60*0.01)</f>
       </c>
     </row>
     <row r="61">
-      <c r="F61" t="s">
-        <v>103</v>
-      </c>
-      <c r="G61" s="19"/>
-      <c r="N61" t="s">
-        <v>103</v>
-      </c>
-      <c r="O61" s="19"/>
+      <c r="A61" s="14" t="str">
+        <f>'data'!$B$13</f>
+      </c>
+      <c r="B61" s="14" t="str">
+        <f>IF(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),IF(OR(D55="X",D55="x",AND(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),IF(OR(D57="X",D57="x",AND(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C61" s="14" t="str">
+        <f>IF(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),IF(OR(D55="X",D55="x",AND(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),IF(OR(D57="X",D57="x",AND(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D61" s="14" t="str">
+        <f>IF(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),IF(OR(D55="X",D55="x",AND(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),IF(OR(D57="X",D57="x",AND(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="E61" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F61" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="G61" s="18" t="str">
+        <f>RANK(U61,$U$60:$U$62)+COUNTIF($U$59:U60,U61)</f>
+      </c>
+      <c r="I61" s="14" t="str">
+        <f>'data'!$B$25</f>
+      </c>
+      <c r="J61" s="14" t="str">
+        <f>IF(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),IF(OR(L55="X",L55="x",AND(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),IF(OR(L57="X",L57="x",AND(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K61" s="14" t="str">
+        <f>IF(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),IF(OR(L55="X",L55="x",AND(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),IF(OR(L57="X",L57="x",AND(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L61" s="14" t="str">
+        <f>IF(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),IF(OR(L55="X",L55="x",AND(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),IF(OR(L57="X",L57="x",AND(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="M61" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N61" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="O61" s="18" t="str">
+        <f>RANK(AC61,$AC$60:$AC$62)+COUNTIF($AC$59:AC60,AC61)</f>
+      </c>
+      <c r="U61" t="str">
+        <f>=(B61*1000000)-(C61*10000)+(D61*100)+(E61*1)-(F61*0.01)</f>
+      </c>
+      <c r="AC61" t="str">
+        <f>=(J61*1000000)-(K61*10000)+(L61*100)+(M61*1)-(N61*0.01)</f>
+      </c>
     </row>
     <row r="62">
-      <c r="F62" t="s">
+      <c r="A62" s="14" t="str">
+        <f>'data'!$B$14</f>
+      </c>
+      <c r="B62" s="14" t="str">
+        <f>IF(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),IF(OR(D56="X",D56="x",AND(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),IF(OR(D57="X",D57="x",AND(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C62" s="14" t="str">
+        <f>IF(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),IF(OR(D56="X",D56="x",AND(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),IF(OR(D57="X",D57="x",AND(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D62" s="14" t="str">
+        <f>IF(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),IF(OR(D56="X",D56="x",AND(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),IF(OR(D57="X",D57="x",AND(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="E62" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F62" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="G62" s="18" t="str">
+        <f>RANK(U62,$U$60:$U$62)+COUNTIF($U$59:U61,U62)</f>
+      </c>
+      <c r="I62" s="14" t="str">
+        <f>'data'!$B$26</f>
+      </c>
+      <c r="J62" s="14" t="str">
+        <f>IF(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),IF(OR(L56="X",L56="x",AND(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),IF(OR(L57="X",L57="x",AND(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K62" s="14" t="str">
+        <f>IF(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),IF(OR(L56="X",L56="x",AND(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),IF(OR(L57="X",L57="x",AND(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L62" s="14" t="str">
+        <f>IF(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),IF(OR(L56="X",L56="x",AND(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),IF(OR(L57="X",L57="x",AND(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="M62" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N62" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="O62" s="18" t="str">
+        <f>RANK(AC62,$AC$60:$AC$62)+COUNTIF($AC$59:AC61,AC62)</f>
+      </c>
+      <c r="U62" t="str">
+        <f>=(B62*1000000)-(C62*10000)+(D62*100)+(E62*1)-(F62*0.01)</f>
+      </c>
+      <c r="AC62" t="str">
+        <f>=(J62*1000000)-(K62*10000)+(L62*100)+(M62*1)-(N62*0.01)</f>
+      </c>
+    </row>
+    <row r="65">
+      <c r="F65" s="13"/>
+      <c r="G65" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="G62" s="19"/>
-      <c r="N62" t="s">
+      <c r="N65" s="13"/>
+      <c r="O65" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="O62" s="19"/>
-    </row>
-    <row r="63">
-      <c r="F63" t="s">
+    </row>
+    <row r="66">
+      <c r="F66" t="s">
         <v>105</v>
       </c>
-      <c r="G63" s="19"/>
-      <c r="N63" t="s">
+      <c r="G66" s="19" t="str">
+        <f>IFERROR(INDEX($A$60:$A$62, MATCH(1, $G$60:$G$62, 0)), "-")</f>
+      </c>
+      <c r="N66" t="s">
         <v>105</v>
       </c>
-      <c r="O63" s="19"/>
+      <c r="O66" s="19" t="str">
+        <f>IFERROR(INDEX($I$60:$I$62, MATCH(1, $O$60:$O$62, 0)), "-")</f>
+      </c>
+    </row>
+    <row r="67">
+      <c r="F67" t="s">
+        <v>106</v>
+      </c>
+      <c r="G67" s="19" t="str">
+        <f>IFERROR(INDEX($A$60:$A$62, MATCH(2, $G$60:$G$62, 0)), "-")</f>
+      </c>
+      <c r="N67" t="s">
+        <v>106</v>
+      </c>
+      <c r="O67" s="19" t="str">
+        <f>IFERROR(INDEX($I$60:$I$62, MATCH(2, $O$60:$O$62, 0)), "-")</f>
+      </c>
+    </row>
+    <row r="68">
+      <c r="F68" t="s">
+        <v>107</v>
+      </c>
+      <c r="G68" s="19" t="str">
+        <f>IFERROR(INDEX($A$60:$A$62, MATCH(3, $G$60:$G$62, 0)), "-")</f>
+      </c>
+      <c r="N68" t="s">
+        <v>107</v>
+      </c>
+      <c r="O68" s="19" t="str">
+        <f>IFERROR(INDEX($I$60:$I$62, MATCH(3, $O$60:$O$62, 0)), "-")</f>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
@@ -3657,17 +3910,17 @@
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="I2:O2"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="I18:O18"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="I34:O34"/>
-    <mergeCell ref="A50:G50"/>
-    <mergeCell ref="I50:O50"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="I19:O19"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="I36:O36"/>
+    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="I53:O53"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageSetup fitToHeight="0" fitToWidth="2" orientation="portrait" pageOrder="downThenOver" paperSize="9"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="33" max="16383" man="true"/>
+    <brk id="35" max="16383" man="true"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="8" max="1048575" man="true"/>
@@ -3684,19 +3937,14 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="3" min="2" width="5"/>
-    <col customWidth="true" max="4" min="4" width="3"/>
-    <col customWidth="true" max="6" min="5" width="5"/>
+    <col customWidth="true" max="6" min="2" width="5"/>
     <col customWidth="true" max="7" min="7" width="30"/>
     <col customWidth="true" max="8" min="8" width="5"/>
     <col customWidth="true" max="9" min="9" width="30"/>
-    <col customWidth="true" max="11" min="10" width="5"/>
-    <col customWidth="true" max="12" min="12" width="3"/>
-    <col customWidth="true" max="14" min="13" width="5"/>
+    <col customWidth="true" max="14" min="10" width="5"/>
     <col customWidth="true" max="15" min="15" width="30"/>
-    <col customWidth="true" max="18" min="16" width="5"/>
-    <col customWidth="true" max="19" min="19" width="30"/>
-    <col customWidth="true" max="20" min="20" width="2"/>
+    <col customWidth="true" max="16" min="16" width="5"/>
+    <col customWidth="true" max="20" min="17" width="10.83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3721,7 +3969,7 @@
     </row>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -3761,7 +4009,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G30)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G36)</f>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -3769,10 +4017,10 @@
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
       <c r="G4" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G13)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G18)</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G14)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G19)</f>
       </c>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
@@ -3780,26 +4028,26 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
       <c r="O4" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G29)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G35)</f>
       </c>
     </row>
     <row r="6">
       <c r="F6" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="G6" s="19"/>
       <c r="N6" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="O6" s="19"/>
     </row>
     <row r="7">
       <c r="F7" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="G7" s="19"/>
       <c r="N7" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O7" s="19"/>
     </row>
@@ -3845,7 +4093,7 @@
     </row>
     <row r="12">
       <c r="A12" s="14" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G62)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G70)</f>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -3853,10 +4101,10 @@
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G45)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G52)</f>
       </c>
       <c r="I12" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G46)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G53)</f>
       </c>
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
@@ -3864,26 +4112,26 @@
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
       <c r="O12" s="14" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G61)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G69)</f>
       </c>
     </row>
     <row r="14">
       <c r="F14" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="G14" s="19"/>
       <c r="N14" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="O14" s="19"/>
     </row>
     <row r="15">
       <c r="F15" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="G15" s="19"/>
       <c r="N15" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O15" s="19"/>
     </row>
@@ -3929,7 +4177,7 @@
     </row>
     <row r="20">
       <c r="A20" s="14" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O30)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O36)</f>
       </c>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -3937,10 +4185,10 @@
       <c r="E20" s="18"/>
       <c r="F20" s="18"/>
       <c r="G20" s="14" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O13)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O18)</f>
       </c>
       <c r="I20" s="14" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O14)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O19)</f>
       </c>
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
@@ -3948,26 +4196,26 @@
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
       <c r="O20" s="14" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O29)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O35)</f>
       </c>
     </row>
     <row r="22">
       <c r="F22" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="G22" s="19"/>
       <c r="N22" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="O22" s="19"/>
     </row>
     <row r="23">
       <c r="F23" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="G23" s="19"/>
       <c r="N23" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O23" s="19"/>
     </row>
@@ -4013,7 +4261,7 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O62)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O70)</f>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -4021,10 +4269,10 @@
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="14" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O45)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O52)</f>
       </c>
       <c r="I28" s="14" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O46)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O53)</f>
       </c>
       <c r="J28" s="18"/>
       <c r="K28" s="18"/>
@@ -4032,26 +4280,26 @@
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
       <c r="O28" s="14" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O61)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O69)</f>
       </c>
     </row>
     <row r="30">
       <c r="F30" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="G30" s="19"/>
       <c r="N30" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="O30" s="19"/>
     </row>
     <row r="31">
       <c r="F31" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="G31" s="19"/>
       <c r="N31" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O31" s="19"/>
     </row>
@@ -4121,21 +4369,21 @@
     </row>
     <row r="43">
       <c r="F43" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="G43" s="19"/>
       <c r="N43" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="O43" s="19"/>
     </row>
     <row r="44">
       <c r="F44" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="G44" s="19"/>
       <c r="N44" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O44" s="19"/>
     </row>
@@ -4205,21 +4453,21 @@
     </row>
     <row r="51">
       <c r="F51" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="G51" s="19"/>
       <c r="N51" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="O51" s="19"/>
     </row>
     <row r="52">
       <c r="F52" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="G52" s="19"/>
       <c r="N52" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O52" s="19"/>
     </row>
@@ -4289,21 +4537,21 @@
     </row>
     <row r="64">
       <c r="F64" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="G64" s="19"/>
       <c r="N64" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="O64" s="19"/>
     </row>
     <row r="65">
       <c r="F65" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="G65" s="19"/>
       <c r="N65" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O65" s="19"/>
     </row>
@@ -4344,13 +4592,13 @@
     </row>
     <row r="77">
       <c r="F77" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="G77" s="19"/>
     </row>
     <row r="78">
       <c r="F78" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="G78" s="19"/>
     </row>
@@ -4417,7 +4665,7 @@
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
-        <f>data!$A$5</f>
+        <f>'data'!$A$5</f>
       </c>
     </row>
     <row r="5">
@@ -4425,7 +4673,7 @@
         <f>"1. " &amp; data!$B$3</f>
       </c>
       <c r="C5" s="23" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G13)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G18)</f>
       </c>
     </row>
     <row r="6">
@@ -4442,7 +4690,7 @@
         <f>"3. " &amp; data!$B$5</f>
       </c>
       <c r="C7" s="23" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G30)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G36)</f>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="20"/>
@@ -4457,10 +4705,10 @@
     </row>
     <row r="9">
       <c r="A9" s="24" t="str">
-        <f>data!$A$8</f>
+        <f>'data'!$A$8</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G45)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G52)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -4483,7 +4731,7 @@
         <f>"2. " &amp; data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G62)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G70)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -4500,13 +4748,13 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O13)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O18)</f>
       </c>
       <c r="I13" s="20"/>
     </row>
     <row r="14">
       <c r="A14" s="24" t="str">
-        <f>data!$A$11</f>
+        <f>'data'!$A$11</f>
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="21">
@@ -4519,7 +4767,7 @@
         <f>"1. " &amp; data!$B$9</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O30)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O36)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -4542,7 +4790,7 @@
         <f>"3. " &amp; data!$B$11</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O45)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O52)</f>
       </c>
       <c r="G17" s="20"/>
     </row>
@@ -4557,10 +4805,10 @@
     </row>
     <row r="19">
       <c r="A19" s="24" t="str">
-        <f>data!$A$14</f>
+        <f>'data'!$A$14</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O62)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O70)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -4624,7 +4872,7 @@
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
-        <f>data!$A$17</f>
+        <f>'data'!$A$17</f>
       </c>
     </row>
     <row r="5">
@@ -4632,7 +4880,7 @@
         <f>"1. " &amp; data!$B$15</f>
       </c>
       <c r="C5" s="23" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G29)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G35)</f>
       </c>
     </row>
     <row r="6">
@@ -4649,7 +4897,7 @@
         <f>"3. " &amp; data!$B$17</f>
       </c>
       <c r="C7" s="23" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G14)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G19)</f>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="20"/>
@@ -4664,10 +4912,10 @@
     </row>
     <row r="9">
       <c r="A9" s="24" t="str">
-        <f>data!$A$20</f>
+        <f>'data'!$A$20</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G61)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G69)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -4690,7 +4938,7 @@
         <f>"2. " &amp; data!$B$19</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G46)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G53)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -4707,13 +4955,13 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O29)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O35)</f>
       </c>
       <c r="I13" s="20"/>
     </row>
     <row r="14">
       <c r="A14" s="24" t="str">
-        <f>data!$A$23</f>
+        <f>'data'!$A$23</f>
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="21">
@@ -4726,7 +4974,7 @@
         <f>"1. " &amp; data!$B$21</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O14)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O19)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -4749,7 +4997,7 @@
         <f>"3. " &amp; data!$B$23</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O61)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O69)</f>
       </c>
       <c r="G17" s="20"/>
     </row>
@@ -4764,10 +5012,10 @@
     </row>
     <row r="19">
       <c r="A19" s="24" t="str">
-        <f>data!$A$26</f>
+        <f>'data'!$A$26</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O46)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O53)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -4009,7 +4009,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G36)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -4017,10 +4017,10 @@
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
       <c r="G4" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G18)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G15)</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G19)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G16)</f>
       </c>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
@@ -4028,7 +4028,7 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
       <c r="O4" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G35)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
       </c>
     </row>
     <row r="6">
@@ -4093,7 +4093,7 @@
     </row>
     <row r="12">
       <c r="A12" s="14" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G70)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -4101,10 +4101,10 @@
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G52)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G49)</f>
       </c>
       <c r="I12" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G53)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
       </c>
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
@@ -4112,7 +4112,7 @@
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
       <c r="O12" s="14" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G69)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
       </c>
     </row>
     <row r="14">
@@ -4177,7 +4177,7 @@
     </row>
     <row r="20">
       <c r="A20" s="14" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O36)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O33)</f>
       </c>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -4185,10 +4185,10 @@
       <c r="E20" s="18"/>
       <c r="F20" s="18"/>
       <c r="G20" s="14" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O18)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O15)</f>
       </c>
       <c r="I20" s="14" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O19)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O16)</f>
       </c>
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
@@ -4196,7 +4196,7 @@
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
       <c r="O20" s="14" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O35)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O32)</f>
       </c>
     </row>
     <row r="22">
@@ -4261,7 +4261,7 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O70)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O67)</f>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -4269,10 +4269,10 @@
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="14" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O52)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O49)</f>
       </c>
       <c r="I28" s="14" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O53)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O50)</f>
       </c>
       <c r="J28" s="18"/>
       <c r="K28" s="18"/>
@@ -4280,7 +4280,7 @@
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
       <c r="O28" s="14" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O69)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O66)</f>
       </c>
     </row>
     <row r="30">
@@ -4673,7 +4673,7 @@
         <f>"1. " &amp; data!$B$3</f>
       </c>
       <c r="C5" s="23" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G18)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G15)</f>
       </c>
     </row>
     <row r="6">
@@ -4690,7 +4690,7 @@
         <f>"3. " &amp; data!$B$5</f>
       </c>
       <c r="C7" s="23" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G36)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="20"/>
@@ -4708,7 +4708,7 @@
         <f>'data'!$A$8</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G52)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G49)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -4731,7 +4731,7 @@
         <f>"2. " &amp; data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G70)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -4748,7 +4748,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O18)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O15)</f>
       </c>
       <c r="I13" s="20"/>
     </row>
@@ -4767,7 +4767,7 @@
         <f>"1. " &amp; data!$B$9</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O36)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O33)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -4790,7 +4790,7 @@
         <f>"3. " &amp; data!$B$11</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O52)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O49)</f>
       </c>
       <c r="G17" s="20"/>
     </row>
@@ -4808,7 +4808,7 @@
         <f>'data'!$A$14</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O70)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O67)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -4880,7 +4880,7 @@
         <f>"1. " &amp; data!$B$15</f>
       </c>
       <c r="C5" s="23" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G35)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
       </c>
     </row>
     <row r="6">
@@ -4897,7 +4897,7 @@
         <f>"3. " &amp; data!$B$17</f>
       </c>
       <c r="C7" s="23" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G19)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G16)</f>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="20"/>
@@ -4915,7 +4915,7 @@
         <f>'data'!$A$20</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G69)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -4938,7 +4938,7 @@
         <f>"2. " &amp; data!$B$19</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G53)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -4955,7 +4955,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O35)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O32)</f>
       </c>
       <c r="I13" s="20"/>
     </row>
@@ -4974,7 +4974,7 @@
         <f>"1. " &amp; data!$B$21</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O19)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O16)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -4997,7 +4997,7 @@
         <f>"3. " &amp; data!$B$23</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O69)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O66)</f>
       </c>
       <c r="G17" s="20"/>
     </row>
@@ -5015,7 +5015,7 @@
         <f>'data'!$A$26</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O53)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O50)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -2671,10 +2671,10 @@
         <f>RANK(AC9,$AC$9:$AC$11)+COUNTIF($AC$8:AC8,AC9)</f>
       </c>
       <c r="U9" t="str">
-        <f>=(B9*1000000)-(C9*10000)+(D9*100)+(E9*1)-(F9*0.01)</f>
+        <f>(B9*1000000)-(C9*10000)+(D9*100)+(E9*1)-(F9*0.01)</f>
       </c>
       <c r="AC9" t="str">
-        <f>=(J9*1000000)-(K9*10000)+(L9*100)+(M9*1)-(N9*0.01)</f>
+        <f>(J9*1000000)-(K9*10000)+(L9*100)+(M9*1)-(N9*0.01)</f>
       </c>
     </row>
     <row r="10">
@@ -2721,10 +2721,10 @@
         <f>RANK(AC10,$AC$9:$AC$11)+COUNTIF($AC$8:AC9,AC10)</f>
       </c>
       <c r="U10" t="str">
-        <f>=(B10*1000000)-(C10*10000)+(D10*100)+(E10*1)-(F10*0.01)</f>
+        <f>(B10*1000000)-(C10*10000)+(D10*100)+(E10*1)-(F10*0.01)</f>
       </c>
       <c r="AC10" t="str">
-        <f>=(J10*1000000)-(K10*10000)+(L10*100)+(M10*1)-(N10*0.01)</f>
+        <f>(J10*1000000)-(K10*10000)+(L10*100)+(M10*1)-(N10*0.01)</f>
       </c>
     </row>
     <row r="11">
@@ -2771,10 +2771,10 @@
         <f>RANK(AC11,$AC$9:$AC$11)+COUNTIF($AC$8:AC10,AC11)</f>
       </c>
       <c r="U11" t="str">
-        <f>=(B11*1000000)-(C11*10000)+(D11*100)+(E11*1)-(F11*0.01)</f>
+        <f>(B11*1000000)-(C11*10000)+(D11*100)+(E11*1)-(F11*0.01)</f>
       </c>
       <c r="AC11" t="str">
-        <f>=(J11*1000000)-(K11*10000)+(L11*100)+(M11*1)-(N11*0.01)</f>
+        <f>(J11*1000000)-(K11*10000)+(L11*100)+(M11*1)-(N11*0.01)</f>
       </c>
     </row>
     <row r="14">
@@ -3029,10 +3029,10 @@
         <f>RANK(AC26,$AC$26:$AC$28)+COUNTIF($AC$25:AC25,AC26)</f>
       </c>
       <c r="U26" t="str">
-        <f>=(B26*1000000)-(C26*10000)+(D26*100)+(E26*1)-(F26*0.01)</f>
+        <f>(B26*1000000)-(C26*10000)+(D26*100)+(E26*1)-(F26*0.01)</f>
       </c>
       <c r="AC26" t="str">
-        <f>=(J26*1000000)-(K26*10000)+(L26*100)+(M26*1)-(N26*0.01)</f>
+        <f>(J26*1000000)-(K26*10000)+(L26*100)+(M26*1)-(N26*0.01)</f>
       </c>
     </row>
     <row r="27">
@@ -3079,10 +3079,10 @@
         <f>RANK(AC27,$AC$26:$AC$28)+COUNTIF($AC$25:AC26,AC27)</f>
       </c>
       <c r="U27" t="str">
-        <f>=(B27*1000000)-(C27*10000)+(D27*100)+(E27*1)-(F27*0.01)</f>
+        <f>(B27*1000000)-(C27*10000)+(D27*100)+(E27*1)-(F27*0.01)</f>
       </c>
       <c r="AC27" t="str">
-        <f>=(J27*1000000)-(K27*10000)+(L27*100)+(M27*1)-(N27*0.01)</f>
+        <f>(J27*1000000)-(K27*10000)+(L27*100)+(M27*1)-(N27*0.01)</f>
       </c>
     </row>
     <row r="28">
@@ -3129,10 +3129,10 @@
         <f>RANK(AC28,$AC$26:$AC$28)+COUNTIF($AC$25:AC27,AC28)</f>
       </c>
       <c r="U28" t="str">
-        <f>=(B28*1000000)-(C28*10000)+(D28*100)+(E28*1)-(F28*0.01)</f>
+        <f>(B28*1000000)-(C28*10000)+(D28*100)+(E28*1)-(F28*0.01)</f>
       </c>
       <c r="AC28" t="str">
-        <f>=(J28*1000000)-(K28*10000)+(L28*100)+(M28*1)-(N28*0.01)</f>
+        <f>(J28*1000000)-(K28*10000)+(L28*100)+(M28*1)-(N28*0.01)</f>
       </c>
     </row>
     <row r="31">
@@ -3387,10 +3387,10 @@
         <f>RANK(AC43,$AC$43:$AC$45)+COUNTIF($AC$42:AC42,AC43)</f>
       </c>
       <c r="U43" t="str">
-        <f>=(B43*1000000)-(C43*10000)+(D43*100)+(E43*1)-(F43*0.01)</f>
+        <f>(B43*1000000)-(C43*10000)+(D43*100)+(E43*1)-(F43*0.01)</f>
       </c>
       <c r="AC43" t="str">
-        <f>=(J43*1000000)-(K43*10000)+(L43*100)+(M43*1)-(N43*0.01)</f>
+        <f>(J43*1000000)-(K43*10000)+(L43*100)+(M43*1)-(N43*0.01)</f>
       </c>
     </row>
     <row r="44">
@@ -3437,10 +3437,10 @@
         <f>RANK(AC44,$AC$43:$AC$45)+COUNTIF($AC$42:AC43,AC44)</f>
       </c>
       <c r="U44" t="str">
-        <f>=(B44*1000000)-(C44*10000)+(D44*100)+(E44*1)-(F44*0.01)</f>
+        <f>(B44*1000000)-(C44*10000)+(D44*100)+(E44*1)-(F44*0.01)</f>
       </c>
       <c r="AC44" t="str">
-        <f>=(J44*1000000)-(K44*10000)+(L44*100)+(M44*1)-(N44*0.01)</f>
+        <f>(J44*1000000)-(K44*10000)+(L44*100)+(M44*1)-(N44*0.01)</f>
       </c>
     </row>
     <row r="45">
@@ -3487,10 +3487,10 @@
         <f>RANK(AC45,$AC$43:$AC$45)+COUNTIF($AC$42:AC44,AC45)</f>
       </c>
       <c r="U45" t="str">
-        <f>=(B45*1000000)-(C45*10000)+(D45*100)+(E45*1)-(F45*0.01)</f>
+        <f>(B45*1000000)-(C45*10000)+(D45*100)+(E45*1)-(F45*0.01)</f>
       </c>
       <c r="AC45" t="str">
-        <f>=(J45*1000000)-(K45*10000)+(L45*100)+(M45*1)-(N45*0.01)</f>
+        <f>(J45*1000000)-(K45*10000)+(L45*100)+(M45*1)-(N45*0.01)</f>
       </c>
     </row>
     <row r="48">
@@ -3745,10 +3745,10 @@
         <f>RANK(AC60,$AC$60:$AC$62)+COUNTIF($AC$59:AC59,AC60)</f>
       </c>
       <c r="U60" t="str">
-        <f>=(B60*1000000)-(C60*10000)+(D60*100)+(E60*1)-(F60*0.01)</f>
+        <f>(B60*1000000)-(C60*10000)+(D60*100)+(E60*1)-(F60*0.01)</f>
       </c>
       <c r="AC60" t="str">
-        <f>=(J60*1000000)-(K60*10000)+(L60*100)+(M60*1)-(N60*0.01)</f>
+        <f>(J60*1000000)-(K60*10000)+(L60*100)+(M60*1)-(N60*0.01)</f>
       </c>
     </row>
     <row r="61">
@@ -3795,10 +3795,10 @@
         <f>RANK(AC61,$AC$60:$AC$62)+COUNTIF($AC$59:AC60,AC61)</f>
       </c>
       <c r="U61" t="str">
-        <f>=(B61*1000000)-(C61*10000)+(D61*100)+(E61*1)-(F61*0.01)</f>
+        <f>(B61*1000000)-(C61*10000)+(D61*100)+(E61*1)-(F61*0.01)</f>
       </c>
       <c r="AC61" t="str">
-        <f>=(J61*1000000)-(K61*10000)+(L61*100)+(M61*1)-(N61*0.01)</f>
+        <f>(J61*1000000)-(K61*10000)+(L61*100)+(M61*1)-(N61*0.01)</f>
       </c>
     </row>
     <row r="62">
@@ -3845,10 +3845,10 @@
         <f>RANK(AC62,$AC$60:$AC$62)+COUNTIF($AC$59:AC61,AC62)</f>
       </c>
       <c r="U62" t="str">
-        <f>=(B62*1000000)-(C62*10000)+(D62*100)+(E62*1)-(F62*0.01)</f>
+        <f>(B62*1000000)-(C62*10000)+(D62*100)+(E62*1)-(F62*0.01)</f>
       </c>
       <c r="AC62" t="str">
-        <f>=(J62*1000000)-(K62*10000)+(L62*100)+(M62*1)-(N62*0.01)</f>
+        <f>(J62*1000000)-(K62*10000)+(L62*100)+(M62*1)-(N62*0.01)</f>
       </c>
     </row>
     <row r="65">

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -591,7 +591,7 @@
       <family val="2"/>
       <b val="1"/>
       <color/>
-      <sz val="150"/>
+      <sz val="200"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1706,242 +1706,242 @@
     <col customWidth="true" max="1" min="1" width="90"/>
   </cols>
   <sheetData>
-    <row r="1" ht="390" customHeight="true">
+    <row r="1" ht="409" customHeight="true">
       <c r="A1" s="30" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="2" ht="390" customHeight="true">
+    <row r="2" ht="409" customHeight="true">
       <c r="A2" s="30" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="3" ht="390" customHeight="true">
+    <row r="3" ht="409" customHeight="true">
       <c r="A3" s="30" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="4" ht="390" customHeight="true">
+    <row r="4" ht="409" customHeight="true">
       <c r="A4" s="30" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="5" ht="390" customHeight="true">
+    <row r="5" ht="409" customHeight="true">
       <c r="A5" s="30" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="6" ht="390" customHeight="true">
+    <row r="6" ht="409" customHeight="true">
       <c r="A6" s="30" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="7" ht="390" customHeight="true">
+    <row r="7" ht="409" customHeight="true">
       <c r="A7" s="30" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="8" ht="390" customHeight="true">
+    <row r="8" ht="409" customHeight="true">
       <c r="A8" s="30" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="9" ht="390" customHeight="true">
+    <row r="9" ht="409" customHeight="true">
       <c r="A9" s="30" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="10" ht="390" customHeight="true">
+    <row r="10" ht="409" customHeight="true">
       <c r="A10" s="30" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="11" ht="390" customHeight="true">
+    <row r="11" ht="409" customHeight="true">
       <c r="A11" s="30" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="12" ht="390" customHeight="true">
+    <row r="12" ht="409" customHeight="true">
       <c r="A12" s="30" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="13" ht="390" customHeight="true">
+    <row r="13" ht="409" customHeight="true">
       <c r="A13" s="30" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="14" ht="390" customHeight="true">
+    <row r="14" ht="409" customHeight="true">
       <c r="A14" s="30" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="15" ht="390" customHeight="true">
+    <row r="15" ht="409" customHeight="true">
       <c r="A15" s="30" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="16" ht="390" customHeight="true">
+    <row r="16" ht="409" customHeight="true">
       <c r="A16" s="30" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="17" ht="390" customHeight="true">
+    <row r="17" ht="409" customHeight="true">
       <c r="A17" s="30" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="18" ht="390" customHeight="true">
+    <row r="18" ht="409" customHeight="true">
       <c r="A18" s="30" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="19" ht="390" customHeight="true">
+    <row r="19" ht="409" customHeight="true">
       <c r="A19" s="30" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="20" ht="390" customHeight="true">
+    <row r="20" ht="409" customHeight="true">
       <c r="A20" s="30" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="21" ht="390" customHeight="true">
+    <row r="21" ht="409" customHeight="true">
       <c r="A21" s="30" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="22" ht="390" customHeight="true">
+    <row r="22" ht="409" customHeight="true">
       <c r="A22" s="30" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="23" ht="390" customHeight="true">
+    <row r="23" ht="409" customHeight="true">
       <c r="A23" s="30" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="24" ht="390" customHeight="true">
+    <row r="24" ht="409" customHeight="true">
       <c r="A24" s="30" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="25" ht="390" customHeight="true">
+    <row r="25" ht="409" customHeight="true">
       <c r="A25" s="30" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="26" ht="390" customHeight="true">
+    <row r="26" ht="409" customHeight="true">
       <c r="A26" s="30" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="27" ht="390" customHeight="true">
+    <row r="27" ht="409" customHeight="true">
       <c r="A27" s="30" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="28" ht="390" customHeight="true">
+    <row r="28" ht="409" customHeight="true">
       <c r="A28" s="30" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="29" ht="390" customHeight="true">
+    <row r="29" ht="409" customHeight="true">
       <c r="A29" s="30" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="30" ht="390" customHeight="true">
+    <row r="30" ht="409" customHeight="true">
       <c r="A30" s="30" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="31" ht="390" customHeight="true">
+    <row r="31" ht="409" customHeight="true">
       <c r="A31" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="32" ht="390" customHeight="true">
+    <row r="32" ht="409" customHeight="true">
       <c r="A32" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="33" ht="390" customHeight="true">
+    <row r="33" ht="409" customHeight="true">
       <c r="A33" s="30" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="34" ht="390" customHeight="true">
+    <row r="34" ht="409" customHeight="true">
       <c r="A34" s="30" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="35" ht="390" customHeight="true">
+    <row r="35" ht="409" customHeight="true">
       <c r="A35" s="30" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="36" ht="390" customHeight="true">
+    <row r="36" ht="409" customHeight="true">
       <c r="A36" s="30" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="37" ht="390" customHeight="true">
+    <row r="37" ht="409" customHeight="true">
       <c r="A37" s="30" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="38" ht="390" customHeight="true">
+    <row r="38" ht="409" customHeight="true">
       <c r="A38" s="30" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="39" ht="390" customHeight="true">
+    <row r="39" ht="409" customHeight="true">
       <c r="A39" s="30" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="40" ht="390" customHeight="true">
+    <row r="40" ht="409" customHeight="true">
       <c r="A40" s="30" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="41" ht="390" customHeight="true">
+    <row r="41" ht="409" customHeight="true">
       <c r="A41" s="30" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="42" ht="390" customHeight="true">
+    <row r="42" ht="409" customHeight="true">
       <c r="A42" s="30" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="43" ht="390" customHeight="true">
+    <row r="43" ht="409" customHeight="true">
       <c r="A43" s="30" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="44" ht="390" customHeight="true">
+    <row r="44" ht="409" customHeight="true">
       <c r="A44" s="30" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="45" ht="390" customHeight="true">
+    <row r="45" ht="409" customHeight="true">
       <c r="A45" s="30" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="46" ht="390" customHeight="true">
+    <row r="46" ht="409" customHeight="true">
       <c r="A46" s="30" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="47" ht="390" customHeight="true">
+    <row r="47" ht="409" customHeight="true">
       <c r="A47" s="30" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="48" ht="390" customHeight="true">
+    <row r="48" ht="409" customHeight="true">
       <c r="A48" s="30" t="s">
         <v>131</v>
       </c>

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -591,7 +591,7 @@
       <family val="2"/>
       <b val="1"/>
       <color/>
-      <sz val="200"/>
+      <sz val="250"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1703,7 +1703,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="90"/>
+    <col customWidth="true" max="1" min="1" width="110"/>
   </cols>
   <sheetData>
     <row r="1" ht="409" customHeight="true">

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -21,6 +21,8 @@
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$23</definedName>
     <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$P$69</definedName>
+    <definedName localSheetId="5" name="_xlnm.Print_Area">'Tree 1'!$A$1:$I$23</definedName>
+    <definedName localSheetId="6" name="_xlnm.Print_Area">'Tree 2'!$A$1:$I$23</definedName>
     <definedName localSheetId="7" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$12</definedName>
     <definedName localSheetId="8" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$12</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$P$85</definedName>
@@ -4635,12 +4637,17 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4655,13 +4662,6 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
       <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
@@ -4834,20 +4834,25 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4862,13 +4867,6 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
       <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
@@ -5041,9 +5039,9 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -787,7 +787,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -4011,7 +4011,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O16)</f>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -4030,7 +4030,7 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
       <c r="O4" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O15)</f>
       </c>
     </row>
     <row r="6">
@@ -4095,7 +4095,7 @@
     </row>
     <row r="12">
       <c r="A12" s="14" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O33)</f>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -4103,10 +4103,10 @@
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G49)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
       </c>
       <c r="I12" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
       </c>
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
@@ -4114,7 +4114,7 @@
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
       <c r="O12" s="14" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O32)</f>
       </c>
     </row>
     <row r="14">
@@ -4179,7 +4179,7 @@
     </row>
     <row r="20">
       <c r="A20" s="14" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O33)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O50)</f>
       </c>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -4187,10 +4187,10 @@
       <c r="E20" s="18"/>
       <c r="F20" s="18"/>
       <c r="G20" s="14" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O15)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G49)</f>
       </c>
       <c r="I20" s="14" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O16)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
       </c>
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
@@ -4198,7 +4198,7 @@
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
       <c r="O20" s="14" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O32)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O49)</f>
       </c>
     </row>
     <row r="22">
@@ -4271,10 +4271,10 @@
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="14" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O49)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
       </c>
       <c r="I28" s="14" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O50)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
       </c>
       <c r="J28" s="18"/>
       <c r="K28" s="18"/>
@@ -4690,7 +4690,7 @@
         <f>"3. " &amp; data!$B$5</f>
       </c>
       <c r="C7" s="23" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O16)</f>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="20"/>
@@ -4708,7 +4708,7 @@
         <f>'data'!$A$8</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G49)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -4731,7 +4731,7 @@
         <f>"2. " &amp; data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O33)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -4748,7 +4748,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O15)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G49)</f>
       </c>
       <c r="I13" s="20"/>
     </row>
@@ -4767,7 +4767,7 @@
         <f>"1. " &amp; data!$B$9</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O33)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O50)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -4790,7 +4790,7 @@
         <f>"3. " &amp; data!$B$11</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O49)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
       </c>
       <c r="G17" s="20"/>
     </row>
@@ -4878,7 +4878,7 @@
         <f>"1. " &amp; data!$B$15</f>
       </c>
       <c r="C5" s="23" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O15)</f>
       </c>
     </row>
     <row r="6">
@@ -4913,7 +4913,7 @@
         <f>'data'!$A$20</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O32)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -4936,7 +4936,7 @@
         <f>"2. " &amp; data!$B$19</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -4953,7 +4953,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O32)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O49)</f>
       </c>
       <c r="I13" s="20"/>
     </row>
@@ -4972,7 +4972,7 @@
         <f>"1. " &amp; data!$B$21</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O16)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -5013,7 +5013,7 @@
         <f>'data'!$A$26</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O50)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -115,6 +115,87 @@
     <t>Pool B</t>
   </si>
   <si>
+    <t>Voldemort</t>
+  </si>
+  <si>
+    <t>Team Chi</t>
+  </si>
+  <si>
+    <t>VOLDEMORT</t>
+  </si>
+  <si>
+    <t>Team Lambda</t>
+  </si>
+  <si>
+    <t>Ron Weasley</t>
+  </si>
+  <si>
+    <t>Team Sigma</t>
+  </si>
+  <si>
+    <t>WEASLEY</t>
+  </si>
+  <si>
+    <t>Pool C</t>
+  </si>
+  <si>
+    <t>Legolas Greenleaf</t>
+  </si>
+  <si>
+    <t>GREENLEAF</t>
+  </si>
+  <si>
+    <t>Xaro Xhoan Daxos</t>
+  </si>
+  <si>
+    <t>Team Omega</t>
+  </si>
+  <si>
+    <t>DAXOS</t>
+  </si>
+  <si>
+    <t>Hermione Granger</t>
+  </si>
+  <si>
+    <t>Team Theta</t>
+  </si>
+  <si>
+    <t>GRANGER</t>
+  </si>
+  <si>
+    <t>Pool D</t>
+  </si>
+  <si>
+    <t>Gandalf The Grey</t>
+  </si>
+  <si>
+    <t>Team Eta</t>
+  </si>
+  <si>
+    <t>GANDALF</t>
+  </si>
+  <si>
+    <t>Ulysses</t>
+  </si>
+  <si>
+    <t>Team Phi</t>
+  </si>
+  <si>
+    <t>ULYSSES</t>
+  </si>
+  <si>
+    <t>Neville Longbottom</t>
+  </si>
+  <si>
+    <t>Team Xi</t>
+  </si>
+  <si>
+    <t>LONGBOTTOM</t>
+  </si>
+  <si>
+    <t>Pool E</t>
+  </si>
+  <si>
     <t>Ygritte</t>
   </si>
   <si>
@@ -124,19 +205,25 @@
     <t>YGRITTE</t>
   </si>
   <si>
-    <t>Team Lambda</t>
-  </si>
-  <si>
-    <t>Ron Weasley</t>
-  </si>
-  <si>
-    <t>Team Sigma</t>
-  </si>
-  <si>
-    <t>WEASLEY</t>
-  </si>
-  <si>
-    <t>Pool C</t>
+    <t>Jon Snow</t>
+  </si>
+  <si>
+    <t>Team Kappa</t>
+  </si>
+  <si>
+    <t>SNOW</t>
+  </si>
+  <si>
+    <t>Quirinus Quirrell</t>
+  </si>
+  <si>
+    <t>Team Rho</t>
+  </si>
+  <si>
+    <t>QUIRRELL</t>
+  </si>
+  <si>
+    <t>Pool F</t>
   </si>
   <si>
     <t>Daenerys Targaryen</t>
@@ -146,93 +233,6 @@
   </si>
   <si>
     <t>TARGARYEN</t>
-  </si>
-  <si>
-    <t>Xaro Xhoan Daxos</t>
-  </si>
-  <si>
-    <t>Team Omega</t>
-  </si>
-  <si>
-    <t>DAXOS</t>
-  </si>
-  <si>
-    <t>Hermione Granger</t>
-  </si>
-  <si>
-    <t>Team Theta</t>
-  </si>
-  <si>
-    <t>GRANGER</t>
-  </si>
-  <si>
-    <t>Pool D</t>
-  </si>
-  <si>
-    <t>Gandalf The Grey</t>
-  </si>
-  <si>
-    <t>Team Eta</t>
-  </si>
-  <si>
-    <t>GANDALF</t>
-  </si>
-  <si>
-    <t>Ulysses</t>
-  </si>
-  <si>
-    <t>Team Phi</t>
-  </si>
-  <si>
-    <t>ULYSSES</t>
-  </si>
-  <si>
-    <t>Neville Longbottom</t>
-  </si>
-  <si>
-    <t>Team Xi</t>
-  </si>
-  <si>
-    <t>LONGBOTTOM</t>
-  </si>
-  <si>
-    <t>Pool E</t>
-  </si>
-  <si>
-    <t>Legolas Greenleaf</t>
-  </si>
-  <si>
-    <t>GREENLEAF</t>
-  </si>
-  <si>
-    <t>Jon Snow</t>
-  </si>
-  <si>
-    <t>Team Kappa</t>
-  </si>
-  <si>
-    <t>SNOW</t>
-  </si>
-  <si>
-    <t>Quirinus Quirrell</t>
-  </si>
-  <si>
-    <t>Team Rho</t>
-  </si>
-  <si>
-    <t>QUIRRELL</t>
-  </si>
-  <si>
-    <t>Pool F</t>
-  </si>
-  <si>
-    <t>Voldemort</t>
-  </si>
-  <si>
-    <t>Team Chi</t>
-  </si>
-  <si>
-    <t>VOLDEMORT</t>
   </si>
   <si>
     <t>Moby Dick</t>
@@ -1215,10 +1215,10 @@
         <v>35</v>
       </c>
       <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
         <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -1226,13 +1226,13 @@
         <v>34</v>
       </c>
       <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
         <v>38</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>39</v>
-      </c>
-      <c r="D10" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -1240,66 +1240,66 @@
         <v>34</v>
       </c>
       <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
         <v>41</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>42</v>
-      </c>
-      <c r="D11" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
         <v>44</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>45</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>46</v>
-      </c>
-      <c r="D12" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s">
         <v>48</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>49</v>
-      </c>
-      <c r="D13" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" t="s">
         <v>51</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>52</v>
-      </c>
-      <c r="D14" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s">
         <v>54</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>55</v>
-      </c>
-      <c r="C15" t="s">
-        <v>18</v>
       </c>
       <c r="D15" t="s">
         <v>56</v>
@@ -1307,7 +1307,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s">
         <v>57</v>
@@ -1321,7 +1321,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B17" t="s">
         <v>60</v>

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -85,13 +85,91 @@
     <t>Pool A</t>
   </si>
   <si>
+    <t>Cersei Lannister</t>
+  </si>
+  <si>
+    <t>Team Gamma</t>
+  </si>
+  <si>
+    <t>LANNISTER</t>
+  </si>
+  <si>
     <t>Katniss Everdeen</t>
   </si>
   <si>
+    <t>Team Lambda</t>
+  </si>
+  <si>
+    <t>EVERDEEN</t>
+  </si>
+  <si>
+    <t>Ron Weasley</t>
+  </si>
+  <si>
+    <t>Team Sigma</t>
+  </si>
+  <si>
+    <t>WEASLEY</t>
+  </si>
+  <si>
+    <t>Pool B</t>
+  </si>
+  <si>
+    <t>Eddard Stark</t>
+  </si>
+  <si>
+    <t>Team Epsilon</t>
+  </si>
+  <si>
+    <t>STARK</t>
+  </si>
+  <si>
+    <t>Moby Dick</t>
+  </si>
+  <si>
+    <t>Team Nu</t>
+  </si>
+  <si>
+    <t>DICK</t>
+  </si>
+  <si>
+    <t>Tyrion Lannister</t>
+  </si>
+  <si>
+    <t>Team Upsilon</t>
+  </si>
+  <si>
+    <t>Pool C</t>
+  </si>
+  <si>
+    <t>Gandalf The Grey</t>
+  </si>
+  <si>
+    <t>Team Eta</t>
+  </si>
+  <si>
+    <t>GANDALF</t>
+  </si>
+  <si>
+    <t>Legolas Greenleaf</t>
+  </si>
+  <si>
     <t>Team Mu</t>
   </si>
   <si>
-    <t>EVERDEEN</t>
+    <t>GREENLEAF</t>
+  </si>
+  <si>
+    <t>Voldemort</t>
+  </si>
+  <si>
+    <t>Team Chi</t>
+  </si>
+  <si>
+    <t>VOLDEMORT</t>
+  </si>
+  <si>
+    <t>Pool D</t>
   </si>
   <si>
     <t>Inigo Montoya</t>
@@ -103,6 +181,96 @@
     <t>MONTOYA</t>
   </si>
   <si>
+    <t>Petyr Baelish</t>
+  </si>
+  <si>
+    <t>Team Pi</t>
+  </si>
+  <si>
+    <t>BAELISH</t>
+  </si>
+  <si>
+    <t>Xaro Xhoan Daxos</t>
+  </si>
+  <si>
+    <t>Team Omega</t>
+  </si>
+  <si>
+    <t>DAXOS</t>
+  </si>
+  <si>
+    <t>Pool E</t>
+  </si>
+  <si>
+    <t>Daenerys Targaryen</t>
+  </si>
+  <si>
+    <t>Team Delta</t>
+  </si>
+  <si>
+    <t>TARGARYEN</t>
+  </si>
+  <si>
+    <t>Samwise Gamgee</t>
+  </si>
+  <si>
+    <t>Team Tau</t>
+  </si>
+  <si>
+    <t>GAMGEE</t>
+  </si>
+  <si>
+    <t>Pool F</t>
+  </si>
+  <si>
+    <t>Frodo Baggins</t>
+  </si>
+  <si>
+    <t>Team Zeta</t>
+  </si>
+  <si>
+    <t>BAGGINS</t>
+  </si>
+  <si>
+    <t>Neville Longbottom</t>
+  </si>
+  <si>
+    <t>Team Xi</t>
+  </si>
+  <si>
+    <t>LONGBOTTOM</t>
+  </si>
+  <si>
+    <t>Ulysses</t>
+  </si>
+  <si>
+    <t>Team Phi</t>
+  </si>
+  <si>
+    <t>ULYSSES</t>
+  </si>
+  <si>
+    <t>Pool G</t>
+  </si>
+  <si>
+    <t>Hermione Granger</t>
+  </si>
+  <si>
+    <t>Team Theta</t>
+  </si>
+  <si>
+    <t>GRANGER</t>
+  </si>
+  <si>
+    <t>Othello</t>
+  </si>
+  <si>
+    <t>Team Omicron</t>
+  </si>
+  <si>
+    <t>OTHELLO</t>
+  </si>
+  <si>
     <t>Willy Wonka</t>
   </si>
   <si>
@@ -112,88 +280,25 @@
     <t>WONKA</t>
   </si>
   <si>
-    <t>Pool B</t>
-  </si>
-  <si>
-    <t>Voldemort</t>
-  </si>
-  <si>
-    <t>Team Chi</t>
-  </si>
-  <si>
-    <t>VOLDEMORT</t>
-  </si>
-  <si>
-    <t>Team Lambda</t>
-  </si>
-  <si>
-    <t>Ron Weasley</t>
-  </si>
-  <si>
-    <t>Team Sigma</t>
-  </si>
-  <si>
-    <t>WEASLEY</t>
-  </si>
-  <si>
-    <t>Pool C</t>
-  </si>
-  <si>
-    <t>Legolas Greenleaf</t>
-  </si>
-  <si>
-    <t>GREENLEAF</t>
-  </si>
-  <si>
-    <t>Xaro Xhoan Daxos</t>
-  </si>
-  <si>
-    <t>Team Omega</t>
-  </si>
-  <si>
-    <t>DAXOS</t>
-  </si>
-  <si>
-    <t>Hermione Granger</t>
-  </si>
-  <si>
-    <t>Team Theta</t>
-  </si>
-  <si>
-    <t>GRANGER</t>
-  </si>
-  <si>
-    <t>Pool D</t>
-  </si>
-  <si>
-    <t>Gandalf The Grey</t>
-  </si>
-  <si>
-    <t>Team Eta</t>
-  </si>
-  <si>
-    <t>GANDALF</t>
-  </si>
-  <si>
-    <t>Ulysses</t>
-  </si>
-  <si>
-    <t>Team Phi</t>
-  </si>
-  <si>
-    <t>ULYSSES</t>
-  </si>
-  <si>
-    <t>Neville Longbottom</t>
-  </si>
-  <si>
-    <t>Team Xi</t>
-  </si>
-  <si>
-    <t>LONGBOTTOM</t>
-  </si>
-  <si>
-    <t>Pool E</t>
+    <t>Pool H</t>
+  </si>
+  <si>
+    <t>Jon Snow</t>
+  </si>
+  <si>
+    <t>Team Kappa</t>
+  </si>
+  <si>
+    <t>SNOW</t>
+  </si>
+  <si>
+    <t>Quirinus Quirrell</t>
+  </si>
+  <si>
+    <t>Team Rho</t>
+  </si>
+  <si>
+    <t>QUIRRELL</t>
   </si>
   <si>
     <t>Ygritte</t>
@@ -203,111 +308,6 @@
   </si>
   <si>
     <t>YGRITTE</t>
-  </si>
-  <si>
-    <t>Jon Snow</t>
-  </si>
-  <si>
-    <t>Team Kappa</t>
-  </si>
-  <si>
-    <t>SNOW</t>
-  </si>
-  <si>
-    <t>Quirinus Quirrell</t>
-  </si>
-  <si>
-    <t>Team Rho</t>
-  </si>
-  <si>
-    <t>QUIRRELL</t>
-  </si>
-  <si>
-    <t>Pool F</t>
-  </si>
-  <si>
-    <t>Daenerys Targaryen</t>
-  </si>
-  <si>
-    <t>Team Delta</t>
-  </si>
-  <si>
-    <t>TARGARYEN</t>
-  </si>
-  <si>
-    <t>Moby Dick</t>
-  </si>
-  <si>
-    <t>Team Nu</t>
-  </si>
-  <si>
-    <t>DICK</t>
-  </si>
-  <si>
-    <t>Samwise Gamgee</t>
-  </si>
-  <si>
-    <t>Team Tau</t>
-  </si>
-  <si>
-    <t>GAMGEE</t>
-  </si>
-  <si>
-    <t>Pool G</t>
-  </si>
-  <si>
-    <t>Eddard Stark</t>
-  </si>
-  <si>
-    <t>Team Epsilon</t>
-  </si>
-  <si>
-    <t>STARK</t>
-  </si>
-  <si>
-    <t>Othello</t>
-  </si>
-  <si>
-    <t>Team Omicron</t>
-  </si>
-  <si>
-    <t>OTHELLO</t>
-  </si>
-  <si>
-    <t>Tyrion Lannister</t>
-  </si>
-  <si>
-    <t>Team Upsilon</t>
-  </si>
-  <si>
-    <t>LANNISTER</t>
-  </si>
-  <si>
-    <t>Pool H</t>
-  </si>
-  <si>
-    <t>Cersei Lannister</t>
-  </si>
-  <si>
-    <t>Team Gamma</t>
-  </si>
-  <si>
-    <t>Petyr Baelish</t>
-  </si>
-  <si>
-    <t>Team Pi</t>
-  </si>
-  <si>
-    <t>BAELISH</t>
-  </si>
-  <si>
-    <t>Frodo Baggins</t>
-  </si>
-  <si>
-    <t>Team Zeta</t>
-  </si>
-  <si>
-    <t>BAGGINS</t>
   </si>
   <si>
     <t>Shiaijo A</t>
@@ -1184,13 +1184,13 @@
         <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
@@ -1198,242 +1198,242 @@
         <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s">
         <v>60</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>61</v>
-      </c>
-      <c r="D17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" t="s">
         <v>63</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>64</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>65</v>
-      </c>
-      <c r="D18" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" t="s">
         <v>67</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>68</v>
-      </c>
-      <c r="D19" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" t="s">
         <v>70</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>71</v>
-      </c>
-      <c r="D20" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" t="s">
         <v>73</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>74</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>75</v>
-      </c>
-      <c r="D21" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" t="s">
         <v>77</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>78</v>
-      </c>
-      <c r="D22" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" t="s">
         <v>80</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>81</v>
-      </c>
-      <c r="D23" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" t="s">
         <v>83</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>84</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>85</v>
-      </c>
-      <c r="D24" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B25" t="s">
         <v>86</v>
@@ -1447,7 +1447,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B26" t="s">
         <v>89</v>

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
   <si>
     <t>Number of pools</t>
   </si>
@@ -79,6 +79,9 @@
     <t>Display Name</t>
   </si>
   <si>
+    <t>Player Number</t>
+  </si>
+  <si>
     <t>Metadata</t>
   </si>
   <si>
@@ -94,6 +97,9 @@
     <t>LANNISTER</t>
   </si>
   <si>
+    <t>K1</t>
+  </si>
+  <si>
     <t>Katniss Everdeen</t>
   </si>
   <si>
@@ -103,6 +109,9 @@
     <t>EVERDEEN</t>
   </si>
   <si>
+    <t>K2</t>
+  </si>
+  <si>
     <t>Ron Weasley</t>
   </si>
   <si>
@@ -112,6 +121,9 @@
     <t>WEASLEY</t>
   </si>
   <si>
+    <t>K3</t>
+  </si>
+  <si>
     <t>Pool B</t>
   </si>
   <si>
@@ -124,6 +136,9 @@
     <t>STARK</t>
   </si>
   <si>
+    <t>K4</t>
+  </si>
+  <si>
     <t>Moby Dick</t>
   </si>
   <si>
@@ -133,12 +148,18 @@
     <t>DICK</t>
   </si>
   <si>
+    <t>K5</t>
+  </si>
+  <si>
     <t>Tyrion Lannister</t>
   </si>
   <si>
     <t>Team Upsilon</t>
   </si>
   <si>
+    <t>K6</t>
+  </si>
+  <si>
     <t>Pool C</t>
   </si>
   <si>
@@ -151,6 +172,9 @@
     <t>GANDALF</t>
   </si>
   <si>
+    <t>K7</t>
+  </si>
+  <si>
     <t>Legolas Greenleaf</t>
   </si>
   <si>
@@ -160,6 +184,9 @@
     <t>GREENLEAF</t>
   </si>
   <si>
+    <t>K8</t>
+  </si>
+  <si>
     <t>Voldemort</t>
   </si>
   <si>
@@ -169,6 +196,9 @@
     <t>VOLDEMORT</t>
   </si>
   <si>
+    <t>K9</t>
+  </si>
+  <si>
     <t>Pool D</t>
   </si>
   <si>
@@ -181,6 +211,9 @@
     <t>MONTOYA</t>
   </si>
   <si>
+    <t>K10</t>
+  </si>
+  <si>
     <t>Petyr Baelish</t>
   </si>
   <si>
@@ -190,6 +223,9 @@
     <t>BAELISH</t>
   </si>
   <si>
+    <t>K11</t>
+  </si>
+  <si>
     <t>Xaro Xhoan Daxos</t>
   </si>
   <si>
@@ -199,6 +235,9 @@
     <t>DAXOS</t>
   </si>
   <si>
+    <t>K12</t>
+  </si>
+  <si>
     <t>Pool E</t>
   </si>
   <si>
@@ -211,6 +250,12 @@
     <t>TARGARYEN</t>
   </si>
   <si>
+    <t>K13</t>
+  </si>
+  <si>
+    <t>K14</t>
+  </si>
+  <si>
     <t>Samwise Gamgee</t>
   </si>
   <si>
@@ -220,6 +265,9 @@
     <t>GAMGEE</t>
   </si>
   <si>
+    <t>K15</t>
+  </si>
+  <si>
     <t>Pool F</t>
   </si>
   <si>
@@ -232,6 +280,9 @@
     <t>BAGGINS</t>
   </si>
   <si>
+    <t>K16</t>
+  </si>
+  <si>
     <t>Neville Longbottom</t>
   </si>
   <si>
@@ -241,6 +292,9 @@
     <t>LONGBOTTOM</t>
   </si>
   <si>
+    <t>K17</t>
+  </si>
+  <si>
     <t>Ulysses</t>
   </si>
   <si>
@@ -250,6 +304,9 @@
     <t>ULYSSES</t>
   </si>
   <si>
+    <t>K18</t>
+  </si>
+  <si>
     <t>Pool G</t>
   </si>
   <si>
@@ -262,6 +319,9 @@
     <t>GRANGER</t>
   </si>
   <si>
+    <t>K19</t>
+  </si>
+  <si>
     <t>Othello</t>
   </si>
   <si>
@@ -271,6 +331,9 @@
     <t>OTHELLO</t>
   </si>
   <si>
+    <t>K20</t>
+  </si>
+  <si>
     <t>Willy Wonka</t>
   </si>
   <si>
@@ -280,6 +343,9 @@
     <t>WONKA</t>
   </si>
   <si>
+    <t>K21</t>
+  </si>
+  <si>
     <t>Pool H</t>
   </si>
   <si>
@@ -292,6 +358,9 @@
     <t>SNOW</t>
   </si>
   <si>
+    <t>K22</t>
+  </si>
+  <si>
     <t>Quirinus Quirrell</t>
   </si>
   <si>
@@ -301,6 +370,9 @@
     <t>QUIRRELL</t>
   </si>
   <si>
+    <t>K23</t>
+  </si>
+  <si>
     <t>Ygritte</t>
   </si>
   <si>
@@ -310,6 +382,9 @@
     <t>YGRITTE</t>
   </si>
   <si>
+    <t>K24</t>
+  </si>
+  <si>
     <t>Shiaijo A</t>
   </si>
   <si>
@@ -356,78 +431,6 @@
   </si>
   <si>
     <t>3.</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>B1</t>
-  </si>
-  <si>
-    <t>B2</t>
-  </si>
-  <si>
-    <t>B3</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>D2</t>
-  </si>
-  <si>
-    <t>D3</t>
-  </si>
-  <si>
-    <t>E1</t>
-  </si>
-  <si>
-    <t>E2</t>
-  </si>
-  <si>
-    <t>E3</t>
-  </si>
-  <si>
-    <t>F1</t>
-  </si>
-  <si>
-    <t>F2</t>
-  </si>
-  <si>
-    <t>F3</t>
-  </si>
-  <si>
-    <t>G1</t>
-  </si>
-  <si>
-    <t>G2</t>
-  </si>
-  <si>
-    <t>G3</t>
-  </si>
-  <si>
-    <t>H1</t>
-  </si>
-  <si>
-    <t>H2</t>
-  </si>
-  <si>
-    <t>H3</t>
   </si>
   <si>
     <t>Round 1 - Match 1</t>
@@ -1122,341 +1125,416 @@
       <c r="E2" t="s">
         <v>15</v>
       </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>49</v>
+      </c>
+      <c r="E10" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>53</v>
+      </c>
+      <c r="E11" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>58</v>
+      </c>
+      <c r="E12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>62</v>
+      </c>
+      <c r="E13" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>66</v>
+      </c>
+      <c r="E14" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>71</v>
+      </c>
+      <c r="E15" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="E16" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>76</v>
+      </c>
+      <c r="E17" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>81</v>
+      </c>
+      <c r="E18" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>85</v>
+      </c>
+      <c r="E19" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
-        <v>71</v>
+        <v>89</v>
+      </c>
+      <c r="E20" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>94</v>
+      </c>
+      <c r="E21" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s">
-        <v>78</v>
+        <v>98</v>
+      </c>
+      <c r="E22" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>102</v>
+      </c>
+      <c r="E23" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>85</v>
+        <v>107</v>
+      </c>
+      <c r="E24" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>111</v>
+      </c>
+      <c r="E25" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>115</v>
+      </c>
+      <c r="E26" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1474,96 +1552,96 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="28" t="s">
-        <v>108</v>
+      <c r="A1" s="28" t="str">
+        <f>'data'!$E$3</f>
       </c>
       <c r="B1" s="29" t="str">
         <f>'data'!D3</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="28" t="s">
-        <v>109</v>
+      <c r="A2" s="28" t="str">
+        <f>'data'!$E$4</f>
       </c>
       <c r="B2" s="29" t="str">
         <f>'data'!D4</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="28" t="s">
-        <v>110</v>
+      <c r="A3" s="28" t="str">
+        <f>'data'!$E$5</f>
       </c>
       <c r="B3" s="29" t="str">
         <f>'data'!D5</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="28" t="s">
-        <v>111</v>
+      <c r="A4" s="28" t="str">
+        <f>'data'!$E$6</f>
       </c>
       <c r="B4" s="29" t="str">
         <f>'data'!D6</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="28" t="s">
-        <v>112</v>
+      <c r="A5" s="28" t="str">
+        <f>'data'!$E$7</f>
       </c>
       <c r="B5" s="29" t="str">
         <f>'data'!D7</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="28" t="s">
-        <v>113</v>
+      <c r="A6" s="28" t="str">
+        <f>'data'!$E$8</f>
       </c>
       <c r="B6" s="29" t="str">
         <f>'data'!D8</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="28" t="s">
-        <v>114</v>
+      <c r="A7" s="28" t="str">
+        <f>'data'!$E$9</f>
       </c>
       <c r="B7" s="29" t="str">
         <f>'data'!D9</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="28" t="s">
-        <v>115</v>
+      <c r="A8" s="28" t="str">
+        <f>'data'!$E$10</f>
       </c>
       <c r="B8" s="29" t="str">
         <f>'data'!D10</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="28" t="s">
-        <v>116</v>
+      <c r="A9" s="28" t="str">
+        <f>'data'!$E$11</f>
       </c>
       <c r="B9" s="29" t="str">
         <f>'data'!D11</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="28" t="s">
-        <v>117</v>
+      <c r="A10" s="28" t="str">
+        <f>'data'!$E$12</f>
       </c>
       <c r="B10" s="29" t="str">
         <f>'data'!D12</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="28" t="s">
-        <v>118</v>
+      <c r="A11" s="28" t="str">
+        <f>'data'!$E$13</f>
       </c>
       <c r="B11" s="29" t="str">
         <f>'data'!D13</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="28" t="s">
-        <v>119</v>
+      <c r="A12" s="28" t="str">
+        <f>'data'!$E$14</f>
       </c>
       <c r="B12" s="29" t="str">
         <f>'data'!D14</f>
@@ -1592,96 +1670,96 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="28" t="s">
-        <v>120</v>
+      <c r="A1" s="28" t="str">
+        <f>'data'!$E$15</f>
       </c>
       <c r="B1" s="29" t="str">
         <f>'data'!D15</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="28" t="s">
-        <v>121</v>
+      <c r="A2" s="28" t="str">
+        <f>'data'!$E$16</f>
       </c>
       <c r="B2" s="29" t="str">
         <f>'data'!D16</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="28" t="s">
-        <v>122</v>
+      <c r="A3" s="28" t="str">
+        <f>'data'!$E$17</f>
       </c>
       <c r="B3" s="29" t="str">
         <f>'data'!D17</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="28" t="s">
-        <v>123</v>
+      <c r="A4" s="28" t="str">
+        <f>'data'!$E$18</f>
       </c>
       <c r="B4" s="29" t="str">
         <f>'data'!D18</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="28" t="s">
-        <v>124</v>
+      <c r="A5" s="28" t="str">
+        <f>'data'!$E$19</f>
       </c>
       <c r="B5" s="29" t="str">
         <f>'data'!D19</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="28" t="s">
-        <v>125</v>
+      <c r="A6" s="28" t="str">
+        <f>'data'!$E$20</f>
       </c>
       <c r="B6" s="29" t="str">
         <f>'data'!D20</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="28" t="s">
-        <v>126</v>
+      <c r="A7" s="28" t="str">
+        <f>'data'!$E$21</f>
       </c>
       <c r="B7" s="29" t="str">
         <f>'data'!D21</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="28" t="s">
-        <v>127</v>
+      <c r="A8" s="28" t="str">
+        <f>'data'!$E$22</f>
       </c>
       <c r="B8" s="29" t="str">
         <f>'data'!D22</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="28" t="s">
-        <v>128</v>
+      <c r="A9" s="28" t="str">
+        <f>'data'!$E$23</f>
       </c>
       <c r="B9" s="29" t="str">
         <f>'data'!D23</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="28" t="s">
-        <v>129</v>
+      <c r="A10" s="28" t="str">
+        <f>'data'!$E$24</f>
       </c>
       <c r="B10" s="29" t="str">
         <f>'data'!D24</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="28" t="s">
-        <v>130</v>
+      <c r="A11" s="28" t="str">
+        <f>'data'!$E$25</f>
       </c>
       <c r="B11" s="29" t="str">
         <f>'data'!D25</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="28" t="s">
-        <v>131</v>
+      <c r="A12" s="28" t="str">
+        <f>'data'!$E$26</f>
       </c>
       <c r="B12" s="29" t="str">
         <f>'data'!D26</f>
@@ -1710,242 +1788,242 @@
   <sheetData>
     <row r="1" ht="409" customHeight="true">
       <c r="A1" s="30" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" ht="409" customHeight="true">
       <c r="A2" s="30" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" ht="409" customHeight="true">
       <c r="A3" s="30" t="s">
-        <v>109</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" ht="409" customHeight="true">
       <c r="A4" s="30" t="s">
-        <v>109</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" ht="409" customHeight="true">
       <c r="A5" s="30" t="s">
-        <v>110</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="409" customHeight="true">
       <c r="A6" s="30" t="s">
-        <v>110</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" ht="409" customHeight="true">
       <c r="A7" s="30" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" ht="409" customHeight="true">
       <c r="A8" s="30" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" ht="409" customHeight="true">
       <c r="A9" s="30" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" ht="409" customHeight="true">
       <c r="A10" s="30" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" ht="409" customHeight="true">
       <c r="A11" s="30" t="s">
-        <v>113</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" ht="409" customHeight="true">
       <c r="A12" s="30" t="s">
-        <v>113</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" ht="409" customHeight="true">
       <c r="A13" s="30" t="s">
-        <v>114</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" ht="409" customHeight="true">
       <c r="A14" s="30" t="s">
-        <v>114</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" ht="409" customHeight="true">
       <c r="A15" s="30" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" ht="409" customHeight="true">
       <c r="A16" s="30" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" ht="409" customHeight="true">
       <c r="A17" s="30" t="s">
-        <v>116</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" ht="409" customHeight="true">
       <c r="A18" s="30" t="s">
-        <v>116</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" ht="409" customHeight="true">
       <c r="A19" s="30" t="s">
-        <v>117</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" ht="409" customHeight="true">
       <c r="A20" s="30" t="s">
-        <v>117</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" ht="409" customHeight="true">
       <c r="A21" s="30" t="s">
-        <v>118</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" ht="409" customHeight="true">
       <c r="A22" s="30" t="s">
-        <v>118</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" ht="409" customHeight="true">
       <c r="A23" s="30" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" ht="409" customHeight="true">
       <c r="A24" s="30" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" ht="409" customHeight="true">
       <c r="A25" s="30" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" ht="409" customHeight="true">
       <c r="A26" s="30" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" ht="409" customHeight="true">
       <c r="A27" s="30" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" ht="409" customHeight="true">
       <c r="A28" s="30" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" ht="409" customHeight="true">
       <c r="A29" s="30" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" ht="409" customHeight="true">
       <c r="A30" s="30" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" ht="409" customHeight="true">
       <c r="A31" s="30" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" ht="409" customHeight="true">
       <c r="A32" s="30" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" ht="409" customHeight="true">
       <c r="A33" s="30" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" ht="409" customHeight="true">
       <c r="A34" s="30" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" ht="409" customHeight="true">
       <c r="A35" s="30" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" ht="409" customHeight="true">
       <c r="A36" s="30" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" ht="409" customHeight="true">
       <c r="A37" s="30" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" ht="409" customHeight="true">
       <c r="A38" s="30" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" ht="409" customHeight="true">
       <c r="A39" s="30" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" ht="409" customHeight="true">
       <c r="A40" s="30" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" ht="409" customHeight="true">
       <c r="A41" s="30" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" ht="409" customHeight="true">
       <c r="A42" s="30" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" ht="409" customHeight="true">
       <c r="A43" s="30" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" ht="409" customHeight="true">
       <c r="A44" s="30" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" ht="409" customHeight="true">
       <c r="A45" s="30" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" ht="409" customHeight="true">
       <c r="A46" s="30" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47" ht="409" customHeight="true">
       <c r="A47" s="30" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" ht="409" customHeight="true">
       <c r="A48" s="30" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2182,7 +2260,7 @@
     </row>
     <row r="13">
       <c r="E13" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
@@ -2193,7 +2271,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -2203,7 +2281,7 @@
     </row>
     <row r="15">
       <c r="E15" s="32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -2213,7 +2291,7 @@
     </row>
     <row r="16">
       <c r="E16" s="32" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -2223,7 +2301,7 @@
     </row>
     <row r="17">
       <c r="E17" s="32" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
@@ -2233,7 +2311,7 @@
     </row>
     <row r="18">
       <c r="E18" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
@@ -2243,7 +2321,7 @@
     </row>
     <row r="19">
       <c r="E19" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
@@ -2316,35 +2394,35 @@
     </row>
     <row r="6" ht="17" customHeight="true">
       <c r="B6" s="12" t="str">
-        <f>"1. " &amp; data!$B$3</f>
+        <f>data!$E$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="D6" s="12" t="str">
-        <f>"1. " &amp; data!$B$12</f>
+        <f>data!$E$12&amp;" "&amp;data!$B$12</f>
       </c>
       <c r="F6" s="12" t="str">
-        <f>"1. " &amp; data!$B$21</f>
+        <f>data!$E$21&amp;" "&amp;data!$B$21</f>
       </c>
     </row>
     <row r="7" ht="17" customHeight="true">
       <c r="B7" s="12" t="str">
-        <f>"2. " &amp; data!$B$4</f>
+        <f>data!$E$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="D7" s="12" t="str">
-        <f>"2. " &amp; data!$B$13</f>
+        <f>data!$E$13&amp;" "&amp;data!$B$13</f>
       </c>
       <c r="F7" s="12" t="str">
-        <f>"2. " &amp; data!$B$22</f>
+        <f>data!$E$22&amp;" "&amp;data!$B$22</f>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="12" t="str">
-        <f>"3. " &amp; data!$B$5</f>
+        <f>data!$E$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="D8" s="12" t="str">
-        <f>"3. " &amp; data!$B$14</f>
+        <f>data!$E$14&amp;" "&amp;data!$B$14</f>
       </c>
       <c r="F8" s="12" t="str">
-        <f>"3. " &amp; data!$B$23</f>
+        <f>data!$E$23&amp;" "&amp;data!$B$23</f>
       </c>
     </row>
     <row r="11">
@@ -2360,35 +2438,35 @@
     </row>
     <row r="12">
       <c r="B12" s="12" t="str">
-        <f>"1. " &amp; data!$B$6</f>
+        <f>data!$E$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="D12" s="12" t="str">
-        <f>"1. " &amp; data!$B$15</f>
+        <f>data!$E$15&amp;" "&amp;data!$B$15</f>
       </c>
       <c r="F12" s="12" t="str">
-        <f>"1. " &amp; data!$B$24</f>
+        <f>data!$E$24&amp;" "&amp;data!$B$24</f>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="12" t="str">
-        <f>"2. " &amp; data!$B$7</f>
+        <f>data!$E$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="D13" s="12" t="str">
-        <f>"2. " &amp; data!$B$16</f>
+        <f>data!$E$16&amp;" "&amp;data!$B$16</f>
       </c>
       <c r="F13" s="12" t="str">
-        <f>"2. " &amp; data!$B$25</f>
+        <f>data!$E$25&amp;" "&amp;data!$B$25</f>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="12" t="str">
-        <f>"3. " &amp; data!$B$8</f>
+        <f>data!$E$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="D14" s="12" t="str">
-        <f>"3. " &amp; data!$B$17</f>
+        <f>data!$E$17&amp;" "&amp;data!$B$17</f>
       </c>
       <c r="F14" s="12" t="str">
-        <f>"3. " &amp; data!$B$26</f>
+        <f>data!$E$26&amp;" "&amp;data!$B$26</f>
       </c>
     </row>
     <row r="17">
@@ -2401,26 +2479,26 @@
     </row>
     <row r="18">
       <c r="B18" s="12" t="str">
-        <f>"1. " &amp; data!$B$9</f>
+        <f>data!$E$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="D18" s="12" t="str">
-        <f>"1. " &amp; data!$B$18</f>
+        <f>data!$E$18&amp;" "&amp;data!$B$18</f>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="12" t="str">
-        <f>"2. " &amp; data!$B$10</f>
+        <f>data!$E$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="D19" s="12" t="str">
-        <f>"2. " &amp; data!$B$19</f>
+        <f>data!$E$19&amp;" "&amp;data!$B$19</f>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="12" t="str">
-        <f>"3. " &amp; data!$B$11</f>
+        <f>data!$E$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="D20" s="12" t="str">
-        <f>"3. " &amp; data!$B$20</f>
+        <f>data!$E$20&amp;" "&amp;data!$B$20</f>
       </c>
     </row>
   </sheetData>
@@ -2455,7 +2533,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -2464,7 +2542,7 @@
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
       <c r="I1" s="13" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
@@ -2495,27 +2573,27 @@
     </row>
     <row r="3">
       <c r="A3" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$E$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -2523,10 +2601,10 @@
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
       <c r="G4" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$E$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>'data'!$B$16</f>
+        <f>data!$E$16&amp;" "&amp;data!$B$16</f>
       </c>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
@@ -2534,12 +2612,12 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
       <c r="O4" s="14" t="str">
-        <f>'data'!$B$15</f>
+        <f>data!$E$15&amp;" "&amp;data!$B$15</f>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$E$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
@@ -2547,10 +2625,10 @@
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
       <c r="G5" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$E$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="I5" s="14" t="str">
-        <f>'data'!$B$17</f>
+        <f>data!$E$17&amp;" "&amp;data!$B$17</f>
       </c>
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>
@@ -2558,12 +2636,12 @@
       <c r="M5" s="18"/>
       <c r="N5" s="18"/>
       <c r="O5" s="14" t="str">
-        <f>'data'!$B$15</f>
+        <f>data!$E$15&amp;" "&amp;data!$B$15</f>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$E$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -2571,10 +2649,10 @@
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="G6" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$E$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="I6" s="14" t="str">
-        <f>'data'!$B$17</f>
+        <f>data!$E$17&amp;" "&amp;data!$B$17</f>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
@@ -2582,56 +2660,56 @@
       <c r="M6" s="18"/>
       <c r="N6" s="18"/>
       <c r="O6" s="14" t="str">
-        <f>'data'!$B$16</f>
+        <f>data!$E$16&amp;" "&amp;data!$B$16</f>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$E$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="B9" s="14" t="str">
         <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x",AND(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x",AND(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))*1),0)</f>
@@ -2652,7 +2730,7 @@
         <f>RANK(U9,$U$9:$U$11)+COUNTIF($U$8:U8,U9)</f>
       </c>
       <c r="I9" s="14" t="str">
-        <f>'data'!$B$15</f>
+        <f>data!$E$15&amp;" "&amp;data!$B$15</f>
       </c>
       <c r="J9" s="14" t="str">
         <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x",AND(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x",AND(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))*1),0)</f>
@@ -2681,7 +2759,7 @@
     </row>
     <row r="10">
       <c r="A10" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$E$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="B10" s="14" t="str">
         <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x",AND(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x",AND(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))*1),0)</f>
@@ -2702,7 +2780,7 @@
         <f>RANK(U10,$U$9:$U$11)+COUNTIF($U$8:U9,U10)</f>
       </c>
       <c r="I10" s="14" t="str">
-        <f>'data'!$B$16</f>
+        <f>data!$E$16&amp;" "&amp;data!$B$16</f>
       </c>
       <c r="J10" s="14" t="str">
         <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x",AND(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x",AND(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))*1),0)</f>
@@ -2731,7 +2809,7 @@
     </row>
     <row r="11">
       <c r="A11" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$E$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="B11" s="14" t="str">
         <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x",AND(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x",AND(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))*1),0)</f>
@@ -2752,7 +2830,7 @@
         <f>RANK(U11,$U$9:$U$11)+COUNTIF($U$8:U10,U11)</f>
       </c>
       <c r="I11" s="14" t="str">
-        <f>'data'!$B$17</f>
+        <f>data!$E$17&amp;" "&amp;data!$B$17</f>
       </c>
       <c r="J11" s="14" t="str">
         <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x",AND(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x",AND(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))*1),0)</f>
@@ -2782,22 +2860,22 @@
     <row r="14">
       <c r="F14" s="13"/>
       <c r="G14" s="13" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15">
       <c r="F15" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G15" s="19" t="str">
         <f>IFERROR(INDEX($A$9:$A$11, MATCH(1, $G$9:$G$11, 0)), "-")</f>
       </c>
       <c r="N15" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O15" s="19" t="str">
         <f>IFERROR(INDEX($I$9:$I$11, MATCH(1, $O$9:$O$11, 0)), "-")</f>
@@ -2805,13 +2883,13 @@
     </row>
     <row r="16">
       <c r="F16" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G16" s="19" t="str">
         <f>IFERROR(INDEX($A$9:$A$11, MATCH(2, $G$9:$G$11, 0)), "-")</f>
       </c>
       <c r="N16" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O16" s="19" t="str">
         <f>IFERROR(INDEX($I$9:$I$11, MATCH(2, $O$9:$O$11, 0)), "-")</f>
@@ -2819,13 +2897,13 @@
     </row>
     <row r="17">
       <c r="F17" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="G17" s="19" t="str">
         <f>IFERROR(INDEX($A$9:$A$11, MATCH(3, $G$9:$G$11, 0)), "-")</f>
       </c>
       <c r="N17" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="O17" s="19" t="str">
         <f>IFERROR(INDEX($I$9:$I$11, MATCH(3, $O$9:$O$11, 0)), "-")</f>
@@ -2853,27 +2931,27 @@
     </row>
     <row r="20">
       <c r="A20" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O20" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="str">
-        <f>'data'!$B$7</f>
+        <f>data!$E$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -2881,10 +2959,10 @@
       <c r="E21" s="18"/>
       <c r="F21" s="18"/>
       <c r="G21" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$E$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="I21" s="14" t="str">
-        <f>'data'!$B$19</f>
+        <f>data!$E$19&amp;" "&amp;data!$B$19</f>
       </c>
       <c r="J21" s="18"/>
       <c r="K21" s="18"/>
@@ -2892,12 +2970,12 @@
       <c r="M21" s="18"/>
       <c r="N21" s="18"/>
       <c r="O21" s="14" t="str">
-        <f>'data'!$B$18</f>
+        <f>data!$E$18&amp;" "&amp;data!$B$18</f>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="str">
-        <f>'data'!$B$8</f>
+        <f>data!$E$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -2905,10 +2983,10 @@
       <c r="E22" s="18"/>
       <c r="F22" s="18"/>
       <c r="G22" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$E$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="I22" s="14" t="str">
-        <f>'data'!$B$20</f>
+        <f>data!$E$20&amp;" "&amp;data!$B$20</f>
       </c>
       <c r="J22" s="18"/>
       <c r="K22" s="18"/>
@@ -2916,12 +2994,12 @@
       <c r="M22" s="18"/>
       <c r="N22" s="18"/>
       <c r="O22" s="14" t="str">
-        <f>'data'!$B$18</f>
+        <f>data!$E$18&amp;" "&amp;data!$B$18</f>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="str">
-        <f>'data'!$B$8</f>
+        <f>data!$E$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -2929,10 +3007,10 @@
       <c r="E23" s="18"/>
       <c r="F23" s="18"/>
       <c r="G23" s="14" t="str">
-        <f>'data'!$B$7</f>
+        <f>data!$E$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="I23" s="14" t="str">
-        <f>'data'!$B$20</f>
+        <f>data!$E$20&amp;" "&amp;data!$B$20</f>
       </c>
       <c r="J23" s="18"/>
       <c r="K23" s="18"/>
@@ -2940,56 +3018,56 @@
       <c r="M23" s="18"/>
       <c r="N23" s="18"/>
       <c r="O23" s="14" t="str">
-        <f>'data'!$B$19</f>
+        <f>data!$E$19&amp;" "&amp;data!$B$19</f>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="K25" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="L25" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="O25" s="13" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$E$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="B26" s="14" t="str">
         <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x",AND(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x",AND(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))*1),0)</f>
@@ -3010,7 +3088,7 @@
         <f>RANK(U26,$U$26:$U$28)+COUNTIF($U$25:U25,U26)</f>
       </c>
       <c r="I26" s="14" t="str">
-        <f>'data'!$B$18</f>
+        <f>data!$E$18&amp;" "&amp;data!$B$18</f>
       </c>
       <c r="J26" s="14" t="str">
         <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x",AND(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x",AND(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))*1),0)</f>
@@ -3039,7 +3117,7 @@
     </row>
     <row r="27">
       <c r="A27" s="14" t="str">
-        <f>'data'!$B$7</f>
+        <f>data!$E$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="B27" s="14" t="str">
         <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x",AND(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),IF(OR(D23="X",D23="x",AND(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))*1),0)</f>
@@ -3060,7 +3138,7 @@
         <f>RANK(U27,$U$26:$U$28)+COUNTIF($U$25:U26,U27)</f>
       </c>
       <c r="I27" s="14" t="str">
-        <f>'data'!$B$19</f>
+        <f>data!$E$19&amp;" "&amp;data!$B$19</f>
       </c>
       <c r="J27" s="14" t="str">
         <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x",AND(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),IF(OR(L23="X",L23="x",AND(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))*1),0)</f>
@@ -3089,7 +3167,7 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="str">
-        <f>'data'!$B$8</f>
+        <f>data!$E$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="B28" s="14" t="str">
         <f>IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x",AND(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),IF(OR(D23="X",D23="x",AND(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")))*1),0)</f>
@@ -3110,7 +3188,7 @@
         <f>RANK(U28,$U$26:$U$28)+COUNTIF($U$25:U27,U28)</f>
       </c>
       <c r="I28" s="14" t="str">
-        <f>'data'!$B$20</f>
+        <f>data!$E$20&amp;" "&amp;data!$B$20</f>
       </c>
       <c r="J28" s="14" t="str">
         <f>IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x",AND(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),IF(OR(L23="X",L23="x",AND(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")))*1),0)</f>
@@ -3140,22 +3218,22 @@
     <row r="31">
       <c r="F31" s="13"/>
       <c r="G31" s="13" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="N31" s="13"/>
       <c r="O31" s="13" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32">
       <c r="F32" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G32" s="19" t="str">
         <f>IFERROR(INDEX($A$26:$A$28, MATCH(1, $G$26:$G$28, 0)), "-")</f>
       </c>
       <c r="N32" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O32" s="19" t="str">
         <f>IFERROR(INDEX($I$26:$I$28, MATCH(1, $O$26:$O$28, 0)), "-")</f>
@@ -3163,13 +3241,13 @@
     </row>
     <row r="33">
       <c r="F33" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G33" s="19" t="str">
         <f>IFERROR(INDEX($A$26:$A$28, MATCH(2, $G$26:$G$28, 0)), "-")</f>
       </c>
       <c r="N33" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O33" s="19" t="str">
         <f>IFERROR(INDEX($I$26:$I$28, MATCH(2, $O$26:$O$28, 0)), "-")</f>
@@ -3177,13 +3255,13 @@
     </row>
     <row r="34">
       <c r="F34" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="G34" s="19" t="str">
         <f>IFERROR(INDEX($A$26:$A$28, MATCH(3, $G$26:$G$28, 0)), "-")</f>
       </c>
       <c r="N34" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="O34" s="19" t="str">
         <f>IFERROR(INDEX($I$26:$I$28, MATCH(3, $O$26:$O$28, 0)), "-")</f>
@@ -3211,27 +3289,27 @@
     </row>
     <row r="37">
       <c r="A37" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L37" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O37" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="str">
-        <f>'data'!$B$10</f>
+        <f>data!$E$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="B38" s="18"/>
       <c r="C38" s="18"/>
@@ -3239,10 +3317,10 @@
       <c r="E38" s="18"/>
       <c r="F38" s="18"/>
       <c r="G38" s="14" t="str">
-        <f>'data'!$B$9</f>
+        <f>data!$E$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="I38" s="14" t="str">
-        <f>'data'!$B$22</f>
+        <f>data!$E$22&amp;" "&amp;data!$B$22</f>
       </c>
       <c r="J38" s="18"/>
       <c r="K38" s="18"/>
@@ -3250,12 +3328,12 @@
       <c r="M38" s="18"/>
       <c r="N38" s="18"/>
       <c r="O38" s="14" t="str">
-        <f>'data'!$B$21</f>
+        <f>data!$E$21&amp;" "&amp;data!$B$21</f>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="str">
-        <f>'data'!$B$11</f>
+        <f>data!$E$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="B39" s="18"/>
       <c r="C39" s="18"/>
@@ -3263,10 +3341,10 @@
       <c r="E39" s="18"/>
       <c r="F39" s="18"/>
       <c r="G39" s="14" t="str">
-        <f>'data'!$B$9</f>
+        <f>data!$E$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="I39" s="14" t="str">
-        <f>'data'!$B$23</f>
+        <f>data!$E$23&amp;" "&amp;data!$B$23</f>
       </c>
       <c r="J39" s="18"/>
       <c r="K39" s="18"/>
@@ -3274,12 +3352,12 @@
       <c r="M39" s="18"/>
       <c r="N39" s="18"/>
       <c r="O39" s="14" t="str">
-        <f>'data'!$B$21</f>
+        <f>data!$E$21&amp;" "&amp;data!$B$21</f>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="str">
-        <f>'data'!$B$11</f>
+        <f>data!$E$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="B40" s="18"/>
       <c r="C40" s="18"/>
@@ -3287,10 +3365,10 @@
       <c r="E40" s="18"/>
       <c r="F40" s="18"/>
       <c r="G40" s="14" t="str">
-        <f>'data'!$B$10</f>
+        <f>data!$E$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="I40" s="14" t="str">
-        <f>'data'!$B$23</f>
+        <f>data!$E$23&amp;" "&amp;data!$B$23</f>
       </c>
       <c r="J40" s="18"/>
       <c r="K40" s="18"/>
@@ -3298,56 +3376,56 @@
       <c r="M40" s="18"/>
       <c r="N40" s="18"/>
       <c r="O40" s="14" t="str">
-        <f>'data'!$B$22</f>
+        <f>data!$E$22&amp;" "&amp;data!$B$22</f>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="K42" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="L42" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="M42" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="N42" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="O42" s="13" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="str">
-        <f>'data'!$B$9</f>
+        <f>data!$E$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="B43" s="14" t="str">
         <f>IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x",AND(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),IF(OR(D39="X",D39="x",AND(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))*1),0)</f>
@@ -3368,7 +3446,7 @@
         <f>RANK(U43,$U$43:$U$45)+COUNTIF($U$42:U42,U43)</f>
       </c>
       <c r="I43" s="14" t="str">
-        <f>'data'!$B$21</f>
+        <f>data!$E$21&amp;" "&amp;data!$B$21</f>
       </c>
       <c r="J43" s="14" t="str">
         <f>IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x",AND(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),IF(OR(L39="X",L39="x",AND(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))*1),0)</f>
@@ -3397,7 +3475,7 @@
     </row>
     <row r="44">
       <c r="A44" s="14" t="str">
-        <f>'data'!$B$10</f>
+        <f>data!$E$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="B44" s="14" t="str">
         <f>IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x",AND(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),IF(OR(D40="X",D40="x",AND(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))*1),0)</f>
@@ -3418,7 +3496,7 @@
         <f>RANK(U44,$U$43:$U$45)+COUNTIF($U$42:U43,U44)</f>
       </c>
       <c r="I44" s="14" t="str">
-        <f>'data'!$B$22</f>
+        <f>data!$E$22&amp;" "&amp;data!$B$22</f>
       </c>
       <c r="J44" s="14" t="str">
         <f>IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x",AND(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),IF(OR(L40="X",L40="x",AND(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))*1),0)</f>
@@ -3447,7 +3525,7 @@
     </row>
     <row r="45">
       <c r="A45" s="14" t="str">
-        <f>'data'!$B$11</f>
+        <f>data!$E$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="B45" s="14" t="str">
         <f>IF(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),IF(OR(D39="X",D39="x",AND(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),IF(OR(D40="X",D40="x",AND(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")))*1),0)</f>
@@ -3468,7 +3546,7 @@
         <f>RANK(U45,$U$43:$U$45)+COUNTIF($U$42:U44,U45)</f>
       </c>
       <c r="I45" s="14" t="str">
-        <f>'data'!$B$23</f>
+        <f>data!$E$23&amp;" "&amp;data!$B$23</f>
       </c>
       <c r="J45" s="14" t="str">
         <f>IF(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),IF(OR(L39="X",L39="x",AND(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),IF(OR(L40="X",L40="x",AND(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-","")))*1),0)</f>
@@ -3498,22 +3576,22 @@
     <row r="48">
       <c r="F48" s="13"/>
       <c r="G48" s="13" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="N48" s="13"/>
       <c r="O48" s="13" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49">
       <c r="F49" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G49" s="19" t="str">
         <f>IFERROR(INDEX($A$43:$A$45, MATCH(1, $G$43:$G$45, 0)), "-")</f>
       </c>
       <c r="N49" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O49" s="19" t="str">
         <f>IFERROR(INDEX($I$43:$I$45, MATCH(1, $O$43:$O$45, 0)), "-")</f>
@@ -3521,13 +3599,13 @@
     </row>
     <row r="50">
       <c r="F50" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G50" s="19" t="str">
         <f>IFERROR(INDEX($A$43:$A$45, MATCH(2, $G$43:$G$45, 0)), "-")</f>
       </c>
       <c r="N50" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O50" s="19" t="str">
         <f>IFERROR(INDEX($I$43:$I$45, MATCH(2, $O$43:$O$45, 0)), "-")</f>
@@ -3535,13 +3613,13 @@
     </row>
     <row r="51">
       <c r="F51" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="G51" s="19" t="str">
         <f>IFERROR(INDEX($A$43:$A$45, MATCH(3, $G$43:$G$45, 0)), "-")</f>
       </c>
       <c r="N51" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="O51" s="19" t="str">
         <f>IFERROR(INDEX($I$43:$I$45, MATCH(3, $O$43:$O$45, 0)), "-")</f>
@@ -3569,27 +3647,27 @@
     </row>
     <row r="54">
       <c r="A54" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I54" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L54" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O54" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="str">
-        <f>'data'!$B$13</f>
+        <f>data!$E$13&amp;" "&amp;data!$B$13</f>
       </c>
       <c r="B55" s="18"/>
       <c r="C55" s="18"/>
@@ -3597,10 +3675,10 @@
       <c r="E55" s="18"/>
       <c r="F55" s="18"/>
       <c r="G55" s="14" t="str">
-        <f>'data'!$B$12</f>
+        <f>data!$E$12&amp;" "&amp;data!$B$12</f>
       </c>
       <c r="I55" s="14" t="str">
-        <f>'data'!$B$25</f>
+        <f>data!$E$25&amp;" "&amp;data!$B$25</f>
       </c>
       <c r="J55" s="18"/>
       <c r="K55" s="18"/>
@@ -3608,12 +3686,12 @@
       <c r="M55" s="18"/>
       <c r="N55" s="18"/>
       <c r="O55" s="14" t="str">
-        <f>'data'!$B$24</f>
+        <f>data!$E$24&amp;" "&amp;data!$B$24</f>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="str">
-        <f>'data'!$B$14</f>
+        <f>data!$E$14&amp;" "&amp;data!$B$14</f>
       </c>
       <c r="B56" s="18"/>
       <c r="C56" s="18"/>
@@ -3621,10 +3699,10 @@
       <c r="E56" s="18"/>
       <c r="F56" s="18"/>
       <c r="G56" s="14" t="str">
-        <f>'data'!$B$12</f>
+        <f>data!$E$12&amp;" "&amp;data!$B$12</f>
       </c>
       <c r="I56" s="14" t="str">
-        <f>'data'!$B$26</f>
+        <f>data!$E$26&amp;" "&amp;data!$B$26</f>
       </c>
       <c r="J56" s="18"/>
       <c r="K56" s="18"/>
@@ -3632,12 +3710,12 @@
       <c r="M56" s="18"/>
       <c r="N56" s="18"/>
       <c r="O56" s="14" t="str">
-        <f>'data'!$B$24</f>
+        <f>data!$E$24&amp;" "&amp;data!$B$24</f>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="str">
-        <f>'data'!$B$14</f>
+        <f>data!$E$14&amp;" "&amp;data!$B$14</f>
       </c>
       <c r="B57" s="18"/>
       <c r="C57" s="18"/>
@@ -3645,10 +3723,10 @@
       <c r="E57" s="18"/>
       <c r="F57" s="18"/>
       <c r="G57" s="14" t="str">
-        <f>'data'!$B$13</f>
+        <f>data!$E$13&amp;" "&amp;data!$B$13</f>
       </c>
       <c r="I57" s="14" t="str">
-        <f>'data'!$B$26</f>
+        <f>data!$E$26&amp;" "&amp;data!$B$26</f>
       </c>
       <c r="J57" s="18"/>
       <c r="K57" s="18"/>
@@ -3656,56 +3734,56 @@
       <c r="M57" s="18"/>
       <c r="N57" s="18"/>
       <c r="O57" s="14" t="str">
-        <f>'data'!$B$25</f>
+        <f>data!$E$25&amp;" "&amp;data!$B$25</f>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="I59" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="J59" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="K59" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="L59" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="M59" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="N59" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="O59" s="13" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="str">
-        <f>'data'!$B$12</f>
+        <f>data!$E$12&amp;" "&amp;data!$B$12</f>
       </c>
       <c r="B60" s="14" t="str">
         <f>IF(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),IF(OR(D55="X",D55="x",AND(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),IF(OR(D56="X",D56="x",AND(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))*1),0)</f>
@@ -3726,7 +3804,7 @@
         <f>RANK(U60,$U$60:$U$62)+COUNTIF($U$59:U59,U60)</f>
       </c>
       <c r="I60" s="14" t="str">
-        <f>'data'!$B$24</f>
+        <f>data!$E$24&amp;" "&amp;data!$B$24</f>
       </c>
       <c r="J60" s="14" t="str">
         <f>IF(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),IF(OR(L55="X",L55="x",AND(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),IF(OR(L56="X",L56="x",AND(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))*1),0)</f>
@@ -3755,7 +3833,7 @@
     </row>
     <row r="61">
       <c r="A61" s="14" t="str">
-        <f>'data'!$B$13</f>
+        <f>data!$E$13&amp;" "&amp;data!$B$13</f>
       </c>
       <c r="B61" s="14" t="str">
         <f>IF(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),IF(OR(D55="X",D55="x",AND(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),IF(OR(D57="X",D57="x",AND(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))*1),0)</f>
@@ -3776,7 +3854,7 @@
         <f>RANK(U61,$U$60:$U$62)+COUNTIF($U$59:U60,U61)</f>
       </c>
       <c r="I61" s="14" t="str">
-        <f>'data'!$B$25</f>
+        <f>data!$E$25&amp;" "&amp;data!$B$25</f>
       </c>
       <c r="J61" s="14" t="str">
         <f>IF(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),IF(OR(L55="X",L55="x",AND(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),IF(OR(L57="X",L57="x",AND(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))*1),0)</f>
@@ -3805,7 +3883,7 @@
     </row>
     <row r="62">
       <c r="A62" s="14" t="str">
-        <f>'data'!$B$14</f>
+        <f>data!$E$14&amp;" "&amp;data!$B$14</f>
       </c>
       <c r="B62" s="14" t="str">
         <f>IF(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),IF(OR(D56="X",D56="x",AND(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),IF(OR(D57="X",D57="x",AND(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")))*1),0)</f>
@@ -3826,7 +3904,7 @@
         <f>RANK(U62,$U$60:$U$62)+COUNTIF($U$59:U61,U62)</f>
       </c>
       <c r="I62" s="14" t="str">
-        <f>'data'!$B$26</f>
+        <f>data!$E$26&amp;" "&amp;data!$B$26</f>
       </c>
       <c r="J62" s="14" t="str">
         <f>IF(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),IF(OR(L56="X",L56="x",AND(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),IF(OR(L57="X",L57="x",AND(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")))*1),0)</f>
@@ -3856,22 +3934,22 @@
     <row r="65">
       <c r="F65" s="13"/>
       <c r="G65" s="13" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="N65" s="13"/>
       <c r="O65" s="13" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
     </row>
     <row r="66">
       <c r="F66" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G66" s="19" t="str">
         <f>IFERROR(INDEX($A$60:$A$62, MATCH(1, $G$60:$G$62, 0)), "-")</f>
       </c>
       <c r="N66" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O66" s="19" t="str">
         <f>IFERROR(INDEX($I$60:$I$62, MATCH(1, $O$60:$O$62, 0)), "-")</f>
@@ -3879,13 +3957,13 @@
     </row>
     <row r="67">
       <c r="F67" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G67" s="19" t="str">
         <f>IFERROR(INDEX($A$60:$A$62, MATCH(2, $G$60:$G$62, 0)), "-")</f>
       </c>
       <c r="N67" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O67" s="19" t="str">
         <f>IFERROR(INDEX($I$60:$I$62, MATCH(2, $O$60:$O$62, 0)), "-")</f>
@@ -3893,13 +3971,13 @@
     </row>
     <row r="68">
       <c r="F68" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="G68" s="19" t="str">
         <f>IFERROR(INDEX($A$60:$A$62, MATCH(3, $G$60:$G$62, 0)), "-")</f>
       </c>
       <c r="N68" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="O68" s="19" t="str">
         <f>IFERROR(INDEX($I$60:$I$62, MATCH(3, $O$60:$O$62, 0)), "-")</f>
@@ -3951,7 +4029,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -3960,7 +4038,7 @@
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
       <c r="I1" s="13" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
@@ -3971,7 +4049,7 @@
     </row>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -3980,7 +4058,7 @@
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
       <c r="I2" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
@@ -3991,22 +4069,22 @@
     </row>
     <row r="3">
       <c r="A3" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
@@ -4035,27 +4113,27 @@
     </row>
     <row r="6">
       <c r="F6" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G6" s="19"/>
       <c r="N6" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O6" s="19"/>
     </row>
     <row r="7">
       <c r="F7" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G7" s="19"/>
       <c r="N7" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O7" s="19"/>
     </row>
     <row r="10">
       <c r="A10" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -4064,7 +4142,7 @@
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="I10" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
@@ -4075,22 +4153,22 @@
     </row>
     <row r="11">
       <c r="A11" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I11" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O11" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12">
@@ -4119,27 +4197,27 @@
     </row>
     <row r="14">
       <c r="F14" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G14" s="19"/>
       <c r="N14" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O14" s="19"/>
     </row>
     <row r="15">
       <c r="F15" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G15" s="19"/>
       <c r="N15" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O15" s="19"/>
     </row>
     <row r="18">
       <c r="A18" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -4148,7 +4226,7 @@
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
       <c r="I18" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
@@ -4159,22 +4237,22 @@
     </row>
     <row r="19">
       <c r="A19" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I19" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L19" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O19" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20">
@@ -4203,27 +4281,27 @@
     </row>
     <row r="22">
       <c r="F22" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G22" s="19"/>
       <c r="N22" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O22" s="19"/>
     </row>
     <row r="23">
       <c r="F23" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G23" s="19"/>
       <c r="N23" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O23" s="19"/>
     </row>
     <row r="26">
       <c r="A26" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
@@ -4232,7 +4310,7 @@
       <c r="F26" s="13"/>
       <c r="G26" s="13"/>
       <c r="I26" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J26" s="13"/>
       <c r="K26" s="13"/>
@@ -4243,22 +4321,22 @@
     </row>
     <row r="27">
       <c r="A27" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O27" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28">
@@ -4287,27 +4365,27 @@
     </row>
     <row r="30">
       <c r="F30" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G30" s="19"/>
       <c r="N30" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O30" s="19"/>
     </row>
     <row r="31">
       <c r="F31" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G31" s="19"/>
       <c r="N31" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O31" s="19"/>
     </row>
     <row r="39">
       <c r="A39" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B39" s="13"/>
       <c r="C39" s="13"/>
@@ -4316,7 +4394,7 @@
       <c r="F39" s="13"/>
       <c r="G39" s="13"/>
       <c r="I39" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J39" s="13"/>
       <c r="K39" s="13"/>
@@ -4327,22 +4405,22 @@
     </row>
     <row r="40">
       <c r="A40" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L40" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O40" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41">
@@ -4371,27 +4449,27 @@
     </row>
     <row r="43">
       <c r="F43" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G43" s="19"/>
       <c r="N43" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O43" s="19"/>
     </row>
     <row r="44">
       <c r="F44" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G44" s="19"/>
       <c r="N44" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O44" s="19"/>
     </row>
     <row r="47">
       <c r="A47" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B47" s="13"/>
       <c r="C47" s="13"/>
@@ -4400,7 +4478,7 @@
       <c r="F47" s="13"/>
       <c r="G47" s="13"/>
       <c r="I47" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J47" s="13"/>
       <c r="K47" s="13"/>
@@ -4411,22 +4489,22 @@
     </row>
     <row r="48">
       <c r="A48" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I48" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L48" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O48" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49">
@@ -4455,27 +4533,27 @@
     </row>
     <row r="51">
       <c r="F51" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G51" s="19"/>
       <c r="N51" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O51" s="19"/>
     </row>
     <row r="52">
       <c r="F52" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G52" s="19"/>
       <c r="N52" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O52" s="19"/>
     </row>
     <row r="60">
       <c r="A60" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B60" s="13"/>
       <c r="C60" s="13"/>
@@ -4484,7 +4562,7 @@
       <c r="F60" s="13"/>
       <c r="G60" s="13"/>
       <c r="I60" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J60" s="13"/>
       <c r="K60" s="13"/>
@@ -4495,22 +4573,22 @@
     </row>
     <row r="61">
       <c r="A61" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G61" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L61" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O61" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62">
@@ -4539,27 +4617,27 @@
     </row>
     <row r="64">
       <c r="F64" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G64" s="19"/>
       <c r="N64" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O64" s="19"/>
     </row>
     <row r="65">
       <c r="F65" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G65" s="19"/>
       <c r="N65" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O65" s="19"/>
     </row>
     <row r="73">
       <c r="A73" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B73" s="13"/>
       <c r="C73" s="13"/>
@@ -4570,13 +4648,13 @@
     </row>
     <row r="74">
       <c r="A74" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="75">
@@ -4594,13 +4672,13 @@
     </row>
     <row r="77">
       <c r="F77" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G77" s="19"/>
     </row>
     <row r="78">
       <c r="F78" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G78" s="19"/>
     </row>
@@ -4670,7 +4748,7 @@
     </row>
     <row r="5">
       <c r="A5" s="25" t="str">
-        <f>"1. " &amp; data!$B$3</f>
+        <f>data!$E$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="C5" s="23" t="str">
         <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G15)</f>
@@ -4678,7 +4756,7 @@
     </row>
     <row r="6">
       <c r="A6" s="26" t="str">
-        <f>"2. " &amp; data!$B$4</f>
+        <f>data!$E$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="D6" s="22"/>
       <c r="E6" s="21">
@@ -4687,7 +4765,7 @@
     </row>
     <row r="7">
       <c r="A7" s="27" t="str">
-        <f>"3. " &amp; data!$B$5</f>
+        <f>data!$E$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="C7" s="23" t="str">
         <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O16)</f>
@@ -4716,7 +4794,7 @@
     </row>
     <row r="10">
       <c r="A10" s="25" t="str">
-        <f>"1. " &amp; data!$B$6</f>
+        <f>data!$E$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="21">
@@ -4728,7 +4806,7 @@
     </row>
     <row r="11">
       <c r="A11" s="26" t="str">
-        <f>"2. " &amp; data!$B$7</f>
+        <f>data!$E$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
         <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O33)</f>
@@ -4739,7 +4817,7 @@
     </row>
     <row r="12">
       <c r="A12" s="27" t="str">
-        <f>"3. " &amp; data!$B$8</f>
+        <f>data!$E$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="I12" s="21">
         <v>13</v>
@@ -4764,7 +4842,7 @@
     </row>
     <row r="15">
       <c r="A15" s="25" t="str">
-        <f>"1. " &amp; data!$B$9</f>
+        <f>data!$E$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="C15" s="23" t="str">
         <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O50)</f>
@@ -4777,7 +4855,7 @@
     </row>
     <row r="16">
       <c r="A16" s="26" t="str">
-        <f>"2. " &amp; data!$B$10</f>
+        <f>data!$E$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="G16" s="21">
         <v>10</v>
@@ -4787,7 +4865,7 @@
     </row>
     <row r="17">
       <c r="A17" s="27" t="str">
-        <f>"3. " &amp; data!$B$11</f>
+        <f>data!$E$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="C17" s="23" t="str">
         <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
@@ -4815,17 +4893,17 @@
     </row>
     <row r="20">
       <c r="A20" s="25" t="str">
-        <f>"1. " &amp; data!$B$12</f>
+        <f>data!$E$12&amp;" "&amp;data!$B$12</f>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="26" t="str">
-        <f>"2. " &amp; data!$B$13</f>
+        <f>data!$E$13&amp;" "&amp;data!$B$13</f>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="27" t="str">
-        <f>"3. " &amp; data!$B$14</f>
+        <f>data!$E$14&amp;" "&amp;data!$B$14</f>
       </c>
     </row>
     <row r="23">
@@ -4875,7 +4953,7 @@
     </row>
     <row r="5">
       <c r="A5" s="25" t="str">
-        <f>"1. " &amp; data!$B$15</f>
+        <f>data!$E$15&amp;" "&amp;data!$B$15</f>
       </c>
       <c r="C5" s="23" t="str">
         <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O15)</f>
@@ -4883,7 +4961,7 @@
     </row>
     <row r="6">
       <c r="A6" s="26" t="str">
-        <f>"2. " &amp; data!$B$16</f>
+        <f>data!$E$16&amp;" "&amp;data!$B$16</f>
       </c>
       <c r="D6" s="22"/>
       <c r="E6" s="21">
@@ -4892,7 +4970,7 @@
     </row>
     <row r="7">
       <c r="A7" s="27" t="str">
-        <f>"3. " &amp; data!$B$17</f>
+        <f>data!$E$17&amp;" "&amp;data!$B$17</f>
       </c>
       <c r="C7" s="23" t="str">
         <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G16)</f>
@@ -4921,7 +4999,7 @@
     </row>
     <row r="10">
       <c r="A10" s="25" t="str">
-        <f>"1. " &amp; data!$B$18</f>
+        <f>data!$E$18&amp;" "&amp;data!$B$18</f>
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="21">
@@ -4933,7 +5011,7 @@
     </row>
     <row r="11">
       <c r="A11" s="26" t="str">
-        <f>"2. " &amp; data!$B$19</f>
+        <f>data!$E$19&amp;" "&amp;data!$B$19</f>
       </c>
       <c r="C11" s="23" t="str">
         <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
@@ -4944,7 +5022,7 @@
     </row>
     <row r="12">
       <c r="A12" s="27" t="str">
-        <f>"3. " &amp; data!$B$20</f>
+        <f>data!$E$20&amp;" "&amp;data!$B$20</f>
       </c>
       <c r="I12" s="21">
         <v>14</v>
@@ -4969,7 +5047,7 @@
     </row>
     <row r="15">
       <c r="A15" s="25" t="str">
-        <f>"1. " &amp; data!$B$21</f>
+        <f>data!$E$21&amp;" "&amp;data!$B$21</f>
       </c>
       <c r="C15" s="23" t="str">
         <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
@@ -4982,7 +5060,7 @@
     </row>
     <row r="16">
       <c r="A16" s="26" t="str">
-        <f>"2. " &amp; data!$B$22</f>
+        <f>data!$E$22&amp;" "&amp;data!$B$22</f>
       </c>
       <c r="G16" s="21">
         <v>12</v>
@@ -4992,7 +5070,7 @@
     </row>
     <row r="17">
       <c r="A17" s="27" t="str">
-        <f>"3. " &amp; data!$B$23</f>
+        <f>data!$E$23&amp;" "&amp;data!$B$23</f>
       </c>
       <c r="C17" s="23" t="str">
         <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O66)</f>
@@ -5020,17 +5098,17 @@
     </row>
     <row r="20">
       <c r="A20" s="25" t="str">
-        <f>"1. " &amp; data!$B$24</f>
+        <f>data!$E$24&amp;" "&amp;data!$B$24</f>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="26" t="str">
-        <f>"2. " &amp; data!$B$25</f>
+        <f>data!$E$25&amp;" "&amp;data!$B$25</f>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="27" t="str">
-        <f>"3. " &amp; data!$B$26</f>
+        <f>data!$E$26&amp;" "&amp;data!$B$26</f>
       </c>
     </row>
     <row r="23">

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -25,6 +25,7 @@
     <definedName localSheetId="6" name="_xlnm.Print_Area">'Tree 2'!$A$1:$I$23</definedName>
     <definedName localSheetId="7" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$12</definedName>
     <definedName localSheetId="8" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$12</definedName>
+    <definedName localSheetId="9" name="_xlnm.Print_Area">'Tags'!$A$1:$A$48</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$P$85</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
@@ -806,13 +807,13 @@
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
@@ -1783,7 +1784,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="110"/>
+    <col customWidth="true" max="1" min="1" width="88"/>
   </cols>
   <sheetData>
     <row r="1" ht="409" customHeight="true">

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -810,7 +810,7 @@
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
@@ -1548,8 +1548,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
@@ -1666,8 +1666,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">

--- a/pools-example-medium.xlsx
+++ b/pools-example-medium.xlsx
@@ -813,7 +813,7 @@
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
